--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032643318176</t>
+    <t xml:space="preserve">2.9603259563446</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">3.13860011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12387990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028104782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930172920227</t>
+    <t xml:space="preserve">3.12388038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588908195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06663608551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500029563904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028080940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930196762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.16476845741272</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">3.17131066322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16149735450745</t>
+    <t xml:space="preserve">3.16149759292603</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205790519714</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">3.15822649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14514207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168428421021</t>
+    <t xml:space="preserve">3.14514183998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168452262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.30051827430725</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">3.34140658378601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463206291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790364265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39374446868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393044471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977174758911</t>
+    <t xml:space="preserve">3.43463277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43790411949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39374423027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393092155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977150917053</t>
   </si>
   <si>
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0306544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08789801597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17294669151306</t>
+    <t xml:space="preserve">3.14841318130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03065395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08789825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17294645309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.10752463340759</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">3.18112421035767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19257283210754</t>
+    <t xml:space="preserve">3.19257307052612</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">3.0339252948761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303698539734</t>
+    <t xml:space="preserve">2.99303674697876</t>
   </si>
   <si>
     <t xml:space="preserve">3.04373860359192</t>
@@ -149,184 +149,184 @@
     <t xml:space="preserve">3.23019027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23346090316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22528338432312</t>
+    <t xml:space="preserve">3.2334611415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22528386116028</t>
   </si>
   <si>
     <t xml:space="preserve">3.11406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1222448348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0911693572998</t>
+    <t xml:space="preserve">3.14023542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12224459648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09116959571838</t>
   </si>
   <si>
     <t xml:space="preserve">3.08299160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11897349357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135581016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1042537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07481384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14677786827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13696455955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383476257324</t>
+    <t xml:space="preserve">3.11897373199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425353050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07481408119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14677739143372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13696432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383500099182</t>
   </si>
   <si>
     <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10916042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36921095848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5098671913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51640963554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54094219207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50168943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35612654685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32014489173889</t>
+    <t xml:space="preserve">3.10916018486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36921119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645525932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986695289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51640939712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54094243049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50169014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3561270236969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
     <t xml:space="preserve">3.29724717140198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36103320121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575316429138</t>
+    <t xml:space="preserve">3.36103343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3757529258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.3773889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38556623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136143684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150345802307</t>
+    <t xml:space="preserve">3.35285544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38556599617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150298118591</t>
   </si>
   <si>
     <t xml:space="preserve">3.47061419487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4673433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281029701233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3970148563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860478401184</t>
+    <t xml:space="preserve">3.46734285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39701509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337037086487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48860549926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.45916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50823140144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584956169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5785596370697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59818625450134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6390745639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360807418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725279808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996335029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636401176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5671112537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897912025452</t>
+    <t xml:space="preserve">3.41827702522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50823211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57855987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472893714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547594070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818696975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907504081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178583145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897888183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355753898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38065958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3381359577179</t>
+    <t xml:space="preserve">3.38065934181213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33813571929932</t>
   </si>
   <si>
     <t xml:space="preserve">3.28743386268616</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">3.32668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27598547935486</t>
+    <t xml:space="preserve">3.27598571777344</t>
   </si>
   <si>
     <t xml:space="preserve">3.2432746887207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21874141693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25962948799133</t>
+    <t xml:space="preserve">3.21874165534973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962996482849</t>
   </si>
   <si>
     <t xml:space="preserve">3.15495538711548</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">3.07644963264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08462738990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1255156993866</t>
+    <t xml:space="preserve">3.08462715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12551593780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.27107858657837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31850934028625</t>
+    <t xml:space="preserve">3.31850957870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.33486461639404</t>
@@ -371,52 +371,52 @@
     <t xml:space="preserve">3.36757564544678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40846419334412</t>
+    <t xml:space="preserve">3.40846395492554</t>
   </si>
   <si>
     <t xml:space="preserve">3.30869603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818110466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48206305503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454153060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528877258301</t>
+    <t xml:space="preserve">3.24818062782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033158302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48206281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655070304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528948783875</t>
   </si>
   <si>
     <t xml:space="preserve">3.58183097839355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309290885925</t>
+    <t xml:space="preserve">3.63253307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309362411499</t>
   </si>
   <si>
     <t xml:space="preserve">3.66851496696472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64071083068848</t>
+    <t xml:space="preserve">3.6407105922699</t>
   </si>
   <si>
     <t xml:space="preserve">3.61617708206177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62435507774353</t>
+    <t xml:space="preserve">3.62435531616211</t>
   </si>
   <si>
     <t xml:space="preserve">3.75192713737488</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.76174020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72412276268005</t>
+    <t xml:space="preserve">3.72412300109863</t>
   </si>
   <si>
     <t xml:space="preserve">3.77809572219849</t>
@@ -434,40 +434,40 @@
     <t xml:space="preserve">3.77646040916443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79118037223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720788955688</t>
+    <t xml:space="preserve">3.79118013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720765113831</t>
   </si>
   <si>
     <t xml:space="preserve">3.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79445147514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071574211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91548109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86314392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89258360862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529463768005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440585136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655704498291</t>
+    <t xml:space="preserve">3.79445099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9154806137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314415931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8925838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529439926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655680656433</t>
   </si>
   <si>
     <t xml:space="preserve">3.86150860786438</t>
@@ -476,55 +476,55 @@
     <t xml:space="preserve">3.96454739570618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8516948223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04305267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618318557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767743110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968660354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898474693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94164991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02669763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398732185364</t>
+    <t xml:space="preserve">3.85169506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.043053150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618247032166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767766952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898427009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384553909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94164967536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398708343506</t>
   </si>
   <si>
     <t xml:space="preserve">3.97272515296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00216484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141759872437</t>
+    <t xml:space="preserve">4.0021653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97926783561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
     <t xml:space="preserve">4.08884811401367</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">4.27693510055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048881530762</t>
+    <t xml:space="preserve">4.44048929214478</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33009004592896</t>
+    <t xml:space="preserve">4.33009099960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506771087646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350831985474</t>
+    <t xml:space="preserve">4.59586572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350784301758</t>
   </si>
   <si>
     <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99248361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439710617065</t>
+    <t xml:space="preserve">4.9924840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439567565918</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710765838623</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.96386241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02928352355957</t>
+    <t xml:space="preserve">5.02928400039673</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337240219116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283723831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150548934937</t>
+    <t xml:space="preserve">5.19283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">5.28688097000122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36456918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270084381104</t>
+    <t xml:space="preserve">5.36456871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3686580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492233276367</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.56901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55265522003174</t>
+    <t xml:space="preserve">5.55265617370605</t>
   </si>
   <si>
     <t xml:space="preserve">5.30323648452759</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">5.5485668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59354400634766</t>
+    <t xml:space="preserve">5.59354448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70803213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709867477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80207538604736</t>
+    <t xml:space="preserve">5.70803260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80207586288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.82251977920532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85114240646362</t>
+    <t xml:space="preserve">5.85114145278931</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43816900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4790563583374</t>
+    <t xml:space="preserve">5.4381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47905683517456</t>
   </si>
   <si>
     <t xml:space="preserve">5.48723459243774</t>
@@ -659,25 +659,25 @@
     <t xml:space="preserve">5.46679019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60581064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083345413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64308166503906</t>
+    <t xml:space="preserve">5.60581159591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5608344078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64308214187622</t>
   </si>
   <si>
     <t xml:space="preserve">5.69674682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4614462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546560287476</t>
+    <t xml:space="preserve">5.46144533157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546607971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.70500230789185</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">5.73802709579468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756427764893</t>
+    <t xml:space="preserve">5.78756475448608</t>
   </si>
   <si>
     <t xml:space="preserve">5.80407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948587417603</t>
+    <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315103530884</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">6.10129833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84122943878174</t>
+    <t xml:space="preserve">5.84122896194458</t>
   </si>
   <si>
     <t xml:space="preserve">5.82471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80820465087891</t>
+    <t xml:space="preserve">5.80820417404175</t>
   </si>
   <si>
     <t xml:space="preserve">5.73389911651611</t>
@@ -716,97 +716,97 @@
     <t xml:space="preserve">5.75866794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133762359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233310699463</t>
+    <t xml:space="preserve">5.65133810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233215332031</t>
   </si>
   <si>
     <t xml:space="preserve">5.7793083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77105140686035</t>
+    <t xml:space="preserve">5.77105188369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68849086761475</t>
+    <t xml:space="preserve">5.68849039077759</t>
   </si>
   <si>
     <t xml:space="preserve">5.56877565383911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57703256607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5233678817749</t>
+    <t xml:space="preserve">5.63069772720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52336740493774</t>
   </si>
   <si>
     <t xml:space="preserve">5.54813528060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48621511459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934713363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30045080184937</t>
+    <t xml:space="preserve">5.48621463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639219284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934808731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568340301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30045127868652</t>
   </si>
   <si>
     <t xml:space="preserve">5.12294387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19312143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15183973312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17248010635376</t>
+    <t xml:space="preserve">5.1931209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17248106002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39952516555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74628305435181</t>
+    <t xml:space="preserve">5.3995246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74628353118896</t>
   </si>
   <si>
     <t xml:space="preserve">5.75041198730469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60592889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977066040039</t>
+    <t xml:space="preserve">5.60592842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977161407471</t>
   </si>
   <si>
     <t xml:space="preserve">5.77518033981323</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86599826812744</t>
+    <t xml:space="preserve">5.87012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86599779129028</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">5.89489459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0476336479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204736709595</t>
+    <t xml:space="preserve">6.04763221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204689025879</t>
   </si>
   <si>
     <t xml:space="preserve">5.86186981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332715988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827306747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955429077148</t>
+    <t xml:space="preserve">5.95268678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955476760864</t>
   </si>
   <si>
     <t xml:space="preserve">6.17560386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973136901855</t>
+    <t xml:space="preserve">6.1797308921814</t>
   </si>
   <si>
     <t xml:space="preserve">6.19211578369141</t>
@@ -860,40 +860,40 @@
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385887145996</t>
+    <t xml:space="preserve">6.18385934829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193870544434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16734743118286</t>
+    <t xml:space="preserve">6.1673469543457</t>
   </si>
   <si>
     <t xml:space="preserve">6.13845109939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15083456039429</t>
+    <t xml:space="preserve">6.15083503723145</t>
   </si>
   <si>
     <t xml:space="preserve">5.98158359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05176162719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09716987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798780441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06001758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98571252822876</t>
+    <t xml:space="preserve">6.05176115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09717035293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06001710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98571157455444</t>
   </si>
   <si>
     <t xml:space="preserve">6.0889139175415</t>
@@ -902,52 +902,52 @@
     <t xml:space="preserve">5.91140651702881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87425374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93617486953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96094369888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00222396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2292685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85260915756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371187210083</t>
+    <t xml:space="preserve">5.87425327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93617534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9609432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00222444534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22926902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200807571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207696914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85260820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371091842651</t>
   </si>
   <si>
     <t xml:space="preserve">6.75353479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77004623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574165344238</t>
+    <t xml:space="preserve">6.77004671096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492372512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574117660522</t>
   </si>
   <si>
     <t xml:space="preserve">6.58015489578247</t>
@@ -959,85 +959,85 @@
     <t xml:space="preserve">6.43980026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52649021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631313323975</t>
+    <t xml:space="preserve">6.52649068832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631265640259</t>
   </si>
   <si>
     <t xml:space="preserve">6.57189893722534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65446043014526</t>
+    <t xml:space="preserve">6.65446090698242</t>
   </si>
   <si>
     <t xml:space="preserve">6.71638202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61318016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53061771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684532165527</t>
+    <t xml:space="preserve">6.6131796836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53061819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684436798096</t>
   </si>
   <si>
     <t xml:space="preserve">6.44805669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65858840942383</t>
+    <t xml:space="preserve">6.65858793258667</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62556314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905170440674</t>
+    <t xml:space="preserve">6.625563621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777143478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50584936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6090521812439</t>
   </si>
   <si>
     <t xml:space="preserve">6.7287654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84848070144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75766324996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90214490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70812511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6874852180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71225357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77417421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466758728027</t>
+    <t xml:space="preserve">6.84848022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75766229629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90214395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70812559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748617172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7122540473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466711044312</t>
   </si>
   <si>
     <t xml:space="preserve">7.44705152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47594785690308</t>
+    <t xml:space="preserve">7.47594833374023</t>
   </si>
   <si>
     <t xml:space="preserve">7.47182035446167</t>
@@ -1046,118 +1046,118 @@
     <t xml:space="preserve">7.46356391906738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64932870864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078510284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619382858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171073913574</t>
+    <t xml:space="preserve">7.64932680130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334707260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171026229858</t>
   </si>
   <si>
     <t xml:space="preserve">7.75665760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95893287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57915067672729</t>
+    <t xml:space="preserve">7.95893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57914924621582</t>
   </si>
   <si>
     <t xml:space="preserve">7.28192806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40989971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605604171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331747055054</t>
+    <t xml:space="preserve">7.40989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1333179473877</t>
   </si>
   <si>
     <t xml:space="preserve">7.22413444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41402578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769285202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3810019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19936656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01773023605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488348007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79481506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335676193237</t>
+    <t xml:space="preserve">7.41402626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769189834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787257194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38100147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33972120285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011560440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01773071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7948145866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335771560669</t>
   </si>
   <si>
     <t xml:space="preserve">6.790687084198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25303173065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1911096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84022378921509</t>
+    <t xml:space="preserve">7.25303077697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19111061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84022426605225</t>
   </si>
   <si>
     <t xml:space="preserve">7.05075550079346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2365198135376</t>
+    <t xml:space="preserve">7.23651933670044</t>
   </si>
   <si>
     <t xml:space="preserve">7.43053913116455</t>
@@ -1169,52 +1169,52 @@
     <t xml:space="preserve">7.26128768920898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2571587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036252975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27779912948608</t>
+    <t xml:space="preserve">7.25715970993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036062240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2778000831604</t>
   </si>
   <si>
     <t xml:space="preserve">8.23138618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12405681610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768173217773</t>
+    <t xml:space="preserve">8.12405586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768077850342</t>
   </si>
   <si>
     <t xml:space="preserve">8.41302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1405668258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789905548096</t>
+    <t xml:space="preserve">8.14056777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789810180664</t>
   </si>
   <si>
     <t xml:space="preserve">8.17359256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09103107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19836044311523</t>
+    <t xml:space="preserve">8.09103202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19836139678955</t>
   </si>
   <si>
     <t xml:space="preserve">8.18184852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14469623565674</t>
+    <t xml:space="preserve">8.20661544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14469718933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.15295314788818</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">8.45430088043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348533630371</t>
+    <t xml:space="preserve">8.35522842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348438262939</t>
   </si>
   <si>
     <t xml:space="preserve">8.33045959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47907161712646</t>
+    <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.52035140991211</t>
@@ -1256,58 +1256,58 @@
     <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83408451080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86710929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6689624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42953395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67109203338623</t>
+    <t xml:space="preserve">8.83408546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65245056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42953300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.74605655670166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70441150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77104568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75438690185547</t>
+    <t xml:space="preserve">8.70440864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77104663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75438594818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.24628257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30875396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3462381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41287517547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87933158874512</t>
+    <t xml:space="preserve">8.30875492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34623718261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41287326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55447769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87932968139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946681976318</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269454956055</t>
+    <t xml:space="preserve">8.81269359588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.82102394104004</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">8.47118186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452117919922</t>
+    <t xml:space="preserve">8.45452213287354</t>
   </si>
   <si>
     <t xml:space="preserve">8.25461196899414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58779621124268</t>
+    <t xml:space="preserve">8.58779525756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49617004394531</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">8.08802032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59612464904785</t>
+    <t xml:space="preserve">8.59612560272217</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12134075164795</t>
+    <t xml:space="preserve">8.16298770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.121337890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.99639558792114</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">7.92142963409424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78815603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323499679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312103271484</t>
+    <t xml:space="preserve">7.78815698623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062694549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312198638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.74234342575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67154216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241008758545</t>
+    <t xml:space="preserve">7.67154264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572813034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.721519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241056442261</t>
   </si>
   <si>
     <t xml:space="preserve">7.57158708572388</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">7.82980346679688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6340594291687</t>
+    <t xml:space="preserve">7.54659938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
     <t xml:space="preserve">7.84229755401611</t>
@@ -1433,55 +1433,55 @@
     <t xml:space="preserve">7.792320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319055557251</t>
+    <t xml:space="preserve">7.61740064620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71318864822388</t>
   </si>
   <si>
     <t xml:space="preserve">7.74650812149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6882004737854</t>
+    <t xml:space="preserve">7.68820095062256</t>
   </si>
   <si>
     <t xml:space="preserve">7.44664287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28838109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14677810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17131614685059</t>
+    <t xml:space="preserve">7.28838062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14677858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637241363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1713171005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.47951221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3295783996582</t>
+    <t xml:space="preserve">8.32957744598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955570220947</t>
+    <t xml:space="preserve">8.23378944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.52948760986328</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">9.0542516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01260375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07923984527588</t>
+    <t xml:space="preserve">8.99594402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0792407989502</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
@@ -1511,37 +1511,37 @@
     <t xml:space="preserve">9.09589958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0209321975708</t>
+    <t xml:space="preserve">9.02093315124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02926254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66276168823242</t>
+    <t xml:space="preserve">8.66276264190674</t>
   </si>
   <si>
     <t xml:space="preserve">8.57113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02138328552246</t>
+    <t xml:space="preserve">8.02138423919678</t>
   </si>
   <si>
     <t xml:space="preserve">8.08385562896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15049362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00055980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354567527771</t>
+    <t xml:space="preserve">8.15049266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00056076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35456657409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.9839015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82563877105713</t>
+    <t xml:space="preserve">7.82563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.9922308921814</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07969093322754</t>
+    <t xml:space="preserve">8.07969188690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.28376579284668</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">8.53781795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46285247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60445404052734</t>
+    <t xml:space="preserve">8.46285152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60445499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.13799858093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07552528381348</t>
+    <t xml:space="preserve">8.07552623748779</t>
   </si>
   <si>
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243278503418</t>
+    <t xml:space="preserve">7.5424337387085</t>
   </si>
   <si>
     <t xml:space="preserve">8.01721858978271</t>
@@ -1589,49 +1589,49 @@
     <t xml:space="preserve">8.20046997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19214057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09634971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14216327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12550258636475</t>
+    <t xml:space="preserve">8.19213962554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09635066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14216232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">8.17964649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94641733169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25877666473389</t>
+    <t xml:space="preserve">7.94641828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.9755711555481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8922758102417</t>
+    <t xml:space="preserve">7.89227676391602</t>
   </si>
   <si>
     <t xml:space="preserve">7.81730937957764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62989377975464</t>
+    <t xml:space="preserve">7.6298942565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.79648447036743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75483751296997</t>
+    <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.22129440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32541370391846</t>
+    <t xml:space="preserve">8.32541275024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.21296405792236</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">8.18381118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19630718231201</t>
+    <t xml:space="preserve">8.19630527496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.22962379455566</t>
@@ -1655,67 +1655,67 @@
     <t xml:space="preserve">8.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944412231445</t>
+    <t xml:space="preserve">8.62944316864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
+    <t xml:space="preserve">8.51282978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69607925415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.83768272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77937698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37910461425781</t>
+    <t xml:space="preserve">8.77937602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237773895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37910556793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.56235599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59567546844482</t>
+    <t xml:space="preserve">9.59567451477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.54569721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39576530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28748035430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29580879211426</t>
+    <t xml:space="preserve">9.39576435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28747844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571895599365</t>
+    <t xml:space="preserve">9.49571800231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0375919342041</t>
+    <t xml:space="preserve">9.66231155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.229172706604</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96262741088867</t>
+    <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
     <t xml:space="preserve">9.13754844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16253757476807</t>
+    <t xml:space="preserve">9.16253662109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0709114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56280517578125</t>
+    <t xml:space="preserve">8.56280612945557</t>
   </si>
   <si>
     <t xml:space="preserve">8.64610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592227935791</t>
+    <t xml:space="preserve">9.04592037200928</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10422992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94596672058105</t>
+    <t xml:space="preserve">9.10422897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
     <t xml:space="preserve">8.91264915466309</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">8.83797168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781467437744</t>
+    <t xml:space="preserve">8.65155220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781372070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.59223651885986</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">8.98202228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.702392578125</t>
+    <t xml:space="preserve">8.70239353179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.77018260955811</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">8.6430778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48207950592041</t>
+    <t xml:space="preserve">8.5159740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48208045959473</t>
   </si>
   <si>
     <t xml:space="preserve">8.49055290222168</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">8.38039684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.427001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30413341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2617654800415</t>
+    <t xml:space="preserve">8.42700099945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30413436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26176452636719</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226417541504</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">8.39310741424561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33379173278809</t>
+    <t xml:space="preserve">8.33379077911377</t>
   </si>
   <si>
     <t xml:space="preserve">8.31260776519775</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">8.27871417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28718662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29566097259521</t>
+    <t xml:space="preserve">8.28718566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2956600189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500335693359</t>
+    <t xml:space="preserve">8.10500431060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397640228271</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32531642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45242214202881</t>
+    <t xml:space="preserve">8.44394874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444648742676</t>
+    <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.66849803924561</t>
@@ -1865,25 +1865,25 @@
     <t xml:space="preserve">8.56681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44818496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091833114624</t>
+    <t xml:space="preserve">8.44818592071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60918235778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57528972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2024507522583</t>
+    <t xml:space="preserve">8.57528877258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
     <t xml:space="preserve">8.35921192169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17279243469238</t>
+    <t xml:space="preserve">8.1727933883667</t>
   </si>
   <si>
     <t xml:space="preserve">8.11771392822266</t>
@@ -1898,43 +1898,43 @@
     <t xml:space="preserve">8.13466167449951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9651894569397</t>
+    <t xml:space="preserve">7.96518993377686</t>
   </si>
   <si>
     <t xml:space="preserve">7.9016375541687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79995346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961273193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792816162109</t>
+    <t xml:space="preserve">7.79995441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640298843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329113006592</t>
+    <t xml:space="preserve">8.25329208374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7236909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671510696411</t>
+    <t xml:space="preserve">7.72369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671701431274</t>
   </si>
   <si>
     <t xml:space="preserve">7.82113838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71945524215698</t>
+    <t xml:space="preserve">7.71945381164551</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540273666382</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">7.6601390838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71098136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66002655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41429042816162</t>
+    <t xml:space="preserve">7.71098184585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66002559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41429138183594</t>
   </si>
   <si>
     <t xml:space="preserve">8.31684398651123</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">8.42276477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19821357727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21939849853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46513175964355</t>
+    <t xml:space="preserve">8.19821262359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24058246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21939754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.53292083740234</t>
@@ -1982,37 +1982,37 @@
     <t xml:space="preserve">8.46936893463135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89728736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01591682434082</t>
+    <t xml:space="preserve">8.8972864151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01591777801514</t>
   </si>
   <si>
     <t xml:space="preserve">8.88881206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13042545318604</t>
+    <t xml:space="preserve">8.90575981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13042449951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.22363376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18974018096924</t>
+    <t xml:space="preserve">8.18973922729492</t>
   </si>
   <si>
     <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49902725219727</t>
+    <t xml:space="preserve">8.49902629852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.76170825958252</t>
@@ -2027,37 +2027,37 @@
     <t xml:space="preserve">8.54139423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69392013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85491752624512</t>
+    <t xml:space="preserve">8.69391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85491847991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.02439022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28707122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57517623901367</t>
+    <t xml:space="preserve">9.28707218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57517528533936</t>
   </si>
   <si>
     <t xml:space="preserve">9.47349166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401802062988</t>
+    <t xml:space="preserve">9.42265033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401992797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.60906887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65143775939941</t>
+    <t xml:space="preserve">9.65143871307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.53280639648438</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">9.63449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56670093536377</t>
+    <t xml:space="preserve">9.56670188903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.75312042236328</t>
@@ -2075,16 +2075,16 @@
     <t xml:space="preserve">9.76159381866455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78701400756836</t>
+    <t xml:space="preserve">9.78701496124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.83785629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.871750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327838897705</t>
+    <t xml:space="preserve">9.87174987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327743530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.79548931121826</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">9.91411781311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9734354019165</t>
+    <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0242757797241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0835905075073</t>
+    <t xml:space="preserve">10.1344337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.083589553833</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158023834229</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">9.93953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0666437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1768016815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2276411056519</t>
+    <t xml:space="preserve">10.0666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1768007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2276401519775</t>
   </si>
   <si>
     <t xml:space="preserve">10.1598539352417</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">10.2615356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2530641555786</t>
+    <t xml:space="preserve">10.2530632019043</t>
   </si>
   <si>
     <t xml:space="preserve">10.1683263778687</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">9.82938289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94801330566406</t>
+    <t xml:space="preserve">9.94801235198975</t>
   </si>
   <si>
     <t xml:space="preserve">9.998854637146</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">9.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0581693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73617267608643</t>
+    <t xml:space="preserve">10.0581703186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73617362976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296436309814</t>
+    <t xml:space="preserve">9.64296340942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.54975318908691</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">8.16431903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32108020782471</t>
+    <t xml:space="preserve">8.32108116149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603221893311</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674419403076</t>
+    <t xml:space="preserve">7.70674467086792</t>
   </si>
   <si>
     <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39322185516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153728485107</t>
+    <t xml:space="preserve">7.39322137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153680801392</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072456359863</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">6.61364889144897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6137638092041</t>
+    <t xml:space="preserve">5.61376333236694</t>
   </si>
   <si>
     <t xml:space="preserve">5.52479076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9824800491333</t>
+    <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
     <t xml:space="preserve">5.08416318893433</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59258031845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80865669250488</t>
+    <t xml:space="preserve">5.59257984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80865716934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.50784397125244</t>
@@ -2240,28 +2240,28 @@
     <t xml:space="preserve">5.26210927963257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84690237045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1604266166687</t>
+    <t xml:space="preserve">4.84690284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16042566299438</t>
   </si>
   <si>
     <t xml:space="preserve">4.89774465560913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76216650009155</t>
+    <t xml:space="preserve">4.76216602325439</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481937408447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41463375091553</t>
+    <t xml:space="preserve">5.41463422775269</t>
   </si>
   <si>
     <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20279407501221</t>
+    <t xml:space="preserve">5.20279359817505</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">5.10111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93163919448853</t>
+    <t xml:space="preserve">4.93163871765137</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129655838013</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">5.73663139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9315242767334</t>
+    <t xml:space="preserve">5.93152379989624</t>
   </si>
   <si>
     <t xml:space="preserve">6.07557582855225</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53326511383057</t>
+    <t xml:space="preserve">5.53326463699341</t>
   </si>
   <si>
     <t xml:space="preserve">5.49513339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87220859527588</t>
+    <t xml:space="preserve">5.87220907211304</t>
   </si>
   <si>
     <t xml:space="preserve">5.93576049804688</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">6.13065385818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88068246841431</t>
+    <t xml:space="preserve">5.88068294525146</t>
   </si>
   <si>
     <t xml:space="preserve">5.6773157119751</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289386749268</t>
+    <t xml:space="preserve">5.81289339065552</t>
   </si>
   <si>
     <t xml:space="preserve">5.75357818603516</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">6.05015468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91881370544434</t>
+    <t xml:space="preserve">5.91881418228149</t>
   </si>
   <si>
     <t xml:space="preserve">6.03320741653442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35520458221436</t>
+    <t xml:space="preserve">6.3552041053772</t>
   </si>
   <si>
     <t xml:space="preserve">6.29165267944336</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">6.94835710525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91022539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04156637191772</t>
+    <t xml:space="preserve">6.91022491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04156684875488</t>
   </si>
   <si>
     <t xml:space="preserve">7.24916982650757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10088157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00343561172485</t>
+    <t xml:space="preserve">7.10088205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0034351348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.70685911178589</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71533250808716</t>
+    <t xml:space="preserve">6.71533298492432</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64330720901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55009698867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6094126701355</t>
+    <t xml:space="preserve">6.64330673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55009746551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60941314697266</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12641716003418</t>
+    <t xml:space="preserve">6.28741598129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12641763687134</t>
   </si>
   <si>
     <t xml:space="preserve">6.1518383026123</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912773132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07981252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04591751098633</t>
+    <t xml:space="preserve">6.13912725448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07981300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04591798782349</t>
   </si>
   <si>
     <t xml:space="preserve">6.36367797851562</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47383451461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807168960571</t>
+    <t xml:space="preserve">6.47383499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807216644287</t>
   </si>
   <si>
     <t xml:space="preserve">6.27046823501587</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">6.22386360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336442947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0840482711792</t>
+    <t xml:space="preserve">6.14336347579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08404874801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.95270824432373</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">6.07133817672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18149614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02049684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931287765503</t>
+    <t xml:space="preserve">6.18149566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02049732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931240081787</t>
   </si>
   <si>
     <t xml:space="preserve">6.3848614692688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32978343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32130908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420576095581</t>
+    <t xml:space="preserve">6.32978391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32131004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420623779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.25775814056396</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">6.2747049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.232337474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3085994720459</t>
+    <t xml:space="preserve">6.23233699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30859994888306</t>
   </si>
   <si>
     <t xml:space="preserve">6.37215185165405</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">6.986487865448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019725799561</t>
+    <t xml:space="preserve">7.16019678115845</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377777099609</t>
+    <t xml:space="preserve">6.97377729415894</t>
   </si>
   <si>
     <t xml:space="preserve">6.73227977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75346422195435</t>
+    <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
     <t xml:space="preserve">7.0161452293396</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">6.85938453674316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79583263397217</t>
+    <t xml:space="preserve">6.79583168029785</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10946989059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0543909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04168128967285</t>
+    <t xml:space="preserve">6.10947036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05439138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04168081283569</t>
   </si>
   <si>
     <t xml:space="preserve">6.16031122207642</t>
@@ -2558,25 +2558,25 @@
     <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2153902053833</t>
+    <t xml:space="preserve">6.21538972854614</t>
   </si>
   <si>
     <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09252262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00778675079346</t>
+    <t xml:space="preserve">6.09252309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00778722763062</t>
   </si>
   <si>
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089670181274</t>
+    <t xml:space="preserve">5.57563257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4908971786499</t>
   </si>
   <si>
     <t xml:space="preserve">5.6010537147522</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787210464478</t>
+    <t xml:space="preserve">5.25787258148193</t>
   </si>
   <si>
     <t xml:space="preserve">5.28752994537354</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0587420463562</t>
+    <t xml:space="preserve">5.05874252319336</t>
   </si>
   <si>
     <t xml:space="preserve">5.01213788986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176616668701</t>
+    <t xml:space="preserve">5.29176664352417</t>
   </si>
   <si>
     <t xml:space="preserve">5.40616035461426</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">5.76205205917358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81713056564331</t>
+    <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
     <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93988275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74075317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82125329971313</t>
+    <t xml:space="preserve">6.93988227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74075365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82125282287598</t>
   </si>
   <si>
     <t xml:space="preserve">7.04580307006836</t>
@@ -2633,52 +2633,52 @@
     <t xml:space="preserve">8.09653091430664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88045310974121</t>
+    <t xml:space="preserve">7.88045406341553</t>
   </si>
   <si>
     <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49914169311523</t>
+    <t xml:space="preserve">7.49914073944092</t>
   </si>
   <si>
     <t xml:space="preserve">7.45253610610962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845594406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200832366943</t>
+    <t xml:space="preserve">7.62624502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200880050659</t>
   </si>
   <si>
     <t xml:space="preserve">7.77453327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77029705047607</t>
+    <t xml:space="preserve">7.77029657363892</t>
   </si>
   <si>
     <t xml:space="preserve">7.85079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87197923660278</t>
+    <t xml:space="preserve">7.8719801902771</t>
   </si>
   <si>
     <t xml:space="preserve">7.8423228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67284917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8126654624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7957181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63471937179565</t>
+    <t xml:space="preserve">7.67285013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63471794128418</t>
   </si>
   <si>
     <t xml:space="preserve">7.91011047363281</t>
@@ -2690,37 +2690,37 @@
     <t xml:space="preserve">7.8550329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68556070327759</t>
+    <t xml:space="preserve">7.68556118011475</t>
   </si>
   <si>
     <t xml:space="preserve">7.52456188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47795677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5881142616272</t>
+    <t xml:space="preserve">7.4779577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58811378479004</t>
   </si>
   <si>
     <t xml:space="preserve">7.56693077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41016817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22374868392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32543230056763</t>
+    <t xml:space="preserve">7.41016864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22374820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32543325424194</t>
   </si>
   <si>
     <t xml:space="preserve">7.31695938110352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18985366821289</t>
+    <t xml:space="preserve">7.18985414505005</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2729,13 +2729,13 @@
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15596008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319229125977</t>
+    <t xml:space="preserve">7.15595960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63895606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319276809692</t>
   </si>
   <si>
     <t xml:space="preserve">7.74911308288574</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">7.85926914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21516132354736</t>
+    <t xml:space="preserve">8.21516036987305</t>
   </si>
   <si>
     <t xml:space="preserve">8.2321081161499</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79148006439209</t>
+    <t xml:space="preserve">8.20668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30837154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14313411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79147911071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.65166616439819</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0372142791748</t>
+    <t xml:space="preserve">8.03721618652344</t>
   </si>
   <si>
     <t xml:space="preserve">7.92282152175903</t>
@@ -2780,22 +2780,22 @@
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033866882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63460445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0075569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3973445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78712844848633</t>
+    <t xml:space="preserve">8.88033962249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63460350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00755786895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39734363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.68544578552246</t>
@@ -2816,19 +2816,19 @@
     <t xml:space="preserve">9.60059547424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96507549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04133892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71075248718262</t>
+    <t xml:space="preserve">8.96507453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04133701324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0498104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71075344085693</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">9.48196506500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69380474090576</t>
+    <t xml:space="preserve">9.69380569458008</t>
   </si>
   <si>
     <t xml:space="preserve">10.041223526001</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433300018311</t>
+    <t xml:space="preserve">9.52433204650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.43112277984619</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689128875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08806610107422</t>
+    <t xml:space="preserve">8.96689224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0880651473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.2092399597168</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43427658081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63334941864014</t>
+    <t xml:space="preserve">9.43427753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63335037231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.68528079986572</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">9.47755432128906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32175922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21789646148682</t>
+    <t xml:space="preserve">9.3217601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21789455413818</t>
   </si>
   <si>
     <t xml:space="preserve">9.1140308380127</t>
@@ -2915,31 +2915,31 @@
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882362365723</t>
+    <t xml:space="preserve">9.01882457733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.26117134094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51217555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46889877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26982879638672</t>
+    <t xml:space="preserve">9.51217460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46889972686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2698278427124</t>
   </si>
   <si>
     <t xml:space="preserve">9.31310367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33041381835938</t>
+    <t xml:space="preserve">9.33041477203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34772491455078</t>
+    <t xml:space="preserve">9.3477258682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.1313419342041</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00151252746582</t>
+    <t xml:space="preserve">9.00151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">8.75916385650635</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">9.36503505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41696739196777</t>
+    <t xml:space="preserve">9.41696834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.16596412658691</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">8.99285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.252516746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1746187210083</t>
+    <t xml:space="preserve">9.25251579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17461967468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706092834473</t>
+    <t xml:space="preserve">8.83706188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72454261779785</t>
+    <t xml:space="preserve">8.72454357147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.63798999786377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68126678466797</t>
+    <t xml:space="preserve">8.68126583099365</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44324684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36967658996582</t>
+    <t xml:space="preserve">8.44324588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.26581287384033</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74185371398926</t>
+    <t xml:space="preserve">8.74185562133789</t>
   </si>
   <si>
     <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131450653076</t>
+    <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
     <t xml:space="preserve">8.42160797119141</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">8.3610200881958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47354030609131</t>
+    <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
     <t xml:space="preserve">8.63366222381592</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">8.61202335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59904193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50383186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5427827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58605766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81975173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80244159698486</t>
+    <t xml:space="preserve">8.59904098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50383281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54278182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81975078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80244064331055</t>
   </si>
   <si>
     <t xml:space="preserve">7.92825508117676</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">7.99749851226807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96287775039673</t>
+    <t xml:space="preserve">7.96287679672241</t>
   </si>
   <si>
     <t xml:space="preserve">7.91959953308105</t>
@@ -3119,19 +3119,19 @@
     <t xml:space="preserve">7.91527318954468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95854902267456</t>
+    <t xml:space="preserve">7.95854806900024</t>
   </si>
   <si>
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439136505127</t>
+    <t xml:space="preserve">7.82439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">7.65128612518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53011131286621</t>
+    <t xml:space="preserve">7.53011226654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.556077003479</t>
@@ -3140,16 +3140,16 @@
     <t xml:space="preserve">7.49981832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39162731170654</t>
+    <t xml:space="preserve">7.39162683486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.35267782211304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09734678268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16658878326416</t>
+    <t xml:space="preserve">7.09734630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.166588306427</t>
   </si>
   <si>
     <t xml:space="preserve">7.05839776992798</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51280117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42192077636719</t>
+    <t xml:space="preserve">7.33969449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51280164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42191982269287</t>
   </si>
   <si>
     <t xml:space="preserve">7.37431669235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33104038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15360689163208</t>
+    <t xml:space="preserve">7.3310399055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15360641479492</t>
   </si>
   <si>
     <t xml:space="preserve">7.06272506713867</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">7.2012095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27045202255249</t>
+    <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
     <t xml:space="preserve">7.19255542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25747013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2617974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24448680877686</t>
+    <t xml:space="preserve">7.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2444863319397</t>
   </si>
   <si>
     <t xml:space="preserve">7.40461015701294</t>
@@ -3212,10 +3212,10 @@
     <t xml:space="preserve">7.31805658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700607299805</t>
+    <t xml:space="preserve">7.41759252548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700654983521</t>
   </si>
   <si>
     <t xml:space="preserve">7.36566114425659</t>
@@ -3224,37 +3224,37 @@
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14062309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07138109207153</t>
+    <t xml:space="preserve">7.23583078384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14062356948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07138061523438</t>
   </si>
   <si>
     <t xml:space="preserve">7.02377605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01944923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91991281509399</t>
+    <t xml:space="preserve">7.01944828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88961935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91991329193115</t>
   </si>
   <si>
     <t xml:space="preserve">6.88096380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66458177566528</t>
+    <t xml:space="preserve">6.66458129882812</t>
   </si>
   <si>
     <t xml:space="preserve">6.42223310470581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4698371887207</t>
+    <t xml:space="preserve">6.46983766555786</t>
   </si>
   <si>
     <t xml:space="preserve">6.42656135559082</t>
@@ -3266,25 +3266,25 @@
     <t xml:space="preserve">6.5131139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54340791702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63861608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49147605895996</t>
+    <t xml:space="preserve">6.54340744018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63861560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4914755821228</t>
   </si>
   <si>
     <t xml:space="preserve">6.36164569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47849321365356</t>
+    <t xml:space="preserve">6.47849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">6.43088817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5693736076355</t>
+    <t xml:space="preserve">6.56937313079834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44387149810791</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">6.21883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21450567245483</t>
+    <t xml:space="preserve">6.21450614929199</t>
   </si>
   <si>
     <t xml:space="preserve">6.10198736190796</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">5.88560438156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20152282714844</t>
+    <t xml:space="preserve">6.2015233039856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11497020721436</t>
@@ -3326,34 +3326,34 @@
     <t xml:space="preserve">6.08034896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70817041397095</t>
+    <t xml:space="preserve">5.70817089080811</t>
   </si>
   <si>
     <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46149492263794</t>
+    <t xml:space="preserve">5.4614953994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.29704427719116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53073692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55670309066772</t>
+    <t xml:space="preserve">5.53073740005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55670356750488</t>
   </si>
   <si>
     <t xml:space="preserve">5.55237579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63460063934326</t>
+    <t xml:space="preserve">5.63460111618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89425945281982</t>
+    <t xml:space="preserve">5.89425992965698</t>
   </si>
   <si>
     <t xml:space="preserve">5.83367252349854</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99812269210815</t>
+    <t xml:space="preserve">5.99812364578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.1539192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11064195632935</t>
+    <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.145263671875</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">6.18421220779419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34000825881958</t>
+    <t xml:space="preserve">6.34000778198242</t>
   </si>
   <si>
     <t xml:space="preserve">6.19286775588989</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">6.26211023330688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30105972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45685386657715</t>
+    <t xml:space="preserve">6.30105924606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
     <t xml:space="preserve">6.24479961395264</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51744222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34433507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10631465911865</t>
+    <t xml:space="preserve">6.51744174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34433555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10631418228149</t>
   </si>
   <si>
     <t xml:space="preserve">6.27900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19044828414917</t>
+    <t xml:space="preserve">6.19044780731201</t>
   </si>
   <si>
     <t xml:space="preserve">6.12845516204834</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">6.27458190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34543037414551</t>
+    <t xml:space="preserve">6.34543085098267</t>
   </si>
   <si>
     <t xml:space="preserve">6.4162802696228</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">5.86277055740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67679119110107</t>
+    <t xml:space="preserve">5.67679166793823</t>
   </si>
   <si>
     <t xml:space="preserve">5.57937431335449</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">5.40225076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65022325515747</t>
+    <t xml:space="preserve">5.65022373199463</t>
   </si>
   <si>
     <t xml:space="preserve">5.59708642959595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61922693252563</t>
+    <t xml:space="preserve">5.61922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.62808275222778</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">5.81406211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79192209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6059422492981</t>
+    <t xml:space="preserve">5.79192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60594177246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">5.88933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77863788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92476367950439</t>
+    <t xml:space="preserve">5.77863740921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92476415634155</t>
   </si>
   <si>
     <t xml:space="preserve">5.85834264755249</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948635101318</t>
+    <t xml:space="preserve">5.84948682785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.94690418243408</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07531833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07974672317505</t>
+    <t xml:space="preserve">6.07531881332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07974624633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.95576000213623</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660989761353</t>
+    <t xml:space="preserve">6.02660942077637</t>
   </si>
   <si>
     <t xml:space="preserve">5.99561309814453</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">5.96018838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95133209228516</t>
+    <t xml:space="preserve">5.95133256912231</t>
   </si>
   <si>
     <t xml:space="preserve">6.01775360107422</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8760552406311</t>
+    <t xml:space="preserve">5.87605571746826</t>
   </si>
   <si>
     <t xml:space="preserve">5.89819526672363</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">5.61037063598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67236423492432</t>
+    <t xml:space="preserve">5.67236375808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.73435640335083</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">5.5572338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59265851974487</t>
+    <t xml:space="preserve">5.59265804290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68564796447754</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">5.8671989440918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6546516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62365436553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121957778931</t>
+    <t xml:space="preserve">5.65465116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62365484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68121910095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7299280166626</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3188624382019</t>
+    <t xml:space="preserve">6.31886291503906</t>
   </si>
   <si>
     <t xml:space="preserve">6.25244140625</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">6.17273569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08417415618896</t>
+    <t xml:space="preserve">6.08417463302612</t>
   </si>
   <si>
     <t xml:space="preserve">6.06203413009644</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">6.29672241210938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4472770690918</t>
+    <t xml:space="preserve">6.44727659225464</t>
   </si>
   <si>
     <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4738450050354</t>
+    <t xml:space="preserve">6.47384452819824</t>
   </si>
   <si>
     <t xml:space="preserve">6.42513656616211</t>
@@ -3758,22 +3758,22 @@
     <t xml:space="preserve">6.53141021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668706893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75724220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7926664352417</t>
+    <t xml:space="preserve">6.60668754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75724172592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79266691207886</t>
   </si>
   <si>
     <t xml:space="preserve">6.65539598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54912233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52255392074585</t>
+    <t xml:space="preserve">6.54912185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52255344390869</t>
   </si>
   <si>
     <t xml:space="preserve">6.53583812713623</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">6.63325548171997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49155712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5136981010437</t>
+    <t xml:space="preserve">6.49155759811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51369762420654</t>
   </si>
   <si>
     <t xml:space="preserve">6.50926971435547</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">6.4074239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55355024337769</t>
+    <t xml:space="preserve">6.55355072021484</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425228118896</t>
@@ -3830,34 +3830,34 @@
     <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98307418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06720733642578</t>
+    <t xml:space="preserve">6.96093368530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98307371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06720685958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.32846307754517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63842868804932</t>
+    <t xml:space="preserve">7.63842916488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81998014450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58529138565063</t>
+    <t xml:space="preserve">7.81997919082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58529186248779</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20890617370605</t>
+    <t xml:space="preserve">7.2089056968689</t>
   </si>
   <si>
     <t xml:space="preserve">7.19562149047852</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">7.3018946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52329874038696</t>
+    <t xml:space="preserve">7.5232982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.49230241775513</t>
@@ -3881,34 +3881,34 @@
     <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34617614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48787403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34174728393555</t>
+    <t xml:space="preserve">7.34617567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48787450790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
     <t xml:space="preserve">7.10263252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31517934799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22661733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32403612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35060405731201</t>
+    <t xml:space="preserve">7.3151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32403564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35060358047485</t>
   </si>
   <si>
     <t xml:space="preserve">7.25318574905396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17790842056274</t>
+    <t xml:space="preserve">7.1779088973999</t>
   </si>
   <si>
     <t xml:space="preserve">7.2753267288208</t>
@@ -3917,13 +3917,13 @@
     <t xml:space="preserve">7.29303884506226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41259670257568</t>
+    <t xml:space="preserve">7.41259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">7.44802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48344612121582</t>
+    <t xml:space="preserve">7.48344564437866</t>
   </si>
   <si>
     <t xml:space="preserve">7.36388778686523</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">7.20004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95207691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74838590621948</t>
+    <t xml:space="preserve">6.95207738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74838542938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.00078582763672</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">7.17348098754883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31960773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38602828979492</t>
+    <t xml:space="preserve">7.31960821151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38602876663208</t>
   </si>
   <si>
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3993124961853</t>
+    <t xml:space="preserve">7.39931201934814</t>
   </si>
   <si>
     <t xml:space="preserve">7.27975463867188</t>
@@ -4013,22 +4013,22 @@
     <t xml:space="preserve">7.45687770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54543972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68270921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60300397872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67828130722046</t>
+    <t xml:space="preserve">7.54543924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47458934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68270969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60300445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71370649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828178405762</t>
   </si>
   <si>
     <t xml:space="preserve">7.85610342025757</t>
@@ -4160,9 +4160,6 @@
     <t xml:space="preserve">7.53237581253052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67828178405762</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.69651889801025</t>
   </si>
   <si>
@@ -5397,6 +5394,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.1400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960000038147</t>
   </si>
 </sst>
 </file>
@@ -53671,7 +53671,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1844" t="s">
-        <v>1382</v>
+        <v>1338</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -53697,7 +53697,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1845" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -53723,7 +53723,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1846" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -53749,7 +53749,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G1847" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -53801,7 +53801,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53827,7 +53827,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1850" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -53853,7 +53853,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1851" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -53879,7 +53879,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1852" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -53905,7 +53905,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1853" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -53957,7 +53957,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G1855" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -53983,7 +53983,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1856" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -54009,7 +54009,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G1857" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54035,7 +54035,7 @@
         <v>8</v>
       </c>
       <c r="G1858" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -54061,7 +54061,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1859" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -54087,7 +54087,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1860" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54113,7 +54113,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1861" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -54139,7 +54139,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1862" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -54165,7 +54165,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1863" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -54191,7 +54191,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1864" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -54217,7 +54217,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1865" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -54243,7 +54243,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54269,7 +54269,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1867" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -54295,7 +54295,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -54321,7 +54321,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1869" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -54347,7 +54347,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1870" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54373,7 +54373,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1871" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -54399,7 +54399,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -54425,7 +54425,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1873" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -54451,7 +54451,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1874" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -54477,7 +54477,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -54503,7 +54503,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1876" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -54529,7 +54529,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1877" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -54555,7 +54555,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -54581,7 +54581,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G1879" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -54607,7 +54607,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1880" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -54633,7 +54633,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G1881" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -54659,7 +54659,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1882" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -54685,7 +54685,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1883" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -54711,7 +54711,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1884" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -54737,7 +54737,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1885" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -54763,7 +54763,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1886" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -54789,7 +54789,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1887" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -54815,7 +54815,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1888" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -54841,7 +54841,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1889" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -54867,7 +54867,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -54893,7 +54893,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G1891" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54919,7 +54919,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1892" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -54945,7 +54945,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -54971,7 +54971,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1894" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -54997,7 +54997,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -55023,7 +55023,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -55049,7 +55049,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1897" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -55075,7 +55075,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1898" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -55101,7 +55101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1899" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -55127,7 +55127,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -55153,7 +55153,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1901" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -55179,7 +55179,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1902" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -55205,7 +55205,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1903" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -55231,7 +55231,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1904" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55257,7 +55257,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1905" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -55283,7 +55283,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1906" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55309,7 +55309,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1907" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -55335,7 +55335,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -55361,7 +55361,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1909" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -55387,7 +55387,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G1910" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -55413,7 +55413,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1911" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -55439,7 +55439,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1912" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -55465,7 +55465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -55491,7 +55491,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1914" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -55517,7 +55517,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1915" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -55543,7 +55543,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1916" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -55569,7 +55569,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1917" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -55595,7 +55595,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1918" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -55621,7 +55621,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1919" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -55647,7 +55647,7 @@
         <v>7.75</v>
       </c>
       <c r="G1920" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -55673,7 +55673,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1921" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -55699,7 +55699,7 @@
         <v>7.875</v>
       </c>
       <c r="G1922" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55725,7 +55725,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1923" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -55751,7 +55751,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1924" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -55777,7 +55777,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1925" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -55803,7 +55803,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -55829,7 +55829,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -55855,7 +55855,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1928" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -55881,7 +55881,7 @@
         <v>8</v>
       </c>
       <c r="G1929" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -55907,7 +55907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1930" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -55933,7 +55933,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1931" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -55959,7 +55959,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1932" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55985,7 +55985,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1933" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56037,7 +56037,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1935" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -56089,7 +56089,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -56141,7 +56141,7 @@
         <v>8.75</v>
       </c>
       <c r="G1939" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -56167,7 +56167,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1940" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -56193,7 +56193,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -56219,7 +56219,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -56245,7 +56245,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -56297,7 +56297,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1945" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -56323,7 +56323,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1946" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -56349,7 +56349,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -56375,7 +56375,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -56401,7 +56401,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1949" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -56427,7 +56427,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -56453,7 +56453,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1951" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -56479,7 +56479,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1952" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -56505,7 +56505,7 @@
         <v>9.125</v>
       </c>
       <c r="G1953" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -56531,7 +56531,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G1954" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -56557,7 +56557,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1955" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -56583,7 +56583,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1956" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -56609,7 +56609,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1957" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56661,7 +56661,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1959" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56687,7 +56687,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1960" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56713,7 +56713,7 @@
         <v>9</v>
       </c>
       <c r="G1961" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56739,7 +56739,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56765,7 +56765,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56791,7 +56791,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1964" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56817,7 +56817,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1965" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56843,7 +56843,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1966" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56869,7 +56869,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G1967" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56895,7 +56895,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G1968" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56921,7 +56921,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1969" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56947,7 +56947,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1970" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56973,7 +56973,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1971" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56999,7 +56999,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1972" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57025,7 +57025,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57051,7 +57051,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G1974" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57077,7 +57077,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1975" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57103,7 +57103,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1976" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57129,7 +57129,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57155,7 +57155,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1978" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57181,7 +57181,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1979" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57233,7 +57233,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1981" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57259,7 +57259,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G1982" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57285,7 +57285,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1983" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57311,7 +57311,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G1984" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57337,7 +57337,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1985" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57363,7 +57363,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57389,7 +57389,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1987" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57415,7 +57415,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1988" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57441,7 +57441,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1989" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57467,7 +57467,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1990" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57493,7 +57493,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1991" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57519,7 +57519,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G1992" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57545,7 +57545,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1993" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57571,7 +57571,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1994" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57597,7 +57597,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57623,7 +57623,7 @@
         <v>8.75</v>
       </c>
       <c r="G1996" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57649,7 +57649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1997" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57675,7 +57675,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57701,7 +57701,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1999" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57727,7 +57727,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57753,7 +57753,7 @@
         <v>9.25</v>
       </c>
       <c r="G2001" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57779,7 +57779,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2002" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57805,7 +57805,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2003" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57831,7 +57831,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2004" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57857,7 +57857,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57883,7 +57883,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G2006" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57909,7 +57909,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2007" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57935,7 +57935,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G2008" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57961,7 +57961,7 @@
         <v>9.375</v>
       </c>
       <c r="G2009" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57987,7 +57987,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2010" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58013,7 +58013,7 @@
         <v>9.73499965667725</v>
       </c>
       <c r="G2011" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58039,7 +58039,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2012" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58065,7 +58065,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2013" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58117,7 +58117,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2015" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58143,7 +58143,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2016" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58169,7 +58169,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G2017" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58195,7 +58195,7 @@
         <v>9</v>
       </c>
       <c r="G2018" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58247,7 +58247,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2020" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58273,7 +58273,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G2021" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58299,7 +58299,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58325,7 +58325,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2023" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58377,7 +58377,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2025" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58403,7 +58403,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2026" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58429,7 +58429,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G2027" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58455,7 +58455,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58533,7 +58533,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58559,7 +58559,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G2032" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58585,7 +58585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2033" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58611,7 +58611,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58637,7 +58637,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2035" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58663,7 +58663,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G2036" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58689,7 +58689,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G2037" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58715,7 +58715,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G2038" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58741,7 +58741,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G2039" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58767,7 +58767,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58793,7 +58793,7 @@
         <v>9.25</v>
       </c>
       <c r="G2041" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58819,7 +58819,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58845,7 +58845,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G2043" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58871,7 +58871,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2044" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58897,7 +58897,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58923,7 +58923,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2046" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58949,7 +58949,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2047" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58975,7 +58975,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2048" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59001,7 +59001,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2049" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59027,7 +59027,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2050" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59053,7 +59053,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G2051" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59079,7 +59079,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2052" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59105,7 +59105,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59131,7 +59131,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2054" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59157,7 +59157,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59183,7 +59183,7 @@
         <v>9.125</v>
       </c>
       <c r="G2056" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59209,7 +59209,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G2057" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59235,7 +59235,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2058" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59261,7 +59261,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2059" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59287,7 +59287,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2060" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59313,7 +59313,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2061" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59339,7 +59339,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2062" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59365,7 +59365,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2063" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59391,7 +59391,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2064" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59417,7 +59417,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2065" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59443,7 +59443,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G2066" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59469,7 +59469,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G2067" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59495,7 +59495,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2068" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59521,7 +59521,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2069" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59547,7 +59547,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G2070" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59573,7 +59573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59599,7 +59599,7 @@
         <v>9.5</v>
       </c>
       <c r="G2072" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59625,7 +59625,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2073" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59651,7 +59651,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2074" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59677,7 +59677,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59703,7 +59703,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2076" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59729,7 +59729,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2077" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59755,7 +59755,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59781,7 +59781,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2079" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59807,7 +59807,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2080" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59833,7 +59833,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2081" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59859,7 +59859,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2082" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59885,7 +59885,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2083" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59911,7 +59911,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2084" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59937,7 +59937,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59963,7 +59963,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2086" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59989,7 +59989,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2087" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60015,7 +60015,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2088" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60041,7 +60041,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G2089" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60067,7 +60067,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2090" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60093,7 +60093,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2091" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60119,7 +60119,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G2092" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60145,7 +60145,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2093" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60171,7 +60171,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60197,7 +60197,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2095" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60223,7 +60223,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2096" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60249,7 +60249,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2097" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60275,7 +60275,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2098" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60301,7 +60301,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G2099" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60327,7 +60327,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2100" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60353,7 +60353,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G2101" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60379,7 +60379,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G2102" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60405,7 +60405,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2103" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60431,7 +60431,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2104" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60457,7 +60457,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2105" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60483,7 +60483,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2106" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60509,7 +60509,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2107" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60535,7 +60535,7 @@
         <v>8.875</v>
       </c>
       <c r="G2108" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60561,7 +60561,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2109" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60587,7 +60587,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2110" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60613,7 +60613,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G2111" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60639,7 +60639,7 @@
         <v>9.125</v>
       </c>
       <c r="G2112" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60665,7 +60665,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2113" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60691,7 +60691,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G2114" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60717,7 +60717,7 @@
         <v>9.25</v>
       </c>
       <c r="G2115" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60743,7 +60743,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2116" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60769,7 +60769,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2117" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60795,7 +60795,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2118" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60821,7 +60821,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2119" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60847,7 +60847,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2120" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60873,7 +60873,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2121" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60899,7 +60899,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60925,7 +60925,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60951,7 +60951,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60977,7 +60977,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G2125" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61003,7 +61003,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G2126" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61029,7 +61029,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2127" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61055,7 +61055,7 @@
         <v>9.25</v>
       </c>
       <c r="G2128" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61081,7 +61081,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2129" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61107,7 +61107,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G2130" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61133,7 +61133,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2131" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61159,7 +61159,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G2132" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61185,7 +61185,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2133" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61211,7 +61211,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2134" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61237,7 +61237,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2135" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61263,7 +61263,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2136" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61289,7 +61289,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G2137" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61315,7 +61315,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G2138" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61341,7 +61341,7 @@
         <v>9.25</v>
       </c>
       <c r="G2139" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61367,7 +61367,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61393,7 +61393,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2141" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61419,7 +61419,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2142" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61445,7 +61445,7 @@
         <v>9.375</v>
       </c>
       <c r="G2143" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61471,7 +61471,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2144" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61497,7 +61497,7 @@
         <v>9.375</v>
       </c>
       <c r="G2145" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61523,7 +61523,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2146" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61549,7 +61549,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2147" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61575,7 +61575,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61601,7 +61601,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2149" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61627,7 +61627,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2150" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61653,7 +61653,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2151" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61679,7 +61679,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2152" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61705,7 +61705,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61731,7 +61731,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2154" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61757,7 +61757,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2155" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61783,7 +61783,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G2156" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61809,7 +61809,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2157" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61835,7 +61835,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61861,7 +61861,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2159" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61887,7 +61887,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61913,7 +61913,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2161" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61939,7 +61939,7 @@
         <v>9.625</v>
       </c>
       <c r="G2162" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61965,7 +61965,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G2163" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61991,7 +61991,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G2164" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62017,7 +62017,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G2165" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62043,7 +62043,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2166" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62069,7 +62069,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G2167" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62095,7 +62095,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62121,7 +62121,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G2169" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62147,7 +62147,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G2170" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62173,7 +62173,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2171" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62199,7 +62199,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2172" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62225,7 +62225,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2173" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62251,7 +62251,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2174" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62277,7 +62277,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2175" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62303,7 +62303,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62329,7 +62329,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G2177" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62355,7 +62355,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G2178" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62381,7 +62381,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2179" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62407,7 +62407,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2180" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62433,7 +62433,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2181" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62459,7 +62459,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G2182" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62485,7 +62485,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2183" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62511,7 +62511,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2184" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62537,7 +62537,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2185" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62563,7 +62563,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2186" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62589,7 +62589,7 @@
         <v>10.5</v>
       </c>
       <c r="G2187" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62615,7 +62615,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2188" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62641,7 +62641,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62667,7 +62667,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2190" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62693,7 +62693,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2191" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62719,7 +62719,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2192" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62745,7 +62745,7 @@
         <v>10.25</v>
       </c>
       <c r="G2193" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62771,7 +62771,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2194" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62797,7 +62797,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2195" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62823,7 +62823,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2196" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62849,7 +62849,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2197" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62875,7 +62875,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2198" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62901,7 +62901,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2199" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62927,7 +62927,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2200" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62953,7 +62953,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2201" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62979,7 +62979,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2202" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63005,7 +63005,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63031,7 +63031,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2204" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63057,7 +63057,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63083,7 +63083,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2206" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63109,7 +63109,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2207" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63135,7 +63135,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2208" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63161,7 +63161,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2209" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63187,7 +63187,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2210" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63213,7 +63213,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2211" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63239,7 +63239,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G2212" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63265,7 +63265,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G2213" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63291,7 +63291,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2214" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63317,7 +63317,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2215" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63343,7 +63343,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2216" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63369,7 +63369,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2217" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63395,7 +63395,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2218" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63421,7 +63421,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2219" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63447,7 +63447,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2220" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63473,7 +63473,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2221" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63499,7 +63499,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2222" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63525,7 +63525,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63551,7 +63551,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63577,7 +63577,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2225" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63603,7 +63603,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2226" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63629,7 +63629,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2227" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63655,7 +63655,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2228" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63681,7 +63681,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2229" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63707,7 +63707,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2230" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63733,7 +63733,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2231" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63759,7 +63759,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2232" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63785,7 +63785,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2233" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63811,7 +63811,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2234" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63837,7 +63837,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63863,7 +63863,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2236" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63889,7 +63889,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2237" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63915,7 +63915,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2238" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63941,7 +63941,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2239" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63967,7 +63967,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2240" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63993,7 +63993,7 @@
         <v>11.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64019,7 +64019,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2242" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64045,7 +64045,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64071,7 +64071,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2244" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64097,7 +64097,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2245" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64123,7 +64123,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2246" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64149,7 +64149,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G2247" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64175,7 +64175,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2248" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64201,7 +64201,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64227,7 +64227,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G2250" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64253,7 +64253,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2251" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64279,7 +64279,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G2252" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64305,7 +64305,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2253" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64331,7 +64331,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2254" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64357,7 +64357,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2255" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64383,7 +64383,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2256" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64409,7 +64409,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2257" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64435,7 +64435,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2258" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64461,7 +64461,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64487,7 +64487,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2260" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64513,7 +64513,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2261" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64539,7 +64539,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2262" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64565,7 +64565,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64591,7 +64591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64617,7 +64617,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G2265" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64643,7 +64643,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2266" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64669,7 +64669,7 @@
         <v>12</v>
       </c>
       <c r="G2267" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64695,7 +64695,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2268" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64721,7 +64721,7 @@
         <v>12</v>
       </c>
       <c r="G2269" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64747,7 +64747,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2270" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64773,7 +64773,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2271" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64799,7 +64799,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G2272" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64825,7 +64825,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G2273" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64851,7 +64851,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2274" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64877,7 +64877,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2275" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64903,7 +64903,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G2276" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64929,7 +64929,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2277" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64955,7 +64955,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64981,7 +64981,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2279" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65007,7 +65007,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65033,7 +65033,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2281" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65059,7 +65059,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2282" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65085,7 +65085,7 @@
         <v>11.25</v>
       </c>
       <c r="G2283" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65111,7 +65111,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2284" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65137,7 +65137,7 @@
         <v>11.5</v>
       </c>
       <c r="G2285" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65163,7 +65163,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2286" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65189,7 +65189,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2287" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65215,7 +65215,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2288" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65241,7 +65241,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2289" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65267,7 +65267,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2290" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65293,7 +65293,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2291" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65319,7 +65319,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2292" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65345,7 +65345,7 @@
         <v>12.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65371,7 +65371,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G2294" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65397,7 +65397,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2295" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65423,7 +65423,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2296" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65449,7 +65449,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2297" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65475,7 +65475,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2298" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65501,7 +65501,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65527,7 +65527,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65553,7 +65553,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G2301" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65579,7 +65579,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G2302" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65605,7 +65605,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G2303" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65631,7 +65631,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2304" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65657,7 +65657,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65683,7 +65683,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G2306" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65709,7 +65709,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2307" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65735,7 +65735,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G2308" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65761,7 +65761,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2309" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65787,7 +65787,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2310" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65813,7 +65813,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2311" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65839,7 +65839,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2312" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65865,7 +65865,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G2313" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65891,7 +65891,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2314" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65917,7 +65917,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2315" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65943,7 +65943,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2316" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65969,7 +65969,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2317" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65995,7 +65995,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2318" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66021,7 +66021,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2319" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66047,7 +66047,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2320" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66073,7 +66073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2321" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66099,7 +66099,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G2322" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66125,7 +66125,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2323" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66151,7 +66151,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66177,7 +66177,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2325" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66203,7 +66203,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2326" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66229,7 +66229,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2327" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66255,7 +66255,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2328" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66281,7 +66281,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66307,7 +66307,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2330" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66333,7 +66333,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66359,7 +66359,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2332" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66385,7 +66385,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2333" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66411,7 +66411,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2334" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66437,7 +66437,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2335" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66463,7 +66463,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2336" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66489,7 +66489,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2337" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66515,7 +66515,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66541,7 +66541,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G2339" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66567,7 +66567,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2340" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66593,7 +66593,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66619,7 +66619,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66645,7 +66645,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2343" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66671,7 +66671,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2344" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66697,7 +66697,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2345" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66723,7 +66723,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2346" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66749,7 +66749,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66775,7 +66775,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G2348" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66801,7 +66801,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G2349" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66827,7 +66827,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2350" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66853,7 +66853,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66879,7 +66879,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66905,7 +66905,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G2353" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66931,7 +66931,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G2354" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66957,7 +66957,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G2355" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66983,7 +66983,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G2356" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67009,7 +67009,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67035,7 +67035,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2358" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67061,7 +67061,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2359" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67087,7 +67087,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2360" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67113,7 +67113,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2361" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67139,7 +67139,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2362" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67165,7 +67165,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G2363" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67191,7 +67191,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67217,7 +67217,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2365" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67243,7 +67243,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2366" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67269,7 +67269,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2367" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67295,7 +67295,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2368" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67321,7 +67321,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2369" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67347,7 +67347,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67373,7 +67373,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G2371" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67399,7 +67399,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2372" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67425,7 +67425,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G2373" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67451,7 +67451,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67477,7 +67477,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G2375" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67503,7 +67503,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G2376" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67529,7 +67529,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67555,7 +67555,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2378" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67581,7 +67581,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67607,7 +67607,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2380" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67633,7 +67633,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67659,7 +67659,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G2382" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67685,7 +67685,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G2383" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67711,7 +67711,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G2384" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67737,7 +67737,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2385" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67763,7 +67763,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G2386" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67789,7 +67789,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2387" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67815,7 +67815,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2388" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67841,7 +67841,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2389" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67867,7 +67867,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2390" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67893,7 +67893,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67919,7 +67919,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2392" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67945,7 +67945,7 @@
         <v>14.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67971,7 +67971,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67997,7 +67997,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G2395" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68023,7 +68023,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68049,7 +68049,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2397" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68075,7 +68075,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2398" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68101,7 +68101,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68127,7 +68127,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2400" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68153,7 +68153,7 @@
         <v>14.25</v>
       </c>
       <c r="G2401" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68179,7 +68179,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G2402" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68205,7 +68205,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G2403" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68213,7 +68213,7 @@
     </row>
     <row r="2404">
       <c r="A2404" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2404" t="n">
         <v>192314</v>
@@ -68231,9 +68231,35 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2404" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H2404" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>45944.6520138889</v>
+      </c>
+      <c r="B2405" t="n">
+        <v>250051</v>
+      </c>
+      <c r="C2405" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>14.039999961853</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>13.960000038147</v>
+      </c>
+      <c r="G2405" t="s">
         <v>1794</v>
       </c>
-      <c r="H2404" t="s">
+      <c r="H2405" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="1795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1796">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9603259563446</t>
+    <t xml:space="preserve">2.96032619476318</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13860011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12388038635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588908195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06663608551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500029563904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028080940247</t>
+    <t xml:space="preserve">3.13860034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1238796710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588955879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06663632392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0650007724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028057098389</t>
   </si>
   <si>
     <t xml:space="preserve">3.18930196762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16476845741272</t>
+    <t xml:space="preserve">3.1647686958313</t>
   </si>
   <si>
     <t xml:space="preserve">3.17131066322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16149759292603</t>
+    <t xml:space="preserve">3.16149735450745</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205790519714</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">3.15822649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14514183998108</t>
+    <t xml:space="preserve">3.14514231681824</t>
   </si>
   <si>
     <t xml:space="preserve">3.15168452262878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30051827430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34140658378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790411949158</t>
+    <t xml:space="preserve">3.30051803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34140682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463230133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.437903881073</t>
   </si>
   <si>
     <t xml:space="preserve">3.39374423027039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38393092155457</t>
+    <t xml:space="preserve">3.38393115997314</t>
   </si>
   <si>
     <t xml:space="preserve">3.33977150917053</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03065395355225</t>
+    <t xml:space="preserve">3.14841294288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0306544303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.08789825439453</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">3.10752463340759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18112421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257307052612</t>
+    <t xml:space="preserve">3.18112373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257283210754</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0339252948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373860359192</t>
+    <t xml:space="preserve">3.03392553329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303722381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373836517334</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878680229187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23019027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2334611415863</t>
+    <t xml:space="preserve">3.23019003868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23346161842346</t>
   </si>
   <si>
     <t xml:space="preserve">3.22528386116028</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">3.14023542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12224459648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09116959571838</t>
+    <t xml:space="preserve">3.1222448348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09116911888123</t>
   </si>
   <si>
     <t xml:space="preserve">3.08299160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11897373199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425353050232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07481408119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14677739143372</t>
+    <t xml:space="preserve">3.11897349357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07481384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14677762985229</t>
   </si>
   <si>
     <t xml:space="preserve">3.13696432113647</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">3.36921119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42645525932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50986695289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51640939712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54094243049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50169014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552061080933</t>
+    <t xml:space="preserve">3.42645478248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51641035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54094266891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50168943405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552156448364</t>
   </si>
   <si>
     <t xml:space="preserve">3.3561270236969</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724717140198</t>
+    <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
     <t xml:space="preserve">3.36103343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3757529258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3773889541626</t>
+    <t xml:space="preserve">3.37575316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
     <t xml:space="preserve">3.35285544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38556599617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136215209961</t>
+    <t xml:space="preserve">3.38556623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136143684387</t>
   </si>
   <si>
     <t xml:space="preserve">3.51150298118591</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">3.47061419487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46734285354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696970939636</t>
+    <t xml:space="preserve">3.46734309196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696947097778</t>
   </si>
   <si>
     <t xml:space="preserve">3.44281005859375</t>
@@ -263,37 +263,37 @@
     <t xml:space="preserve">3.39701509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41337037086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916557312012</t>
+    <t xml:space="preserve">3.41337060928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488605260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916604995728</t>
   </si>
   <si>
     <t xml:space="preserve">3.41827702522278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50823211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729794502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57855987548828</t>
+    <t xml:space="preserve">3.50823187828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57855939865112</t>
   </si>
   <si>
     <t xml:space="preserve">3.60472893714905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56547594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59818696975708</t>
+    <t xml:space="preserve">3.56547617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818625450134</t>
   </si>
   <si>
     <t xml:space="preserve">3.63907504081726</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">3.66360855102539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64725303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996311187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56711149215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897888183594</t>
+    <t xml:space="preserve">3.64725255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996335029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178559303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636401176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897912025452</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355753898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38065934181213</t>
+    <t xml:space="preserve">3.38065981864929</t>
   </si>
   <si>
     <t xml:space="preserve">3.33813571929932</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">3.32668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27598571777344</t>
+    <t xml:space="preserve">3.2759850025177</t>
   </si>
   <si>
     <t xml:space="preserve">3.2432746887207</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">3.25962996482849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15495538711548</t>
+    <t xml:space="preserve">3.15495562553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.07644963264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08462715148926</t>
+    <t xml:space="preserve">3.08462738990784</t>
   </si>
   <si>
     <t xml:space="preserve">3.12551593780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27107858657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486461639404</t>
+    <t xml:space="preserve">3.27107834815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850981712341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486437797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.36757564544678</t>
@@ -377,46 +377,46 @@
     <t xml:space="preserve">3.30869603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818062782288</t>
+    <t xml:space="preserve">3.24818086624146</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528948783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851496696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6407105922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435531616211</t>
+    <t xml:space="preserve">3.48206305503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421401023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528853416443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183169364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309338569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64071083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435507774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.75192713737488</t>
@@ -425,103 +425,103 @@
     <t xml:space="preserve">3.76174020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72412300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809572219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77646040916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720765113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79445099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9154806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86314415931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8925838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529439926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150860786438</t>
+    <t xml:space="preserve">3.72412323951721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118037223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91548156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258337020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440632820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655632972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150813102722</t>
   </si>
   <si>
     <t xml:space="preserve">3.96454739570618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85169506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.043053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618247032166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767766952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898427009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94164967536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02669715881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272515296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0021653175354</t>
+    <t xml:space="preserve">3.85169553756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898474693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138457775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165015220642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02669763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398732185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272443771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00216484069824</t>
   </si>
   <si>
     <t xml:space="preserve">4.0561375617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97926783561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524877548218</t>
+    <t xml:space="preserve">3.97926759719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524972915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.04141712188721</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">4.08884811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08394193649292</t>
+    <t xml:space="preserve">4.08394145965576</t>
   </si>
   <si>
     <t xml:space="preserve">4.16244792938232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693510055542</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.44048929214478</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">4.41595649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33009099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37506771087646</t>
+    <t xml:space="preserve">4.33009004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37506723403931</t>
   </si>
   <si>
     <t xml:space="preserve">4.59586572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76350784301758</t>
+    <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
     <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9924840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439567565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710765838623</t>
+    <t xml:space="preserve">4.99248456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
     <t xml:space="preserve">4.83301877975464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90661764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96386241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928400039673</t>
+    <t xml:space="preserve">4.90661811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96386194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928352355957</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337240219116</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">5.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13150501251221</t>
+    <t xml:space="preserve">5.13150453567505</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28688097000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3686580657959</t>
+    <t xml:space="preserve">5.28688144683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36865711212158</t>
   </si>
   <si>
     <t xml:space="preserve">5.46270132064819</t>
@@ -614,58 +614,58 @@
     <t xml:space="preserve">5.55265617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30323648452759</t>
+    <t xml:space="preserve">5.30323696136475</t>
   </si>
   <si>
     <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5485668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354448318481</t>
+    <t xml:space="preserve">5.54856729507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354496002197</t>
   </si>
   <si>
     <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70803260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709819793701</t>
+    <t xml:space="preserve">5.70803165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709915161133</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207586288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82251977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114145278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48723459243774</t>
+    <t xml:space="preserve">5.82252025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78572082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816900253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4790563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">5.46679019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60581159591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5608344078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64308214187622</t>
+    <t xml:space="preserve">5.60581111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64308166503906</t>
   </si>
   <si>
     <t xml:space="preserve">5.69674682617188</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">5.46144533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290363311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70500230789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73802709579468</t>
+    <t xml:space="preserve">5.57290458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546560287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.705002784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73802757263184</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756475448608</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">5.80407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315103530884</t>
+    <t xml:space="preserve">5.84948587417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315055847168</t>
   </si>
   <si>
     <t xml:space="preserve">6.10129833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84122896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471656799316</t>
+    <t xml:space="preserve">5.84122943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471704483032</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820417404175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133810043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7793083190918</t>
+    <t xml:space="preserve">5.73389959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77930879592896</t>
   </si>
   <si>
     <t xml:space="preserve">5.77105188369751</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68849039077759</t>
+    <t xml:space="preserve">5.68849086761475</t>
   </si>
   <si>
     <t xml:space="preserve">5.56877565383911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069772720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5770320892334</t>
+    <t xml:space="preserve">5.63069725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57703256607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.52336740493774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54813528060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621463775635</t>
+    <t xml:space="preserve">5.54813575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621416091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.53162336349487</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">5.55639219284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32934808731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568340301514</t>
+    <t xml:space="preserve">5.32934713363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568292617798</t>
   </si>
   <si>
     <t xml:space="preserve">5.16009664535522</t>
@@ -770,37 +770,37 @@
     <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30045127868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1931209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230255126953</t>
+    <t xml:space="preserve">5.30045175552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19312143325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230302810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248106002808</t>
+    <t xml:space="preserve">5.17248058319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3995246887207</t>
+    <t xml:space="preserve">5.39952516555786</t>
   </si>
   <si>
     <t xml:space="preserve">5.74628353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75041198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592842102051</t>
+    <t xml:space="preserve">5.75041151046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592889785767</t>
   </si>
   <si>
     <t xml:space="preserve">5.71325874328613</t>
@@ -809,49 +809,49 @@
     <t xml:space="preserve">5.72977161407471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77518033981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76692390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87012577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86599779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94443082809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04763221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204689025879</t>
+    <t xml:space="preserve">5.77517986297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7669243812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87012624740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86599731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94443130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89489412307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04763317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204736709595</t>
   </si>
   <si>
     <t xml:space="preserve">5.86186981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95268678665161</t>
+    <t xml:space="preserve">5.95268726348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.97332763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955476760864</t>
+    <t xml:space="preserve">6.06827306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955381393433</t>
   </si>
   <si>
     <t xml:space="preserve">6.17560386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1797308921814</t>
+    <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
     <t xml:space="preserve">6.19211578369141</t>
@@ -860,127 +860,127 @@
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12193870544434</t>
+    <t xml:space="preserve">6.18385982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12193822860718</t>
   </si>
   <si>
     <t xml:space="preserve">6.1673469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13845109939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15083503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98158359527588</t>
+    <t xml:space="preserve">6.13845062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9815845489502</t>
   </si>
   <si>
     <t xml:space="preserve">6.05176115036011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09717035293579</t>
+    <t xml:space="preserve">6.09716939926147</t>
   </si>
   <si>
     <t xml:space="preserve">6.18798732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15909147262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06001710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98571157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0889139175415</t>
+    <t xml:space="preserve">6.15909099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06001663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9857120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08891439437866</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140651702881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87425327301025</t>
+    <t xml:space="preserve">5.87425374984741</t>
   </si>
   <si>
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9609432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00222444534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22926902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200807571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207696914673</t>
+    <t xml:space="preserve">5.96094369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00222396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200712203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207649230957</t>
   </si>
   <si>
     <t xml:space="preserve">6.88976097106934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85260820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75353479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004671096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392824172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43980026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52649068832397</t>
+    <t xml:space="preserve">6.8526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7535343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574022293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43980073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.45631265640259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57189893722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71638202667236</t>
+    <t xml:space="preserve">6.57189846038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65446043014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71638154983521</t>
   </si>
   <si>
     <t xml:space="preserve">6.6131796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684436798096</t>
+    <t xml:space="preserve">6.53061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684484481812</t>
   </si>
   <si>
     <t xml:space="preserve">6.44805669784546</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">6.625563621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56777143478394</t>
+    <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.50584936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55125904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6090521812439</t>
+    <t xml:space="preserve">6.5512580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905170440674</t>
   </si>
   <si>
     <t xml:space="preserve">6.7287654876709</t>
@@ -1013,94 +1013,94 @@
     <t xml:space="preserve">6.84848022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75766229629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90214395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70812559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748617172241</t>
+    <t xml:space="preserve">6.75766277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90214490890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70812511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.7122540473938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417469024658</t>
+    <t xml:space="preserve">6.77417516708374</t>
   </si>
   <si>
     <t xml:space="preserve">7.43466711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44705152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47182035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932680130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480489730835</t>
+    <t xml:space="preserve">7.44705247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594785690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4718189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356344223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.76078462600708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84334707260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171026229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57914924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28192806243896</t>
+    <t xml:space="preserve">7.84334802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619287490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915067672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28192758560181</t>
   </si>
   <si>
     <t xml:space="preserve">7.40989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1333179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413444519043</t>
+    <t xml:space="preserve">7.28605699539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331747055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241358757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2943115234375</t>
+    <t xml:space="preserve">7.46769237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431200027466</t>
   </si>
   <si>
     <t xml:space="preserve">7.1787257194519</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">7.24890375137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38100147247314</t>
+    <t xml:space="preserve">7.3810019493103</t>
   </si>
   <si>
     <t xml:space="preserve">7.33972120285034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19936752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011560440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01773071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488443374634</t>
+    <t xml:space="preserve">7.1993670463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0177321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488395690918</t>
   </si>
   <si>
     <t xml:space="preserve">6.96406602859497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7948145866394</t>
+    <t xml:space="preserve">6.79481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">6.74940633773804</t>
@@ -1139,31 +1139,31 @@
     <t xml:space="preserve">6.68335771560669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.790687084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25303077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19111061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84022426605225</t>
+    <t xml:space="preserve">6.79068660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25303173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19111108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965183258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84022378921509</t>
   </si>
   <si>
     <t xml:space="preserve">7.05075550079346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23651933670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669689178467</t>
+    <t xml:space="preserve">7.2365198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669593811035</t>
   </si>
   <si>
     <t xml:space="preserve">7.26128768920898</t>
@@ -1172,19 +1172,19 @@
     <t xml:space="preserve">7.25715970993042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36036062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2778000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23138618469238</t>
+    <t xml:space="preserve">7.36036157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27779960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2313871383667</t>
   </si>
   <si>
     <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40476608276367</t>
+    <t xml:space="preserve">8.40476512908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.62768077850342</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">8.41302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14056777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789810180664</t>
+    <t xml:space="preserve">8.14056873321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789905548096</t>
   </si>
   <si>
     <t xml:space="preserve">8.17359256744385</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">8.18184852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20661544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14469718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295314788818</t>
+    <t xml:space="preserve">8.206618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14469623565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295219421387</t>
   </si>
   <si>
     <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430088043213</t>
+    <t xml:space="preserve">8.45430183410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.35522842407227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36348438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33045959472656</t>
+    <t xml:space="preserve">8.36348342895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33046054840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.47907066345215</t>
@@ -1241,43 +1241,43 @@
     <t xml:space="preserve">8.52035140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71024322509766</t>
+    <t xml:space="preserve">8.79280281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71024227142334</t>
   </si>
   <si>
     <t xml:space="preserve">8.82582950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66070652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86711025238037</t>
+    <t xml:space="preserve">8.66070556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83408451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86710929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.66896152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42953300476074</t>
+    <t xml:space="preserve">8.6524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42953395843506</t>
   </si>
   <si>
     <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74605655670166</t>
+    <t xml:space="preserve">8.74605751037598</t>
   </si>
   <si>
     <t xml:space="preserve">8.70440864562988</t>
@@ -1286,46 +1286,46 @@
     <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75438594818115</t>
+    <t xml:space="preserve">8.75438785552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.24628257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30875492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34623718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41287326812744</t>
+    <t xml:space="preserve">8.30875396728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34623908996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41287422180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.55447769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84601306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87932968139648</t>
+    <t xml:space="preserve">8.84601211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87933158874512</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82935333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81269359588623</t>
+    <t xml:space="preserve">8.82935428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81269454956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939872741699</t>
+    <t xml:space="preserve">8.8626708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939682006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.5044994354248</t>
@@ -1337,22 +1337,22 @@
     <t xml:space="preserve">8.47118186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452213287354</t>
+    <t xml:space="preserve">8.45452308654785</t>
   </si>
   <si>
     <t xml:space="preserve">8.25461196899414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58779525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49617004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42120456695557</t>
+    <t xml:space="preserve">8.58779621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49617099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3628978729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42120361328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21712970733643</t>
@@ -1370,76 +1370,76 @@
     <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.121337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142963409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554893493652</t>
+    <t xml:space="preserve">8.12133979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639654159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78815603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554798126221</t>
   </si>
   <si>
     <t xml:space="preserve">7.76733255386353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85062694549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312198638916</t>
+    <t xml:space="preserve">7.85062837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6132345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312246322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.74234342575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67154264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572813034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145137786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.721519947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241056442261</t>
+    <t xml:space="preserve">7.67154169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72151947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241104125977</t>
   </si>
   <si>
     <t xml:space="preserve">7.57158708572388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82980346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54659938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63405895233154</t>
+    <t xml:space="preserve">7.82980442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54659986495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6340594291687</t>
   </si>
   <si>
     <t xml:space="preserve">7.84229755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.792320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61740064620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71318864822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650812149048</t>
+    <t xml:space="preserve">7.79231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61740016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650764465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.68820095062256</t>
@@ -1448,73 +1448,73 @@
     <t xml:space="preserve">7.44664287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28838062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14677858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163152694702</t>
+    <t xml:space="preserve">7.28838109970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14677810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163200378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.66321277618408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04637241363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1713171005249</t>
+    <t xml:space="preserve">8.04637336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17131614685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.47951221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32957744598389</t>
+    <t xml:space="preserve">8.32957935333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23378944396973</t>
+    <t xml:space="preserve">8.23378849029541</t>
   </si>
   <si>
     <t xml:space="preserve">8.37955665588379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52948760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0542516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99594402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01260280609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0792407989502</t>
+    <t xml:space="preserve">8.5294885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05425262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99594497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01260471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07923984527588</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09589958190918</t>
+    <t xml:space="preserve">9.11255931854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09590148925781</t>
   </si>
   <si>
     <t xml:space="preserve">9.02093315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02926254272461</t>
+    <t xml:space="preserve">9.02926349639893</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276264190674</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">8.57113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02138423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08385562896729</t>
+    <t xml:space="preserve">8.02138519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0838565826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.15049266815186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00056076049805</t>
+    <t xml:space="preserve">8.00055980682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.35456657409668</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">7.9839015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82563972473145</t>
+    <t xml:space="preserve">7.82563924789429</t>
   </si>
   <si>
     <t xml:space="preserve">7.9922308921814</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07969188690186</t>
+    <t xml:space="preserve">8.07969093322754</t>
   </si>
   <si>
     <t xml:space="preserve">8.28376579284668</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">8.53781795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46285152435303</t>
+    <t xml:space="preserve">8.46285247802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445499420166</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01721858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26294136047363</t>
+    <t xml:space="preserve">7.54243278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26294231414795</t>
   </si>
   <si>
     <t xml:space="preserve">8.04220771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19213962554932</t>
+    <t xml:space="preserve">8.20047092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19214057922363</t>
   </si>
   <si>
     <t xml:space="preserve">8.09635066986084</t>
@@ -1598,55 +1598,55 @@
     <t xml:space="preserve">8.14216232299805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12550354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17964649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94641828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25877571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9755711555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81730937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21296405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18381118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630527496338</t>
+    <t xml:space="preserve">8.12550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17964553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94641733169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97557163238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8922758102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81731033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989282608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21296501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18381023406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1963062286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73772811889648</t>
+    <t xml:space="preserve">8.73772716522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.43786334991455</t>
@@ -1661,67 +1661,67 @@
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51282978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768272399902</t>
+    <t xml:space="preserve">8.5128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69608020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768177032471</t>
   </si>
   <si>
     <t xml:space="preserve">8.77937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87100124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37910556793213</t>
+    <t xml:space="preserve">8.87100028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37910652160645</t>
   </si>
   <si>
     <t xml:space="preserve">9.56235599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59567451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54569721221924</t>
+    <t xml:space="preserve">9.59567546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54569816589355</t>
   </si>
   <si>
     <t xml:space="preserve">9.39576435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28747844696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29580974578857</t>
+    <t xml:space="preserve">9.28747940063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29580879211426</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35411643981934</t>
+    <t xml:space="preserve">9.49571990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35411739349365</t>
   </si>
   <si>
     <t xml:space="preserve">9.66231155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17086601257324</t>
+    <t xml:space="preserve">9.17086505889893</t>
   </si>
   <si>
     <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.229172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27082061767578</t>
+    <t xml:space="preserve">9.22917461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2708215713501</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
@@ -1736,43 +1736,43 @@
     <t xml:space="preserve">9.0709114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56280612945557</t>
+    <t xml:space="preserve">8.56280708312988</t>
   </si>
   <si>
     <t xml:space="preserve">8.64610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592037200928</t>
+    <t xml:space="preserve">9.04592227935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10422897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94596767425537</t>
+    <t xml:space="preserve">9.10422992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94596672058105</t>
   </si>
   <si>
     <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83797168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65155220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223651885986</t>
+    <t xml:space="preserve">8.83797073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65155124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223747253418</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">8.5159740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48208045959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49055290222168</t>
+    <t xml:space="preserve">8.48207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.490553855896</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039684295654</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26176452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34226417541504</t>
+    <t xml:space="preserve">8.26176643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34226608276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.39310741424561</t>
@@ -1820,46 +1820,46 @@
     <t xml:space="preserve">8.31260776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27871417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28718566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023887634277</t>
+    <t xml:space="preserve">8.27871322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28718662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2956600189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10500431060791</t>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10500335693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75323390960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44394874572754</t>
+    <t xml:space="preserve">8.75323486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44394779205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.3253173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45242309570312</t>
+    <t xml:space="preserve">8.45242118835449</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444744110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66849803924561</t>
+    <t xml:space="preserve">8.52444839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66849708557129</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1868,16 +1868,16 @@
     <t xml:space="preserve">8.44818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60918235778809</t>
+    <t xml:space="preserve">8.60918426513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57528877258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20244979858398</t>
+    <t xml:space="preserve">8.57528972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2024507522583</t>
   </si>
   <si>
     <t xml:space="preserve">8.35921192169189</t>
@@ -1886,34 +1886,34 @@
     <t xml:space="preserve">8.1727933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11771392822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03297805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89740037918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13466167449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96518993377686</t>
+    <t xml:space="preserve">8.11771583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03297901153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89740133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13466262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9651894569397</t>
   </si>
   <si>
     <t xml:space="preserve">7.9016375541687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79995441436768</t>
+    <t xml:space="preserve">7.79995346069336</t>
   </si>
   <si>
     <t xml:space="preserve">7.82961177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73640298843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792911529541</t>
+    <t xml:space="preserve">7.73640203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792863845825</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">7.72369194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95671701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6601390838623</t>
+    <t xml:space="preserve">7.95671653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113790512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66014051437378</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41429138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123722076416</t>
+    <t xml:space="preserve">8.41429042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684303283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19821262359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24058246612549</t>
+    <t xml:space="preserve">8.19821357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24058151245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.21939754486084</t>
@@ -1973,25 +1973,25 @@
     <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53292083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71934032440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46936893463135</t>
+    <t xml:space="preserve">8.53291988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71933937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46936798095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01591777801514</t>
+    <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
     <t xml:space="preserve">8.88881206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90575981140137</t>
+    <t xml:space="preserve">8.90576076507568</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270755767822</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">8.13042449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22363376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18973922729492</t>
+    <t xml:space="preserve">8.22363471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
     <t xml:space="preserve">8.37192249298096</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">8.76170825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81254959106445</t>
+    <t xml:space="preserve">8.81255054473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.60070991516113</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">8.54139423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697143554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85491847991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02439022064209</t>
+    <t xml:space="preserve">8.69392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8549165725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02438926696777</t>
   </si>
   <si>
     <t xml:space="preserve">9.28707218170166</t>
@@ -2045,34 +2045,34 @@
     <t xml:space="preserve">9.57517528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349166870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65143871307373</t>
+    <t xml:space="preserve">9.47349262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42264938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6514368057251</t>
   </si>
   <si>
     <t xml:space="preserve">9.53280639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63449001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56670188903809</t>
+    <t xml:space="preserve">9.63448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56670093536377</t>
   </si>
   <si>
     <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76159381866455</t>
+    <t xml:space="preserve">9.76159477233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.78701496124268</t>
@@ -2081,46 +2081,46 @@
     <t xml:space="preserve">9.83785629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87174987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79548931121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91411781311035</t>
+    <t xml:space="preserve">9.871750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79548835754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82090950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91411876678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0242757797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1344337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083589553833</t>
+    <t xml:space="preserve">10.0242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0835914611816</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158023834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93953990936279</t>
+    <t xml:space="preserve">9.93953895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1768007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2276401519775</t>
+    <t xml:space="preserve">10.1768016815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
     <t xml:space="preserve">10.1598539352417</t>
@@ -2132,22 +2132,22 @@
     <t xml:space="preserve">10.2530632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1683263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1937484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82938289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94801235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.998854637146</t>
+    <t xml:space="preserve">10.168327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1937475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496969223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82938385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94801330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.92259311676025</t>
@@ -2162,94 +2162,94 @@
     <t xml:space="preserve">9.73617362976074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84632968902588</t>
+    <t xml:space="preserve">9.8463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.64296340942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54975318908691</t>
+    <t xml:space="preserve">9.54975414276123</t>
   </si>
   <si>
     <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16431903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01603221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00332069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70674467086792</t>
+    <t xml:space="preserve">8.1643180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01603126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00331974029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70674419403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39322137832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153680801392</t>
+    <t xml:space="preserve">7.39322185516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71109580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61364889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61376333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52479076385498</t>
+    <t xml:space="preserve">6.71109533309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61364936828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6137638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52479124069214</t>
   </si>
   <si>
     <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09687423706055</t>
+    <t xml:space="preserve">5.08416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484846115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
     <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80865716934204</t>
+    <t xml:space="preserve">5.59258031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80865669250488</t>
   </si>
   <si>
     <t xml:space="preserve">5.50784397125244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210927963257</t>
+    <t xml:space="preserve">5.26210975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16042566299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89774465560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76216602325439</t>
+    <t xml:space="preserve">5.1604266166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89774417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76216697692871</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481937408447</t>
@@ -2261,19 +2261,19 @@
     <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20279359817505</t>
+    <t xml:space="preserve">5.20279407501221</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466283798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93163871765137</t>
+    <t xml:space="preserve">5.16466236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10111093521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93163919448853</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129655838013</t>
@@ -2282,31 +2282,31 @@
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93152379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07557582855225</t>
+    <t xml:space="preserve">5.73663091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9315242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
     <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53326463699341</t>
+    <t xml:space="preserve">5.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49513339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87220907211304</t>
+    <t xml:space="preserve">5.8722095489502</t>
   </si>
   <si>
     <t xml:space="preserve">5.93576049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10099601745605</t>
+    <t xml:space="preserve">6.10099649429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.13065385818481</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">5.88068294525146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6773157119751</t>
+    <t xml:space="preserve">5.67731618881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289339065552</t>
+    <t xml:space="preserve">5.81289434432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.75357818603516</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">5.65189552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91881418228149</t>
+    <t xml:space="preserve">6.05015516281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91881370544434</t>
   </si>
   <si>
     <t xml:space="preserve">6.03320741653442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3552041053772</t>
+    <t xml:space="preserve">6.35520458221436</t>
   </si>
   <si>
     <t xml:space="preserve">6.29165267944336</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91022491455078</t>
+    <t xml:space="preserve">6.94835662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91022539138794</t>
   </si>
   <si>
     <t xml:space="preserve">7.04156684875488</t>
@@ -2366,25 +2366,25 @@
     <t xml:space="preserve">7.24916982650757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10088205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0034351348877</t>
+    <t xml:space="preserve">7.10088109970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00343561172485</t>
   </si>
   <si>
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5755181312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71533298492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69838571548462</t>
+    <t xml:space="preserve">6.57551860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71533250808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72804355621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69838523864746</t>
   </si>
   <si>
     <t xml:space="preserve">6.64330673217773</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">6.55009746551514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60941314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33402013778687</t>
+    <t xml:space="preserve">6.6094126701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33402061462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.3255467414856</t>
@@ -2405,28 +2405,28 @@
     <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28741598129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12641763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1518383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01626014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31707334518433</t>
+    <t xml:space="preserve">6.14760065078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28741550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12641716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15183782577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01626062393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31707286834717</t>
   </si>
   <si>
     <t xml:space="preserve">6.13912725448608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07981300354004</t>
+    <t xml:space="preserve">6.07981204986572</t>
   </si>
   <si>
     <t xml:space="preserve">6.04591798782349</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47383499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27046823501587</t>
+    <t xml:space="preserve">6.47383451461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807121276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27046871185303</t>
   </si>
   <si>
     <t xml:space="preserve">6.06286525726318</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">6.22386360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336347579956</t>
+    <t xml:space="preserve">6.14336442947388</t>
   </si>
   <si>
     <t xml:space="preserve">6.08404874801636</t>
@@ -2465,52 +2465,52 @@
     <t xml:space="preserve">5.95270824432373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07133817672729</t>
+    <t xml:space="preserve">6.07133865356445</t>
   </si>
   <si>
     <t xml:space="preserve">6.18149566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02049732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32978391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32131004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420623779297</t>
+    <t xml:space="preserve">6.02049684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931287765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38486194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3213095664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420576095581</t>
   </si>
   <si>
     <t xml:space="preserve">6.25775814056396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2747049331665</t>
+    <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30859994888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37215185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.986487865448</t>
+    <t xml:space="preserve">6.3085994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37215089797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483285903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98648834228516</t>
   </si>
   <si>
     <t xml:space="preserve">7.16019678115845</t>
@@ -2519,25 +2519,25 @@
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377729415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73227977752686</t>
+    <t xml:space="preserve">6.97377681732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73228025436401</t>
   </si>
   <si>
     <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0161452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90175247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85938453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79583168029785</t>
+    <t xml:space="preserve">7.01614475250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90175294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85938405990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79583215713501</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
@@ -2549,25 +2549,25 @@
     <t xml:space="preserve">6.05439138412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04168081283569</t>
+    <t xml:space="preserve">6.04168128967285</t>
   </si>
   <si>
     <t xml:space="preserve">6.16031122207642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09675931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21538972854614</t>
+    <t xml:space="preserve">6.09676027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2153902053833</t>
   </si>
   <si>
     <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09252309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00778722763062</t>
+    <t xml:space="preserve">6.09252214431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0077862739563</t>
   </si>
   <si>
     <t xml:space="preserve">5.90610313415527</t>
@@ -2576,49 +2576,49 @@
     <t xml:space="preserve">5.57563257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4908971786499</t>
+    <t xml:space="preserve">5.49089670181274</t>
   </si>
   <si>
     <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46547555923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25787258148193</t>
+    <t xml:space="preserve">5.46547603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25787210464478</t>
   </si>
   <si>
     <t xml:space="preserve">5.28752994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06297969818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05874252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01213788986206</t>
+    <t xml:space="preserve">5.06297922134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0587420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0121374130249</t>
   </si>
   <si>
     <t xml:space="preserve">5.29176664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40616035461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43158102035522</t>
+    <t xml:space="preserve">5.40616083145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43158149719238</t>
   </si>
   <si>
     <t xml:space="preserve">5.76205205917358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81713008880615</t>
+    <t xml:space="preserve">5.81713056564331</t>
   </si>
   <si>
     <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93988227844238</t>
+    <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
     <t xml:space="preserve">6.74075365066528</t>
@@ -2630,58 +2630,58 @@
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09653091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303623199463</t>
+    <t xml:space="preserve">8.09652996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303527832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.49914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45253610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200880050659</t>
+    <t xml:space="preserve">7.45253562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200784683228</t>
   </si>
   <si>
     <t xml:space="preserve">7.77453327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77029657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8719801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8423228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67285013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63471794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011047363281</t>
+    <t xml:space="preserve">7.77029705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87197923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84232139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67284917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571771621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63471937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011095046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537460327148</t>
@@ -2690,61 +2690,61 @@
     <t xml:space="preserve">7.8550329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68556118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52456188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4779577255249</t>
+    <t xml:space="preserve">7.68556070327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5245623588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47795677185059</t>
   </si>
   <si>
     <t xml:space="preserve">7.58811378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56693077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41016864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730154037476</t>
+    <t xml:space="preserve">7.56693029403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4101676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730201721191</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32543325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985414505005</t>
+    <t xml:space="preserve">7.32543230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31695795059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985366821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18138122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15595960617065</t>
+    <t xml:space="preserve">7.18138074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64319276809692</t>
+    <t xml:space="preserve">7.64319324493408</t>
   </si>
   <si>
     <t xml:space="preserve">7.74911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53727340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926914215088</t>
+    <t xml:space="preserve">7.53727197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926866531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.21516036987305</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837154388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14313411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79147911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65166616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03721618652344</t>
+    <t xml:space="preserve">8.20668888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30837059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14313507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79147958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65166568756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03721523284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.92282152175903</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033962249756</t>
+    <t xml:space="preserve">8.88033771514893</t>
   </si>
   <si>
     <t xml:space="preserve">8.63460350036621</t>
@@ -2789,25 +2789,25 @@
     <t xml:space="preserve">8.00755786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39734363555908</t>
+    <t xml:space="preserve">8.39734268188477</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965435028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78712940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68544578552246</t>
+    <t xml:space="preserve">8.78712844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16844081878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20233535766602</t>
+    <t xml:space="preserve">9.16844177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20233631134033</t>
   </si>
   <si>
     <t xml:space="preserve">9.5582275390625</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">9.60059547424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96507453918457</t>
+    <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133701324463</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">9.21928405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0498104095459</t>
+    <t xml:space="preserve">9.04981231689453</t>
   </si>
   <si>
     <t xml:space="preserve">9.71075344085693</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">9.39722919464111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44807052612305</t>
+    <t xml:space="preserve">9.44806957244873</t>
   </si>
   <si>
     <t xml:space="preserve">9.48196506500244</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">9.69380569458008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.041223526001</t>
+    <t xml:space="preserve">10.0412244796753</t>
   </si>
   <si>
     <t xml:space="preserve">9.74464702606201</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43112277984619</t>
+    <t xml:space="preserve">9.52433395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43112373352051</t>
   </si>
   <si>
     <t xml:space="preserve">9.02747917175293</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">9.0880651473999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2092399597168</t>
+    <t xml:space="preserve">9.20924091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386215209961</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43427753448486</t>
+    <t xml:space="preserve">9.43427848815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.63335037231445</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40831184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47755432128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3217601776123</t>
+    <t xml:space="preserve">9.40831279754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47755336761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
     <t xml:space="preserve">9.21789455413818</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">9.26117134094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46889972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2698278427124</t>
+    <t xml:space="preserve">9.51217555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46889877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26982688903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.31310367584229</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3477258682251</t>
+    <t xml:space="preserve">9.34772491455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.1313419342041</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.00151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75916385650635</t>
+    <t xml:space="preserve">8.75916481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840728759766</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">9.20058536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36503505706787</t>
+    <t xml:space="preserve">9.36503601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.41696834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16596412658691</t>
+    <t xml:space="preserve">9.1659631729126</t>
   </si>
   <si>
     <t xml:space="preserve">8.99285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25251579284668</t>
+    <t xml:space="preserve">9.252516746521</t>
   </si>
   <si>
     <t xml:space="preserve">9.17461967468262</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71588802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77647495269775</t>
+    <t xml:space="preserve">8.83706283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71588706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77647590637207</t>
   </si>
   <si>
     <t xml:space="preserve">8.98420238494873</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395664215088</t>
+    <t xml:space="preserve">8.66395568847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84571838378906</t>
+    <t xml:space="preserve">8.84571743011475</t>
   </si>
   <si>
     <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78512954711914</t>
+    <t xml:space="preserve">8.78513050079346</t>
   </si>
   <si>
     <t xml:space="preserve">8.72454357147217</t>
@@ -3035,22 +3035,22 @@
     <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26581287384033</t>
+    <t xml:space="preserve">8.26581192016602</t>
   </si>
   <si>
     <t xml:space="preserve">8.19656944274902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74185562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43891906738281</t>
+    <t xml:space="preserve">8.23119163513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28744983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74185466766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4389181137085</t>
   </si>
   <si>
     <t xml:space="preserve">8.39131355285645</t>
@@ -3059,22 +3059,22 @@
     <t xml:space="preserve">8.42160797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3610200881958</t>
+    <t xml:space="preserve">8.36102104187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366222381592</t>
+    <t xml:space="preserve">8.63366317749023</t>
   </si>
   <si>
     <t xml:space="preserve">8.67261219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62933444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202335357666</t>
+    <t xml:space="preserve">8.62933540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202430725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.59904098510742</t>
@@ -3092,43 +3092,43 @@
     <t xml:space="preserve">8.81975078582764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80244064331055</t>
+    <t xml:space="preserve">8.80244159698486</t>
   </si>
   <si>
     <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85901308059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93691110610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87632369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96287679672241</t>
+    <t xml:space="preserve">7.85901403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93691158294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87632417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749803543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.91959953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91527318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95854806900024</t>
+    <t xml:space="preserve">7.91527271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9585485458374</t>
   </si>
   <si>
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128612518311</t>
+    <t xml:space="preserve">7.82439184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128660202026</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011226654053</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">7.49981832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39162683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35267782211304</t>
+    <t xml:space="preserve">7.39162635803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3526782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.09734630584717</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51280164718628</t>
+    <t xml:space="preserve">7.33969497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51280117034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.42191982269287</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927816390991</t>
+    <t xml:space="preserve">7.14927864074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.2012095451355</t>
@@ -3191,19 +3191,19 @@
     <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19255542755127</t>
+    <t xml:space="preserve">7.19255495071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.25746965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26179790496826</t>
+    <t xml:space="preserve">7.26179838180542</t>
   </si>
   <si>
     <t xml:space="preserve">7.2444863319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40461015701294</t>
+    <t xml:space="preserve">7.40460968017578</t>
   </si>
   <si>
     <t xml:space="preserve">7.45654106140137</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">7.31805658340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41759252548218</t>
+    <t xml:space="preserve">7.41759204864502</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700654983521</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583078384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14062356948853</t>
+    <t xml:space="preserve">7.23583126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14062309265137</t>
   </si>
   <si>
     <t xml:space="preserve">7.07138061523438</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">7.01944828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88961935043335</t>
+    <t xml:space="preserve">6.88961887359619</t>
   </si>
   <si>
     <t xml:space="preserve">6.91991329193115</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">6.66458129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42223310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46983766555786</t>
+    <t xml:space="preserve">6.42223358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4698371887207</t>
   </si>
   <si>
     <t xml:space="preserve">6.42656135559082</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">6.44387149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55639028549194</t>
+    <t xml:space="preserve">6.5563907623291</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56504583358765</t>
+    <t xml:space="preserve">6.56504535675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.49580335617065</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">6.10198736190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88560438156128</t>
+    <t xml:space="preserve">5.88560485839844</t>
   </si>
   <si>
     <t xml:space="preserve">6.2015233039856</t>
@@ -3329,34 +3329,34 @@
     <t xml:space="preserve">5.70817089080811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60863494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4614953994751</t>
+    <t xml:space="preserve">5.60863542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46149492263794</t>
   </si>
   <si>
     <t xml:space="preserve">5.29704427719116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53073740005493</t>
+    <t xml:space="preserve">5.53073787689209</t>
   </si>
   <si>
     <t xml:space="preserve">5.55670356750488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53506469726562</t>
+    <t xml:space="preserve">5.55237531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53506517410278</t>
   </si>
   <si>
     <t xml:space="preserve">5.89425992965698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83367252349854</t>
+    <t xml:space="preserve">5.83367300033569</t>
   </si>
   <si>
     <t xml:space="preserve">5.87262153625488</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8509840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7341365814209</t>
+    <t xml:space="preserve">5.85098361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73413705825806</t>
   </si>
   <si>
     <t xml:space="preserve">6.05438280105591</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">6.29673147201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37895679473877</t>
+    <t xml:space="preserve">6.37895631790161</t>
   </si>
   <si>
     <t xml:space="preserve">5.99812364578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1539192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1106424331665</t>
+    <t xml:space="preserve">6.15391874313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11064291000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.145263671875</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">6.19286775588989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12362480163574</t>
+    <t xml:space="preserve">6.1236252784729</t>
   </si>
   <si>
     <t xml:space="preserve">6.17555713653564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26211023330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30105924606323</t>
+    <t xml:space="preserve">6.26210975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30105876922607</t>
   </si>
   <si>
     <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24479961395264</t>
+    <t xml:space="preserve">6.24480009078979</t>
   </si>
   <si>
     <t xml:space="preserve">6.11929798126221</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34433555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10631418228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27900981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19044780731201</t>
+    <t xml:space="preserve">6.34433603286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10631465911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27901029586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19044828414917</t>
   </si>
   <si>
     <t xml:space="preserve">6.12845516204834</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42956447601318</t>
+    <t xml:space="preserve">6.38971185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42956495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.3764271736145</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">6.27458190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34543085098267</t>
+    <t xml:space="preserve">6.34543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">6.4162802696228</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">5.40225076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65022373199463</t>
+    <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.59708642959595</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">5.62808275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63251113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80077838897705</t>
+    <t xml:space="preserve">5.63251066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80077791213989</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60594177246094</t>
+    <t xml:space="preserve">5.79192113876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6059422492981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066444396973</t>
+    <t xml:space="preserve">5.53952169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066492080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.66793537139893</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">5.88933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77863740921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92476415634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85834264755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40667915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57494640350342</t>
+    <t xml:space="preserve">5.77863693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92476367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85834217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40667867660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57494592666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948682785034</t>
+    <t xml:space="preserve">5.84948635101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.94690418243408</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">5.90262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16387939453125</t>
+    <t xml:space="preserve">6.07088994979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16387987136841</t>
   </si>
   <si>
     <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07531881332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07974624633789</t>
+    <t xml:space="preserve">6.07531833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07974576950073</t>
   </si>
   <si>
     <t xml:space="preserve">5.95576000213623</t>
@@ -3608,16 +3608,16 @@
     <t xml:space="preserve">5.97790050506592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14616775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18159198760986</t>
+    <t xml:space="preserve">6.14616727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18159246444702</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27015352249146</t>
+    <t xml:space="preserve">6.27015399932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.04432153701782</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99561309814453</t>
+    <t xml:space="preserve">6.02660894393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99561262130737</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95133256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01775360107422</t>
+    <t xml:space="preserve">5.95133209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01775312423706</t>
   </si>
   <si>
     <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87605571746826</t>
+    <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
     <t xml:space="preserve">5.89819526672363</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">5.63693857192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48195648193359</t>
+    <t xml:space="preserve">5.48195600509644</t>
   </si>
   <si>
     <t xml:space="preserve">5.27383661270142</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">5.39782285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5572338104248</t>
+    <t xml:space="preserve">5.55723333358765</t>
   </si>
   <si>
     <t xml:space="preserve">5.59265804290771</t>
@@ -3686,16 +3686,16 @@
     <t xml:space="preserve">5.68564796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8671989440918</t>
+    <t xml:space="preserve">5.86719846725464</t>
   </si>
   <si>
     <t xml:space="preserve">5.65465116500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62365484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121910095215</t>
+    <t xml:space="preserve">5.62365436553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68121957778931</t>
   </si>
   <si>
     <t xml:space="preserve">5.7299280166626</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00889730453491</t>
+    <t xml:space="preserve">6.00889682769775</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">6.25244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17273569107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08417463302612</t>
+    <t xml:space="preserve">6.17273616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08417415618896</t>
   </si>
   <si>
     <t xml:space="preserve">6.06203413009644</t>
@@ -3737,16 +3737,16 @@
     <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47384452819824</t>
+    <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
     <t xml:space="preserve">6.42513656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428714752197</t>
+    <t xml:space="preserve">6.23915719985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428762435913</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">6.79266691207886</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539598464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54912185668945</t>
+    <t xml:space="preserve">6.65539646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54912233352661</t>
   </si>
   <si>
     <t xml:space="preserve">6.52255344390869</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">6.53583812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49598550796509</t>
+    <t xml:space="preserve">6.49598598480225</t>
   </si>
   <si>
     <t xml:space="preserve">6.64211225509644</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">6.46941709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33214664459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4074239730835</t>
+    <t xml:space="preserve">6.33214712142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40742444992065</t>
   </si>
   <si>
     <t xml:space="preserve">6.55355072021484</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">6.66425228118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94764852523804</t>
+    <t xml:space="preserve">6.9476490020752</t>
   </si>
   <si>
     <t xml:space="preserve">6.92993688583374</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093368530273</t>
+    <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
     <t xml:space="preserve">6.98307371139526</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">7.58529186248779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24875831604004</t>
+    <t xml:space="preserve">7.2487587928772</t>
   </si>
   <si>
     <t xml:space="preserve">7.2089056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19562149047852</t>
+    <t xml:space="preserve">7.19562101364136</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
@@ -3872,25 +3872,25 @@
     <t xml:space="preserve">7.3018946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5232982635498</t>
+    <t xml:space="preserve">7.52329874038696</t>
   </si>
   <si>
     <t xml:space="preserve">7.49230241775513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42145299911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34617567062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48787450790405</t>
+    <t xml:space="preserve">7.42145252227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34617519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
     <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10263252258301</t>
+    <t xml:space="preserve">7.10263204574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.3151798248291</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">7.2753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29303884506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41259717941284</t>
+    <t xml:space="preserve">7.2930383682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41259670257568</t>
   </si>
   <si>
     <t xml:space="preserve">7.44802093505859</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">6.74838542938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00078582763672</t>
+    <t xml:space="preserve">7.00078630447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451217651367</t>
+    <t xml:space="preserve">6.89451169967651</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">6.81480693817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81037902832031</t>
+    <t xml:space="preserve">6.81037855148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26204252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761365890503</t>
+    <t xml:space="preserve">7.26204204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25761413574219</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,16 +3983,16 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1203441619873</t>
+    <t xml:space="preserve">7.10705947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12034368515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17348098754883</t>
+    <t xml:space="preserve">7.17348146438599</t>
   </si>
   <si>
     <t xml:space="preserve">7.31960821151733</t>
@@ -4019,16 +4019,16 @@
     <t xml:space="preserve">7.47458934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68270969390869</t>
+    <t xml:space="preserve">7.68271017074585</t>
   </si>
   <si>
     <t xml:space="preserve">7.60300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71370649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67828178405762</t>
+    <t xml:space="preserve">7.71370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828130722046</t>
   </si>
   <si>
     <t xml:space="preserve">7.85610342025757</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">7.81506776809692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88802003860474</t>
+    <t xml:space="preserve">7.79683017730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88802051544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.07040309906006</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">7.90169954299927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80138921737671</t>
+    <t xml:space="preserve">7.74211454391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80138969421387</t>
   </si>
   <si>
     <t xml:space="preserve">7.95185470581055</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">7.94273519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09775924682617</t>
+    <t xml:space="preserve">8.09776020050049</t>
   </si>
   <si>
     <t xml:space="preserve">8.22086811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30293941497803</t>
+    <t xml:space="preserve">8.30293846130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.45340538024902</t>
@@ -4085,28 +4085,28 @@
     <t xml:space="preserve">8.13423633575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03392696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09319972991943</t>
+    <t xml:space="preserve">8.03392601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09320068359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.03848552703857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70563840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71931743621826</t>
+    <t xml:space="preserve">7.70563793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7193169593811</t>
   </si>
   <si>
     <t xml:space="preserve">7.78771066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75579404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73299551010132</t>
+    <t xml:space="preserve">7.75579357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73299598693848</t>
   </si>
   <si>
     <t xml:space="preserve">7.71475791931152</t>
@@ -4118,16 +4118,16 @@
     <t xml:space="preserve">7.60988855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56885242462158</t>
+    <t xml:space="preserve">7.45030355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56885290145874</t>
   </si>
   <si>
     <t xml:space="preserve">7.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55517339706421</t>
+    <t xml:space="preserve">7.55517292022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.59164953231812</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">7.50501823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45942354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54149532318115</t>
+    <t xml:space="preserve">7.45942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54149484634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.60076904296875</t>
@@ -4157,34 +4157,34 @@
     <t xml:space="preserve">7.55061340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53237581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69651889801025</t>
+    <t xml:space="preserve">7.53237628936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69651937484741</t>
   </si>
   <si>
     <t xml:space="preserve">7.65548372268677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64636468887329</t>
+    <t xml:space="preserve">7.64636516571045</t>
   </si>
   <si>
     <t xml:space="preserve">7.48678016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4183874130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3317551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.381911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40470838546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52781629562378</t>
+    <t xml:space="preserve">7.41838693618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33175563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38191080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40470790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52781581878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.39102935791016</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">7.29527902603149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24056482315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26792144775391</t>
+    <t xml:space="preserve">7.24056434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26792192459106</t>
   </si>
   <si>
     <t xml:space="preserve">7.25880289077759</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">7.06274175643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08554029464722</t>
+    <t xml:space="preserve">7.08553981781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.01258707046509</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">6.6797399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54751253128052</t>
+    <t xml:space="preserve">6.54751300811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.50191783905029</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">6.67062091827393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60222721099854</t>
+    <t xml:space="preserve">6.60222768783569</t>
   </si>
   <si>
     <t xml:space="preserve">6.59310865402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52927494049072</t>
+    <t xml:space="preserve">6.52927446365356</t>
   </si>
   <si>
     <t xml:space="preserve">6.43808364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69341897964478</t>
+    <t xml:space="preserve">6.69341850280762</t>
   </si>
   <si>
     <t xml:space="preserve">6.75725221633911</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">6.50647735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37880945205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28761911392212</t>
+    <t xml:space="preserve">6.37880992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28761863708496</t>
   </si>
   <si>
     <t xml:space="preserve">6.45176219940186</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">6.47911977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58398962020874</t>
+    <t xml:space="preserve">6.58398914337158</t>
   </si>
   <si>
     <t xml:space="preserve">6.97155094146729</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">7.03994417190552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03538465499878</t>
+    <t xml:space="preserve">7.03538513183594</t>
   </si>
   <si>
     <t xml:space="preserve">7.06730175018311</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">7.21320724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18129014968872</t>
+    <t xml:space="preserve">7.18129062652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.28615999221802</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">7.29983901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23600482940674</t>
+    <t xml:space="preserve">7.2360053062439</t>
   </si>
   <si>
     <t xml:space="preserve">7.20408821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96097278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86066293716431</t>
+    <t xml:space="preserve">7.96097230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86066341400146</t>
   </si>
   <si>
     <t xml:space="preserve">7.97921180725098</t>
@@ -4394,34 +4394,34 @@
     <t xml:space="preserve">7.97009229660034</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05672454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98377180099487</t>
+    <t xml:space="preserve">8.05672359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98377084732056</t>
   </si>
   <si>
     <t xml:space="preserve">8.28926086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31661796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20262908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29838085174561</t>
+    <t xml:space="preserve">8.31661891937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20263004302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29837989807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.25278472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2664623260498</t>
+    <t xml:space="preserve">8.26646327972412</t>
   </si>
   <si>
     <t xml:space="preserve">8.32117748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08408164978027</t>
+    <t xml:space="preserve">8.08408069610596</t>
   </si>
   <si>
     <t xml:space="preserve">8.04304504394531</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">8.04760456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20718860626221</t>
+    <t xml:space="preserve">8.20718955993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.16615295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06128406524658</t>
+    <t xml:space="preserve">8.06128311157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.16159343719482</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">8.34397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38957118988037</t>
+    <t xml:space="preserve">8.38957023620605</t>
   </si>
   <si>
     <t xml:space="preserve">8.37589263916016</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">8.2755823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44884490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32573795318604</t>
+    <t xml:space="preserve">8.44884586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32573699951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.57195281982422</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">8.64034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.535475730896</t>
+    <t xml:space="preserve">8.53547668457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.62666797637939</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">8.43516635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54459571838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68138313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79081249237061</t>
+    <t xml:space="preserve">8.54459476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68138217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79081153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.84552574157715</t>
@@ -4571,37 +4571,37 @@
     <t xml:space="preserve">8.23910522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93817520141602</t>
+    <t xml:space="preserve">8.01112747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">7.93361568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85154342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594921112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.065842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17071342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14335632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12055683135986</t>
+    <t xml:space="preserve">7.85154390335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594873428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68284130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06584358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14335536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12055778503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.13879585266113</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">8.50811958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67226314544678</t>
+    <t xml:space="preserve">8.67226409912109</t>
   </si>
   <si>
     <t xml:space="preserve">8.75433540344238</t>
@@ -5397,6 +5397,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.960000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -68239,7 +68242,7 @@
     </row>
     <row r="2405">
       <c r="A2405" s="1" t="n">
-        <v>45944.6520138889</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2405" t="n">
         <v>250051</v>
@@ -68260,6 +68263,32 @@
         <v>1794</v>
       </c>
       <c r="H2405" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>45945.6496064815</v>
+      </c>
+      <c r="B2406" t="n">
+        <v>204111</v>
+      </c>
+      <c r="C2406" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>13.8900003433228</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>13.9200000762939</v>
+      </c>
+      <c r="G2406" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H2406" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1797">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032619476318</t>
+    <t xml:space="preserve">2.96032571792603</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13860034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1238796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588955879211</t>
+    <t xml:space="preserve">3.13859987258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12388014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588908195496</t>
   </si>
   <si>
     <t xml:space="preserve">3.06663632392883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0650007724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647686958313</t>
+    <t xml:space="preserve">3.06500053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028080940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476893424988</t>
   </si>
   <si>
     <t xml:space="preserve">3.17131066322327</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">3.16149735450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205790519714</t>
+    <t xml:space="preserve">3.13205766677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.15822649002075</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">3.15168452262878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30051803588867</t>
+    <t xml:space="preserve">3.30051851272583</t>
   </si>
   <si>
     <t xml:space="preserve">3.34140682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463230133057</t>
+    <t xml:space="preserve">3.43463277816772</t>
   </si>
   <si>
     <t xml:space="preserve">3.437903881073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39374423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977150917053</t>
+    <t xml:space="preserve">3.39374375343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393068313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977174758911</t>
   </si>
   <si>
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841294288635</t>
+    <t xml:space="preserve">3.14841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">3.0306544303894</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">3.08789825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17294645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752463340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18112373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257283210754</t>
+    <t xml:space="preserve">3.1729462146759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18112421035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257307052612</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03392553329468</t>
+    <t xml:space="preserve">3.0339252948761</t>
   </si>
   <si>
     <t xml:space="preserve">2.99303722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04373836517334</t>
+    <t xml:space="preserve">3.04373860359192</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878680229187</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">3.23346161842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22528386116028</t>
+    <t xml:space="preserve">3.22528338432312</t>
   </si>
   <si>
     <t xml:space="preserve">3.11406707763672</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">3.14023542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1222448348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09116911888123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08299160003662</t>
+    <t xml:space="preserve">3.12224459648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0829918384552</t>
   </si>
   <si>
     <t xml:space="preserve">3.11897349357605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08135604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425329208374</t>
+    <t xml:space="preserve">3.08135581016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425353050232</t>
   </si>
   <si>
     <t xml:space="preserve">3.07481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14677762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13696432113647</t>
+    <t xml:space="preserve">3.14677786827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13696455955505</t>
   </si>
   <si>
     <t xml:space="preserve">3.21383500099182</t>
@@ -194,55 +194,55 @@
     <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10916018486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36921119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645478248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50986766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51641035079956</t>
+    <t xml:space="preserve">3.10916066169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36921095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5098671913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51640963554382</t>
   </si>
   <si>
     <t xml:space="preserve">3.54094266891479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50168943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552156448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3561270236969</t>
+    <t xml:space="preserve">3.50168991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35612678527832</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724740982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36103343963623</t>
+    <t xml:space="preserve">3.29724764823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36103320121765</t>
   </si>
   <si>
     <t xml:space="preserve">3.37575316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37738871574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35285544395447</t>
+    <t xml:space="preserve">3.3773889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35285592079163</t>
   </si>
   <si>
     <t xml:space="preserve">3.38556623458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43136143684387</t>
+    <t xml:space="preserve">3.43136167526245</t>
   </si>
   <si>
     <t xml:space="preserve">3.51150298118591</t>
@@ -251,70 +251,70 @@
     <t xml:space="preserve">3.47061419487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46734309196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337060928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.488605260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41827702522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50823187828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57855939865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472893714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547617912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59818625450134</t>
+    <t xml:space="preserve">3.4673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281029701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3970148563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337013244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4591658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50823140144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57856011390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547570228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5981867313385</t>
   </si>
   <si>
     <t xml:space="preserve">3.63907504081726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66360855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725255966187</t>
+    <t xml:space="preserve">3.66360807418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725279808044</t>
   </si>
   <si>
     <t xml:space="preserve">3.67996335029602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67178559303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636401176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56711101531982</t>
+    <t xml:space="preserve">3.67178535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5671112537384</t>
   </si>
   <si>
     <t xml:space="preserve">3.46897912025452</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.40355753898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38065981864929</t>
+    <t xml:space="preserve">3.38065958023071</t>
   </si>
   <si>
     <t xml:space="preserve">3.33813571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28743386268616</t>
+    <t xml:space="preserve">3.28743410110474</t>
   </si>
   <si>
     <t xml:space="preserve">3.32668685913086</t>
@@ -344,166 +344,166 @@
     <t xml:space="preserve">3.21874165534973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25962996482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495562553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07644963264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462738990784</t>
+    <t xml:space="preserve">3.25962972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0764491558075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462691307068</t>
   </si>
   <si>
     <t xml:space="preserve">3.12551593780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27107834815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850981712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486437797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846395492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30869603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818086624146</t>
+    <t xml:space="preserve">3.27107906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850957870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3675754070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30869626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818062782288</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206305503845</t>
+    <t xml:space="preserve">3.48206281661987</t>
   </si>
   <si>
     <t xml:space="preserve">3.54421401023865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61454200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528853416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183169364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309338569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851472854614</t>
+    <t xml:space="preserve">3.61454224586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253283500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851496696472</t>
   </si>
   <si>
     <t xml:space="preserve">3.64071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61617755889893</t>
+    <t xml:space="preserve">3.61617732048035</t>
   </si>
   <si>
     <t xml:space="preserve">3.62435507774353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75192713737488</t>
+    <t xml:space="preserve">3.75192737579346</t>
   </si>
   <si>
     <t xml:space="preserve">3.76174020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72412323951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809619903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77646064758301</t>
+    <t xml:space="preserve">3.72412276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809548377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646040916443</t>
   </si>
   <si>
     <t xml:space="preserve">3.79118037223816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73720788955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79445123672485</t>
+    <t xml:space="preserve">3.73720765113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730309486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445099830627</t>
   </si>
   <si>
     <t xml:space="preserve">3.99071598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91548156738281</t>
+    <t xml:space="preserve">3.91548037528992</t>
   </si>
   <si>
     <t xml:space="preserve">3.86314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89258337020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440632820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150813102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454739570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04305267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898474693298</t>
+    <t xml:space="preserve">3.8925838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529439926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641573905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655752182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9645471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618294715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767695426941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898427009583</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138457775116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94165015220642</t>
+    <t xml:space="preserve">3.94164967536926</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99398732185364</t>
+    <t xml:space="preserve">3.9939866065979</t>
   </si>
   <si>
     <t xml:space="preserve">3.97272443771362</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">4.00707197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01524972915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08394145965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16244792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.01524877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884763717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08394193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16244840621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.44048929214478</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">4.59586572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76350831985474</t>
+    <t xml:space="preserve">4.76350879669189</t>
   </si>
   <si>
     <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99248456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439710617065</t>
+    <t xml:space="preserve">4.99248361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8043966293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83301877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90661811828613</t>
+    <t xml:space="preserve">4.83301830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90661859512329</t>
   </si>
   <si>
     <t xml:space="preserve">4.96386194229126</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">5.03337240219116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150453567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
+    <t xml:space="preserve">5.19283819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150548934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830396652222</t>
   </si>
   <si>
     <t xml:space="preserve">5.28688144683838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36456918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865711212158</t>
+    <t xml:space="preserve">5.36456871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3686580657959</t>
   </si>
   <si>
     <t xml:space="preserve">5.46270132064819</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">5.55265617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30323696136475</t>
+    <t xml:space="preserve">5.30323648452759</t>
   </si>
   <si>
     <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54856729507446</t>
+    <t xml:space="preserve">5.5485668182373</t>
   </si>
   <si>
     <t xml:space="preserve">5.59354496002197</t>
@@ -629,40 +629,40 @@
     <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709915161133</t>
+    <t xml:space="preserve">5.70803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709867477417</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207586288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82252025604248</t>
+    <t xml:space="preserve">5.82251977920532</t>
   </si>
   <si>
     <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78572082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4790563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4872350692749</t>
+    <t xml:space="preserve">5.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47905683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48723411560059</t>
   </si>
   <si>
     <t xml:space="preserve">5.46679019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60581111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083345413208</t>
+    <t xml:space="preserve">5.60581064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5608344078064</t>
   </si>
   <si>
     <t xml:space="preserve">5.64308166503906</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">5.46144533157349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290458679199</t>
+    <t xml:space="preserve">5.57290410995483</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546560287476</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">5.705002784729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73802757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756475448608</t>
+    <t xml:space="preserve">5.73802709579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756523132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.80407667160034</t>
@@ -701,70 +701,70 @@
     <t xml:space="preserve">6.10129833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84122943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80820417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73389959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866746902466</t>
+    <t xml:space="preserve">5.84122896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80820465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73389911651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866842269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.65133762359619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81233310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77930879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77105188369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68849086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56877565383911</t>
+    <t xml:space="preserve">5.81233263015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77930784225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77105140686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84535789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.63069725036621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57703256607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52336740493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621416091919</t>
+    <t xml:space="preserve">5.5770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5233678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813528060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621463775635</t>
   </si>
   <si>
     <t xml:space="preserve">5.53162336349487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55639219284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934713363647</t>
+    <t xml:space="preserve">5.55639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934761047363</t>
   </si>
   <si>
     <t xml:space="preserve">5.27568292617798</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009664535522</t>
+    <t xml:space="preserve">5.16009616851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.14771223068237</t>
@@ -773,19 +773,19 @@
     <t xml:space="preserve">5.30045175552368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12294340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19312143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230302810669</t>
+    <t xml:space="preserve">5.12294387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1931209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248058319092</t>
+    <t xml:space="preserve">5.17248010635376</t>
   </si>
   <si>
     <t xml:space="preserve">5.34998798370361</t>
@@ -794,67 +794,67 @@
     <t xml:space="preserve">5.39952516555786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74628353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041151046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325874328613</t>
+    <t xml:space="preserve">5.74628305435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
     <t xml:space="preserve">5.72977161407471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77517986297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7669243812561</t>
+    <t xml:space="preserve">5.77517938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
     <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94443130493164</t>
+    <t xml:space="preserve">5.86599779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
     <t xml:space="preserve">5.89489412307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04763317108154</t>
+    <t xml:space="preserve">6.04763269424438</t>
   </si>
   <si>
     <t xml:space="preserve">5.93204736709595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86186981201172</t>
+    <t xml:space="preserve">5.8618688583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.95268726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97332763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827306747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17560386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17973184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19211578369141</t>
+    <t xml:space="preserve">5.97332811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17560338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17973136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19211626052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275615692139</t>
@@ -875,109 +875,109 @@
     <t xml:space="preserve">6.15083456039429</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9815845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05176115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09716939926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06001663208008</t>
+    <t xml:space="preserve">5.98158407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05176162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09717035293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06001758575439</t>
   </si>
   <si>
     <t xml:space="preserve">5.9857120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08891439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87425374984741</t>
+    <t xml:space="preserve">6.0889139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87425422668457</t>
   </si>
   <si>
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96094369888306</t>
+    <t xml:space="preserve">5.96094417572021</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8526086807251</t>
+    <t xml:space="preserve">6.22926902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200664520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85260772705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.81958389282227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89801645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371187210083</t>
+    <t xml:space="preserve">6.89801597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371234893799</t>
   </si>
   <si>
     <t xml:space="preserve">6.7535343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77004623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492324829102</t>
+    <t xml:space="preserve">6.77004718780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492372512817</t>
   </si>
   <si>
     <t xml:space="preserve">6.69574022293091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58015537261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43980073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52649021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631265640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57189846038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65446043014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71638154983521</t>
+    <t xml:space="preserve">6.58015441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43979978561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52648973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57189893722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65446090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71638202667236</t>
   </si>
   <si>
     <t xml:space="preserve">6.6131796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061866760254</t>
+    <t xml:space="preserve">6.53061771392822</t>
   </si>
   <si>
     <t xml:space="preserve">6.66684484481812</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">6.44805669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65858793258667</t>
+    <t xml:space="preserve">6.65858840942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538654327393</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50584936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5512580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905170440674</t>
+    <t xml:space="preserve">6.50585031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125856399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905122756958</t>
   </si>
   <si>
     <t xml:space="preserve">6.7287654876709</t>
@@ -1022,85 +1022,85 @@
     <t xml:space="preserve">6.70812511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68748569488525</t>
+    <t xml:space="preserve">6.6874852180481</t>
   </si>
   <si>
     <t xml:space="preserve">6.7122540473938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466711044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594785690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4718189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356344223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619287490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665712356567</t>
+    <t xml:space="preserve">6.77417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47181987762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932680130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7607855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334707260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619382858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665760040283</t>
   </si>
   <si>
     <t xml:space="preserve">7.95893287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92590951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57915067672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28192758560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605699539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2241358757019</t>
+    <t xml:space="preserve">7.92590856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28192806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40989923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769237518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431200027466</t>
+    <t xml:space="preserve">7.46769285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431343078613</t>
   </si>
   <si>
     <t xml:space="preserve">7.1787257194519</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">7.24890375137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3810019493103</t>
+    <t xml:space="preserve">7.38100147247314</t>
   </si>
   <si>
     <t xml:space="preserve">7.33972120285034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1993670463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0177321434021</t>
+    <t xml:space="preserve">7.19936656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011655807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01773118972778</t>
   </si>
   <si>
     <t xml:space="preserve">7.05488395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96406602859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79481410980225</t>
+    <t xml:space="preserve">6.96406650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7948145866394</t>
   </si>
   <si>
     <t xml:space="preserve">6.74940633773804</t>
@@ -1139,43 +1139,43 @@
     <t xml:space="preserve">6.68335771560669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79068660736084</t>
+    <t xml:space="preserve">6.79068756103516</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965183258057</t>
+    <t xml:space="preserve">7.19111061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965230941772</t>
   </si>
   <si>
     <t xml:space="preserve">6.84022378921509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05075550079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2365198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053865432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669593811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128768920898</t>
+    <t xml:space="preserve">7.05075645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23652029037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128816604614</t>
   </si>
   <si>
     <t xml:space="preserve">7.25715970993042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36036157608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27779960632324</t>
+    <t xml:space="preserve">7.36036109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2778000831604</t>
   </si>
   <si>
     <t xml:space="preserve">8.2313871383667</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40476512908936</t>
+    <t xml:space="preserve">8.40476608276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.62768077850342</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">8.41302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14056873321533</t>
+    <t xml:space="preserve">8.14056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.24789905548096</t>
@@ -1205,34 +1205,34 @@
     <t xml:space="preserve">8.09103202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19836139678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18184852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.206618309021</t>
+    <t xml:space="preserve">8.19836235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18185043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20661640167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.14469623565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15295219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20248985290527</t>
+    <t xml:space="preserve">8.1529541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20249080657959</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33046054840088</t>
+    <t xml:space="preserve">8.35522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33045959472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.47907066345215</t>
@@ -1241,28 +1241,28 @@
     <t xml:space="preserve">8.52035140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280281066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070556640625</t>
+    <t xml:space="preserve">8.79280471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070461273193</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408451080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86710929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896152496338</t>
+    <t xml:space="preserve">8.86711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6689624786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.6524486541748</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">8.67721843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42953395843506</t>
+    <t xml:space="preserve">8.42953300476074</t>
   </si>
   <si>
     <t xml:space="preserve">8.67109107971191</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">8.74605751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70440864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77104663848877</t>
+    <t xml:space="preserve">8.7044095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77104568481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.75438785552979</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">8.24628257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30875396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34623908996582</t>
+    <t xml:space="preserve">8.30875492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3462381362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.41287422180176</t>
@@ -1304,145 +1304,145 @@
     <t xml:space="preserve">8.55447769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87933158874512</t>
+    <t xml:space="preserve">8.8460111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82935428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81269454956055</t>
+    <t xml:space="preserve">8.82935333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81269550323486</t>
   </si>
   <si>
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8626708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5044994354248</t>
+    <t xml:space="preserve">8.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50449848175049</t>
   </si>
   <si>
     <t xml:space="preserve">8.62111377716064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47118186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45452308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461196899414</t>
+    <t xml:space="preserve">8.47118091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45452117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461292266846</t>
   </si>
   <si>
     <t xml:space="preserve">8.58779621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49617099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3628978729248</t>
+    <t xml:space="preserve">8.49617004394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36289596557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.42120361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21712970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08802032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63777256011963</t>
+    <t xml:space="preserve">8.21712875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08802127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59612464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63777351379395</t>
   </si>
   <si>
     <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78815603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6132345199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234342575073</t>
+    <t xml:space="preserve">8.121337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78815650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733303070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323499679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234437942505</t>
   </si>
   <si>
     <t xml:space="preserve">7.67154169082642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62572860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241104125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57158708572388</t>
+    <t xml:space="preserve">7.62573003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72152042388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57158660888672</t>
   </si>
   <si>
     <t xml:space="preserve">7.82980442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659986495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6340594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229755401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79231929779053</t>
+    <t xml:space="preserve">7.54659795761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405847549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229707717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79232025146484</t>
   </si>
   <si>
     <t xml:space="preserve">7.61740016937256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71319007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68820095062256</t>
+    <t xml:space="preserve">7.71319055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6882004737854</t>
   </si>
   <si>
     <t xml:space="preserve">7.44664287567139</t>
@@ -1454,34 +1454,34 @@
     <t xml:space="preserve">7.14677810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19259071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637336730957</t>
+    <t xml:space="preserve">7.19259119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163248062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321229934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637241363525</t>
   </si>
   <si>
     <t xml:space="preserve">8.17131614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951221466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32957935333252</t>
+    <t xml:space="preserve">8.47951126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32957744598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955665588379</t>
+    <t xml:space="preserve">8.23378944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955760955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.5294885635376</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">9.05425262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01260471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427436828613</t>
+    <t xml:space="preserve">8.99594593048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01260375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427532196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07923984527588</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">9.11255931854248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09590148925781</t>
+    <t xml:space="preserve">9.09589958190918</t>
   </si>
   <si>
     <t xml:space="preserve">9.02093315124512</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">9.02926349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66276264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57113552093506</t>
+    <t xml:space="preserve">8.66276168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.02138519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0838565826416</t>
+    <t xml:space="preserve">8.08385562896729</t>
   </si>
   <si>
     <t xml:space="preserve">8.15049266815186</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">8.35456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9839015007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82563924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9922308921814</t>
+    <t xml:space="preserve">7.98390054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563972473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99223136901855</t>
   </si>
   <si>
     <t xml:space="preserve">8.27127170562744</t>
@@ -1553,79 +1553,79 @@
     <t xml:space="preserve">8.07969093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28376579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53781795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46285247802734</t>
+    <t xml:space="preserve">8.28376483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46285343170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13799858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00472450256348</t>
+    <t xml:space="preserve">8.13799953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00472545623779</t>
   </si>
   <si>
     <t xml:space="preserve">7.54243278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0172176361084</t>
+    <t xml:space="preserve">8.01721858978271</t>
   </si>
   <si>
     <t xml:space="preserve">8.26294231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04220771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20047092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19214057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09635066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12550258636475</t>
+    <t xml:space="preserve">8.04220867156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19213962554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09634971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14216327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">8.17964553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94641733169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25877666473389</t>
+    <t xml:space="preserve">7.94641923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2587776184082</t>
   </si>
   <si>
     <t xml:space="preserve">7.97557163238525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8922758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81731033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62989282608032</t>
+    <t xml:space="preserve">7.89227533340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81730937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989377975464</t>
   </si>
   <si>
     <t xml:space="preserve">7.79648494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75483751296997</t>
+    <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.22129344940186</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21296501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18381023406982</t>
+    <t xml:space="preserve">8.21296405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18381118774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.1963062286377</t>
@@ -1646,40 +1646,40 @@
     <t xml:space="preserve">8.22962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73772716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43786334991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38788509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62944316864014</t>
+    <t xml:space="preserve">8.73772621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43786430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38788414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62944221496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768177032471</t>
+    <t xml:space="preserve">8.51282978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69608116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768367767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.77937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37910652160645</t>
+    <t xml:space="preserve">8.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37910556793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.56235599517822</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">9.59567546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54569816589355</t>
+    <t xml:space="preserve">9.54569625854492</t>
   </si>
   <si>
     <t xml:space="preserve">9.39576435089111</t>
@@ -1697,31 +1697,31 @@
     <t xml:space="preserve">9.28747940063477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29580879211426</t>
+    <t xml:space="preserve">9.29580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571990966797</t>
+    <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411739349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03759288787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22917461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2708215713501</t>
+    <t xml:space="preserve">9.66231060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22917366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
@@ -1730,49 +1730,49 @@
     <t xml:space="preserve">9.13754844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16253662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0709114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56280708312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64610290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06258201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10422992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94596672058105</t>
+    <t xml:space="preserve">9.16253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07091236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56280517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64610385894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06258106231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1042308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
     <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83797073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65155124664307</t>
+    <t xml:space="preserve">8.83797168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65155029296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.58376312255859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47360706329346</t>
+    <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
     <t xml:space="preserve">8.72781467437744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59223747253418</t>
+    <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">8.38039684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700099945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30413436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26176643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34226608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39310741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33379077911377</t>
+    <t xml:space="preserve">8.42700004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30413341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2617654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34226512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39310646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33379173278809</t>
   </si>
   <si>
     <t xml:space="preserve">8.31260776519775</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">8.2956600189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839824676514</t>
+    <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
     <t xml:space="preserve">8.10500335693359</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">8.19397640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44394779205322</t>
+    <t xml:space="preserve">8.75323581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.3253173828125</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66849708557129</t>
+    <t xml:space="preserve">8.52444744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57528972625732</t>
+    <t xml:space="preserve">8.57528877258301</t>
   </si>
   <si>
     <t xml:space="preserve">8.2024507522583</t>
@@ -1886,49 +1886,49 @@
     <t xml:space="preserve">8.1727933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11771583557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03297901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89740133285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13466262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9651894569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9016375541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961177825928</t>
+    <t xml:space="preserve">8.11771488189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03297805786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89740037918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13466167449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96518898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90163803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961225509644</t>
   </si>
   <si>
     <t xml:space="preserve">7.73640203475952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72792863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2363452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329208374023</t>
+    <t xml:space="preserve">7.72792911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23634624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329303741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72369194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671653747559</t>
+    <t xml:space="preserve">7.72369050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671558380127</t>
   </si>
   <si>
     <t xml:space="preserve">7.82113790512085</t>
@@ -1937,28 +1937,28 @@
     <t xml:space="preserve">7.71945476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66014051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71098184585571</t>
+    <t xml:space="preserve">7.57540225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6601390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71098232269287</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41429042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42276477813721</t>
+    <t xml:space="preserve">8.41429138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684494018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">8.19821357727051</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">8.21939754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53291988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71933937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46936798095703</t>
+    <t xml:space="preserve">8.46513175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71934032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46936893463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90576076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97354793548584</t>
+    <t xml:space="preserve">8.8888111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.13042449951172</t>
@@ -2012,58 +2012,58 @@
     <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49902629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76170825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81255054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60070991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69392013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8549165725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02438926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28707218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57517528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47349262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42264938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3040189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53280639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63448905944824</t>
+    <t xml:space="preserve">8.49902534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7617073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81254959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60070896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85491847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02439022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28707122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57517433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47349071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42265033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53280735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63449001312256</t>
   </si>
   <si>
     <t xml:space="preserve">9.56670093536377</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">9.86327838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79548835754395</t>
+    <t xml:space="preserve">9.79548931121826</t>
   </si>
   <si>
     <t xml:space="preserve">9.82090950012207</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">10.0242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344327926636</t>
+    <t xml:space="preserve">10.1344318389893</t>
   </si>
   <si>
     <t xml:space="preserve">10.0835914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0158023834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93953895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0666446685791</t>
+    <t xml:space="preserve">10.0158014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93953990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0666437149048</t>
   </si>
   <si>
     <t xml:space="preserve">10.1768016815186</t>
@@ -2123,49 +2123,49 @@
     <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598539352417</t>
+    <t xml:space="preserve">10.1598529815674</t>
   </si>
   <si>
     <t xml:space="preserve">10.2615356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2530632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.168327331543</t>
+    <t xml:space="preserve">10.2530641555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1683263778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.1937475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0496969223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82938385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94801330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99885559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92259311676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51585960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73617362976074</t>
+    <t xml:space="preserve">10.0496959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82938289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94801235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.998854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92259216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51586055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581712722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73617267608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.8463306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296340942383</t>
+    <t xml:space="preserve">9.64296436309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.54975414276123</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1643180847168</t>
+    <t xml:space="preserve">8.16431999206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.32108020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01603126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00331974029541</t>
+    <t xml:space="preserve">8.01603221893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
     <t xml:space="preserve">7.70674419403076</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39322185516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153776168823</t>
+    <t xml:space="preserve">7.39322090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153680801392</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71109533309937</t>
+    <t xml:space="preserve">6.71109628677368</t>
   </si>
   <si>
     <t xml:space="preserve">6.61364936828613</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484846115112</t>
+    <t xml:space="preserve">5.08416318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484798431396</t>
   </si>
   <si>
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647438049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59258031845093</t>
+    <t xml:space="preserve">5.62647342681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59257984161377</t>
   </si>
   <si>
     <t xml:space="preserve">5.80865669250488</t>
@@ -2240,58 +2240,58 @@
     <t xml:space="preserve">5.26210975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84690284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1604266166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89774417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76216697692871</t>
+    <t xml:space="preserve">4.84690237045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16042613983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89774465560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76216602325439</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481937408447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41463422775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19008350372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20279407501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0163745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10111093521118</t>
+    <t xml:space="preserve">5.41463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1900839805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20279359817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01637506484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466283798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10111141204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.93163919448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96129655838013</t>
+    <t xml:space="preserve">4.96129608154297</t>
   </si>
   <si>
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663091659546</t>
+    <t xml:space="preserve">5.73663139343262</t>
   </si>
   <si>
     <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70273685455322</t>
+    <t xml:space="preserve">6.07557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70273733139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.53326511383057</t>
@@ -2300,19 +2300,19 @@
     <t xml:space="preserve">5.49513339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8722095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93576049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10099649429321</t>
+    <t xml:space="preserve">5.87220859527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93576097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10099601745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.13065385818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88068294525146</t>
+    <t xml:space="preserve">5.88068246841431</t>
   </si>
   <si>
     <t xml:space="preserve">5.67731618881226</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">5.66460561752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65189552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05015516281128</t>
+    <t xml:space="preserve">5.65189504623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05015420913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">6.29165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39333534240723</t>
+    <t xml:space="preserve">6.39333581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835662841797</t>
+    <t xml:space="preserve">6.94835710525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.91022539138794</t>
@@ -2363,37 +2363,37 @@
     <t xml:space="preserve">7.04156684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24916982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00343561172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70685911178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57551860809326</t>
+    <t xml:space="preserve">7.24917030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00343656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70685863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
     <t xml:space="preserve">6.71533250808716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72804355621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69838523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64330673217773</t>
+    <t xml:space="preserve">6.72804307937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69838571548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64330720901489</t>
   </si>
   <si>
     <t xml:space="preserve">6.55009746551514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6094126701355</t>
+    <t xml:space="preserve">6.60941219329834</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402061462402</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14760065078735</t>
+    <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">6.28741550445557</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">6.15183782577515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01626062393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31707286834717</t>
+    <t xml:space="preserve">6.01625967025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
     <t xml:space="preserve">6.13912725448608</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24504709243774</t>
+    <t xml:space="preserve">6.2450475692749</t>
   </si>
   <si>
     <t xml:space="preserve">6.47383451461792</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">6.27046871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523319244385</t>
+    <t xml:space="preserve">6.06286478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523271560669</t>
   </si>
   <si>
     <t xml:space="preserve">6.22386360168457</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">6.14336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08404874801636</t>
+    <t xml:space="preserve">6.08404922485352</t>
   </si>
   <si>
     <t xml:space="preserve">5.95270824432373</t>
@@ -2471,91 +2471,91 @@
     <t xml:space="preserve">6.18149566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02049684524536</t>
+    <t xml:space="preserve">6.02049732208252</t>
   </si>
   <si>
     <t xml:space="preserve">5.99931287765503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38486194610596</t>
+    <t xml:space="preserve">6.3848614692688</t>
   </si>
   <si>
     <t xml:space="preserve">6.32978343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3213095664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25775814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27470541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23233699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3085994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37215089797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98648834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16019678115845</t>
+    <t xml:space="preserve">6.32131004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25775766372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2747049331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.232337474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30859994888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37215137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.986487865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16019630432129</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377681732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73228025436401</t>
+    <t xml:space="preserve">6.97377729415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73227977752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01614475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90175294876099</t>
+    <t xml:space="preserve">7.0161452293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90175247192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.85938405990601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79583215713501</t>
+    <t xml:space="preserve">6.79583263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10947036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05439138412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04168128967285</t>
+    <t xml:space="preserve">6.10946989059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0543909072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04168081283569</t>
   </si>
   <si>
     <t xml:space="preserve">6.16031122207642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09676027297974</t>
+    <t xml:space="preserve">6.09675979614258</t>
   </si>
   <si>
     <t xml:space="preserve">6.2153902053833</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09252214431763</t>
+    <t xml:space="preserve">6.09252262115479</t>
   </si>
   <si>
     <t xml:space="preserve">6.0077862739563</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">5.49089670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6010537147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46547603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25787210464478</t>
+    <t xml:space="preserve">5.60105323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46547555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25787162780762</t>
   </si>
   <si>
     <t xml:space="preserve">5.28752994537354</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">5.0121374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616083145142</t>
+    <t xml:space="preserve">5.29176616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616035461426</t>
   </si>
   <si>
     <t xml:space="preserve">5.43158149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76205205917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81713056564331</t>
+    <t xml:space="preserve">5.76205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
     <t xml:space="preserve">5.83831453323364</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075365066528</t>
+    <t xml:space="preserve">6.74075317382812</t>
   </si>
   <si>
     <t xml:space="preserve">6.82125282287598</t>
@@ -2630,121 +2630,121 @@
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09652996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49914073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45253562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845737457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200784683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87197923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84232139587402</t>
+    <t xml:space="preserve">8.09653091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49914169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45253658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453374862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079622268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87198066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84232234954834</t>
   </si>
   <si>
     <t xml:space="preserve">7.67284917831421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81266593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571771621704</t>
+    <t xml:space="preserve">7.81266498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.63471937179565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91011095046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82537460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8550329208374</t>
+    <t xml:space="preserve">7.91010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8253755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85503387451172</t>
   </si>
   <si>
     <t xml:space="preserve">7.68556070327759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5245623588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47795677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58811378479004</t>
+    <t xml:space="preserve">7.52456283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47795724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5881142616272</t>
   </si>
   <si>
     <t xml:space="preserve">7.56693029403687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4101676940918</t>
+    <t xml:space="preserve">7.41016817092896</t>
   </si>
   <si>
     <t xml:space="preserve">7.28730201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22374820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32543230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31695795059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06275033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18138074874878</t>
+    <t xml:space="preserve">7.22374868392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32543277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3169584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0627498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
     <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63895606994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319324493408</t>
+    <t xml:space="preserve">7.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319276809692</t>
   </si>
   <si>
     <t xml:space="preserve">7.74911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53727197647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926866531372</t>
+    <t xml:space="preserve">7.53727293014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926914215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.21516036987305</t>
@@ -2756,46 +2756,46 @@
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837059020996</t>
+    <t xml:space="preserve">8.20668792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30836963653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.14313507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79147958755493</t>
+    <t xml:space="preserve">7.79148054122925</t>
   </si>
   <si>
     <t xml:space="preserve">7.65166568756104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03721523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92282152175903</t>
+    <t xml:space="preserve">8.0372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92282295227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63460350036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00755786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39734268188477</t>
+    <t xml:space="preserve">8.88033866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63460445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3973445892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965435028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78712844848633</t>
+    <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.68544673919678</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16844177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20233631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5582275390625</t>
+    <t xml:space="preserve">9.16844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55822658538818</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71075344085693</t>
+    <t xml:space="preserve">9.04133796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04981136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71075248718262</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">9.44806957244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196506500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69380569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0412244796753</t>
+    <t xml:space="preserve">9.48196411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69380474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0412225723267</t>
   </si>
   <si>
     <t xml:space="preserve">9.74464702606201</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43112373352051</t>
+    <t xml:space="preserve">9.52433204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43112277984619</t>
   </si>
   <si>
     <t xml:space="preserve">9.02747917175293</t>
@@ -2873,40 +2873,40 @@
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0880651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20924091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24386215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33906936645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43427848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63335037231445</t>
+    <t xml:space="preserve">8.96689128875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08806610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2092399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24386119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33906841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43427658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63334941864014</t>
   </si>
   <si>
     <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40831279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47755336761475</t>
+    <t xml:space="preserve">9.40831184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47755527496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21789455413818</t>
+    <t xml:space="preserve">9.2178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.1140308380127</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882457733154</t>
+    <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.26117134094238</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.46889877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26982688903809</t>
+    <t xml:space="preserve">9.2698278427124</t>
   </si>
   <si>
     <t xml:space="preserve">9.31310367584229</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34772491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1313419342041</t>
+    <t xml:space="preserve">9.3477258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13134288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.12268733978271</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00151348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75916481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82840728759766</t>
+    <t xml:space="preserve">9.00151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75916385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82840633392334</t>
   </si>
   <si>
     <t xml:space="preserve">9.05344486236572</t>
@@ -2966,34 +2966,34 @@
     <t xml:space="preserve">9.20058536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36503601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41696834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1659631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99285793304443</t>
+    <t xml:space="preserve">9.36503505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41696739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16596412658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.252516746521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17461967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94958114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83706283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71588706970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77647590637207</t>
+    <t xml:space="preserve">9.1746187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94958019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83706092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71588802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77647495269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.98420238494873</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395568847656</t>
+    <t xml:space="preserve">8.66395664215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84571743011475</t>
+    <t xml:space="preserve">8.84571838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78513050079346</t>
+    <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
     <t xml:space="preserve">8.72454357147217</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26581192016602</t>
+    <t xml:space="preserve">8.26581287384033</t>
   </si>
   <si>
     <t xml:space="preserve">8.19656944274902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23119163513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28744983673096</t>
+    <t xml:space="preserve">8.23119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.74185466766357</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42160797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36102104187012</t>
+    <t xml:space="preserve">8.42160701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3610200881958</t>
   </si>
   <si>
     <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366317749023</t>
+    <t xml:space="preserve">8.63366222381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.67261219024658</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">8.62933540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59904098510742</t>
+    <t xml:space="preserve">8.61202335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59904193878174</t>
   </si>
   <si>
     <t xml:space="preserve">8.50383281707764</t>
@@ -3086,76 +3086,76 @@
     <t xml:space="preserve">8.54278182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80244159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92825508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85901403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93691158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87632417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96287727355957</t>
+    <t xml:space="preserve">8.58605766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81975173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80244064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92825603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85901308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9369101524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87632465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96287679672241</t>
   </si>
   <si>
     <t xml:space="preserve">7.91959953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91527271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9585485458374</t>
+    <t xml:space="preserve">7.91527318954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95854902267456</t>
   </si>
   <si>
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128660202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53011226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.556077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39162635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3526782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09734630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.166588306427</t>
+    <t xml:space="preserve">7.82439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128612518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53011178970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55607748031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981784820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39162731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35267782211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09734678268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16658878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.05839776992798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18389987945557</t>
+    <t xml:space="preserve">7.18389940261841</t>
   </si>
   <si>
     <t xml:space="preserve">7.11032962799072</t>
@@ -3164,64 +3164,64 @@
     <t xml:space="preserve">7.33969497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51280117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42191982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37431669235229</t>
+    <t xml:space="preserve">7.51280164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42192029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37431621551514</t>
   </si>
   <si>
     <t xml:space="preserve">7.3310399055481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15360641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06272506713867</t>
+    <t xml:space="preserve">7.15360736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06272554397583</t>
   </si>
   <si>
     <t xml:space="preserve">7.14927864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2012095451355</t>
+    <t xml:space="preserve">7.20121049880981</t>
   </si>
   <si>
     <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19255495071411</t>
+    <t xml:space="preserve">7.19255542755127</t>
   </si>
   <si>
     <t xml:space="preserve">7.25746965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26179838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2444863319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40460968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654106140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31805658340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41759204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700654983521</t>
+    <t xml:space="preserve">7.2617974281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24448728561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40461015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654153823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3180570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
     <t xml:space="preserve">7.36566114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34402227401733</t>
+    <t xml:space="preserve">7.34402275085449</t>
   </si>
   <si>
     <t xml:space="preserve">7.23583126068115</t>
@@ -3230,37 +3230,37 @@
     <t xml:space="preserve">7.14062309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07138061523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02377605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01944828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88961887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91991329193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88096380233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66458129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42223358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4698371887207</t>
+    <t xml:space="preserve">7.07138109207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02377653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01944875717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91991281509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8809642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66458177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42223310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46983766555786</t>
   </si>
   <si>
     <t xml:space="preserve">6.42656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40492248535156</t>
+    <t xml:space="preserve">6.40492296218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
@@ -3269,34 +3269,34 @@
     <t xml:space="preserve">6.54340744018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63861560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4914755821228</t>
+    <t xml:space="preserve">6.63861608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49147605895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.36164569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43088817596436</t>
+    <t xml:space="preserve">6.47849321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43088865280151</t>
   </si>
   <si>
     <t xml:space="preserve">6.56937313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44387149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5563907623291</t>
+    <t xml:space="preserve">6.44387197494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55639028549194</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56504535675049</t>
+    <t xml:space="preserve">6.5650463104248</t>
   </si>
   <si>
     <t xml:space="preserve">6.49580335617065</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">6.10198736190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88560485839844</t>
+    <t xml:space="preserve">5.88560438156128</t>
   </si>
   <si>
     <t xml:space="preserve">6.2015233039856</t>
@@ -3320,43 +3320,43 @@
     <t xml:space="preserve">6.11497020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05005550384521</t>
+    <t xml:space="preserve">6.05005502700806</t>
   </si>
   <si>
     <t xml:space="preserve">6.08034896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70817089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60863542556763</t>
+    <t xml:space="preserve">5.70817041397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
     <t xml:space="preserve">5.46149492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29704427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53073787689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55670356750488</t>
+    <t xml:space="preserve">5.297043800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53073692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
     <t xml:space="preserve">5.55237531661987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63460159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53506517410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89425992965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367300033569</t>
+    <t xml:space="preserve">5.63460063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53506469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89425945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367252349854</t>
   </si>
   <si>
     <t xml:space="preserve">5.87262153625488</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73413705825806</t>
+    <t xml:space="preserve">5.8509840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7341365814209</t>
   </si>
   <si>
     <t xml:space="preserve">6.05438280105591</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37030124664307</t>
+    <t xml:space="preserve">6.37030172348022</t>
   </si>
   <si>
     <t xml:space="preserve">6.38761186599731</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">6.29673147201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37895631790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99812364578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15391874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11064291000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.145263671875</t>
+    <t xml:space="preserve">6.37895679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99812316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1539192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11064195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14526319503784</t>
   </si>
   <si>
     <t xml:space="preserve">6.18421220779419</t>
@@ -3416,43 +3416,43 @@
     <t xml:space="preserve">6.19286775588989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1236252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17555713653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26210975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30105876922607</t>
+    <t xml:space="preserve">6.12362480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1755576133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26211023330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30105924606323</t>
   </si>
   <si>
     <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24480009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11929798126221</t>
+    <t xml:space="preserve">6.24479961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11929750442505</t>
   </si>
   <si>
     <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51744174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34433603286743</t>
+    <t xml:space="preserve">6.51744222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34433555603027</t>
   </si>
   <si>
     <t xml:space="preserve">6.10631465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27901029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19044828414917</t>
+    <t xml:space="preserve">6.27900981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19044780731201</t>
   </si>
   <si>
     <t xml:space="preserve">6.12845516204834</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42956495285034</t>
+    <t xml:space="preserve">6.38971138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42956447601318</t>
   </si>
   <si>
     <t xml:space="preserve">6.3764271736145</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">6.27458190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34543132781982</t>
+    <t xml:space="preserve">6.34543085098267</t>
   </si>
   <si>
     <t xml:space="preserve">6.4162802696228</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">5.40225076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65022325515747</t>
+    <t xml:space="preserve">5.65022373199463</t>
   </si>
   <si>
     <t xml:space="preserve">5.59708642959595</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">5.62808275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63251066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80077791213989</t>
+    <t xml:space="preserve">5.63251113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80077838897705</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79192113876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6059422492981</t>
+    <t xml:space="preserve">5.79192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60594177246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066492080688</t>
+    <t xml:space="preserve">5.53952121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066444396973</t>
   </si>
   <si>
     <t xml:space="preserve">5.66793537139893</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">5.88933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77863693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92476367950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85834217071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40667867660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57494592666626</t>
+    <t xml:space="preserve">5.77863740921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92476415634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85834264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40667915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57494640350342</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948635101318</t>
+    <t xml:space="preserve">5.84948682785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.94690418243408</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">5.90262317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07088994979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16387987136841</t>
+    <t xml:space="preserve">6.07089042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16387939453125</t>
   </si>
   <si>
     <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07531833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07974576950073</t>
+    <t xml:space="preserve">6.07531881332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07974624633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.95576000213623</t>
@@ -3608,16 +3608,16 @@
     <t xml:space="preserve">5.97790050506592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14616727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18159246444702</t>
+    <t xml:space="preserve">6.14616775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18159198760986</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27015399932861</t>
+    <t xml:space="preserve">6.27015352249146</t>
   </si>
   <si>
     <t xml:space="preserve">6.04432153701782</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660894393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99561262130737</t>
+    <t xml:space="preserve">6.02660942077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99561309814453</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95133209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01775312423706</t>
+    <t xml:space="preserve">5.95133256912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01775360107422</t>
   </si>
   <si>
     <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8760552406311</t>
+    <t xml:space="preserve">5.87605571746826</t>
   </si>
   <si>
     <t xml:space="preserve">5.89819526672363</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">5.63693857192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48195600509644</t>
+    <t xml:space="preserve">5.48195648193359</t>
   </si>
   <si>
     <t xml:space="preserve">5.27383661270142</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">5.39782285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55723333358765</t>
+    <t xml:space="preserve">5.5572338104248</t>
   </si>
   <si>
     <t xml:space="preserve">5.59265804290771</t>
@@ -3686,16 +3686,16 @@
     <t xml:space="preserve">5.68564796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86719846725464</t>
+    <t xml:space="preserve">5.8671989440918</t>
   </si>
   <si>
     <t xml:space="preserve">5.65465116500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62365436553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121957778931</t>
+    <t xml:space="preserve">5.62365484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68121910095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7299280166626</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00889682769775</t>
+    <t xml:space="preserve">6.00889730453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">6.25244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17273616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08417415618896</t>
+    <t xml:space="preserve">6.17273569107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08417463302612</t>
   </si>
   <si>
     <t xml:space="preserve">6.06203413009644</t>
@@ -3737,16 +3737,16 @@
     <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4738450050354</t>
+    <t xml:space="preserve">6.47384452819824</t>
   </si>
   <si>
     <t xml:space="preserve">6.42513656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915719985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428762435913</t>
+    <t xml:space="preserve">6.23915672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428714752197</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">6.79266691207886</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54912233352661</t>
+    <t xml:space="preserve">6.65539598464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54912185668945</t>
   </si>
   <si>
     <t xml:space="preserve">6.52255344390869</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">6.53583812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49598598480225</t>
+    <t xml:space="preserve">6.49598550796509</t>
   </si>
   <si>
     <t xml:space="preserve">6.64211225509644</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">6.46941709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33214712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40742444992065</t>
+    <t xml:space="preserve">6.33214664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4074239730835</t>
   </si>
   <si>
     <t xml:space="preserve">6.55355072021484</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">6.66425228118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9476490020752</t>
+    <t xml:space="preserve">6.94764852523804</t>
   </si>
   <si>
     <t xml:space="preserve">6.92993688583374</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093320846558</t>
+    <t xml:space="preserve">6.96093368530273</t>
   </si>
   <si>
     <t xml:space="preserve">6.98307371139526</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">7.58529186248779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2487587928772</t>
+    <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
     <t xml:space="preserve">7.2089056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19562101364136</t>
+    <t xml:space="preserve">7.19562149047852</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
@@ -3872,25 +3872,25 @@
     <t xml:space="preserve">7.3018946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52329874038696</t>
+    <t xml:space="preserve">7.5232982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.49230241775513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42145252227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34617519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48787403106689</t>
+    <t xml:space="preserve">7.42145299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34617567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48787450790405</t>
   </si>
   <si>
     <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10263204574585</t>
+    <t xml:space="preserve">7.10263252258301</t>
   </si>
   <si>
     <t xml:space="preserve">7.3151798248291</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">7.2753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2930383682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41259670257568</t>
+    <t xml:space="preserve">7.29303884506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">7.44802093505859</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">6.74838542938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00078630447388</t>
+    <t xml:space="preserve">7.00078582763672</t>
   </si>
   <si>
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451169967651</t>
+    <t xml:space="preserve">6.89451217651367</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">6.81480693817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81037855148315</t>
+    <t xml:space="preserve">6.81037902832031</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26204204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761413574219</t>
+    <t xml:space="preserve">7.26204252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25761365890503</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,16 +3983,16 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12034368515015</t>
+    <t xml:space="preserve">7.10705900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1203441619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17348146438599</t>
+    <t xml:space="preserve">7.17348098754883</t>
   </si>
   <si>
     <t xml:space="preserve">7.31960821151733</t>
@@ -4019,16 +4019,16 @@
     <t xml:space="preserve">7.47458934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68271017074585</t>
+    <t xml:space="preserve">7.68270969390869</t>
   </si>
   <si>
     <t xml:space="preserve">7.60300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67828130722046</t>
+    <t xml:space="preserve">7.71370649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828178405762</t>
   </si>
   <si>
     <t xml:space="preserve">7.85610342025757</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">7.81506776809692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79683017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88802051544189</t>
+    <t xml:space="preserve">7.79682922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">8.07040309906006</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">7.90169954299927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74211454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80138969421387</t>
+    <t xml:space="preserve">7.74211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80138921737671</t>
   </si>
   <si>
     <t xml:space="preserve">7.95185470581055</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">7.94273519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09776020050049</t>
+    <t xml:space="preserve">8.09775924682617</t>
   </si>
   <si>
     <t xml:space="preserve">8.22086811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30293846130371</t>
+    <t xml:space="preserve">8.30293941497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.45340538024902</t>
@@ -4085,28 +4085,28 @@
     <t xml:space="preserve">8.13423633575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03392601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09320068359375</t>
+    <t xml:space="preserve">8.03392696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09319972991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.03848552703857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70563793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7193169593811</t>
+    <t xml:space="preserve">7.70563840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71931743621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.78771066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75579357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73299598693848</t>
+    <t xml:space="preserve">7.75579404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73299551010132</t>
   </si>
   <si>
     <t xml:space="preserve">7.71475791931152</t>
@@ -4118,16 +4118,16 @@
     <t xml:space="preserve">7.60988855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45030355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56885290145874</t>
+    <t xml:space="preserve">7.45030403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56885242462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55517292022705</t>
+    <t xml:space="preserve">7.55517339706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.59164953231812</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">7.50501823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54149484634399</t>
+    <t xml:space="preserve">7.45942354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54149532318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.60076904296875</t>
@@ -4157,34 +4157,34 @@
     <t xml:space="preserve">7.55061340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53237628936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69651937484741</t>
+    <t xml:space="preserve">7.53237581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">7.65548372268677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64636516571045</t>
+    <t xml:space="preserve">7.64636468887329</t>
   </si>
   <si>
     <t xml:space="preserve">7.48678016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41838693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33175563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38191080093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40470790863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52781581878662</t>
+    <t xml:space="preserve">7.4183874130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3317551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.381911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40470838546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52781629562378</t>
   </si>
   <si>
     <t xml:space="preserve">7.39102935791016</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">7.29527902603149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24056434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26792192459106</t>
+    <t xml:space="preserve">7.24056482315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">7.25880289077759</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">7.06274175643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08553981781006</t>
+    <t xml:space="preserve">7.08554029464722</t>
   </si>
   <si>
     <t xml:space="preserve">7.01258707046509</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">6.6797399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54751300811768</t>
+    <t xml:space="preserve">6.54751253128052</t>
   </si>
   <si>
     <t xml:space="preserve">6.50191783905029</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">6.67062091827393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60222768783569</t>
+    <t xml:space="preserve">6.60222721099854</t>
   </si>
   <si>
     <t xml:space="preserve">6.59310865402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52927446365356</t>
+    <t xml:space="preserve">6.52927494049072</t>
   </si>
   <si>
     <t xml:space="preserve">6.43808364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69341850280762</t>
+    <t xml:space="preserve">6.69341897964478</t>
   </si>
   <si>
     <t xml:space="preserve">6.75725221633911</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">6.50647735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37880992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28761863708496</t>
+    <t xml:space="preserve">6.37880945205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28761911392212</t>
   </si>
   <si>
     <t xml:space="preserve">6.45176219940186</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">6.47911977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58398914337158</t>
+    <t xml:space="preserve">6.58398962020874</t>
   </si>
   <si>
     <t xml:space="preserve">6.97155094146729</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">7.03994417190552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03538513183594</t>
+    <t xml:space="preserve">7.03538465499878</t>
   </si>
   <si>
     <t xml:space="preserve">7.06730175018311</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">7.21320724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18129062652588</t>
+    <t xml:space="preserve">7.18129014968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.28615999221802</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">7.29983901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2360053062439</t>
+    <t xml:space="preserve">7.23600482940674</t>
   </si>
   <si>
     <t xml:space="preserve">7.20408821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96097230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86066341400146</t>
+    <t xml:space="preserve">7.96097278594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86066293716431</t>
   </si>
   <si>
     <t xml:space="preserve">7.97921180725098</t>
@@ -4394,34 +4394,34 @@
     <t xml:space="preserve">7.97009229660034</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05672359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98377084732056</t>
+    <t xml:space="preserve">8.05672454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">8.28926086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31661891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20263004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29837989807129</t>
+    <t xml:space="preserve">8.31661796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20262908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29838085174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.25278472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26646327972412</t>
+    <t xml:space="preserve">8.2664623260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.32117748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08408069610596</t>
+    <t xml:space="preserve">8.08408164978027</t>
   </si>
   <si>
     <t xml:space="preserve">8.04304504394531</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">8.04760456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20718955993652</t>
+    <t xml:space="preserve">8.20718860626221</t>
   </si>
   <si>
     <t xml:space="preserve">8.16615295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06128311157227</t>
+    <t xml:space="preserve">8.06128406524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.16159343719482</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">8.34397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38957023620605</t>
+    <t xml:space="preserve">8.38957118988037</t>
   </si>
   <si>
     <t xml:space="preserve">8.37589263916016</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">8.2755823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44884586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32573699951172</t>
+    <t xml:space="preserve">8.44884490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32573795318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.57195281982422</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">8.64034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53547668457031</t>
+    <t xml:space="preserve">8.535475730896</t>
   </si>
   <si>
     <t xml:space="preserve">8.62666797637939</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">8.43516635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54459476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68138217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79081153869629</t>
+    <t xml:space="preserve">8.54459571838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68138313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79081249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.84552574157715</t>
@@ -4571,37 +4571,37 @@
     <t xml:space="preserve">8.23910522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112747192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93817567825317</t>
+    <t xml:space="preserve">8.01112842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93817520141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.93361568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85154390335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68284130096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06584358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14335536956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12055778503418</t>
+    <t xml:space="preserve">7.85154342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594921112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6828408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.065842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17071342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14335632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12055683135986</t>
   </si>
   <si>
     <t xml:space="preserve">8.13879585266113</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">8.50811958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67226409912109</t>
+    <t xml:space="preserve">8.67226314544678</t>
   </si>
   <si>
     <t xml:space="preserve">8.75433540344238</t>
@@ -5400,6 +5400,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.039999961853</t>
   </si>
 </sst>
 </file>
@@ -68268,7 +68271,7 @@
     </row>
     <row r="2406">
       <c r="A2406" s="1" t="n">
-        <v>45945.6496064815</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2406" t="n">
         <v>204111</v>
@@ -68289,6 +68292,32 @@
         <v>1795</v>
       </c>
       <c r="H2406" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" s="1" t="n">
+        <v>45946.6495833333</v>
+      </c>
+      <c r="B2407" t="n">
+        <v>241824</v>
+      </c>
+      <c r="C2407" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2407" t="n">
+        <v>13.8199996948242</v>
+      </c>
+      <c r="E2407" t="n">
+        <v>13.8199996948242</v>
+      </c>
+      <c r="F2407" t="n">
+        <v>14.039999961853</v>
+      </c>
+      <c r="G2407" t="s">
+        <v>1796</v>
+      </c>
+      <c r="H2407" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032571792603</t>
+    <t xml:space="preserve">2.96032619476318</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
@@ -59,49 +59,49 @@
     <t xml:space="preserve">3.06500053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05028080940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16476893424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17131066322327</t>
+    <t xml:space="preserve">3.05028128623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930172920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17131090164185</t>
   </si>
   <si>
     <t xml:space="preserve">3.16149735450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514231681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168452262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30051851272583</t>
+    <t xml:space="preserve">3.13205742835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822625160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168404579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30051803588867</t>
   </si>
   <si>
     <t xml:space="preserve">3.34140682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463277816772</t>
+    <t xml:space="preserve">3.43463253974915</t>
   </si>
   <si>
     <t xml:space="preserve">3.437903881073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39374375343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393068313599</t>
+    <t xml:space="preserve">3.39374423027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393044471741</t>
   </si>
   <si>
     <t xml:space="preserve">3.33977174758911</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841318130493</t>
+    <t xml:space="preserve">3.14841341972351</t>
   </si>
   <si>
     <t xml:space="preserve">3.0306544303894</t>
@@ -119,46 +119,46 @@
     <t xml:space="preserve">3.08789825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1729462146759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18112421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19911503791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0339252948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303722381592</t>
+    <t xml:space="preserve">3.17294669151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752463340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18112397193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257283210754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19911527633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03392601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303698539734</t>
   </si>
   <si>
     <t xml:space="preserve">3.04373860359192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12878680229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23019003868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23346161842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22528338432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11406707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14023542404175</t>
+    <t xml:space="preserve">3.12878656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23019027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23346138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2252836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1140673160553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14023566246033</t>
   </si>
   <si>
     <t xml:space="preserve">3.12224459648132</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">3.0911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0829918384552</t>
+    <t xml:space="preserve">3.08299136161804</t>
   </si>
   <si>
     <t xml:space="preserve">3.11897349357605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08135581016541</t>
+    <t xml:space="preserve">3.08135628700256</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425353050232</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13696455955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383500099182</t>
+    <t xml:space="preserve">3.1369640827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383476257324</t>
   </si>
   <si>
     <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10916066169739</t>
+    <t xml:space="preserve">3.10915994644165</t>
   </si>
   <si>
     <t xml:space="preserve">3.36921095848083</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">3.5098671913147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51640963554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54094266891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50168991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552108764648</t>
+    <t xml:space="preserve">3.5164098739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54094290733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50168967247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552084922791</t>
   </si>
   <si>
     <t xml:space="preserve">3.35612678527832</t>
@@ -224,28 +224,28 @@
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724764823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36103320121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3773889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35285592079163</t>
+    <t xml:space="preserve">3.29724717140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36103343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3757529258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738823890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35285568237305</t>
   </si>
   <si>
     <t xml:space="preserve">3.38556623458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43136167526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150298118591</t>
+    <t xml:space="preserve">3.43136119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150321960449</t>
   </si>
   <si>
     <t xml:space="preserve">3.47061419487</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">3.4673433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48696970939636</t>
+    <t xml:space="preserve">3.4869692325592</t>
   </si>
   <si>
     <t xml:space="preserve">3.44281029701233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3970148563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337013244629</t>
+    <t xml:space="preserve">3.39701509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337037086487</t>
   </si>
   <si>
     <t xml:space="preserve">3.48860549926758</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">3.4591658115387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50823140144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729794502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584956169128</t>
+    <t xml:space="preserve">3.41827726364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50823187828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729842185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584932327271</t>
   </si>
   <si>
     <t xml:space="preserve">3.57856011390686</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.56547570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5981867313385</t>
+    <t xml:space="preserve">3.59818696975708</t>
   </si>
   <si>
     <t xml:space="preserve">3.63907504081726</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">3.66360807418823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64725279808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996335029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636425018311</t>
+    <t xml:space="preserve">3.64725303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6799635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178559303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636377334595</t>
   </si>
   <si>
     <t xml:space="preserve">3.5671112537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46897912025452</t>
+    <t xml:space="preserve">3.4689793586731</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355753898621</t>
@@ -335,40 +335,40 @@
     <t xml:space="preserve">3.32668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2759850025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2432746887207</t>
+    <t xml:space="preserve">3.27598547935486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24327445030212</t>
   </si>
   <si>
     <t xml:space="preserve">3.21874165534973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25962972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495538711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0764491558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462691307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12551593780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27107906341553</t>
+    <t xml:space="preserve">3.25963020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1549551486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07644963264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12551546096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27107834815979</t>
   </si>
   <si>
     <t xml:space="preserve">3.31850957870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33486461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3675754070282</t>
+    <t xml:space="preserve">3.3348650932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36757516860962</t>
   </si>
   <si>
     <t xml:space="preserve">3.4084644317627</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">3.30869626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033158302307</t>
+    <t xml:space="preserve">3.24818086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033134460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.48206281661987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54421401023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454224586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655046463013</t>
+    <t xml:space="preserve">3.54421424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655070304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.57528924942017</t>
@@ -404,100 +404,100 @@
     <t xml:space="preserve">3.63253283500671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60309314727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851496696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617732048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435507774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75192737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412276268005</t>
+    <t xml:space="preserve">3.60309290885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851449012756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6407105922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7519268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7617404460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412252426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.77809548377991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77646040916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118037223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720765113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730309486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79445099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91548037528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86314392089844</t>
+    <t xml:space="preserve">3.77645993232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.791179895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720717430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730333328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071621894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91548085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314368247986</t>
   </si>
   <si>
     <t xml:space="preserve">3.8925838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92529439926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641573905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655752182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150860786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9645471572876</t>
+    <t xml:space="preserve">3.92529487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150908470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454691886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.85169529914856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04305362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618294715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767695426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898427009583</t>
+    <t xml:space="preserve">4.043053150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618342399597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968588829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8189845085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138457775116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94164967536926</t>
+    <t xml:space="preserve">3.941650390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">4.0561375617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97926759719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524877548218</t>
+    <t xml:space="preserve">3.97926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">4.04141759872437</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">4.08884763717651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08394193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16244840621948</t>
+    <t xml:space="preserve">4.0839409828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16244745254517</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048929214478</t>
+    <t xml:space="preserve">4.44048881530762</t>
   </si>
   <si>
     <t xml:space="preserve">4.41595649719238</t>
@@ -551,52 +551,52 @@
     <t xml:space="preserve">4.37506723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78804159164429</t>
+    <t xml:space="preserve">4.59586524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78804111480713</t>
   </si>
   <si>
     <t xml:space="preserve">4.99248361587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8043966293335</t>
+    <t xml:space="preserve">4.80439710617065</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83301830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90661859512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96386194229126</t>
+    <t xml:space="preserve">4.83301877975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90661764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96386241912842</t>
   </si>
   <si>
     <t xml:space="preserve">5.02928352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03337240219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19283819198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150548934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830396652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688144683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456871032715</t>
+    <t xml:space="preserve">5.03337287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19283676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688097000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456966400146</t>
   </si>
   <si>
     <t xml:space="preserve">5.3686580657959</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56492233276367</t>
+    <t xml:space="preserve">5.56492280960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.56901121139526</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">5.55265617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30323648452759</t>
+    <t xml:space="preserve">5.30323600769043</t>
   </si>
   <si>
     <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5485668182373</t>
+    <t xml:space="preserve">5.54856729507446</t>
   </si>
   <si>
     <t xml:space="preserve">5.59354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.601722240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70803213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709867477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80207586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82251977920532</t>
+    <t xml:space="preserve">5.60172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70803260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80207538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82252025604248</t>
   </si>
   <si>
     <t xml:space="preserve">5.85114192962646</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">5.47905683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48723411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46679019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5608344078064</t>
+    <t xml:space="preserve">5.4872350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46678972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083393096924</t>
   </si>
   <si>
     <t xml:space="preserve">5.64308166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69674682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46144533157349</t>
+    <t xml:space="preserve">5.69674730300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4614462852478</t>
   </si>
   <si>
     <t xml:space="preserve">5.57290410995483</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">5.65546560287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.705002784729</t>
+    <t xml:space="preserve">5.70500230789185</t>
   </si>
   <si>
     <t xml:space="preserve">5.73802709579468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84948587417603</t>
+    <t xml:space="preserve">5.78756427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8040771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10129833221436</t>
+    <t xml:space="preserve">6.10129880905151</t>
   </si>
   <si>
     <t xml:space="preserve">5.84122896194458</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866842269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133762359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233263015747</t>
+    <t xml:space="preserve">5.73389863967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233215332031</t>
   </si>
   <si>
     <t xml:space="preserve">5.77930784225464</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">5.77105140686035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84535789489746</t>
+    <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
     <t xml:space="preserve">5.68848991394043</t>
@@ -737,55 +737,55 @@
     <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5770320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5233678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813528060913</t>
+    <t xml:space="preserve">5.63069772720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57703256607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52336740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813575744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.48621463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53162336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568292617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009616851807</t>
+    <t xml:space="preserve">5.53162288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639123916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934713363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009712219238</t>
   </si>
   <si>
     <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30045175552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294387817383</t>
+    <t xml:space="preserve">5.30045080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294435501099</t>
   </si>
   <si>
     <t xml:space="preserve">5.1931209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10230350494385</t>
+    <t xml:space="preserve">5.10230302810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248010635376</t>
+    <t xml:space="preserve">5.17248058319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.34998798370361</t>
@@ -797,25 +797,25 @@
     <t xml:space="preserve">5.74628305435181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75041198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77517938613892</t>
+    <t xml:space="preserve">5.75041246414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77518081665039</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012624740601</t>
+    <t xml:space="preserve">5.87012672424316</t>
   </si>
   <si>
     <t xml:space="preserve">5.86599779129028</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">5.89489412307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04763269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204736709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8618688583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268726348877</t>
+    <t xml:space="preserve">6.0476336479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86186981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268774032593</t>
   </si>
   <si>
     <t xml:space="preserve">5.97332811355591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955476760864</t>
+    <t xml:space="preserve">6.06827306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955429077148</t>
   </si>
   <si>
     <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973136901855</t>
+    <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
     <t xml:space="preserve">6.19211626052856</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385982513428</t>
+    <t xml:space="preserve">6.18385934829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193822860718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1673469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15083456039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98158407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05176162719727</t>
+    <t xml:space="preserve">6.16734743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13845109939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083503723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98158359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05176115036011</t>
   </si>
   <si>
     <t xml:space="preserve">6.09717035293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18798780441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909147262573</t>
+    <t xml:space="preserve">6.18798685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909194946289</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001758575439</t>
@@ -896,40 +896,40 @@
     <t xml:space="preserve">5.9857120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0889139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87425422668457</t>
+    <t xml:space="preserve">6.08891439437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87425374984741</t>
   </si>
   <si>
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96094417572021</t>
+    <t xml:space="preserve">5.96094274520874</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22926902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200664520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207601547241</t>
+    <t xml:space="preserve">6.22926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200807571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207649230957</t>
   </si>
   <si>
     <t xml:space="preserve">6.88976144790649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85260772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958389282227</t>
+    <t xml:space="preserve">6.8526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958293914795</t>
   </si>
   <si>
     <t xml:space="preserve">6.89801597595215</t>
@@ -938,31 +938,31 @@
     <t xml:space="preserve">6.82371234893799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004718780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574022293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43979978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52648973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631313323975</t>
+    <t xml:space="preserve">6.75353479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004671096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574117660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43980073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52649021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631217956543</t>
   </si>
   <si>
     <t xml:space="preserve">6.57189893722534</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">6.71638202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6131796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53061771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684484481812</t>
+    <t xml:space="preserve">6.61318016052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684436798096</t>
   </si>
   <si>
     <t xml:space="preserve">6.44805669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65858840942383</t>
+    <t xml:space="preserve">6.65858745574951</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538654327393</t>
@@ -995,148 +995,148 @@
     <t xml:space="preserve">6.625563621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56777095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50585031509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7287654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84848022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75766277313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90214490890503</t>
+    <t xml:space="preserve">6.56777143478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50584936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5512580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6090521812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72876596450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84848070144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75766324996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90214538574219</t>
   </si>
   <si>
     <t xml:space="preserve">6.70812511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6874852180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7122540473938</t>
+    <t xml:space="preserve">6.68748617172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">6.77417469024658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43466758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705104827881</t>
+    <t xml:space="preserve">7.43466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705200195312</t>
   </si>
   <si>
     <t xml:space="preserve">7.47594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47181987762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932680130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7607855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334707260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619382858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893287658691</t>
+    <t xml:space="preserve">7.47181940078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356344223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480585098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.843346118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6617112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893430709839</t>
   </si>
   <si>
     <t xml:space="preserve">7.92590856552124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57915019989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28192806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40989923477173</t>
+    <t xml:space="preserve">7.57914972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28192758560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40989971160889</t>
   </si>
   <si>
     <t xml:space="preserve">7.28605651855469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13331699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413444519043</t>
+    <t xml:space="preserve">7.1333179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413492202759</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769285202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
+    <t xml:space="preserve">7.46769094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.38100147247314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33972120285034</t>
+    <t xml:space="preserve">7.33972215652466</t>
   </si>
   <si>
     <t xml:space="preserve">7.19936656951904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03011655807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01773118972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7948145866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335771560669</t>
+    <t xml:space="preserve">7.03011512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01773071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406698226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79481554031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335676193237</t>
   </si>
   <si>
     <t xml:space="preserve">6.79068756103516</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">7.19111061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07965230941772</t>
+    <t xml:space="preserve">7.07965278625488</t>
   </si>
   <si>
     <t xml:space="preserve">6.84022378921509</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">7.05075645446777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23652029037476</t>
+    <t xml:space="preserve">7.2365198135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.43053913116455</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">7.26128816604614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25715970993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036109924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2778000831604</t>
+    <t xml:space="preserve">7.25716018676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27779960632324</t>
   </si>
   <si>
     <t xml:space="preserve">8.2313871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12405586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41302108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789905548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17359256744385</t>
+    <t xml:space="preserve">8.12405681610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4130220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14056587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17359352111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.09103202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19836235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18185043334961</t>
+    <t xml:space="preserve">8.19836139678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18184852600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.20661640167236</t>
@@ -1217,64 +1217,64 @@
     <t xml:space="preserve">8.14469623565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1529541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20249080657959</t>
+    <t xml:space="preserve">8.15295219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522937774658</t>
+    <t xml:space="preserve">8.35522651672363</t>
   </si>
   <si>
     <t xml:space="preserve">8.36348533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33045959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47907066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52035140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79280471801758</t>
+    <t xml:space="preserve">8.33046054840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47907161712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52035236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79280376434326</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070461273193</t>
+    <t xml:space="preserve">8.71024417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82583045959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070556640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408451080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86711025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6689624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721843719482</t>
+    <t xml:space="preserve">8.86711120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65244960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721748352051</t>
   </si>
   <si>
     <t xml:space="preserve">8.42953300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67109107971191</t>
+    <t xml:space="preserve">8.67109203338623</t>
   </si>
   <si>
     <t xml:space="preserve">8.74605751037598</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">8.7044095993042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75438785552979</t>
+    <t xml:space="preserve">8.77104663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75438690185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.24628257751465</t>
@@ -1304,40 +1304,40 @@
     <t xml:space="preserve">8.55447769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8460111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8793306350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946681976318</t>
+    <t xml:space="preserve">8.84601211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87933158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946586608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82102394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50449848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111377716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47118091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45452117919922</t>
+    <t xml:space="preserve">8.81269454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82102298736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86267280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5044994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4711799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45452213287354</t>
   </si>
   <si>
     <t xml:space="preserve">8.25461292266846</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">8.49617004394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36289596557617</t>
+    <t xml:space="preserve">8.36289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.42120361328125</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.121337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142868041992</t>
+    <t xml:space="preserve">8.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639654159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142915725708</t>
   </si>
   <si>
     <t xml:space="preserve">7.78815650939941</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">8.02554893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062789916992</t>
+    <t xml:space="preserve">7.76733112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062837600708</t>
   </si>
   <si>
     <t xml:space="preserve">7.61323499679565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86312198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62573003768921</t>
+    <t xml:space="preserve">7.86312246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67154312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572860717773</t>
   </si>
   <si>
     <t xml:space="preserve">7.87145137786865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241056442261</t>
+    <t xml:space="preserve">7.721519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241104125977</t>
   </si>
   <si>
     <t xml:space="preserve">7.57158660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82980442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54659795761108</t>
+    <t xml:space="preserve">7.82980394363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54659843444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405847549438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84229707717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79232025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650812149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6882004737854</t>
+    <t xml:space="preserve">7.84229803085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.792320728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68819999694824</t>
   </si>
   <si>
     <t xml:space="preserve">7.44664287567139</t>
@@ -1457,37 +1457,37 @@
     <t xml:space="preserve">7.19259119033813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47163248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321229934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637241363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17131614685059</t>
+    <t xml:space="preserve">7.47163152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1713171005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.47951126098633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32957744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955760955811</t>
+    <t xml:space="preserve">8.3295783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23378849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955570220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.5294885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05425262451172</t>
+    <t xml:space="preserve">9.05425071716309</t>
   </si>
   <si>
     <t xml:space="preserve">8.99594593048096</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09589958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02093315124512</t>
+    <t xml:space="preserve">9.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09589862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02093410491943</t>
   </si>
   <si>
     <t xml:space="preserve">9.02926349639893</t>
@@ -1523,22 +1523,22 @@
     <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02138519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08385562896729</t>
+    <t xml:space="preserve">8.02138423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0838565826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.15049266815186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00055980682373</t>
+    <t xml:space="preserve">8.00056076049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.35456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98390054702759</t>
+    <t xml:space="preserve">7.98390102386475</t>
   </si>
   <si>
     <t xml:space="preserve">7.82563972473145</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">7.99223136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27127170562744</t>
+    <t xml:space="preserve">8.27127265930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.07969093322754</t>
@@ -1559,25 +1559,25 @@
     <t xml:space="preserve">8.53781890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46285343170166</t>
+    <t xml:space="preserve">8.46285057067871</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13799953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00472545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54243278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01721858978271</t>
+    <t xml:space="preserve">8.13799858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00472450256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54243326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01721954345703</t>
   </si>
   <si>
     <t xml:space="preserve">8.26294231414795</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">8.04220867156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19213962554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09634971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14216327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12550354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17964553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94641923904419</t>
+    <t xml:space="preserve">8.20046901702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19214057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09635066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14216232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12550449371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17964649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94641733169556</t>
   </si>
   <si>
     <t xml:space="preserve">8.2587776184082</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">7.97557163238525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89227533340454</t>
+    <t xml:space="preserve">7.8922758102417</t>
   </si>
   <si>
     <t xml:space="preserve">7.81730937957764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62989377975464</t>
+    <t xml:space="preserve">7.6298942565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.79648494720459</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22129344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541370391846</t>
+    <t xml:space="preserve">8.22129440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541275024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.21296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73772621154785</t>
+    <t xml:space="preserve">8.18381214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73772716522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.43786430358887</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">8.38788414001465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3712272644043</t>
+    <t xml:space="preserve">8.62944507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37122631072998</t>
   </si>
   <si>
     <t xml:space="preserve">8.51282978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69608116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768367767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77937602996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87100124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237964630127</t>
+    <t xml:space="preserve">8.69608020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77937507629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87100028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
     <t xml:space="preserve">9.37910556793213</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">9.56235599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59567546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54569625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39576435089111</t>
+    <t xml:space="preserve">9.59567451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54569721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39576530456543</t>
   </si>
   <si>
     <t xml:space="preserve">9.28747940063477</t>
@@ -1700,28 +1700,28 @@
     <t xml:space="preserve">9.29580974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65398216247559</t>
+    <t xml:space="preserve">9.6539831161499</t>
   </si>
   <si>
     <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35411739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66231060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0375919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22917366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27082061767578</t>
+    <t xml:space="preserve">9.35411643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66231250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03759384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.229172706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2708215713501</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
@@ -1730,49 +1730,49 @@
     <t xml:space="preserve">9.13754844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07091236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56280517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64610385894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592323303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06258106231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1042308807373</t>
+    <t xml:space="preserve">9.16253566741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0709114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56280612945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64610195159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06258201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10422897338867</t>
   </si>
   <si>
     <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91264915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83797168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65155029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376312255859</t>
+    <t xml:space="preserve">8.91264820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83797073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65155124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376407623291</t>
   </si>
   <si>
     <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223651885986</t>
+    <t xml:space="preserve">8.72781372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223747253418</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
@@ -1796,19 +1796,19 @@
     <t xml:space="preserve">8.490553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38039684295654</t>
+    <t xml:space="preserve">8.38039588928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.42700004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30413341522217</t>
+    <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.2617654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34226512908936</t>
+    <t xml:space="preserve">8.34226417541504</t>
   </si>
   <si>
     <t xml:space="preserve">8.39310646057129</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">8.27871322631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28718662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023983001709</t>
+    <t xml:space="preserve">8.28718566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023887634277</t>
   </si>
   <si>
     <t xml:space="preserve">8.2956600189209</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">8.19397640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75323581695557</t>
+    <t xml:space="preserve">8.75323486328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44394874572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3253173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45242118835449</t>
+    <t xml:space="preserve">8.32531929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">8.44818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60918426513672</t>
+    <t xml:space="preserve">8.60918235778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.62613105773926</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">8.57528877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2024507522583</t>
+    <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
     <t xml:space="preserve">8.35921192169189</t>
@@ -1892,58 +1892,58 @@
     <t xml:space="preserve">8.03297805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89740037918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13466167449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96518898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640203475952</t>
+    <t xml:space="preserve">7.89740085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13466262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9651894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90163660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995489120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961130142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.736403465271</t>
   </si>
   <si>
     <t xml:space="preserve">7.72792911529541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23634624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329303741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22787094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72369050979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6601390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71098232269287</t>
+    <t xml:space="preserve">8.2363452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329208374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22787189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66014003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">8.41429138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31684494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123722076416</t>
+    <t xml:space="preserve">8.31684398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123626708984</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
@@ -1970,127 +1970,127 @@
     <t xml:space="preserve">8.21939754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46513175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53292083740234</t>
+    <t xml:space="preserve">8.46513271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53291988372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.71934032440186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46936893463135</t>
+    <t xml:space="preserve">8.46936798095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01591682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8888111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13042449951172</t>
+    <t xml:space="preserve">9.01591777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88881206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13042545318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.22363471984863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18974018096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37192249298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49902534484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7617073059082</t>
+    <t xml:space="preserve">8.18973922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37192344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49902629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76170825958252</t>
   </si>
   <si>
     <t xml:space="preserve">8.81254959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60070896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697143554688</t>
+    <t xml:space="preserve">8.60070991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697238922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.85491847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02439022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28707122802734</t>
+    <t xml:space="preserve">9.02438926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28707218170166</t>
   </si>
   <si>
     <t xml:space="preserve">9.57517433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401802062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906887054443</t>
+    <t xml:space="preserve">9.47349166870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42264938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906982421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.65143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63449001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56670093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75312042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76159477233887</t>
+    <t xml:space="preserve">9.53280639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63449096679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56670188903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7531213760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76159381866455</t>
   </si>
   <si>
     <t xml:space="preserve">9.78701496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83785629272461</t>
+    <t xml:space="preserve">9.83785724639893</t>
   </si>
   <si>
     <t xml:space="preserve">9.871750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86327838897705</t>
+    <t xml:space="preserve">9.86327743530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.79548931121826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82090950012207</t>
+    <t xml:space="preserve">9.82091045379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.91411876678467</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0242748260498</t>
+    <t xml:space="preserve">10.0242757797241</t>
   </si>
   <si>
     <t xml:space="preserve">10.1344318389893</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">10.0835914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0158014297485</t>
+    <t xml:space="preserve">10.0158023834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.93953990936279</t>
@@ -2117,22 +2117,22 @@
     <t xml:space="preserve">10.0666437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1768016815186</t>
+    <t xml:space="preserve">10.1768007278442</t>
   </si>
   <si>
     <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2615356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530641555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1683263778687</t>
+    <t xml:space="preserve">10.1598539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2615365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.168327331543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1937475204468</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">10.0496959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82938289642334</t>
+    <t xml:space="preserve">9.82938385009766</t>
   </si>
   <si>
     <t xml:space="preserve">9.94801235198975</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">9.92259216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51586055755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581712722778</t>
+    <t xml:space="preserve">9.51585865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581703186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.73617267608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8463306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64296436309814</t>
+    <t xml:space="preserve">9.84632968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64296340942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.54975414276123</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16431999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01603221893311</t>
+    <t xml:space="preserve">8.16431903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01603031158447</t>
   </si>
   <si>
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153680801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99072456359863</t>
+    <t xml:space="preserve">7.70674467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60082387924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99072504043579</t>
   </si>
   <si>
     <t xml:space="preserve">6.71109628677368</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">5.6137638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52479124069214</t>
+    <t xml:space="preserve">5.52479076385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416318893433</t>
+    <t xml:space="preserve">5.08416366577148</t>
   </si>
   <si>
     <t xml:space="preserve">5.02484798431396</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647342681885</t>
+    <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">5.80865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50784397125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26210975646973</t>
+    <t xml:space="preserve">5.50784349441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26210927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690237045288</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">4.89774465560913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76216602325439</t>
+    <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481937408447</t>
@@ -2258,40 +2258,40 @@
     <t xml:space="preserve">5.41463375091553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1900839805603</t>
+    <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
     <t xml:space="preserve">5.20279359817505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01637506484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466283798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10111141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93163919448853</t>
+    <t xml:space="preserve">5.0163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10111093521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93163871765137</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129608154297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33837175369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73663139343262</t>
+    <t xml:space="preserve">5.33837223052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73663091659546</t>
   </si>
   <si>
     <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07557582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70273733139038</t>
+    <t xml:space="preserve">6.07557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
     <t xml:space="preserve">5.53326511383057</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">5.88068246841431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67731618881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87644577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81289434432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357818603516</t>
+    <t xml:space="preserve">5.6773157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87644529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81289386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357913970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">5.65189504623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015420913696</t>
+    <t xml:space="preserve">6.05015468597412</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03320741653442</t>
+    <t xml:space="preserve">6.03320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.35520458221436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29165267944336</t>
+    <t xml:space="preserve">6.29165172576904</t>
   </si>
   <si>
     <t xml:space="preserve">6.39333581924438</t>
@@ -2366,19 +2366,19 @@
     <t xml:space="preserve">7.24917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10088205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00343656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70685863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5755181312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71533250808716</t>
+    <t xml:space="preserve">7.10088157653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00343561172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70685911178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57551860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71533298492432</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64330720901489</t>
+    <t xml:space="preserve">6.64330673217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.55009746551514</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">6.60941219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33402061462402</t>
+    <t xml:space="preserve">6.33402013778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.3255467414856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18573236465454</t>
+    <t xml:space="preserve">6.1857328414917</t>
   </si>
   <si>
     <t xml:space="preserve">6.14760112762451</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">6.12641716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15183782577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01625967025757</t>
+    <t xml:space="preserve">6.1518383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.31707334518433</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2450475692749</t>
+    <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
     <t xml:space="preserve">6.47383451461792</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">6.47807121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27046871185303</t>
+    <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.06286478042603</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">6.22386360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336442947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08404922485352</t>
+    <t xml:space="preserve">6.14336490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08404874801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.95270824432373</t>
@@ -2483,61 +2483,61 @@
     <t xml:space="preserve">6.32978343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32131004333496</t>
+    <t xml:space="preserve">6.32131052017212</t>
   </si>
   <si>
     <t xml:space="preserve">6.23657417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19420528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25775766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2747049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.232337474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30859994888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37215137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483381271362</t>
+    <t xml:space="preserve">6.19420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27470588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23233699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3085994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37215185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.986487865448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29577398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97377729415894</t>
+    <t xml:space="preserve">7.16019678115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29577445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97377777099609</t>
   </si>
   <si>
     <t xml:space="preserve">6.73227977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75346374511719</t>
+    <t xml:space="preserve">6.75346326828003</t>
   </si>
   <si>
     <t xml:space="preserve">7.0161452293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90175247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85938405990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79583263397217</t>
+    <t xml:space="preserve">6.90175294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79583215713501</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">6.10946989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0543909072876</t>
+    <t xml:space="preserve">6.05439186096191</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168081283569</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">6.2153902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9484715461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09252262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0077862739563</t>
+    <t xml:space="preserve">5.94847106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09252309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00778675079346</t>
   </si>
   <si>
     <t xml:space="preserve">5.90610313415527</t>
@@ -2576,46 +2576,46 @@
     <t xml:space="preserve">5.57563257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49089670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60105323791504</t>
+    <t xml:space="preserve">5.4908971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787162780762</t>
+    <t xml:space="preserve">5.25787210464478</t>
   </si>
   <si>
     <t xml:space="preserve">5.28752994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06297922134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0587420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0121374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29176616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616035461426</t>
+    <t xml:space="preserve">5.06297969818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01213788986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29176664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616083145142</t>
   </si>
   <si>
     <t xml:space="preserve">5.43158149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76205158233643</t>
+    <t xml:space="preserve">5.76205205917358</t>
   </si>
   <si>
     <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831453323364</t>
+    <t xml:space="preserve">5.83831405639648</t>
   </si>
   <si>
     <t xml:space="preserve">6.93988275527954</t>
@@ -2624,79 +2624,79 @@
     <t xml:space="preserve">6.74075317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82125282287598</t>
+    <t xml:space="preserve">6.82125234603882</t>
   </si>
   <si>
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09653091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49914169311523</t>
+    <t xml:space="preserve">8.09652996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045406341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49914121627808</t>
   </si>
   <si>
     <t xml:space="preserve">7.45253658294678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62624406814575</t>
+    <t xml:space="preserve">7.62624454498291</t>
   </si>
   <si>
     <t xml:space="preserve">7.55845642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62200832366943</t>
+    <t xml:space="preserve">7.62200784683228</t>
   </si>
   <si>
     <t xml:space="preserve">7.77453374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7702956199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079622268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87198066711426</t>
+    <t xml:space="preserve">7.77029657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8719801902771</t>
   </si>
   <si>
     <t xml:space="preserve">7.84232234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67284917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63471937179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91010999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8253755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85503387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68556070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52456283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47795724868774</t>
+    <t xml:space="preserve">7.67285013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6347188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011095046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82537412643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85503339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68555974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5245623588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4779577255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.5881142616272</t>
@@ -2705,82 +2705,82 @@
     <t xml:space="preserve">7.56693029403687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41016817092896</t>
+    <t xml:space="preserve">7.4101676940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.28730201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22374868392944</t>
+    <t xml:space="preserve">7.22374820709229</t>
   </si>
   <si>
     <t xml:space="preserve">7.32543277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3169584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985462188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0627498626709</t>
+    <t xml:space="preserve">7.31695890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985414505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06275081634521</t>
   </si>
   <si>
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15596008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911308288574</t>
+    <t xml:space="preserve">7.15595960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63895606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74911212921143</t>
   </si>
   <si>
     <t xml:space="preserve">7.53727293014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85926914215088</t>
+    <t xml:space="preserve">7.85926866531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.21516036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2321081161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18550300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20668792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30836963653564</t>
+    <t xml:space="preserve">8.23210906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18550395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30837059020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.14313507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79148054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65166568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0372142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92282295227051</t>
+    <t xml:space="preserve">7.79147958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65166616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03721523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92282199859619</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033866882324</t>
+    <t xml:space="preserve">8.88033771514893</t>
   </si>
   <si>
     <t xml:space="preserve">8.63460445404053</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">8.0075569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3973445892334</t>
+    <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965435028076</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">9.16844081878662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20233535766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55822658538818</t>
+    <t xml:space="preserve">9.20233631134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55822849273682</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928310394287</t>
+    <t xml:space="preserve">9.04133892059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.04981136322021</t>
@@ -2837,37 +2837,37 @@
     <t xml:space="preserve">9.44806957244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196411132812</t>
+    <t xml:space="preserve">9.48196506500244</t>
   </si>
   <si>
     <t xml:space="preserve">9.69380474090576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0412225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74464702606201</t>
+    <t xml:space="preserve">10.0412216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74464797973633</t>
   </si>
   <si>
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43112277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02747917175293</t>
+    <t xml:space="preserve">9.52433300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43112373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02747821807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03613376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91496086120605</t>
+    <t xml:space="preserve">9.03613471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91495990753174</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">9.08806610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2092399597168</t>
+    <t xml:space="preserve">9.20924091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386119842529</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">9.33906841278076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43427658081055</t>
+    <t xml:space="preserve">9.43427753448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.63334941864014</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40831184387207</t>
+    <t xml:space="preserve">9.40831279754639</t>
   </si>
   <si>
     <t xml:space="preserve">9.47755527496338</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1140308380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04478931427002</t>
+    <t xml:space="preserve">9.21789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11403179168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26117134094238</t>
+    <t xml:space="preserve">9.2611722946167</t>
   </si>
   <si>
     <t xml:space="preserve">9.51217555999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46889877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2698278427124</t>
+    <t xml:space="preserve">9.46889781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26982688903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.31310367584229</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">9.33041477203369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30444812774658</t>
+    <t xml:space="preserve">9.3044490814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.3477258682251</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.00151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75916385650635</t>
+    <t xml:space="preserve">8.75916481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840633392334</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">9.20058536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36503505706787</t>
+    <t xml:space="preserve">9.36503601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.41696739196777</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">9.1746187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94958019256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83706092834473</t>
+    <t xml:space="preserve">8.94958114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83706188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">8.84571838378906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86302757263184</t>
+    <t xml:space="preserve">8.86302852630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.78512954711914</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">8.72454357147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63798999786377</t>
+    <t xml:space="preserve">8.63798904418945</t>
   </si>
   <si>
     <t xml:space="preserve">8.68126583099365</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26581287384033</t>
+    <t xml:space="preserve">8.26581192016602</t>
   </si>
   <si>
     <t xml:space="preserve">8.19656944274902</t>
@@ -3050,31 +3050,31 @@
     <t xml:space="preserve">8.74185466766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4389181137085</t>
+    <t xml:space="preserve">8.43891716003418</t>
   </si>
   <si>
     <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42160701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3610200881958</t>
+    <t xml:space="preserve">8.42160797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36102104187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67261219024658</t>
+    <t xml:space="preserve">8.63366317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67261123657227</t>
   </si>
   <si>
     <t xml:space="preserve">8.62933540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202335357666</t>
+    <t xml:space="preserve">8.61202430725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.59904193878174</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">8.50383281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54278182983398</t>
+    <t xml:space="preserve">8.54278087615967</t>
   </si>
   <si>
     <t xml:space="preserve">8.58605766296387</t>
@@ -3098,37 +3098,37 @@
     <t xml:space="preserve">7.92825603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85901308059692</t>
+    <t xml:space="preserve">7.85901355743408</t>
   </si>
   <si>
     <t xml:space="preserve">7.9369101524353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87632465362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749851226807</t>
+    <t xml:space="preserve">7.87632417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749755859375</t>
   </si>
   <si>
     <t xml:space="preserve">7.96287679672241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91959953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95854902267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96720409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128612518311</t>
+    <t xml:space="preserve">7.91960000991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9585485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96720457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82439184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128660202026</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011178970337</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">7.3310399055481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15360736846924</t>
+    <t xml:space="preserve">7.15360689163208</t>
   </si>
   <si>
     <t xml:space="preserve">7.06272554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20121049880981</t>
+    <t xml:space="preserve">7.14927911758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20121097564697</t>
   </si>
   <si>
     <t xml:space="preserve">7.27045249938965</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">7.24448728561401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40461015701294</t>
+    <t xml:space="preserve">7.40460968017578</t>
   </si>
   <si>
     <t xml:space="preserve">7.45654153823853</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">7.3180570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41759300231934</t>
+    <t xml:space="preserve">7.41759252548218</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36566114425659</t>
+    <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
     <t xml:space="preserve">7.34402275085449</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">7.02377653121948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01944875717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88961982727051</t>
+    <t xml:space="preserve">7.01944828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88961935043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.91991281509399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8809642791748</t>
+    <t xml:space="preserve">6.88096380233765</t>
   </si>
   <si>
     <t xml:space="preserve">6.66458177566528</t>
@@ -3275,19 +3275,19 @@
     <t xml:space="preserve">6.49147605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36164569854736</t>
+    <t xml:space="preserve">6.36164617538452</t>
   </si>
   <si>
     <t xml:space="preserve">6.47849321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43088865280151</t>
+    <t xml:space="preserve">6.43088817596436</t>
   </si>
   <si>
     <t xml:space="preserve">6.56937313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44387197494507</t>
+    <t xml:space="preserve">6.44387149810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.55639028549194</t>
@@ -3299,25 +3299,25 @@
     <t xml:space="preserve">6.5650463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49580335617065</t>
+    <t xml:space="preserve">6.4958028793335</t>
   </si>
   <si>
     <t xml:space="preserve">6.21883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21450614929199</t>
+    <t xml:space="preserve">6.21450662612915</t>
   </si>
   <si>
     <t xml:space="preserve">6.10198736190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88560438156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2015233039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11497020721436</t>
+    <t xml:space="preserve">5.88560485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20152282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">6.05005502700806</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53506469726562</t>
+    <t xml:space="preserve">5.55237483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53506517410278</t>
   </si>
   <si>
     <t xml:space="preserve">5.89425945281982</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8509840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7341365814209</t>
+    <t xml:space="preserve">5.85098361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73413705825806</t>
   </si>
   <si>
     <t xml:space="preserve">6.05438280105591</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99812316894531</t>
+    <t xml:space="preserve">5.99812364578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.1539192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11064195632935</t>
+    <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.14526319503784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18421220779419</t>
+    <t xml:space="preserve">6.18421268463135</t>
   </si>
   <si>
     <t xml:space="preserve">6.34000778198242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19286775588989</t>
+    <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
     <t xml:space="preserve">6.12362480163574</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">6.26211023330688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30105924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45685434341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24479961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11929750442505</t>
+    <t xml:space="preserve">6.30105876922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45685482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24479913711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
     <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51744222640991</t>
+    <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
     <t xml:space="preserve">6.34433555603027</t>
@@ -68297,13 +68297,13 @@
     </row>
     <row r="2407">
       <c r="A2407" s="1" t="n">
-        <v>45946.6495833333</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2407" t="n">
         <v>241824</v>
       </c>
       <c r="C2407" t="n">
-        <v>14</v>
+        <v>14.039999961853</v>
       </c>
       <c r="D2407" t="n">
         <v>13.8199996948242</v>
@@ -68318,6 +68318,32 @@
         <v>1796</v>
       </c>
       <c r="H2407" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="1" t="n">
+        <v>45947.6493865741</v>
+      </c>
+      <c r="B2408" t="n">
+        <v>224746</v>
+      </c>
+      <c r="C2408" t="n">
+        <v>14.1400003433228</v>
+      </c>
+      <c r="D2408" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E2408" t="n">
+        <v>14.1400003433228</v>
+      </c>
+      <c r="F2408" t="n">
+        <v>13.9799995422363</v>
+      </c>
+      <c r="G2408" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H2408" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1798">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13859987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12388014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588908195496</t>
+    <t xml:space="preserve">3.13860034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12387990951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
     <t xml:space="preserve">3.06663632392883</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">3.06500053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05028128623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930172920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16476821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17131090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16149735450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205742835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822625160217</t>
+    <t xml:space="preserve">3.05028080940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476845741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17131066322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16149759292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822601318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.14514207839966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15168404579163</t>
+    <t xml:space="preserve">3.15168428421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.30051803588867</t>
@@ -95,49 +95,49 @@
     <t xml:space="preserve">3.43463253974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.437903881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39374423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393044471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977174758911</t>
+    <t xml:space="preserve">3.43790364265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39374446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393092155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977150917053</t>
   </si>
   <si>
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841341972351</t>
+    <t xml:space="preserve">3.14841318130493</t>
   </si>
   <si>
     <t xml:space="preserve">3.0306544303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17294669151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752463340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18112397193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257283210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19911527633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03392601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
+    <t xml:space="preserve">3.08789849281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17294645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752439498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18112421035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19911503791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0339252948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303722381592</t>
   </si>
   <si>
     <t xml:space="preserve">3.04373860359192</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">3.12878656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23019027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23346138000488</t>
+    <t xml:space="preserve">3.23019051551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2334611415863</t>
   </si>
   <si>
     <t xml:space="preserve">3.2252836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1140673160553</t>
+    <t xml:space="preserve">3.11406683921814</t>
   </si>
   <si>
     <t xml:space="preserve">3.14023566246033</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">3.0911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897349357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425353050232</t>
+    <t xml:space="preserve">3.0829918384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897325515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135581016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1042537689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.07481384277344</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369640827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383476257324</t>
+    <t xml:space="preserve">3.13696432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383452415466</t>
   </si>
   <si>
     <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10915994644165</t>
+    <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.36921095848083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42645502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5098671913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5164098739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54094290733337</t>
+    <t xml:space="preserve">3.42645454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51640963554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54094243049622</t>
   </si>
   <si>
     <t xml:space="preserve">3.50168967247009</t>
@@ -218,22 +218,22 @@
     <t xml:space="preserve">3.47552084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35612678527832</t>
+    <t xml:space="preserve">3.35612654685974</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724717140198</t>
+    <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
     <t xml:space="preserve">3.36103343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3757529258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738823890686</t>
+    <t xml:space="preserve">3.37575268745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
     <t xml:space="preserve">3.35285568237305</t>
@@ -254,73 +254,73 @@
     <t xml:space="preserve">3.4673433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4869692325592</t>
+    <t xml:space="preserve">3.48697018623352</t>
   </si>
   <si>
     <t xml:space="preserve">3.44281029701233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337037086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4591658115387</t>
+    <t xml:space="preserve">3.3970148563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337084770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48860502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916604995728</t>
   </si>
   <si>
     <t xml:space="preserve">3.41827726364136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50823187828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729842185974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57856011390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59818696975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907504081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360807418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6799635887146</t>
+    <t xml:space="preserve">3.50823211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729746818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57856059074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472822189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547522544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5981867313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360831260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725279808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996311187744</t>
   </si>
   <si>
     <t xml:space="preserve">3.67178559303284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60636377334595</t>
+    <t xml:space="preserve">3.60636401176453</t>
   </si>
   <si>
     <t xml:space="preserve">3.5671112537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4689793586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355753898621</t>
+    <t xml:space="preserve">3.46897912025452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355777740479</t>
   </si>
   <si>
     <t xml:space="preserve">3.38065958023071</t>
@@ -341,112 +341,112 @@
     <t xml:space="preserve">3.24327445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21874165534973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25963020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1549551486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07644963264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12551546096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27107834815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3348650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757516860962</t>
+    <t xml:space="preserve">3.21874141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962996482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07644939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462738990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1255156993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27107906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486485481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36757564544678</t>
   </si>
   <si>
     <t xml:space="preserve">3.4084644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30869626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48206281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421424865723</t>
+    <t xml:space="preserve">3.30869603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818062782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033158302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48206305503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421401023865</t>
   </si>
   <si>
     <t xml:space="preserve">3.61454176902771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309290885925</t>
+    <t xml:space="preserve">3.59655022621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528901100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183121681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309338569641</t>
   </si>
   <si>
     <t xml:space="preserve">3.66851449012756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6407105922699</t>
+    <t xml:space="preserve">3.64071106910706</t>
   </si>
   <si>
     <t xml:space="preserve">3.61617684364319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62435531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7519268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7617404460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809548377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77645993232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.791179895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720717430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730333328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79445123672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071621894836</t>
+    <t xml:space="preserve">3.62435507774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75192737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809572219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646040916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720693588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071669578552</t>
   </si>
   <si>
     <t xml:space="preserve">3.91548085212708</t>
@@ -455,85 +455,85 @@
     <t xml:space="preserve">3.86314368247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8925838470459</t>
+    <t xml:space="preserve">3.89258360862732</t>
   </si>
   <si>
     <t xml:space="preserve">3.92529487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88440561294556</t>
+    <t xml:space="preserve">3.88440632820129</t>
   </si>
   <si>
     <t xml:space="preserve">3.86641526222229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94655656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150908470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454691886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.043053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618342399597</t>
+    <t xml:space="preserve">3.94655680656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150813102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9645471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169458389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618318557739</t>
   </si>
   <si>
     <t xml:space="preserve">3.88767719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86968588829041</t>
+    <t xml:space="preserve">3.86968636512756</t>
   </si>
   <si>
     <t xml:space="preserve">3.8189845085144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9138457775116</t>
+    <t xml:space="preserve">3.91384530067444</t>
   </si>
   <si>
     <t xml:space="preserve">3.941650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02669763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9939866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272443771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00216484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0561375617981</t>
+    <t xml:space="preserve">4.02669811248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398684501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9727246761322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00216436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05613708496094</t>
   </si>
   <si>
     <t xml:space="preserve">3.97926712036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00707149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0839409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16244745254517</t>
+    <t xml:space="preserve">4.00707101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08394145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16244792938232</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.33009004592896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37506723403931</t>
+    <t xml:space="preserve">4.37506771087646</t>
   </si>
   <si>
     <t xml:space="preserve">4.59586524963379</t>
@@ -557,61 +557,61 @@
     <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78804111480713</t>
+    <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
     <t xml:space="preserve">4.99248361587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80439710617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710718154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83301877975464</t>
+    <t xml:space="preserve">4.8043966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83301830291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.90661764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96386241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03337287902832</t>
+    <t xml:space="preserve">4.9638614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928304672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.033371925354</t>
   </si>
   <si>
     <t xml:space="preserve">5.19283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13150501251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688097000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3686580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56492280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56901121139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55265617370605</t>
+    <t xml:space="preserve">5.13150453567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2868800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36865758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56492233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56901073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5526556968689</t>
   </si>
   <si>
     <t xml:space="preserve">5.30323600769043</t>
@@ -623,106 +623,106 @@
     <t xml:space="preserve">5.54856729507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59354496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60172176361084</t>
+    <t xml:space="preserve">5.59354400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
     <t xml:space="preserve">5.70803260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75709819793701</t>
+    <t xml:space="preserve">5.75709867477417</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82252025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4872350692749</t>
+    <t xml:space="preserve">5.82251977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114240646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78572034835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47905731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48723411560059</t>
   </si>
   <si>
     <t xml:space="preserve">5.46678972244263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60581111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083393096924</t>
+    <t xml:space="preserve">5.60581159591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083345413208</t>
   </si>
   <si>
     <t xml:space="preserve">5.64308166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69674730300903</t>
+    <t xml:space="preserve">5.69674634933472</t>
   </si>
   <si>
     <t xml:space="preserve">5.4614462852478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290410995483</t>
+    <t xml:space="preserve">5.57290458679199</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546560287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70500230789185</t>
+    <t xml:space="preserve">5.705002784729</t>
   </si>
   <si>
     <t xml:space="preserve">5.73802709579468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8040771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84948539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10129880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84122896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471656799316</t>
+    <t xml:space="preserve">5.78756475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84948492050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10129833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84122943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471704483032</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389863967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7586669921875</t>
+    <t xml:space="preserve">5.73389911651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866746902466</t>
   </si>
   <si>
     <t xml:space="preserve">5.65133714675903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81233215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77930784225464</t>
+    <t xml:space="preserve">5.81233310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77930736541748</t>
   </si>
   <si>
     <t xml:space="preserve">5.77105140686035</t>
@@ -731,55 +731,55 @@
     <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68848991394043</t>
+    <t xml:space="preserve">5.68849086761475</t>
   </si>
   <si>
     <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069772720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57703256607056</t>
+    <t xml:space="preserve">5.63069820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5770320892334</t>
   </si>
   <si>
     <t xml:space="preserve">5.52336740493774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54813575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639123916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934713363647</t>
+    <t xml:space="preserve">5.54813528060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162384033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934808731079</t>
   </si>
   <si>
     <t xml:space="preserve">5.27568244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30045080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294435501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1931209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230302810669</t>
+    <t xml:space="preserve">5.16009664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771318435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30045127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
@@ -791,43 +791,43 @@
     <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39952516555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74628305435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041246414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325874328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77518081665039</t>
+    <t xml:space="preserve">5.39952564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74628353118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041151046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325969696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77517986297607</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012672424316</t>
+    <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.86599779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94443082809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89489412307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0476336479187</t>
+    <t xml:space="preserve">5.94443130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04763221740723</t>
   </si>
   <si>
     <t xml:space="preserve">5.93204641342163</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">5.86186981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827306747437</t>
+    <t xml:space="preserve">5.95268726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827354431152</t>
   </si>
   <si>
     <t xml:space="preserve">6.10955429077148</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19211626052856</t>
+    <t xml:space="preserve">6.17973136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19211578369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12193822860718</t>
+    <t xml:space="preserve">6.18385982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12193870544434</t>
   </si>
   <si>
     <t xml:space="preserve">6.16734743118286</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">6.13845109939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15083503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98158359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05176115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09717035293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909194946289</t>
+    <t xml:space="preserve">6.15083456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98158407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05176162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09717082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909099578857</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001758575439</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">5.9857120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08891439437866</t>
+    <t xml:space="preserve">6.0889139175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140651702881</t>
@@ -911,40 +911,40 @@
     <t xml:space="preserve">5.96094274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00222396850586</t>
+    <t xml:space="preserve">6.00222444534302</t>
   </si>
   <si>
     <t xml:space="preserve">6.22926807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38200807571411</t>
+    <t xml:space="preserve">6.38200712203979</t>
   </si>
   <si>
     <t xml:space="preserve">6.64207649230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88976144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8526086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801597595215</t>
+    <t xml:space="preserve">6.88976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85260915756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801645278931</t>
   </si>
   <si>
     <t xml:space="preserve">6.82371234893799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75353479385376</t>
+    <t xml:space="preserve">6.75353527069092</t>
   </si>
   <si>
     <t xml:space="preserve">6.77004671096802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60492324829102</t>
+    <t xml:space="preserve">6.60492420196533</t>
   </si>
   <si>
     <t xml:space="preserve">6.69574117660522</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">6.58015537261963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44392776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43980073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52649021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631217956543</t>
+    <t xml:space="preserve">6.44392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43980121612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52649068832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631265640259</t>
   </si>
   <si>
     <t xml:space="preserve">6.57189893722534</t>
@@ -971,61 +971,61 @@
     <t xml:space="preserve">6.65446090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71638202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61318016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53061866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44805669784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65858745574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55538654327393</t>
+    <t xml:space="preserve">6.71638154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6131796836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53061819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4480562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65858793258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55538749694824</t>
   </si>
   <si>
     <t xml:space="preserve">6.625563621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56777143478394</t>
+    <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.50584936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5512580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6090521812439</t>
+    <t xml:space="preserve">6.55125856399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905170440674</t>
   </si>
   <si>
     <t xml:space="preserve">6.72876596450806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84848070144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75766324996948</t>
+    <t xml:space="preserve">6.84848022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75766277313232</t>
   </si>
   <si>
     <t xml:space="preserve">6.90214538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748617172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71225357055664</t>
+    <t xml:space="preserve">6.70812559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6874852180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7122540473938</t>
   </si>
   <si>
     <t xml:space="preserve">6.77417469024658</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">7.44705200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47594738006592</t>
+    <t xml:space="preserve">7.47594833374023</t>
   </si>
   <si>
     <t xml:space="preserve">7.47181940078735</t>
@@ -1049,172 +1049,172 @@
     <t xml:space="preserve">7.64932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95480585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.843346118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6617112159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665664672852</t>
+    <t xml:space="preserve">7.95480442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7607855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665712356567</t>
   </si>
   <si>
     <t xml:space="preserve">7.95893430709839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92590856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57914972305298</t>
+    <t xml:space="preserve">7.9259090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915067672729</t>
   </si>
   <si>
     <t xml:space="preserve">7.28192758560181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40989971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1333179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413492202759</t>
+    <t xml:space="preserve">7.40989923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605604171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331747055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769094467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38100147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33972215652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19936656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011512756348</t>
+    <t xml:space="preserve">7.46769189834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3810019493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3397216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011560440063</t>
   </si>
   <si>
     <t xml:space="preserve">7.01773071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05488443374634</t>
+    <t xml:space="preserve">7.0548849105835</t>
   </si>
   <si>
     <t xml:space="preserve">6.96406698226929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79481554031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335676193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79068756103516</t>
+    <t xml:space="preserve">6.7948145866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79068803787231</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111061096191</t>
+    <t xml:space="preserve">7.19111108779907</t>
   </si>
   <si>
     <t xml:space="preserve">7.07965278625488</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84022378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05075645446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2365198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25716018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036157608032</t>
+    <t xml:space="preserve">6.84022426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05075597763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23652029037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669641494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2571587562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036205291748</t>
   </si>
   <si>
     <t xml:space="preserve">7.27779960632324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2313871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12405681610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4130220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17359352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09103202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19836139678955</t>
+    <t xml:space="preserve">8.23138618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12405586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41302108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1405668258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17359256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09103107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19836235046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.18184852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20661640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14469623565674</t>
+    <t xml:space="preserve">8.20661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14469718933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.15295219421387</t>
@@ -1223,46 +1223,46 @@
     <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430183410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33046054840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47907161712646</t>
+    <t xml:space="preserve">8.45430088043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348438262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33045864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.52035236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71024417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82583045959473</t>
+    <t xml:space="preserve">8.79280281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582950592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.66070556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83408451080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86711120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896152496338</t>
+    <t xml:space="preserve">8.83408546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86710929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896343231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.65244960784912</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">8.67721748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42953300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67109203338623</t>
+    <t xml:space="preserve">8.42953395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.74605751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7044095993042</t>
+    <t xml:space="preserve">8.70440864562988</t>
   </si>
   <si>
     <t xml:space="preserve">8.77104663848877</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">8.30875492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3462381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41287422180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55447769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87933158874512</t>
+    <t xml:space="preserve">8.34623718261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41287517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55447864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946586608887</t>
@@ -1319,91 +1319,91 @@
     <t xml:space="preserve">8.81269454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82102298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86267280578613</t>
+    <t xml:space="preserve">8.82102394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86267185211182</t>
   </si>
   <si>
     <t xml:space="preserve">8.72939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5044994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4711799621582</t>
+    <t xml:space="preserve">8.50450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111377716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47118091583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.45452213287354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25461292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58779621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49617004394531</t>
+    <t xml:space="preserve">8.25461387634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58779716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.496169090271</t>
   </si>
   <si>
     <t xml:space="preserve">8.36289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42120361328125</t>
+    <t xml:space="preserve">8.42120265960693</t>
   </si>
   <si>
     <t xml:space="preserve">8.21712875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59612464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63777351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16298770904541</t>
+    <t xml:space="preserve">8.08802032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59612560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63777256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16298675537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.12133884429932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99639654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142915725708</t>
+    <t xml:space="preserve">7.99639511108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.78815650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02554893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062837600708</t>
+    <t xml:space="preserve">8.02554988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062789916992</t>
   </si>
   <si>
     <t xml:space="preserve">7.61323499679565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86312246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234390258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572860717773</t>
+    <t xml:space="preserve">7.86312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572908401489</t>
   </si>
   <si>
     <t xml:space="preserve">7.87145137786865</t>
@@ -1415,67 +1415,67 @@
     <t xml:space="preserve">7.59241104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57158660888672</t>
+    <t xml:space="preserve">7.57158756256104</t>
   </si>
   <si>
     <t xml:space="preserve">7.82980394363403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63405847549438</t>
+    <t xml:space="preserve">7.54659795761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405799865723</t>
   </si>
   <si>
     <t xml:space="preserve">7.84229803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.792320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61739921569824</t>
+    <t xml:space="preserve">7.79232120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61740016937256</t>
   </si>
   <si>
     <t xml:space="preserve">7.71319007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74650859832764</t>
+    <t xml:space="preserve">7.74650812149048</t>
   </si>
   <si>
     <t xml:space="preserve">7.68819999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44664287567139</t>
+    <t xml:space="preserve">7.44664239883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.28838109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14677810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259119033813</t>
+    <t xml:space="preserve">7.14677858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259166717529</t>
   </si>
   <si>
     <t xml:space="preserve">7.47163152694702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66321182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637336730957</t>
+    <t xml:space="preserve">7.66321229934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637241363525</t>
   </si>
   <si>
     <t xml:space="preserve">8.1713171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3295783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463466644287</t>
+    <t xml:space="preserve">8.47951221466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
     <t xml:space="preserve">8.23378849029541</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">8.5294885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05425071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99594593048096</t>
+    <t xml:space="preserve">9.0542516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99594497680664</t>
   </si>
   <si>
     <t xml:space="preserve">9.01260375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00427532196045</t>
+    <t xml:space="preserve">9.00427436828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07923984527588</t>
@@ -1508,76 +1508,76 @@
     <t xml:space="preserve">9.11255836486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09589862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02093410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02926349639893</t>
+    <t xml:space="preserve">9.0959005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02093315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02926254272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02138423919678</t>
+    <t xml:space="preserve">8.57113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02138328552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.0838565826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15049266815186</t>
+    <t xml:space="preserve">8.15049171447754</t>
   </si>
   <si>
     <t xml:space="preserve">8.00056076049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35456657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98390102386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82563972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99223136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27127265930176</t>
+    <t xml:space="preserve">8.354567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98390007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9922308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.07969093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28376483917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46285057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60445499420166</t>
+    <t xml:space="preserve">8.28376579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53781795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46285152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60445308685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.13799858093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07552623748779</t>
+    <t xml:space="preserve">8.07552719116211</t>
   </si>
   <si>
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01721954345703</t>
+    <t xml:space="preserve">7.5424337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01721858978271</t>
   </si>
   <si>
     <t xml:space="preserve">8.26294231414795</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">8.04220867156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20046901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19214057922363</t>
+    <t xml:space="preserve">8.20046997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19214153289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.09635066986084</t>
@@ -1604,88 +1604,88 @@
     <t xml:space="preserve">8.17964649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94641733169556</t>
+    <t xml:space="preserve">7.94641780853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.2587776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8922758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81730937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6298942565918</t>
+    <t xml:space="preserve">7.9755711555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227628707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81730985641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989473342896</t>
   </si>
   <si>
     <t xml:space="preserve">7.79648494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75483798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541275024414</t>
+    <t xml:space="preserve">7.75483846664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.21296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630527496338</t>
+    <t xml:space="preserve">8.18381023406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1963062286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.22962474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73772716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38788414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62944507598877</t>
+    <t xml:space="preserve">8.73772811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43786334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62944221496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.37122631072998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51282978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77937507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87100028991699</t>
+    <t xml:space="preserve">8.51283073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77937602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87100219726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37910556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56235599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567451477051</t>
+    <t xml:space="preserve">9.37910461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56235504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567546844482</t>
   </si>
   <si>
     <t xml:space="preserve">9.54569721221924</t>
@@ -1694,85 +1694,85 @@
     <t xml:space="preserve">9.39576530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28747940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29580974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539831161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49571895599365</t>
+    <t xml:space="preserve">9.28748035430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29580879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65398216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03759384155273</t>
+    <t xml:space="preserve">9.66231155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.229172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2708215713501</t>
+    <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16253566741943</t>
+    <t xml:space="preserve">9.13754940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16253757476807</t>
   </si>
   <si>
     <t xml:space="preserve">9.0709114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56280612945557</t>
+    <t xml:space="preserve">8.56280708312988</t>
   </si>
   <si>
     <t xml:space="preserve">8.64610195159912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592227935791</t>
+    <t xml:space="preserve">9.04592132568359</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10422897338867</t>
+    <t xml:space="preserve">9.10422992706299</t>
   </si>
   <si>
     <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91264820098877</t>
+    <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.83797073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376407623291</t>
+    <t xml:space="preserve">8.65155029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376312255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223747253418</t>
+    <t xml:space="preserve">8.72781467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2617654800415</t>
+    <t xml:space="preserve">8.26176452636719</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226417541504</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">8.31260776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27871322631836</t>
+    <t xml:space="preserve">8.27871417999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.28718566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023887634277</t>
+    <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2956600189209</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500335693359</t>
+    <t xml:space="preserve">8.10500240325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397640228271</t>
@@ -1844,22 +1844,22 @@
     <t xml:space="preserve">8.75323486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32531929016113</t>
+    <t xml:space="preserve">8.44394779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32531833648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43971157073975</t>
+    <t xml:space="preserve">8.43971061706543</t>
   </si>
   <si>
     <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849803924561</t>
+    <t xml:space="preserve">8.66849899291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">8.44818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60918235778809</t>
+    <t xml:space="preserve">8.6091833114624</t>
   </si>
   <si>
     <t xml:space="preserve">8.62613105773926</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35921192169189</t>
+    <t xml:space="preserve">8.35921096801758</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727933883667</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">8.13466262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9651894569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995489120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.736403465271</t>
+    <t xml:space="preserve">7.96519041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9016375541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640251159668</t>
   </si>
   <si>
     <t xml:space="preserve">7.72792911529541</t>
@@ -1925,37 +1925,37 @@
     <t xml:space="preserve">8.22787189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72369194030762</t>
+    <t xml:space="preserve">7.7236909866333</t>
   </si>
   <si>
     <t xml:space="preserve">7.95671606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82113695144653</t>
+    <t xml:space="preserve">7.82113790512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.71945381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66014003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71098184585571</t>
+    <t xml:space="preserve">7.57540273666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6601390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71098279953003</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41429138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123626708984</t>
+    <t xml:space="preserve">8.41429233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684494018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53291988372803</t>
+    <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.71934032440186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46936798095703</t>
+    <t xml:space="preserve">8.46936893463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">9.01591777801514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575981140137</t>
+    <t xml:space="preserve">8.8888111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575885772705</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270755767822</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">8.60070991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54139423370361</t>
+    <t xml:space="preserve">8.54139518737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.69392013549805</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">8.67697238922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85491847991943</t>
+    <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02438926696777</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">9.42264938354492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3040189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906982421875</t>
+    <t xml:space="preserve">9.30401802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906887054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.65143775939941</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">9.53280639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63449096679688</t>
+    <t xml:space="preserve">9.63449001312256</t>
   </si>
   <si>
     <t xml:space="preserve">9.56670188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7531213760376</t>
+    <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159381866455</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">9.871750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86327743530273</t>
+    <t xml:space="preserve">9.86327648162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.79548931121826</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">9.82091045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91411876678467</t>
+    <t xml:space="preserve">9.91411972045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0242757797241</t>
+    <t xml:space="preserve">10.0242748260498</t>
   </si>
   <si>
     <t xml:space="preserve">10.1344318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0835914611816</t>
+    <t xml:space="preserve">10.0835905075073</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158023834229</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598539352417</t>
+    <t xml:space="preserve">10.1598529815674</t>
   </si>
   <si>
     <t xml:space="preserve">10.2615365982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2530632019043</t>
+    <t xml:space="preserve">10.2530641555786</t>
   </si>
   <si>
     <t xml:space="preserve">10.168327331543</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">10.0496959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82938385009766</t>
+    <t xml:space="preserve">9.82938289642334</t>
   </si>
   <si>
     <t xml:space="preserve">9.94801235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.998854637146</t>
+    <t xml:space="preserve">9.99885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.92259216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51585865020752</t>
+    <t xml:space="preserve">9.51585960388184</t>
   </si>
   <si>
     <t xml:space="preserve">10.0581703186035</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296340942383</t>
+    <t xml:space="preserve">9.64296436309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.54975414276123</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">8.32108116149902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01603031158447</t>
+    <t xml:space="preserve">8.01603126525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.00332069396973</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">7.70674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60082387924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322137832642</t>
+    <t xml:space="preserve">7.6008243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322090148926</t>
   </si>
   <si>
     <t xml:space="preserve">7.29153728485107</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">6.99072504043579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71109628677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61364936828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6137638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52479076385498</t>
+    <t xml:space="preserve">6.71109580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61364889144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61376428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52479124069214</t>
   </si>
   <si>
     <t xml:space="preserve">4.98248052597046</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647438049316</t>
+    <t xml:space="preserve">5.62647390365601</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">5.50784349441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210927963257</t>
+    <t xml:space="preserve">5.26210975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690237045288</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27481937408447</t>
+    <t xml:space="preserve">5.27481889724731</t>
   </si>
   <si>
     <t xml:space="preserve">5.41463375091553</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">5.20279359817505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0163745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466236114502</t>
+    <t xml:space="preserve">5.01637506484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466283798218</t>
   </si>
   <si>
     <t xml:space="preserve">5.10111093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93163871765137</t>
+    <t xml:space="preserve">4.93163824081421</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129608154297</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70273685455322</t>
+    <t xml:space="preserve">5.70273733139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.53326511383057</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">5.93576097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10099601745605</t>
+    <t xml:space="preserve">6.10099649429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.13065385818481</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">5.6773157119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87644529342651</t>
+    <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.81289386749268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75357913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66460561752319</t>
+    <t xml:space="preserve">5.75357866287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66460514068604</t>
   </si>
   <si>
     <t xml:space="preserve">5.65189504623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015468597412</t>
+    <t xml:space="preserve">6.05015420913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">6.35520458221436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29165172576904</t>
+    <t xml:space="preserve">6.2916522026062</t>
   </si>
   <si>
     <t xml:space="preserve">6.39333581924438</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">6.94835710525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91022539138794</t>
+    <t xml:space="preserve">6.91022491455078</t>
   </si>
   <si>
     <t xml:space="preserve">7.04156684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24917030334473</t>
+    <t xml:space="preserve">7.24916982650757</t>
   </si>
   <si>
     <t xml:space="preserve">7.10088157653809</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57551860809326</t>
+    <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
     <t xml:space="preserve">6.71533298492432</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">6.33402013778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3255467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1857328414917</t>
+    <t xml:space="preserve">6.32554721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
     <t xml:space="preserve">6.14760112762451</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">6.28741550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12641716003418</t>
+    <t xml:space="preserve">6.12641668319702</t>
   </si>
   <si>
     <t xml:space="preserve">6.1518383026123</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912725448608</t>
+    <t xml:space="preserve">6.13912773132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981204986572</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">6.04591798782349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36367797851562</t>
+    <t xml:space="preserve">6.36367845535278</t>
   </si>
   <si>
     <t xml:space="preserve">6.24504709243774</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">6.47807121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27046823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06286478042603</t>
+    <t xml:space="preserve">6.27046871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06286525726318</t>
   </si>
   <si>
     <t xml:space="preserve">6.10523271560669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22386360168457</t>
+    <t xml:space="preserve">6.22386312484741</t>
   </si>
   <si>
     <t xml:space="preserve">6.14336490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08404874801636</t>
+    <t xml:space="preserve">6.08404922485352</t>
   </si>
   <si>
     <t xml:space="preserve">5.95270824432373</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">6.32978343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32131052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420576095581</t>
+    <t xml:space="preserve">6.32131004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420528411865</t>
   </si>
   <si>
     <t xml:space="preserve">6.25775814056396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27470588684082</t>
+    <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3085994720459</t>
+    <t xml:space="preserve">6.30859994888306</t>
   </si>
   <si>
     <t xml:space="preserve">6.37215185165405</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">6.85938453674316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79583215713501</t>
+    <t xml:space="preserve">6.79583263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4908971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6010537147522</t>
+    <t xml:space="preserve">5.57563304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49089670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60105323791504</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05874252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01213788986206</t>
+    <t xml:space="preserve">5.0587420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0121374130249</t>
   </si>
   <si>
     <t xml:space="preserve">5.29176664352417</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831405639648</t>
+    <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
     <t xml:space="preserve">6.93988275527954</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">7.88045406341553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53303527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49914121627808</t>
+    <t xml:space="preserve">7.53303480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49914169311523</t>
   </si>
   <si>
     <t xml:space="preserve">7.45253658294678</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">7.77029657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079669952393</t>
+    <t xml:space="preserve">7.85079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719801902771</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">7.6347188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91011095046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82537412643433</t>
+    <t xml:space="preserve">7.91010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82537508010864</t>
   </si>
   <si>
     <t xml:space="preserve">7.85503339767456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68555974960327</t>
+    <t xml:space="preserve">7.68556070327759</t>
   </si>
   <si>
     <t xml:space="preserve">7.5245623588562</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">7.5881142616272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56693029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4101676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730201721191</t>
+    <t xml:space="preserve">7.56693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41016817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730154037476</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374820709229</t>
@@ -2717,19 +2717,19 @@
     <t xml:space="preserve">7.32543277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31695890426636</t>
+    <t xml:space="preserve">7.3169584274292</t>
   </si>
   <si>
     <t xml:space="preserve">7.18985414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06275081634521</t>
+    <t xml:space="preserve">7.06275033950806</t>
   </si>
   <si>
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15595960617065</t>
+    <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">7.64319324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74911212921143</t>
+    <t xml:space="preserve">7.74911308288574</t>
   </si>
   <si>
     <t xml:space="preserve">7.53727293014526</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">8.23210906982422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18550395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20668697357178</t>
+    <t xml:space="preserve">8.18550300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20668792724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.30837059020996</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63460445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0075569152832</t>
+    <t xml:space="preserve">8.88033866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63460350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00755596160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965435028076</t>
+    <t xml:space="preserve">8.93965530395508</t>
   </si>
   <si>
     <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544673919678</t>
+    <t xml:space="preserve">8.68544769287109</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
@@ -2810,22 +2810,22 @@
     <t xml:space="preserve">9.20233631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55822849273682</t>
+    <t xml:space="preserve">9.5582275390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96507549285889</t>
+    <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21928405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981136322021</t>
+    <t xml:space="preserve">9.21928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0498104095459</t>
   </si>
   <si>
     <t xml:space="preserve">9.71075248718262</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.44806957244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196506500244</t>
+    <t xml:space="preserve">9.48196411132812</t>
   </si>
   <si>
     <t xml:space="preserve">9.69380474090576</t>
@@ -5403,6 +5403,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.039999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0600004196167</t>
   </si>
 </sst>
 </file>
@@ -68323,7 +68326,7 @@
     </row>
     <row r="2408">
       <c r="A2408" s="1" t="n">
-        <v>45947.6493865741</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2408" t="n">
         <v>224746</v>
@@ -68344,6 +68347,32 @@
         <v>1792</v>
       </c>
       <c r="H2408" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" s="1" t="n">
+        <v>45950.6495833333</v>
+      </c>
+      <c r="B2409" t="n">
+        <v>114637</v>
+      </c>
+      <c r="C2409" t="n">
+        <v>14.1199998855591</v>
+      </c>
+      <c r="D2409" t="n">
+        <v>13.9700002670288</v>
+      </c>
+      <c r="E2409" t="n">
+        <v>14.039999961853</v>
+      </c>
+      <c r="F2409" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="G2409" t="s">
+        <v>1797</v>
+      </c>
+      <c r="H2409" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1799">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13860034942627</t>
+    <t xml:space="preserve">3.13860011100769</t>
   </si>
   <si>
     <t xml:space="preserve">3.12387990951538</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500053405762</t>
+    <t xml:space="preserve">3.06663608551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0650007724762</t>
   </si>
   <si>
     <t xml:space="preserve">3.05028080940247</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">3.18930196762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16476845741272</t>
+    <t xml:space="preserve">3.1647686958313</t>
   </si>
   <si>
     <t xml:space="preserve">3.17131066322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16149759292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168428421021</t>
+    <t xml:space="preserve">3.16149735450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205742835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514231681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168404579163</t>
   </si>
   <si>
     <t xml:space="preserve">3.30051803588867</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">3.34140682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463253974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790364265442</t>
+    <t xml:space="preserve">3.43463277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.437903881073</t>
   </si>
   <si>
     <t xml:space="preserve">3.39374446868896</t>
@@ -107,118 +107,118 @@
     <t xml:space="preserve">3.33977150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24000334739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14841318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0306544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08789849281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17294645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752439498901</t>
+    <t xml:space="preserve">3.24000310897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14841270446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03065466880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08789825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17294669151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
     <t xml:space="preserve">3.18112421035767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19257259368896</t>
+    <t xml:space="preserve">3.19257283210754</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0339252948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373860359192</t>
+    <t xml:space="preserve">3.03392577171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0437388420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23019051551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2334611415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2252836227417</t>
+    <t xml:space="preserve">3.23019027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23346138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22528338432312</t>
   </si>
   <si>
     <t xml:space="preserve">3.11406683921814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023566246033</t>
+    <t xml:space="preserve">3.14023542404175</t>
   </si>
   <si>
     <t xml:space="preserve">3.12224459648132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0911693572998</t>
+    <t xml:space="preserve">3.09116959571838</t>
   </si>
   <si>
     <t xml:space="preserve">3.0829918384552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11897325515747</t>
+    <t xml:space="preserve">3.11897349357605</t>
   </si>
   <si>
     <t xml:space="preserve">3.08135581016541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1042537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07481384277344</t>
+    <t xml:space="preserve">3.10425353050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07481408119202</t>
   </si>
   <si>
     <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13696432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383452415466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16640424728394</t>
+    <t xml:space="preserve">3.13696479797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16640400886536</t>
   </si>
   <si>
     <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36921095848083</t>
+    <t xml:space="preserve">3.36921072006226</t>
   </si>
   <si>
     <t xml:space="preserve">3.42645454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50986766815186</t>
+    <t xml:space="preserve">3.5098671913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.51640963554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54094243049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50168967247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552084922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35612654685974</t>
+    <t xml:space="preserve">3.54094266891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50168943405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35612678527832</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014465332031</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">3.36103343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37575268745422</t>
+    <t xml:space="preserve">3.3757529258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38556623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136119842529</t>
+    <t xml:space="preserve">3.35285544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3855664730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136191368103</t>
   </si>
   <si>
     <t xml:space="preserve">3.51150321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47061419487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4673433303833</t>
+    <t xml:space="preserve">3.47061443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46734309196472</t>
   </si>
   <si>
     <t xml:space="preserve">3.48697018623352</t>
@@ -263,70 +263,70 @@
     <t xml:space="preserve">3.3970148563385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41337084770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916604995728</t>
+    <t xml:space="preserve">3.41337060928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488605260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916557312012</t>
   </si>
   <si>
     <t xml:space="preserve">3.41827726364136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50823211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729746818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57856059074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472822189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547522544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5981867313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6390745639801</t>
+    <t xml:space="preserve">3.50823187828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57855987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472893714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907504081726</t>
   </si>
   <si>
     <t xml:space="preserve">3.66360831260681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64725279808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996311187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178559303284</t>
+    <t xml:space="preserve">3.64725255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178535461426</t>
   </si>
   <si>
     <t xml:space="preserve">3.60636401176453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5671112537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897912025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38065958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33813571929932</t>
+    <t xml:space="preserve">3.56711149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4689793586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355753898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38065981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33813548088074</t>
   </si>
   <si>
     <t xml:space="preserve">3.28743410110474</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">3.32668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27598547935486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24327445030212</t>
+    <t xml:space="preserve">3.27598524093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2432746887207</t>
   </si>
   <si>
     <t xml:space="preserve">3.21874141693115</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">3.25962996482849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15495586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07644939422607</t>
+    <t xml:space="preserve">3.15495538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07644963264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.08462738990784</t>
@@ -359,49 +359,49 @@
     <t xml:space="preserve">3.1255156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27107906341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486485481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4084644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30869603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818062782288</t>
+    <t xml:space="preserve">3.27107834815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850957870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3675754070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30869626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818110466003</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206305503845</t>
+    <t xml:space="preserve">3.48206281661987</t>
   </si>
   <si>
     <t xml:space="preserve">3.54421401023865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61454176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655022621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528901100159</t>
+    <t xml:space="preserve">3.61454153060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655070304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528924942017</t>
   </si>
   <si>
     <t xml:space="preserve">3.58183121681213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63253307342529</t>
+    <t xml:space="preserve">3.63253235816956</t>
   </si>
   <si>
     <t xml:space="preserve">3.60309338569641</t>
@@ -413,40 +413,40 @@
     <t xml:space="preserve">3.64071106910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61617684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435507774353</t>
+    <t xml:space="preserve">3.61617732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435531616211</t>
   </si>
   <si>
     <t xml:space="preserve">3.75192737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76174068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412300109863</t>
+    <t xml:space="preserve">3.76173996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.77809572219849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77646040916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79445099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071669578552</t>
+    <t xml:space="preserve">3.77646064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118061065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730333328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071598052979</t>
   </si>
   <si>
     <t xml:space="preserve">3.91548085212708</t>
@@ -455,79 +455,79 @@
     <t xml:space="preserve">3.86314368247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89258360862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440632820129</t>
+    <t xml:space="preserve">3.8925838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529439926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440537452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.86641526222229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94655680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150813102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9645471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169458389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04305267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618318557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767719268799</t>
+    <t xml:space="preserve">3.94655561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.043053150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618223190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767743110657</t>
   </si>
   <si>
     <t xml:space="preserve">3.86968636512756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.941650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02669811248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398684501648</t>
+    <t xml:space="preserve">3.81898427009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384553909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94164991378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9939866065979</t>
   </si>
   <si>
     <t xml:space="preserve">3.9727246761322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00216436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05613708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707101821899</t>
+    <t xml:space="preserve">4.0021653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97926735877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707149505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.01524877548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884811401367</t>
+    <t xml:space="preserve">4.04141807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884859085083</t>
   </si>
   <si>
     <t xml:space="preserve">4.08394145965576</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">4.16244792938232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44048881530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595649719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350831985474</t>
+    <t xml:space="preserve">4.27693510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44048976898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595602035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37506818771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59586620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350736618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.78804159164429</t>
@@ -569,31 +569,31 @@
     <t xml:space="preserve">4.83710765838623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83301830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90661764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928304672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.033371925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150453567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2868800163269</t>
+    <t xml:space="preserve">4.83301877975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90661859512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96386194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03337240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830396652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688097000122</t>
   </si>
   <si>
     <t xml:space="preserve">5.36456871032715</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.36865758895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46270179748535</t>
+    <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56901073455811</t>
+    <t xml:space="preserve">5.56901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">5.5526556968689</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54856729507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.601722240448</t>
+    <t xml:space="preserve">5.54856634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60172271728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.70803260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75709867477417</t>
+    <t xml:space="preserve">5.75709819793701</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207538604736</t>
@@ -641,25 +641,25 @@
     <t xml:space="preserve">5.82251977920532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85114240646362</t>
+    <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
     <t xml:space="preserve">5.78572034835815</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43816757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48723411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46678972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581159591675</t>
+    <t xml:space="preserve">5.43816804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4790563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4872350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46679019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581064224243</t>
   </si>
   <si>
     <t xml:space="preserve">5.56083345413208</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">5.69674634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4614462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546560287476</t>
+    <t xml:space="preserve">5.46144580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546607971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.705002784729</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">5.80407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10129833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84122943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80820465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77930736541748</t>
+    <t xml:space="preserve">5.84948539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1012978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84122896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80820417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73389959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7793083190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.77105140686035</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68849086761475</t>
+    <t xml:space="preserve">5.68848991394043</t>
   </si>
   <si>
     <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5770320892334</t>
+    <t xml:space="preserve">5.63069772720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57703256607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.52336740493774</t>
@@ -749,49 +749,49 @@
     <t xml:space="preserve">5.54813528060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48621559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162384033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639266967773</t>
+    <t xml:space="preserve">5.48621463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639219284058</t>
   </si>
   <si>
     <t xml:space="preserve">5.32934808731079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771318435669</t>
+    <t xml:space="preserve">5.27568292617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.30045127868652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230350494385</t>
+    <t xml:space="preserve">5.12294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1931209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230302810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39952564239502</t>
+    <t xml:space="preserve">5.17248153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998750686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39952516555786</t>
   </si>
   <si>
     <t xml:space="preserve">5.74628353118896</t>
@@ -800,46 +800,46 @@
     <t xml:space="preserve">5.75041151046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60592842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77517986297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76692390441895</t>
+    <t xml:space="preserve">5.60592889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77518033981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76692342758179</t>
   </si>
   <si>
     <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599779129028</t>
+    <t xml:space="preserve">5.86599731445312</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443130493164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04763221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204641342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86186981201172</t>
+    <t xml:space="preserve">5.89489412307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04763269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204689025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86186933517456</t>
   </si>
   <si>
     <t xml:space="preserve">5.95268726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97332763671875</t>
+    <t xml:space="preserve">5.97332715988159</t>
   </si>
   <si>
     <t xml:space="preserve">6.06827354431152</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19211578369141</t>
+    <t xml:space="preserve">6.17973232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19211530685425</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275615692139</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">6.18385982513428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12193870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16734743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13845109939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15083456039429</t>
+    <t xml:space="preserve">6.12193822860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16734790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13845062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083503723145</t>
   </si>
   <si>
     <t xml:space="preserve">5.98158407211304</t>
@@ -908,64 +908,64 @@
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96094274520874</t>
+    <t xml:space="preserve">5.9609432220459</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222444534302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976097106934</t>
+    <t xml:space="preserve">6.2292685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976144790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.85260915756226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81958341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371234893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75353527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004671096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015537261963</t>
+    <t xml:space="preserve">6.81958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801740646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75353479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492372512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015441894531</t>
   </si>
   <si>
     <t xml:space="preserve">6.44392871856689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43980121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52649068832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631265640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57189893722534</t>
+    <t xml:space="preserve">6.43980073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52648973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5718994140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.65446090698242</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">6.71638154983521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6131796836853</t>
+    <t xml:space="preserve">6.61318016052246</t>
   </si>
   <si>
     <t xml:space="preserve">6.53061819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66684484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4480562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65858793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55538749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.625563621521</t>
+    <t xml:space="preserve">6.66684532165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44805717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65858745574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55538702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62556409835815</t>
   </si>
   <si>
     <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50584936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125856399536</t>
+    <t xml:space="preserve">6.50584983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72876596450806</t>
+    <t xml:space="preserve">6.7287654876709</t>
   </si>
   <si>
     <t xml:space="preserve">6.84848022460938</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">6.90214538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6874852180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7122540473938</t>
+    <t xml:space="preserve">6.70812511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">6.77417469024658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705200195312</t>
+    <t xml:space="preserve">7.43466758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705104827881</t>
   </si>
   <si>
     <t xml:space="preserve">7.47594833374023</t>
@@ -1049,133 +1049,133 @@
     <t xml:space="preserve">7.64932727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95480442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7607855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9259090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57915067672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28192758560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40989923477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605604171753</t>
+    <t xml:space="preserve">7.95480632781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619382858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893335342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57914972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28192806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605556488037</t>
   </si>
   <si>
     <t xml:space="preserve">7.13331747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22413444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41402626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3810019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19936561584473</t>
+    <t xml:space="preserve">7.22413492202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41402578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769142150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38100147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33972120285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936752319336</t>
   </si>
   <si>
     <t xml:space="preserve">7.03011560440063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01773071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0548849105835</t>
+    <t xml:space="preserve">7.01773166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488443374634</t>
   </si>
   <si>
     <t xml:space="preserve">6.96406698226929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7948145866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7494068145752</t>
+    <t xml:space="preserve">6.79481554031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940633773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.68335723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79068803787231</t>
+    <t xml:space="preserve">6.79068756103516</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84022426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05075597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23652029037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2571587562561</t>
+    <t xml:space="preserve">7.19111013412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965230941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84022331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05075645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23651885986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128721237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25715970993042</t>
   </si>
   <si>
     <t xml:space="preserve">7.36036205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27779960632324</t>
+    <t xml:space="preserve">7.27780055999756</t>
   </si>
   <si>
     <t xml:space="preserve">8.23138618469238</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40476608276367</t>
+    <t xml:space="preserve">8.40476512908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.62768077850342</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">8.1405668258667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24789810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17359256744385</t>
+    <t xml:space="preserve">8.24789714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17359352111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.09103107452393</t>
@@ -1214,46 +1214,46 @@
     <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295219421387</t>
+    <t xml:space="preserve">8.14469623565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295314788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430088043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522842407227</t>
+    <t xml:space="preserve">8.45430278778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522747039795</t>
   </si>
   <si>
     <t xml:space="preserve">8.36348438262939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33045864105225</t>
+    <t xml:space="preserve">8.33045959472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52035236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79280281066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070556640625</t>
+    <t xml:space="preserve">8.52035140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79280376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408546447754</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">8.65244960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67721748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42953395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74605751037598</t>
+    <t xml:space="preserve">8.67721843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42953586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6710901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74605846405029</t>
   </si>
   <si>
     <t xml:space="preserve">8.70440864562988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104663848877</t>
+    <t xml:space="preserve">8.77104568481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.75438690185547</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">8.30875492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34623718261719</t>
+    <t xml:space="preserve">8.3462381362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601306915283</t>
+    <t xml:space="preserve">8.55447769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601211547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.8793306350708</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269454956055</t>
+    <t xml:space="preserve">8.81269264221191</t>
   </si>
   <si>
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939682006836</t>
+    <t xml:space="preserve">8.86267280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939872741699</t>
   </si>
   <si>
     <t xml:space="preserve">8.50450038909912</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">8.47118091583252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461387634277</t>
+    <t xml:space="preserve">8.45452308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461196899414</t>
   </si>
   <si>
     <t xml:space="preserve">8.58779716491699</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">8.36289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42120265960693</t>
+    <t xml:space="preserve">8.42120361328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21712875366211</t>
@@ -1367,55 +1367,55 @@
     <t xml:space="preserve">8.63777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298675537109</t>
+    <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
     <t xml:space="preserve">8.12133884429932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99639511108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78815650939941</t>
+    <t xml:space="preserve">7.9963960647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78815603256226</t>
   </si>
   <si>
     <t xml:space="preserve">8.02554988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733207702637</t>
+    <t xml:space="preserve">7.76733112335205</t>
   </si>
   <si>
     <t xml:space="preserve">7.85062789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61323499679565</t>
+    <t xml:space="preserve">7.61323595046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.86312294006348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74234437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572908401489</t>
+    <t xml:space="preserve">7.74234294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67154169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572956085205</t>
   </si>
   <si>
     <t xml:space="preserve">7.87145137786865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.721519947052</t>
+    <t xml:space="preserve">7.72152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">7.59241104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57158756256104</t>
+    <t xml:space="preserve">7.57158660888672</t>
   </si>
   <si>
     <t xml:space="preserve">7.82980394363403</t>
@@ -1427,61 +1427,61 @@
     <t xml:space="preserve">7.63405799865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84229803085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79232120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319007873535</t>
+    <t xml:space="preserve">7.84229898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79231977462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61740064620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71319103240967</t>
   </si>
   <si>
     <t xml:space="preserve">7.74650812149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68819999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44664239883423</t>
+    <t xml:space="preserve">7.68819952011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4466438293457</t>
   </si>
   <si>
     <t xml:space="preserve">7.28838109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14677858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163152694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321229934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637241363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1713171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47951221466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463562011719</t>
+    <t xml:space="preserve">7.14677906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4716329574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17131805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47951126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3295783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463466644287</t>
   </si>
   <si>
     <t xml:space="preserve">8.23378849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37955570220947</t>
+    <t xml:space="preserve">8.37955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.5294885635376</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">9.0542516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01260375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427436828613</t>
+    <t xml:space="preserve">8.99594593048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01260471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427532196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07923984527588</t>
@@ -1505,25 +1505,25 @@
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0959005355835</t>
+    <t xml:space="preserve">9.11255741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09589862823486</t>
   </si>
   <si>
     <t xml:space="preserve">9.02093315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02926254272461</t>
+    <t xml:space="preserve">9.02926445007324</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02138328552246</t>
+    <t xml:space="preserve">8.57113742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02138519287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.0838565826416</t>
@@ -1532,37 +1532,37 @@
     <t xml:space="preserve">8.15049171447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00056076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354567527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98390007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82563877105713</t>
+    <t xml:space="preserve">8.00055980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35456657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98390102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.9922308921814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27127170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07969093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28376579284668</t>
+    <t xml:space="preserve">8.27127265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07968997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.283766746521</t>
   </si>
   <si>
     <t xml:space="preserve">8.53781795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46285152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60445308685303</t>
+    <t xml:space="preserve">8.46285247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60445499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.13799858093262</t>
@@ -1571,34 +1571,34 @@
     <t xml:space="preserve">8.07552719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00472450256348</t>
+    <t xml:space="preserve">8.00472545623779</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01721858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26294231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04220867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19214153289795</t>
+    <t xml:space="preserve">8.01721954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26294136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04220771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20046901702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19213962554932</t>
   </si>
   <si>
     <t xml:space="preserve">8.09635066986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12550449371338</t>
+    <t xml:space="preserve">8.14216327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">8.17964649200439</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">8.2587776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9755711555481</t>
+    <t xml:space="preserve">7.97557020187378</t>
   </si>
   <si>
     <t xml:space="preserve">7.89227628707886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81730985641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62989473342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483846664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21296405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18381023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73772811889648</t>
+    <t xml:space="preserve">7.81731033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541275024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21296310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18381118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630432128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7377290725708</t>
   </si>
   <si>
     <t xml:space="preserve">8.43786334991455</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">8.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37122631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51283073425293</t>
+    <t xml:space="preserve">8.62944316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37122535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51282978057861</t>
   </si>
   <si>
     <t xml:space="preserve">8.69607925415039</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">8.83768272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77937602996826</t>
+    <t xml:space="preserve">8.77937507629395</t>
   </si>
   <si>
     <t xml:space="preserve">8.87100219726562</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">9.54569721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39576530456543</t>
+    <t xml:space="preserve">9.39576435089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.28748035430908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29580879211426</t>
+    <t xml:space="preserve">9.29581069946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35411643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66231155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086696624756</t>
+    <t xml:space="preserve">9.49571895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35411548614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66231060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086601257324</t>
   </si>
   <si>
     <t xml:space="preserve">9.03759288787842</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13754940032959</t>
+    <t xml:space="preserve">9.13754844665527</t>
   </si>
   <si>
     <t xml:space="preserve">9.16253757476807</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">8.64610195159912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592132568359</t>
+    <t xml:space="preserve">9.04592227935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91264915466309</t>
+    <t xml:space="preserve">8.91264820098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.83797073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155029296875</t>
+    <t xml:space="preserve">8.65155124664307</t>
   </si>
   <si>
     <t xml:space="preserve">8.58376312255859</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">8.72781467437744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59223651885986</t>
+    <t xml:space="preserve">8.59223747253418</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70239353179932</t>
+    <t xml:space="preserve">8.702392578125</t>
   </si>
   <si>
     <t xml:space="preserve">8.77018260955811</t>
@@ -1787,25 +1787,25 @@
     <t xml:space="preserve">8.6430778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5159740447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48207950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.490553855896</t>
+    <t xml:space="preserve">8.51597309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48207855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49055290222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700004577637</t>
+    <t xml:space="preserve">8.42700099945068</t>
   </si>
   <si>
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26176452636719</t>
+    <t xml:space="preserve">8.2617654800415</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226417541504</t>
@@ -1814,28 +1814,28 @@
     <t xml:space="preserve">8.39310646057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33379173278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31260776519775</t>
+    <t xml:space="preserve">8.33378982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31260871887207</t>
   </si>
   <si>
     <t xml:space="preserve">8.27871417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28718566894531</t>
+    <t xml:space="preserve">8.28718662261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2956600189209</t>
+    <t xml:space="preserve">8.29566097259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500240325928</t>
+    <t xml:space="preserve">8.10500335693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397640228271</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">8.75323486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394779205322</t>
+    <t xml:space="preserve">8.44394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.32531833648682</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43971061706543</t>
+    <t xml:space="preserve">8.43971252441406</t>
   </si>
   <si>
     <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849899291992</t>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">8.57528877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20244979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35921096801758</t>
+    <t xml:space="preserve">8.2024507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35921192169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11771488189697</t>
+    <t xml:space="preserve">8.11771392822266</t>
   </si>
   <si>
     <t xml:space="preserve">8.03297805786133</t>
@@ -1898,64 +1898,64 @@
     <t xml:space="preserve">8.13466262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96519041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9016375541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2363452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25329208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22787189483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236909866333</t>
+    <t xml:space="preserve">7.9651894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90163660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961130142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640298843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792959213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23634433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25329113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22787094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72369194030762</t>
   </si>
   <si>
     <t xml:space="preserve">7.95671606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82113790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6601390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71098279953003</t>
+    <t xml:space="preserve">7.82113695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66013956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41429233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123722076416</t>
+    <t xml:space="preserve">8.41429138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">8.24058151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21939754486084</t>
+    <t xml:space="preserve">8.21939659118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.46513271331787</t>
@@ -1976,25 +1976,25 @@
     <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71934032440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46936893463135</t>
+    <t xml:space="preserve">8.71934127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46936798095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01591777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8888111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270755767822</t>
+    <t xml:space="preserve">9.01591873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270660400391</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354793548584</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">8.18973922729492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37192344665527</t>
+    <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.49902629852295</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">8.81254959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60070991516113</t>
+    <t xml:space="preserve">8.60071086883545</t>
   </si>
   <si>
     <t xml:space="preserve">8.54139518737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69392013549805</t>
+    <t xml:space="preserve">8.69391918182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.67697238922119</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02438926696777</t>
+    <t xml:space="preserve">9.02439022064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28707218170166</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">9.57517433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349166870117</t>
+    <t xml:space="preserve">9.47349262237549</t>
   </si>
   <si>
     <t xml:space="preserve">9.42264938354492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30401802062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906887054443</t>
+    <t xml:space="preserve">9.3040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906982421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.65143775939941</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">9.53280639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63449001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75312042236328</t>
+    <t xml:space="preserve">9.63448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56670093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7531213760376</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159381866455</t>
@@ -2078,34 +2078,34 @@
     <t xml:space="preserve">9.78701496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83785724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.871750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327648162842</t>
+    <t xml:space="preserve">9.83785533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87174987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327743530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.79548931121826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82091045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91411972045898</t>
+    <t xml:space="preserve">9.82090950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91411876678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0242748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0835905075073</t>
+    <t xml:space="preserve">10.0242757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.083589553833</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158023834229</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598529815674</t>
+    <t xml:space="preserve">10.1598539352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.2615365982056</t>
@@ -2147,37 +2147,37 @@
     <t xml:space="preserve">9.94801235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99885559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92259216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51585960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73617267608643</t>
+    <t xml:space="preserve">9.998854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92259311676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51585865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73617362976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296436309814</t>
+    <t xml:space="preserve">9.64296340942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.54975414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29554653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16431903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108116149902</t>
+    <t xml:space="preserve">9.29554557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16431999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108211517334</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603126525879</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153728485107</t>
+    <t xml:space="preserve">7.70674514770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072504043579</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">6.61364889144897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61376428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52479124069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98248052597046</t>
+    <t xml:space="preserve">5.6137638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52479076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9824800491333</t>
   </si>
   <si>
     <t xml:space="preserve">5.08416366577148</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647390365601</t>
+    <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80865669250488</t>
+    <t xml:space="preserve">5.80865621566772</t>
   </si>
   <si>
     <t xml:space="preserve">5.50784349441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210975646973</t>
+    <t xml:space="preserve">5.26210927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690237045288</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27481889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41463375091553</t>
+    <t xml:space="preserve">5.27481937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41463422775269</t>
   </si>
   <si>
     <t xml:space="preserve">5.19008350372314</t>
@@ -2270,28 +2270,28 @@
     <t xml:space="preserve">5.16466283798218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10111093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93163824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96129608154297</t>
+    <t xml:space="preserve">5.10111045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93163871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96129655838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.33837223052979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663091659546</t>
+    <t xml:space="preserve">5.7366304397583</t>
   </si>
   <si>
     <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70273733139038</t>
+    <t xml:space="preserve">6.07557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
     <t xml:space="preserve">5.53326511383057</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">5.87220859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93576097488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10099649429321</t>
+    <t xml:space="preserve">5.93576145172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10099601745605</t>
   </si>
   <si>
     <t xml:space="preserve">6.13065385818481</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">5.6773157119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87644577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81289386749268</t>
+    <t xml:space="preserve">5.87644529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81289339065552</t>
   </si>
   <si>
     <t xml:space="preserve">5.75357866287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66460514068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65189504623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05015420913696</t>
+    <t xml:space="preserve">5.66460466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65189552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05015468597412</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
@@ -2342,31 +2342,31 @@
     <t xml:space="preserve">6.03320693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2916522026062</t>
+    <t xml:space="preserve">6.3552041053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29165267944336</t>
   </si>
   <si>
     <t xml:space="preserve">6.39333581924438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79159545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94835710525513</t>
+    <t xml:space="preserve">6.79159593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94835662841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.91022491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04156684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24916982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088157653809</t>
+    <t xml:space="preserve">7.04156637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24917030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088109970093</t>
   </si>
   <si>
     <t xml:space="preserve">7.00343561172485</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5755181312561</t>
+    <t xml:space="preserve">6.57551860809326</t>
   </si>
   <si>
     <t xml:space="preserve">6.71533298492432</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64330673217773</t>
+    <t xml:space="preserve">6.64330720901489</t>
   </si>
   <si>
     <t xml:space="preserve">6.55009746551514</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">6.60941219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33402013778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32554721832275</t>
+    <t xml:space="preserve">6.33402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3255467414856</t>
   </si>
   <si>
     <t xml:space="preserve">6.18573236465454</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741550445557</t>
+    <t xml:space="preserve">6.28741598129272</t>
   </si>
   <si>
     <t xml:space="preserve">6.12641668319702</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31707334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13912773132324</t>
+    <t xml:space="preserve">6.31707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13912725448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981204986572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591798782349</t>
+    <t xml:space="preserve">6.04591846466064</t>
   </si>
   <si>
     <t xml:space="preserve">6.36367845535278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24504709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47383451461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807121276855</t>
+    <t xml:space="preserve">6.24504661560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47383403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807168960571</t>
   </si>
   <si>
     <t xml:space="preserve">6.27046871185303</t>
@@ -2453,28 +2453,28 @@
     <t xml:space="preserve">6.10523271560669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22386312484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14336490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08404922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95270824432373</t>
+    <t xml:space="preserve">6.22386360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14336442947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08404874801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95270776748657</t>
   </si>
   <si>
     <t xml:space="preserve">6.07133865356445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18149566650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02049732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931287765503</t>
+    <t xml:space="preserve">6.18149518966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0204963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931335449219</t>
   </si>
   <si>
     <t xml:space="preserve">6.3848614692688</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">6.32978343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32131004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420528411865</t>
+    <t xml:space="preserve">6.3213095664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420576095581</t>
   </si>
   <si>
     <t xml:space="preserve">6.25775814056396</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30859994888306</t>
+    <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.37215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63483333587646</t>
+    <t xml:space="preserve">6.63483381271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.986487865448</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">7.16019678115845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29577445983887</t>
+    <t xml:space="preserve">7.29577541351318</t>
   </si>
   <si>
     <t xml:space="preserve">6.97377777099609</t>
@@ -2528,43 +2528,43 @@
     <t xml:space="preserve">6.75346326828003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0161452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90175294876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85938453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79583263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44417762756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10946989059448</t>
+    <t xml:space="preserve">7.01614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90175247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85938501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79583215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44417715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10946941375732</t>
   </si>
   <si>
     <t xml:space="preserve">6.05439186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04168081283569</t>
+    <t xml:space="preserve">6.04168128967285</t>
   </si>
   <si>
     <t xml:space="preserve">6.16031122207642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09675979614258</t>
+    <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.2153902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94847106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09252309799194</t>
+    <t xml:space="preserve">5.94847059249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09252262115479</t>
   </si>
   <si>
     <t xml:space="preserve">6.00778675079346</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60105323791504</t>
+    <t xml:space="preserve">5.57563257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49089622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787210464478</t>
+    <t xml:space="preserve">5.25787258148193</t>
   </si>
   <si>
     <t xml:space="preserve">5.28752994537354</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0587420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0121374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29176664352417</t>
+    <t xml:space="preserve">5.05874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01213788986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29176712036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.40616083145142</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831453323364</t>
+    <t xml:space="preserve">5.83831405639648</t>
   </si>
   <si>
     <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075317382812</t>
+    <t xml:space="preserve">6.74075365066528</t>
   </si>
   <si>
     <t xml:space="preserve">6.82125234603882</t>
@@ -2630,37 +2630,37 @@
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09652996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303480148315</t>
+    <t xml:space="preserve">8.09653091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303527832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.49914169311523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45253658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200784683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453374862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079574584961</t>
+    <t xml:space="preserve">7.45253610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845594406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7702956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079669952393</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719801902771</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">7.67285013198853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81266403198242</t>
+    <t xml:space="preserve">7.81266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">7.79571676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6347188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91010999679565</t>
+    <t xml:space="preserve">7.63471984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011095046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537508010864</t>
@@ -2690,76 +2690,76 @@
     <t xml:space="preserve">7.85503339767456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68556070327759</t>
+    <t xml:space="preserve">7.68556022644043</t>
   </si>
   <si>
     <t xml:space="preserve">7.5245623588562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4779577255249</t>
+    <t xml:space="preserve">7.47795677185059</t>
   </si>
   <si>
     <t xml:space="preserve">7.5881142616272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56693077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41016817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22374820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32543277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3169584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985414505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06275033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18138122558594</t>
+    <t xml:space="preserve">7.56693029403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41016912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32543182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31695890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06275081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1813817024231</t>
   </si>
   <si>
     <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63895606994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727293014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21516036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23210906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18550300598145</t>
+    <t xml:space="preserve">7.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21516132354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2321081161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18550395965576</t>
   </si>
   <si>
     <t xml:space="preserve">8.20668792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30837059020996</t>
+    <t xml:space="preserve">8.30837154388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.14313507080078</t>
@@ -2768,43 +2768,43 @@
     <t xml:space="preserve">7.79147958755493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65166616439819</t>
+    <t xml:space="preserve">7.65166568756104</t>
   </si>
   <si>
     <t xml:space="preserve">8.03721523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92282199859619</t>
+    <t xml:space="preserve">7.92282152175903</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033866882324</t>
+    <t xml:space="preserve">8.88033962249756</t>
   </si>
   <si>
     <t xml:space="preserve">8.63460350036621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00755596160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39734363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965530395508</t>
+    <t xml:space="preserve">8.0075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39734268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544769287109</t>
+    <t xml:space="preserve">8.68544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16844081878662</t>
+    <t xml:space="preserve">9.16844177246094</t>
   </si>
   <si>
     <t xml:space="preserve">9.20233631134033</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133892059326</t>
+    <t xml:space="preserve">9.04133796691895</t>
   </si>
   <si>
     <t xml:space="preserve">9.21928310394287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0498104095459</t>
+    <t xml:space="preserve">9.04981136322021</t>
   </si>
   <si>
     <t xml:space="preserve">9.71075248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39722919464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44806957244873</t>
+    <t xml:space="preserve">9.3972282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44807052612305</t>
   </si>
   <si>
     <t xml:space="preserve">9.48196411132812</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">9.69380474090576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0412216186523</t>
+    <t xml:space="preserve">10.041223526001</t>
   </si>
   <si>
     <t xml:space="preserve">9.74464797973633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72769927978516</t>
+    <t xml:space="preserve">9.72769832611084</t>
   </si>
   <si>
     <t xml:space="preserve">9.52433300018311</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">9.43112373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02747821807861</t>
+    <t xml:space="preserve">9.02747917175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03613471984863</t>
+    <t xml:space="preserve">9.03613376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.91495990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01016807556152</t>
+    <t xml:space="preserve">9.01016712188721</t>
   </si>
   <si>
     <t xml:space="preserve">8.96689128875732</t>
@@ -2879,46 +2879,46 @@
     <t xml:space="preserve">9.08806610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20924091339111</t>
+    <t xml:space="preserve">9.20924186706543</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386119842529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33906841278076</t>
+    <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.43427753448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63334941864014</t>
+    <t xml:space="preserve">9.63335037231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40831279754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47755527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32175922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21789455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11403179168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0447883605957</t>
+    <t xml:space="preserve">9.40831184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47755432128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3217601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2178955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1140308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2611722946167</t>
+    <t xml:space="preserve">9.26117134094238</t>
   </si>
   <si>
     <t xml:space="preserve">9.51217555999756</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">9.3044490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3477258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13134288787842</t>
+    <t xml:space="preserve">9.34772491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1313419342041</t>
   </si>
   <si>
     <t xml:space="preserve">9.12268733978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10537719726562</t>
+    <t xml:space="preserve">9.10537624359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.00151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75916481018066</t>
+    <t xml:space="preserve">8.75916385650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840633392334</t>
@@ -2975,34 +2975,34 @@
     <t xml:space="preserve">9.16596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99285888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.252516746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1746187210083</t>
+    <t xml:space="preserve">8.99285793304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25251579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17461967468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706188201904</t>
+    <t xml:space="preserve">8.83706283569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77647495269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98420238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69857788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66395664215088</t>
+    <t xml:space="preserve">8.77647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98420143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69857692718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66395568847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">8.86302852630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78512954711914</t>
+    <t xml:space="preserve">8.78513050079346</t>
   </si>
   <si>
     <t xml:space="preserve">8.72454357147217</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">8.68126583099365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73319816589355</t>
+    <t xml:space="preserve">8.73319911956787</t>
   </si>
   <si>
     <t xml:space="preserve">8.44324588775635</t>
@@ -3038,31 +3038,31 @@
     <t xml:space="preserve">8.26581192016602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28745079040527</t>
+    <t xml:space="preserve">8.19657039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23119163513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28744983673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.74185466766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43891716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39131355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42160797119141</t>
+    <t xml:space="preserve">8.4389181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39131450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42160701751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.36102104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47353935241699</t>
+    <t xml:space="preserve">8.47354030609131</t>
   </si>
   <si>
     <t xml:space="preserve">8.63366317749023</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">8.59904193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50383281707764</t>
+    <t xml:space="preserve">8.50383377075195</t>
   </si>
   <si>
     <t xml:space="preserve">8.54278087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58605766296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81975173950195</t>
+    <t xml:space="preserve">8.58605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81975078582764</t>
   </si>
   <si>
     <t xml:space="preserve">8.80244064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92825603485107</t>
+    <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
     <t xml:space="preserve">7.85901355743408</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">7.99749755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96287679672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91960000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527271270752</t>
+    <t xml:space="preserve">7.9628758430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91960096359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527366638184</t>
   </si>
   <si>
     <t xml:space="preserve">7.9585485458374</t>
@@ -3128,40 +3128,40 @@
     <t xml:space="preserve">7.82439184188843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65128660202026</t>
+    <t xml:space="preserve">7.65128612518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011178970337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55607748031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981784820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39162731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35267782211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09734678268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16658878326416</t>
+    <t xml:space="preserve">7.556077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39162683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3526782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09734630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16658926010132</t>
   </si>
   <si>
     <t xml:space="preserve">7.05839776992798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18389940261841</t>
+    <t xml:space="preserve">7.18390035629272</t>
   </si>
   <si>
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969497680664</t>
+    <t xml:space="preserve">7.33969449996948</t>
   </si>
   <si>
     <t xml:space="preserve">7.51280164718628</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">7.37431621551514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3310399055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15360689163208</t>
+    <t xml:space="preserve">7.33104038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15360641479492</t>
   </si>
   <si>
     <t xml:space="preserve">7.06272554397583</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">7.14927911758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20121097564697</t>
+    <t xml:space="preserve">7.20121002197266</t>
   </si>
   <si>
     <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19255542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25746965408325</t>
+    <t xml:space="preserve">7.19255495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25747013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.2617974281311</t>
@@ -3203,28 +3203,28 @@
     <t xml:space="preserve">7.24448728561401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40460968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654153823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3180570602417</t>
+    <t xml:space="preserve">7.40461015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31805658340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.41759252548218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35700607299805</t>
+    <t xml:space="preserve">7.35700559616089</t>
   </si>
   <si>
     <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34402275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23583126068115</t>
+    <t xml:space="preserve">7.34402227401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23583173751831</t>
   </si>
   <si>
     <t xml:space="preserve">7.14062309265137</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">7.07138109207153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02377653121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01944828033447</t>
+    <t xml:space="preserve">7.02377605438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01944875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.88961935043335</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">6.88096380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66458177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42223310470581</t>
+    <t xml:space="preserve">6.66458129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42223405838013</t>
   </si>
   <si>
     <t xml:space="preserve">6.46983766555786</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">6.5131139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54340744018555</t>
+    <t xml:space="preserve">6.54340791702271</t>
   </si>
   <si>
     <t xml:space="preserve">6.63861608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49147605895996</t>
+    <t xml:space="preserve">6.4914755821228</t>
   </si>
   <si>
     <t xml:space="preserve">6.36164617538452</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">6.43088817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56937313079834</t>
+    <t xml:space="preserve">6.5693736076355</t>
   </si>
   <si>
     <t xml:space="preserve">6.44387149810791</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">6.75978994369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5650463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4958028793335</t>
+    <t xml:space="preserve">6.56504583358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49580335617065</t>
   </si>
   <si>
     <t xml:space="preserve">6.21883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21450662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10198736190796</t>
+    <t xml:space="preserve">6.21450614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1019868850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.88560485839844</t>
@@ -3317,34 +3317,34 @@
     <t xml:space="preserve">6.20152282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1149697303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05005502700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08034896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70817041397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60863494873047</t>
+    <t xml:space="preserve">6.11497020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05005550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0803484916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70817089080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60863447189331</t>
   </si>
   <si>
     <t xml:space="preserve">5.46149492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.297043800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53073692321777</t>
+    <t xml:space="preserve">5.29704427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53073740005493</t>
   </si>
   <si>
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237483978271</t>
+    <t xml:space="preserve">5.55237531661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.63460111618042</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">5.53506517410278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89425945281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87262153625488</t>
+    <t xml:space="preserve">5.89425992965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367300033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87262105941772</t>
   </si>
   <si>
     <t xml:space="preserve">5.81203460693359</t>
@@ -3368,10 +3368,10 @@
     <t xml:space="preserve">5.85098361968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73413705825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05438280105591</t>
+    <t xml:space="preserve">5.7341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05438327789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.08467674255371</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37030172348022</t>
+    <t xml:space="preserve">6.37030124664307</t>
   </si>
   <si>
     <t xml:space="preserve">6.38761186599731</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">6.29673147201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37895679473877</t>
+    <t xml:space="preserve">6.37895631790161</t>
   </si>
   <si>
     <t xml:space="preserve">5.99812364578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1539192199707</t>
+    <t xml:space="preserve">6.15391874313354</t>
   </si>
   <si>
     <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14526319503784</t>
+    <t xml:space="preserve">6.145263671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.18421268463135</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12362480163574</t>
+    <t xml:space="preserve">6.1236252784729</t>
   </si>
   <si>
     <t xml:space="preserve">6.1755576133728</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">6.30105876922607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45685482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24479913711548</t>
+    <t xml:space="preserve">6.45685434341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24479961395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4828200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51744174957275</t>
+    <t xml:space="preserve">6.48282051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5174412727356</t>
   </si>
   <si>
     <t xml:space="preserve">6.34433555603027</t>
@@ -3452,19 +3452,19 @@
     <t xml:space="preserve">6.27900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19044780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12845516204834</t>
+    <t xml:space="preserve">6.19044828414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1284556388855</t>
   </si>
   <si>
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42956447601318</t>
+    <t xml:space="preserve">6.38971185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42956495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.3764271736145</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">6.34543085098267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4162802696228</t>
+    <t xml:space="preserve">6.41627979278564</t>
   </si>
   <si>
     <t xml:space="preserve">5.86277055740356</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">5.40225076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65022373199463</t>
+    <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.59708642959595</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">5.62808275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63251113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80077838897705</t>
+    <t xml:space="preserve">5.63251066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80077791213989</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">5.79192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60594177246094</t>
+    <t xml:space="preserve">5.60594272613525</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66793537139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72107219696045</t>
+    <t xml:space="preserve">5.53952169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66793584823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72107267379761</t>
   </si>
   <si>
     <t xml:space="preserve">5.88933944702148</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">5.77863740921021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92476415634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85834264755249</t>
+    <t xml:space="preserve">5.92476367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85834217071533</t>
   </si>
   <si>
     <t xml:space="preserve">5.40667915344238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57494640350342</t>
+    <t xml:space="preserve">5.57494592666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948682785034</t>
+    <t xml:space="preserve">5.84948635101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.94690418243408</t>
@@ -3581,28 +3581,28 @@
     <t xml:space="preserve">5.76092529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84063005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07089042663574</t>
+    <t xml:space="preserve">5.84063053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07088994979858</t>
   </si>
   <si>
     <t xml:space="preserve">6.16387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96904420852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07531881332397</t>
+    <t xml:space="preserve">5.96904468536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07531833648682</t>
   </si>
   <si>
     <t xml:space="preserve">6.07974624633789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95576000213623</t>
+    <t xml:space="preserve">5.95576047897339</t>
   </si>
   <si>
     <t xml:space="preserve">5.97790050506592</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">6.1550235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27015352249146</t>
+    <t xml:space="preserve">6.27015399932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.04432153701782</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">6.02660942077637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99561309814453</t>
+    <t xml:space="preserve">5.99561262130737</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95133256912231</t>
+    <t xml:space="preserve">5.95133209228516</t>
   </si>
   <si>
     <t xml:space="preserve">6.01775360107422</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87605571746826</t>
+    <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
     <t xml:space="preserve">5.89819526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67236375808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73435640335083</t>
+    <t xml:space="preserve">5.61037111282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67236423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73435688018799</t>
   </si>
   <si>
     <t xml:space="preserve">5.80963373184204</t>
@@ -3677,34 +3677,34 @@
     <t xml:space="preserve">5.39782285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5572338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59265804290771</t>
+    <t xml:space="preserve">5.55723333358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59265851974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.68564796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8671989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65465116500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62365484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7299280166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97347259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00889730453491</t>
+    <t xml:space="preserve">5.86719846725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6546516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62365436553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68121957778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72992849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.973473072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00889682769775</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">6.06203413009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22144508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29672241210938</t>
+    <t xml:space="preserve">6.22144460678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29672193527222</t>
   </si>
   <si>
     <t xml:space="preserve">6.44727659225464</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47384452819824</t>
+    <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
     <t xml:space="preserve">6.42513656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915672302246</t>
+    <t xml:space="preserve">6.23915719985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.35428714752197</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">6.44284868240356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53141021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668754577637</t>
+    <t xml:space="preserve">6.531409740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668706893921</t>
   </si>
   <si>
     <t xml:space="preserve">6.75724172592163</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">6.65539598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54912185668945</t>
+    <t xml:space="preserve">6.54912233352661</t>
   </si>
   <si>
     <t xml:space="preserve">6.52255344390869</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">6.49598550796509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64211225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325548171997</t>
+    <t xml:space="preserve">6.64211177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325595855713</t>
   </si>
   <si>
     <t xml:space="preserve">6.49155759811401</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">6.50926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40299606323242</t>
+    <t xml:space="preserve">6.40299558639526</t>
   </si>
   <si>
     <t xml:space="preserve">6.45613288879395</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">6.36314296722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46941709518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33214664459229</t>
+    <t xml:space="preserve">6.46941661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33214712142944</t>
   </si>
   <si>
     <t xml:space="preserve">6.4074239730835</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">6.66425228118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94764852523804</t>
+    <t xml:space="preserve">6.9476490020752</t>
   </si>
   <si>
     <t xml:space="preserve">6.92993688583374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05392265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96093368530273</t>
+    <t xml:space="preserve">7.0539231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
     <t xml:space="preserve">6.98307371139526</t>
@@ -3839,28 +3839,28 @@
     <t xml:space="preserve">7.06720685958862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63842916488647</t>
+    <t xml:space="preserve">7.32846355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63842821121216</t>
   </si>
   <si>
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997919082642</t>
+    <t xml:space="preserve">7.81998014450073</t>
   </si>
   <si>
     <t xml:space="preserve">7.58529186248779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24875831604004</t>
+    <t xml:space="preserve">7.2487587928772</t>
   </si>
   <si>
     <t xml:space="preserve">7.2089056968689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19562149047852</t>
+    <t xml:space="preserve">7.19562101364136</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
@@ -3869,28 +3869,28 @@
     <t xml:space="preserve">7.20447731018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3018946647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5232982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49230241775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42145299911499</t>
+    <t xml:space="preserve">7.30189514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52329874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49230194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42145252227783</t>
   </si>
   <si>
     <t xml:space="preserve">7.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48787450790405</t>
+    <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
     <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10263252258301</t>
+    <t xml:space="preserve">7.10263204574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.3151798248291</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">7.32403564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35060358047485</t>
+    <t xml:space="preserve">7.35060453414917</t>
   </si>
   <si>
     <t xml:space="preserve">7.25318574905396</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">7.20004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95207738876343</t>
+    <t xml:space="preserve">6.95207691192627</t>
   </si>
   <si>
     <t xml:space="preserve">6.74838542938232</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451217651367</t>
+    <t xml:space="preserve">6.89451169967651</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">6.81480693817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81037902832031</t>
+    <t xml:space="preserve">6.81037855148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26204252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761365890503</t>
+    <t xml:space="preserve">7.26204204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25761413574219</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,31 +3983,31 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1203441619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35946035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17348098754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31960821151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38602876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39931201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27975463867188</t>
+    <t xml:space="preserve">7.10705995559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12034368515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35945987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17348146438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31960773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38602828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40374088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39931297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27975511550903</t>
   </si>
   <si>
     <t xml:space="preserve">7.45687770843506</t>
@@ -4016,19 +4016,19 @@
     <t xml:space="preserve">7.54543924331665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47458934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68270969390869</t>
+    <t xml:space="preserve">7.47459030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68271017074585</t>
   </si>
   <si>
     <t xml:space="preserve">7.60300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71370649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67828178405762</t>
+    <t xml:space="preserve">7.71370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828130722046</t>
   </si>
   <si>
     <t xml:space="preserve">7.85610342025757</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">7.81506776809692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88802003860474</t>
+    <t xml:space="preserve">7.79683017730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88802051544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.07040309906006</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">7.90169954299927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80138921737671</t>
+    <t xml:space="preserve">7.74211454391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80138969421387</t>
   </si>
   <si>
     <t xml:space="preserve">7.95185470581055</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">7.94273519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09775924682617</t>
+    <t xml:space="preserve">8.09776020050049</t>
   </si>
   <si>
     <t xml:space="preserve">8.22086811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30293941497803</t>
+    <t xml:space="preserve">8.30293846130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.45340538024902</t>
@@ -4085,28 +4085,28 @@
     <t xml:space="preserve">8.13423633575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03392696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09319972991943</t>
+    <t xml:space="preserve">8.03392601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09320068359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.03848552703857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70563840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71931743621826</t>
+    <t xml:space="preserve">7.70563793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7193169593811</t>
   </si>
   <si>
     <t xml:space="preserve">7.78771066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75579404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73299551010132</t>
+    <t xml:space="preserve">7.75579357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73299598693848</t>
   </si>
   <si>
     <t xml:space="preserve">7.71475791931152</t>
@@ -4118,16 +4118,16 @@
     <t xml:space="preserve">7.60988855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56885242462158</t>
+    <t xml:space="preserve">7.45030355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56885290145874</t>
   </si>
   <si>
     <t xml:space="preserve">7.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55517339706421</t>
+    <t xml:space="preserve">7.55517292022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.59164953231812</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">7.50501823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45942354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54149532318115</t>
+    <t xml:space="preserve">7.45942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54149484634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.60076904296875</t>
@@ -4157,34 +4157,34 @@
     <t xml:space="preserve">7.55061340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53237581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69651889801025</t>
+    <t xml:space="preserve">7.53237628936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69651937484741</t>
   </si>
   <si>
     <t xml:space="preserve">7.65548372268677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64636468887329</t>
+    <t xml:space="preserve">7.64636516571045</t>
   </si>
   <si>
     <t xml:space="preserve">7.48678016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4183874130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3317551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.381911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40470838546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52781629562378</t>
+    <t xml:space="preserve">7.41838693618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33175563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38191080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40470790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52781581878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.39102935791016</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">7.29527902603149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24056482315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26792144775391</t>
+    <t xml:space="preserve">7.24056434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26792192459106</t>
   </si>
   <si>
     <t xml:space="preserve">7.25880289077759</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">7.06274175643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08554029464722</t>
+    <t xml:space="preserve">7.08553981781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.01258707046509</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">6.6797399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54751253128052</t>
+    <t xml:space="preserve">6.54751300811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.50191783905029</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">6.67062091827393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60222721099854</t>
+    <t xml:space="preserve">6.60222768783569</t>
   </si>
   <si>
     <t xml:space="preserve">6.59310865402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52927494049072</t>
+    <t xml:space="preserve">6.52927446365356</t>
   </si>
   <si>
     <t xml:space="preserve">6.43808364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69341897964478</t>
+    <t xml:space="preserve">6.69341850280762</t>
   </si>
   <si>
     <t xml:space="preserve">6.75725221633911</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">6.50647735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37880945205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28761911392212</t>
+    <t xml:space="preserve">6.37880992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28761863708496</t>
   </si>
   <si>
     <t xml:space="preserve">6.45176219940186</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">6.47911977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58398962020874</t>
+    <t xml:space="preserve">6.58398914337158</t>
   </si>
   <si>
     <t xml:space="preserve">6.97155094146729</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">7.03994417190552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03538465499878</t>
+    <t xml:space="preserve">7.03538513183594</t>
   </si>
   <si>
     <t xml:space="preserve">7.06730175018311</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">7.21320724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18129014968872</t>
+    <t xml:space="preserve">7.18129062652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.28615999221802</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">7.29983901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23600482940674</t>
+    <t xml:space="preserve">7.2360053062439</t>
   </si>
   <si>
     <t xml:space="preserve">7.20408821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96097278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86066293716431</t>
+    <t xml:space="preserve">7.96097230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86066341400146</t>
   </si>
   <si>
     <t xml:space="preserve">7.97921180725098</t>
@@ -4394,34 +4394,34 @@
     <t xml:space="preserve">7.97009229660034</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05672454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98377180099487</t>
+    <t xml:space="preserve">8.05672359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98377084732056</t>
   </si>
   <si>
     <t xml:space="preserve">8.28926086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31661796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20262908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29838085174561</t>
+    <t xml:space="preserve">8.31661891937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20263004302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29837989807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.25278472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2664623260498</t>
+    <t xml:space="preserve">8.26646327972412</t>
   </si>
   <si>
     <t xml:space="preserve">8.32117748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08408164978027</t>
+    <t xml:space="preserve">8.08408069610596</t>
   </si>
   <si>
     <t xml:space="preserve">8.04304504394531</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">8.04760456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20718860626221</t>
+    <t xml:space="preserve">8.20718955993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.16615295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06128406524658</t>
+    <t xml:space="preserve">8.06128311157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.16159343719482</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">8.34397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38957118988037</t>
+    <t xml:space="preserve">8.38957023620605</t>
   </si>
   <si>
     <t xml:space="preserve">8.37589263916016</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">8.2755823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44884490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32573795318604</t>
+    <t xml:space="preserve">8.44884586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32573699951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.57195281982422</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">8.64034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.535475730896</t>
+    <t xml:space="preserve">8.53547668457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.62666797637939</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">8.43516635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54459571838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68138313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79081249237061</t>
+    <t xml:space="preserve">8.54459476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68138217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79081153869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.84552574157715</t>
@@ -4571,37 +4571,37 @@
     <t xml:space="preserve">8.23910522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93817520141602</t>
+    <t xml:space="preserve">8.01112747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">7.93361568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85154342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594921112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.065842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17071342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14335632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12055683135986</t>
+    <t xml:space="preserve">7.85154390335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594873428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68284130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06584358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14335536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12055778503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.13879585266113</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">8.50811958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67226314544678</t>
+    <t xml:space="preserve">8.67226409912109</t>
   </si>
   <si>
     <t xml:space="preserve">8.75433540344238</t>
@@ -5406,6 +5406,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.0600004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0799999237061</t>
   </si>
 </sst>
 </file>
@@ -68352,7 +68355,7 @@
     </row>
     <row r="2409">
       <c r="A2409" s="1" t="n">
-        <v>45950.6495833333</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2409" t="n">
         <v>114637</v>
@@ -68373,6 +68376,32 @@
         <v>1797</v>
       </c>
       <c r="H2409" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" s="1" t="n">
+        <v>45951.6494907407</v>
+      </c>
+      <c r="B2410" t="n">
+        <v>167145</v>
+      </c>
+      <c r="C2410" t="n">
+        <v>14.2399997711182</v>
+      </c>
+      <c r="D2410" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2410" t="n">
+        <v>14.1400003433228</v>
+      </c>
+      <c r="F2410" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="G2410" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H2410" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13859987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1238796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588955879211</t>
+    <t xml:space="preserve">3.13860011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12388038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
     <t xml:space="preserve">3.06663632392883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0650007724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028128623962</t>
+    <t xml:space="preserve">3.06500053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028080940247</t>
   </si>
   <si>
     <t xml:space="preserve">3.18930172920227</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">3.16476845741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17131114006042</t>
+    <t xml:space="preserve">3.17131066322327</t>
   </si>
   <si>
     <t xml:space="preserve">3.16149735450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13205790519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168452262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30051827430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34140682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463182449341</t>
+    <t xml:space="preserve">3.13205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514231681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168404579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30051779747009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34140634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463253974915</t>
   </si>
   <si>
     <t xml:space="preserve">3.437903881073</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">3.38393092155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33977127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24000310897827</t>
+    <t xml:space="preserve">3.33977150917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
     <t xml:space="preserve">3.14841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03065490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08789849281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17294669151306</t>
+    <t xml:space="preserve">3.0306544303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08789825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17294645309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18112397193909</t>
+    <t xml:space="preserve">3.18112421035767</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257259368896</t>
@@ -134,43 +134,43 @@
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03392553329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0437388420105</t>
+    <t xml:space="preserve">3.0339252948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373836517334</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878680229187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23019051551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23346138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22528338432312</t>
+    <t xml:space="preserve">3.23019003868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2334611415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2252836227417</t>
   </si>
   <si>
     <t xml:space="preserve">3.11406683921814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12224459648132</t>
+    <t xml:space="preserve">3.14023566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1222448348999</t>
   </si>
   <si>
     <t xml:space="preserve">3.0911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897349357605</t>
+    <t xml:space="preserve">3.0829918384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897325515747</t>
   </si>
   <si>
     <t xml:space="preserve">3.08135604858398</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">3.07481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14677762985229</t>
+    <t xml:space="preserve">3.14677715301514</t>
   </si>
   <si>
     <t xml:space="preserve">3.13696432113647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21383500099182</t>
+    <t xml:space="preserve">3.21383476257324</t>
   </si>
   <si>
     <t xml:space="preserve">3.16640424728394</t>
@@ -197,79 +197,79 @@
     <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36921119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645478248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50986742973328</t>
+    <t xml:space="preserve">3.36921143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986671447754</t>
   </si>
   <si>
     <t xml:space="preserve">3.51640963554382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54094266891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50168943405151</t>
+    <t xml:space="preserve">3.54094219207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50168991088867</t>
   </si>
   <si>
     <t xml:space="preserve">3.47552084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3561270236969</t>
+    <t xml:space="preserve">3.35612654685974</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724717140198</t>
+    <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
     <t xml:space="preserve">3.36103320121765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37575316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3773889541626</t>
+    <t xml:space="preserve">3.37575268745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738847732544</t>
   </si>
   <si>
     <t xml:space="preserve">3.35285568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3855664730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136167526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150345802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061419487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46734309196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696970939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281053543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337060928345</t>
+    <t xml:space="preserve">3.38556623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150321960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061467170715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44280982017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39701533317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337037086487</t>
   </si>
   <si>
     <t xml:space="preserve">3.488605260849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4591658115387</t>
+    <t xml:space="preserve">3.45916533470154</t>
   </si>
   <si>
     <t xml:space="preserve">3.4182767868042</t>
@@ -278,85 +278,85 @@
     <t xml:space="preserve">3.50823187828064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55729818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584956169128</t>
+    <t xml:space="preserve">3.557297706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584932327271</t>
   </si>
   <si>
     <t xml:space="preserve">3.5785596370697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60472869873047</t>
+    <t xml:space="preserve">3.60472846031189</t>
   </si>
   <si>
     <t xml:space="preserve">3.56547570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5981867313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6472532749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996430397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636401176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5671112537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897840499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355730056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38065934181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33813571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28743410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668685913086</t>
+    <t xml:space="preserve">3.59818696975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907551765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360783576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996335029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178559303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355777740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38065958023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33813548088074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28743433952332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668709754944</t>
   </si>
   <si>
     <t xml:space="preserve">3.27598524093628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2432746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21874165534973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25962996482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495538711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07644963264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462691307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12551546096802</t>
+    <t xml:space="preserve">3.24327445030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21874141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25963020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1549551486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07644939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1255156993866</t>
   </si>
   <si>
     <t xml:space="preserve">3.27107882499695</t>
@@ -365,43 +365,43 @@
     <t xml:space="preserve">3.31850934028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33486437797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846419334412</t>
+    <t xml:space="preserve">3.33486461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36757588386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846395492554</t>
   </si>
   <si>
     <t xml:space="preserve">3.30869626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818134307861</t>
+    <t xml:space="preserve">3.24818062782288</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454224586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528877258301</t>
+    <t xml:space="preserve">3.48206281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421353340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528924942017</t>
   </si>
   <si>
     <t xml:space="preserve">3.58183121681213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63253283500671</t>
+    <t xml:space="preserve">3.63253259658813</t>
   </si>
   <si>
     <t xml:space="preserve">3.60309362411499</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">3.64071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6161777973175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75192713737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7617404460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412323951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809572219849</t>
+    <t xml:space="preserve">3.61617684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435483932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75192666053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809548377991</t>
   </si>
   <si>
     <t xml:space="preserve">3.77646064758301</t>
@@ -437,76 +437,76 @@
     <t xml:space="preserve">3.791179895401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73720741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7944507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91548109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86314344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89258432388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440585136414</t>
+    <t xml:space="preserve">3.73720788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730333328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91548156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258360862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529439926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.86641478538513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94655632972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150860786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454739570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169458389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04305362701416</t>
+    <t xml:space="preserve">3.94655704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454787254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8516948223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305219650269</t>
   </si>
   <si>
     <t xml:space="preserve">3.96618270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88767766952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384530067444</t>
+    <t xml:space="preserve">3.88767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898403167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138457775116</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165015220642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02669811248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398684501648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272443771362</t>
+    <t xml:space="preserve">4.02669763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398732185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272515296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.00216436386108</t>
@@ -515,25 +515,25 @@
     <t xml:space="preserve">4.05613803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524972915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08394241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16244792938232</t>
+    <t xml:space="preserve">3.97926759719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08394193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16244697570801</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693462371826</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">4.44048929214478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41595649719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37506723403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350784301758</t>
+    <t xml:space="preserve">4.41595554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37506771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59586572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
     <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9924840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439710617065</t>
+    <t xml:space="preserve">4.99248361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439615249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710765838623</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">4.90661811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9638614654541</t>
+    <t xml:space="preserve">4.96386241912842</t>
   </si>
   <si>
     <t xml:space="preserve">5.02928352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03337287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150453567505</t>
+    <t xml:space="preserve">5.03337240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
@@ -596,109 +596,109 @@
     <t xml:space="preserve">5.28688049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270084381104</t>
+    <t xml:space="preserve">5.36456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3686580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56901121139526</t>
+    <t xml:space="preserve">5.56901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">5.5526556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30323648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2664361000061</t>
+    <t xml:space="preserve">5.30323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26643705368042</t>
   </si>
   <si>
     <t xml:space="preserve">5.54856729507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59354448318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709867477417</t>
+    <t xml:space="preserve">5.59354400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.601722240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70803260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709819793701</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82251977920532</t>
+    <t xml:space="preserve">5.82251930236816</t>
   </si>
   <si>
     <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78571939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905588150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48723459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46678972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581159591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5608344078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64308166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69674634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4614462852478</t>
+    <t xml:space="preserve">5.78572034835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4790563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4872350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46679019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083393096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6430811882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46144533157349</t>
   </si>
   <si>
     <t xml:space="preserve">5.57290410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6554651260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.705002784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73802757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84948587417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1012978553772</t>
+    <t xml:space="preserve">5.65546560287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70500230789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73802661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8040771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84948492050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10129833221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.84122896194458</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389959335327</t>
+    <t xml:space="preserve">5.73389863967896</t>
   </si>
   <si>
     <t xml:space="preserve">5.75866794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133762359619</t>
+    <t xml:space="preserve">5.65133714675903</t>
   </si>
   <si>
     <t xml:space="preserve">5.81233263015747</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">5.7793083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77105140686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84535789489746</t>
+    <t xml:space="preserve">5.77105188369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84535694122314</t>
   </si>
   <si>
     <t xml:space="preserve">5.68849039077759</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57703304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52336740493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813528060913</t>
+    <t xml:space="preserve">5.63069772720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5233678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813575744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.48621463775635</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">5.55639219284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32934761047363</t>
+    <t xml:space="preserve">5.32934713363647</t>
   </si>
   <si>
     <t xml:space="preserve">5.27568244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771270751953</t>
+    <t xml:space="preserve">5.16009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771318435669</t>
   </si>
   <si>
     <t xml:space="preserve">5.30045127868652</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">5.12294387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19312143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230302810669</t>
+    <t xml:space="preserve">5.1931209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998750686646</t>
+    <t xml:space="preserve">5.17248106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">5.39952516555786</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">5.60592889785767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71325922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977066040039</t>
+    <t xml:space="preserve">5.71325874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977113723755</t>
   </si>
   <si>
     <t xml:space="preserve">5.77518033981323</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86599826812744</t>
+    <t xml:space="preserve">5.87012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86599779129028</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489412307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04763317108154</t>
+    <t xml:space="preserve">5.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04763269424438</t>
   </si>
   <si>
     <t xml:space="preserve">5.93204689025879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86186933517456</t>
+    <t xml:space="preserve">5.86186981201172</t>
   </si>
   <si>
     <t xml:space="preserve">5.95268726348877</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">5.97332763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06827402114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955476760864</t>
+    <t xml:space="preserve">6.06827354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955429077148</t>
   </si>
   <si>
     <t xml:space="preserve">6.17560386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19211626052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21275663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18385934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12193870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16734743118286</t>
+    <t xml:space="preserve">6.17973184585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19211578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21275615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18385982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12193822860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16734790802002</t>
   </si>
   <si>
     <t xml:space="preserve">6.13845062255859</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">5.98158359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05176115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09717035293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798780441284</t>
+    <t xml:space="preserve">6.05176067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09717082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798732757568</t>
   </si>
   <si>
     <t xml:space="preserve">6.15909147262573</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">6.06001710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98571109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08891487121582</t>
+    <t xml:space="preserve">5.9857120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0889139175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140651702881</t>
@@ -905,34 +905,34 @@
     <t xml:space="preserve">5.87425327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93617534637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96094369888306</t>
+    <t xml:space="preserve">5.93617486953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9609432220459</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222444534302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207601547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8526086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958436965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801645278931</t>
+    <t xml:space="preserve">6.2292685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85260820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801597595215</t>
   </si>
   <si>
     <t xml:space="preserve">6.82371187210083</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">6.77004671096802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60492372512817</t>
+    <t xml:space="preserve">6.60492324829102</t>
   </si>
   <si>
     <t xml:space="preserve">6.69574069976807</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">6.58015489578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44392871856689</t>
+    <t xml:space="preserve">6.44392824172974</t>
   </si>
   <si>
     <t xml:space="preserve">6.43980073928833</t>
@@ -962,28 +962,28 @@
     <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45631313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65446043014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71638202667236</t>
+    <t xml:space="preserve">6.45631217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57189893722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65446138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71638154983521</t>
   </si>
   <si>
     <t xml:space="preserve">6.61318016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44805717468262</t>
+    <t xml:space="preserve">6.53061771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4480562210083</t>
   </si>
   <si>
     <t xml:space="preserve">6.65858793258667</t>
@@ -992,163 +992,163 @@
     <t xml:space="preserve">6.55538702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.625563621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50584936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905170440674</t>
+    <t xml:space="preserve">6.62556314468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50584983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905122756958</t>
   </si>
   <si>
     <t xml:space="preserve">6.7287654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84848022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75766229629517</t>
+    <t xml:space="preserve">6.84847974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75766277313232</t>
   </si>
   <si>
     <t xml:space="preserve">6.90214490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812559127808</t>
+    <t xml:space="preserve">6.70812511444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.68748569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7122540473938</t>
+    <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">6.77417469024658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43466758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47182083129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356439590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7607855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.843346118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619382858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66170978546143</t>
+    <t xml:space="preserve">7.43466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594785690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4718189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356344223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932680130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334707260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6617112159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.75665712356567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95893287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590951919556</t>
+    <t xml:space="preserve">7.95893335342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590808868408</t>
   </si>
   <si>
     <t xml:space="preserve">7.57914972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28192758560181</t>
+    <t xml:space="preserve">7.28192853927612</t>
   </si>
   <si>
     <t xml:space="preserve">7.40989923477173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28605699539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1333179473877</t>
+    <t xml:space="preserve">7.28605651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331699371338</t>
   </si>
   <si>
     <t xml:space="preserve">7.22413492202759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41402673721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769237518311</t>
+    <t xml:space="preserve">7.41402626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769189834595</t>
   </si>
   <si>
     <t xml:space="preserve">7.57089328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29431200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890327453613</t>
+    <t xml:space="preserve">7.29431247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787257194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890375137329</t>
   </si>
   <si>
     <t xml:space="preserve">7.38100147247314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1993670463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011655807495</t>
+    <t xml:space="preserve">7.33972263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011608123779</t>
   </si>
   <si>
     <t xml:space="preserve">7.01773118972778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05488443374634</t>
+    <t xml:space="preserve">7.05488395690918</t>
   </si>
   <si>
     <t xml:space="preserve">6.96406650543213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7948145866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940776824951</t>
+    <t xml:space="preserve">6.79481506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940586090088</t>
   </si>
   <si>
     <t xml:space="preserve">6.68335771560669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.790687084198</t>
+    <t xml:space="preserve">6.79068756103516</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111013412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965183258057</t>
+    <t xml:space="preserve">7.19111061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965326309204</t>
   </si>
   <si>
     <t xml:space="preserve">6.84022378921509</t>
@@ -1157,49 +1157,49 @@
     <t xml:space="preserve">7.05075597763062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23651933670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43054008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25715923309326</t>
+    <t xml:space="preserve">7.2365198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2612886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25715970993042</t>
   </si>
   <si>
     <t xml:space="preserve">7.36036157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2778000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23138618469238</t>
+    <t xml:space="preserve">7.27780055999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23138523101807</t>
   </si>
   <si>
     <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40476608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4130220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1405668258667</t>
+    <t xml:space="preserve">8.40476417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41301918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.24789810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17359161376953</t>
+    <t xml:space="preserve">8.17359352111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.09103202819824</t>
@@ -1214,46 +1214,46 @@
     <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20248889923096</t>
+    <t xml:space="preserve">8.14469528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295124053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522747039795</t>
+    <t xml:space="preserve">8.35522842407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.36348533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33045959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47907161712646</t>
+    <t xml:space="preserve">8.33046054840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.52035140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070652008057</t>
+    <t xml:space="preserve">8.79280471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71024417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070556640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408546447754</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.86710929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6689624786377</t>
+    <t xml:space="preserve">8.66896152496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.65244960784912</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74605751037598</t>
+    <t xml:space="preserve">8.74605655670166</t>
   </si>
   <si>
     <t xml:space="preserve">8.7044095993042</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75438594818115</t>
+    <t xml:space="preserve">8.75438690185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.24628257751465</t>
@@ -1295,40 +1295,40 @@
     <t xml:space="preserve">8.30875492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34623908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41287517547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8793306350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82935428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81269359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82102298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8626708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50450038909912</t>
+    <t xml:space="preserve">8.3462381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41287422180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55447673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87932968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82935333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81269454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82102394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5044994354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.62111377716064</t>
@@ -1343,106 +1343,106 @@
     <t xml:space="preserve">8.25461196899414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58779621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49617004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3628978729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42120265960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21712970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08802032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59612560272217</t>
+    <t xml:space="preserve">8.58779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49617099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42120361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21712875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08802127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59612655639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639558792114</t>
+    <t xml:space="preserve">8.16298770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.92142915725708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78815698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733255386353</t>
+    <t xml:space="preserve">7.78815507888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733207702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.85062742233276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6132345199585</t>
+    <t xml:space="preserve">7.61323499679565</t>
   </si>
   <si>
     <t xml:space="preserve">7.863121509552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74234342575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572860717773</t>
+    <t xml:space="preserve">7.74234390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67154216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572908401489</t>
   </si>
   <si>
     <t xml:space="preserve">7.87145185470581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72152042388916</t>
+    <t xml:space="preserve">7.72151947021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.59241104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57158803939819</t>
+    <t xml:space="preserve">7.57158756256104</t>
   </si>
   <si>
     <t xml:space="preserve">7.82980442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659795761108</t>
+    <t xml:space="preserve">7.54659843444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405847549438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84229850769043</t>
+    <t xml:space="preserve">7.84229755401611</t>
   </si>
   <si>
     <t xml:space="preserve">7.79232025146484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319007873535</t>
+    <t xml:space="preserve">7.61740064620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">7.74650859832764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68819999694824</t>
+    <t xml:space="preserve">7.68820095062256</t>
   </si>
   <si>
     <t xml:space="preserve">7.44664287567139</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">7.28838109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14677762985229</t>
+    <t xml:space="preserve">7.14677906036377</t>
   </si>
   <si>
     <t xml:space="preserve">7.19259119033813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47163152694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17131614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47951221466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32957935333252</t>
+    <t xml:space="preserve">7.47163200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321229934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637241363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1713171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47951126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32957744598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.20463562011719</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">8.23378849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37955570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5294885635376</t>
+    <t xml:space="preserve">8.37955665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52948760986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.0542516708374</t>
@@ -1493,67 +1493,67 @@
     <t xml:space="preserve">8.99594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01260375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07923984527588</t>
+    <t xml:space="preserve">9.01260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427627563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0792407989502</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255741119385</t>
+    <t xml:space="preserve">9.11255931854248</t>
   </si>
   <si>
     <t xml:space="preserve">9.0959005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02093410491943</t>
+    <t xml:space="preserve">9.02093315124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02926349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66276264190674</t>
+    <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02138423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08385562896729</t>
+    <t xml:space="preserve">8.02138328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0838565826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.15049266815186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00055980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35456657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98390054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9922308921814</t>
+    <t xml:space="preserve">8.00056076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9839015007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99223041534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07969188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28376483917236</t>
+    <t xml:space="preserve">8.07969093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28376579284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.53781795501709</t>
@@ -1562,58 +1562,58 @@
     <t xml:space="preserve">8.46285152435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13799953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00472450256348</t>
+    <t xml:space="preserve">8.60445308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13799858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00472354888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01721858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26294326782227</t>
+    <t xml:space="preserve">8.01722049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26294231414795</t>
   </si>
   <si>
     <t xml:space="preserve">8.04220771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20046997070312</t>
+    <t xml:space="preserve">8.20047092437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.19214057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09634971618652</t>
+    <t xml:space="preserve">8.09635066986084</t>
   </si>
   <si>
     <t xml:space="preserve">8.14216327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12550258636475</t>
+    <t xml:space="preserve">8.12550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">8.17964649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94641828536987</t>
+    <t xml:space="preserve">7.94641923904419</t>
   </si>
   <si>
     <t xml:space="preserve">8.25877666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227676391602</t>
+    <t xml:space="preserve">7.97557210922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227771759033</t>
   </si>
   <si>
     <t xml:space="preserve">7.81731033325195</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">7.62989377975464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79648399353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483751296997</t>
+    <t xml:space="preserve">7.79648494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.22129344940186</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21296405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18381118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73772811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38788509368896</t>
+    <t xml:space="preserve">8.21296501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18380928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630432128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73772716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43786334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38788604736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.62944316864014</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77937602996826</t>
+    <t xml:space="preserve">8.51283073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77937507629395</t>
   </si>
   <si>
     <t xml:space="preserve">8.87100124359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51237773895264</t>
+    <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
     <t xml:space="preserve">9.37910556793213</t>
@@ -1685,31 +1685,31 @@
     <t xml:space="preserve">9.56235599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59567546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54569816589355</t>
+    <t xml:space="preserve">9.59567356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54569625854492</t>
   </si>
   <si>
     <t xml:space="preserve">9.39576435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28748035430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29580974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65398216247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49571990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35411739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66231155395508</t>
+    <t xml:space="preserve">9.28747940063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29580879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65398120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49571895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35411643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66231250762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.17086601257324</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">9.22917366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2708215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96262741088867</t>
+    <t xml:space="preserve">9.27082061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96262550354004</t>
   </si>
   <si>
     <t xml:space="preserve">9.13754749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16253662109375</t>
+    <t xml:space="preserve">9.16253566741943</t>
   </si>
   <si>
     <t xml:space="preserve">9.0709114074707</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">8.56280708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64610290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06258296966553</t>
+    <t xml:space="preserve">8.64610385894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06258201599121</t>
   </si>
   <si>
     <t xml:space="preserve">9.10422992706299</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">8.65155124664307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58376216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781372070312</t>
+    <t xml:space="preserve">8.58376312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781467437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.59223747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98202323913574</t>
+    <t xml:space="preserve">8.98202133178711</t>
   </si>
   <si>
     <t xml:space="preserve">8.70239353179932</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">8.77018260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6430778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51597499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48207950592041</t>
+    <t xml:space="preserve">8.64307689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5159740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48207855224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.49055290222168</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">8.42700004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30413436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26176643371582</t>
+    <t xml:space="preserve">8.30413341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2617654800415</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39310646057129</t>
+    <t xml:space="preserve">8.39310550689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.33379173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31260871887207</t>
+    <t xml:space="preserve">8.31260776519775</t>
   </si>
   <si>
     <t xml:space="preserve">8.27871322631836</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">8.28718566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023887634277</t>
+    <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2956600189209</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500335693359</t>
+    <t xml:space="preserve">8.10500431060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397735595703</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32531833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45242214202881</t>
+    <t xml:space="preserve">8.44394874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">8.52444839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849708557129</t>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44818592071533</t>
+    <t xml:space="preserve">8.44818496704102</t>
   </si>
   <si>
     <t xml:space="preserve">8.6091833114624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62613105773926</t>
+    <t xml:space="preserve">8.62613010406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528877258301</t>
@@ -1880,40 +1880,40 @@
     <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35921192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17279243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11771488189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03297805786133</t>
+    <t xml:space="preserve">8.35921287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1727933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11771297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03297710418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13466262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9651894569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163660049438</t>
+    <t xml:space="preserve">8.13466167449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96518898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9016375541687</t>
   </si>
   <si>
     <t xml:space="preserve">7.79995441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82961130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792863845825</t>
+    <t xml:space="preserve">7.82961177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
@@ -1922,37 +1922,37 @@
     <t xml:space="preserve">8.25329208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22787094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72369146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945571899414</t>
+    <t xml:space="preserve">8.22787189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113790512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66013956069946</t>
+    <t xml:space="preserve">7.66014003753662</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66002655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41429042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684398651123</t>
+    <t xml:space="preserve">8.66002559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41429138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684494018555</t>
   </si>
   <si>
     <t xml:space="preserve">8.43123817443848</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">8.42276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19821357727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21939849853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46513175964355</t>
+    <t xml:space="preserve">8.19821262359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24058246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21939754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.53292083740234</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">8.71934127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46936798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8972864151001</t>
+    <t xml:space="preserve">8.46936893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13042449951172</t>
+    <t xml:space="preserve">8.88881206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90576076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13042545318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.22363471984863</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37192153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49902629852295</t>
+    <t xml:space="preserve">8.37192249298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49902725219727</t>
   </si>
   <si>
     <t xml:space="preserve">8.76170825958252</t>
@@ -2021,67 +2021,67 @@
     <t xml:space="preserve">8.81254959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60070991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69391822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85491752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02438926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28707218170166</t>
+    <t xml:space="preserve">8.60071086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85491847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02439022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28707122802734</t>
   </si>
   <si>
     <t xml:space="preserve">9.57517528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42264842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401802062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906887054443</t>
+    <t xml:space="preserve">9.47349071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42264938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906982421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.65143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56669998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75311946868896</t>
+    <t xml:space="preserve">9.53280639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63449001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56670093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78701591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83785438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.871750831604</t>
+    <t xml:space="preserve">9.78701496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83785533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87174987792969</t>
   </si>
   <si>
     <t xml:space="preserve">9.86327743530273</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">9.82090950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91411876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97343444824219</t>
+    <t xml:space="preserve">9.91411972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97343349456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0242757797241</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">10.0835905075073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0158023834229</t>
+    <t xml:space="preserve">10.0158014297485</t>
   </si>
   <si>
     <t xml:space="preserve">9.93953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0666446685791</t>
+    <t xml:space="preserve">10.0666437149048</t>
   </si>
   <si>
     <t xml:space="preserve">10.1768007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2276430130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1598539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2615356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530641555786</t>
+    <t xml:space="preserve">10.2276420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1598529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2615375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530632019043</t>
   </si>
   <si>
     <t xml:space="preserve">10.1683263778687</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">10.1937475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0496950149536</t>
+    <t xml:space="preserve">10.0496969223022</t>
   </si>
   <si>
     <t xml:space="preserve">9.82938289642334</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">9.998854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92259216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51585865020752</t>
+    <t xml:space="preserve">9.92259311676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51585960388184</t>
   </si>
   <si>
     <t xml:space="preserve">10.0581703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73617362976074</t>
+    <t xml:space="preserve">9.73617267608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296436309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54975414276123</t>
+    <t xml:space="preserve">9.64296340942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54975509643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.29554557800293</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">8.16431999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32108020782471</t>
+    <t xml:space="preserve">8.32108116149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603126525879</t>
@@ -2186,31 +2186,31 @@
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674514770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322233200073</t>
+    <t xml:space="preserve">7.70674419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60082530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322137832642</t>
   </si>
   <si>
     <t xml:space="preserve">7.29153728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99072504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71109533309937</t>
+    <t xml:space="preserve">6.99072456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">6.61364936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61376333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5247917175293</t>
+    <t xml:space="preserve">5.6137638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52479124069214</t>
   </si>
   <si>
     <t xml:space="preserve">4.9824800491333</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">5.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02484750747681</t>
+    <t xml:space="preserve">5.02484846115112</t>
   </si>
   <si>
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647485733032</t>
+    <t xml:space="preserve">5.62647390365601</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80865669250488</t>
+    <t xml:space="preserve">5.80865716934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.50784349441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210975646973</t>
+    <t xml:space="preserve">5.26210927963257</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690237045288</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">4.89774417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76216650009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27481937408447</t>
+    <t xml:space="preserve">4.76216602325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27481985092163</t>
   </si>
   <si>
     <t xml:space="preserve">5.41463422775269</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">5.0163745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10111093521118</t>
+    <t xml:space="preserve">5.16466283798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10111045837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.93163871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96129608154297</t>
+    <t xml:space="preserve">4.96129655838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.33837175369263</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">5.73663091659546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9315242767334</t>
+    <t xml:space="preserve">5.93152379989624</t>
   </si>
   <si>
     <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70273637771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53326511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49513339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87220859527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93576049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10099601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13065433502197</t>
+    <t xml:space="preserve">5.70273733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53326463699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49513387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87220907211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93576097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1009955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13065385818481</t>
   </si>
   <si>
     <t xml:space="preserve">5.88068294525146</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289386749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357866287231</t>
+    <t xml:space="preserve">5.81289339065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
@@ -2333,52 +2333,52 @@
     <t xml:space="preserve">5.65189504623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015420913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03320741653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3552041053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2916522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39333581924438</t>
+    <t xml:space="preserve">6.05015468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91881322860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03320693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35520458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29165267944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39333534240723</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835710525513</t>
+    <t xml:space="preserve">6.94835662841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.91022491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04156637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24917078018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088157653809</t>
+    <t xml:space="preserve">7.04156732559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24916982650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088205337524</t>
   </si>
   <si>
     <t xml:space="preserve">7.0034351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70685911178589</t>
+    <t xml:space="preserve">6.70685863494873</t>
   </si>
   <si>
     <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71533298492432</t>
+    <t xml:space="preserve">6.71533346176147</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64330720901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55009746551514</t>
+    <t xml:space="preserve">6.64330673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55009794235229</t>
   </si>
   <si>
     <t xml:space="preserve">6.6094126701355</t>
@@ -2408,37 +2408,37 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12641668319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1518383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01626062393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31707334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13912677764893</t>
+    <t xml:space="preserve">6.28741598129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12641763687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15183782577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01626014709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31707239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13912725448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981204986572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36367893218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24504709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47383451461792</t>
+    <t xml:space="preserve">6.04591798782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36367845535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2450475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47383499145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.47807168960571</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286573410034</t>
+    <t xml:space="preserve">6.06286478042603</t>
   </si>
   <si>
     <t xml:space="preserve">6.10523319244385</t>
@@ -2456,46 +2456,46 @@
     <t xml:space="preserve">6.22386360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336442947388</t>
+    <t xml:space="preserve">6.14336395263672</t>
   </si>
   <si>
     <t xml:space="preserve">6.08404874801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95270824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07133865356445</t>
+    <t xml:space="preserve">5.95270872116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07133817672729</t>
   </si>
   <si>
     <t xml:space="preserve">6.18149518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0204963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931287765503</t>
+    <t xml:space="preserve">6.02049732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931240081787</t>
   </si>
   <si>
     <t xml:space="preserve">6.38486194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32978343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32131004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23657464981079</t>
+    <t xml:space="preserve">6.32978391647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3213095664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23657321929932</t>
   </si>
   <si>
     <t xml:space="preserve">6.19420623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25775861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2747049331665</t>
+    <t xml:space="preserve">6.25775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.23233699798584</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">6.98648834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019678115845</t>
+    <t xml:space="preserve">7.16019630432129</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">7.0161452293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90175247192383</t>
+    <t xml:space="preserve">6.90175199508667</t>
   </si>
   <si>
     <t xml:space="preserve">6.85938405990601</t>
@@ -2540,28 +2540,28 @@
     <t xml:space="preserve">6.79583215713501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44417715072632</t>
+    <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
     <t xml:space="preserve">6.10946989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0543909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04168081283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16031122207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09675931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2153902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94847059249878</t>
+    <t xml:space="preserve">6.05439138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04168128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16031169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09675884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21538972854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
     <t xml:space="preserve">6.09252309799194</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">6.00778675079346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90610265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57563257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60105323791504</t>
+    <t xml:space="preserve">5.90610313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57563209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49089670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2591,37 +2591,37 @@
     <t xml:space="preserve">5.28752994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06297922134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05874252319336</t>
+    <t xml:space="preserve">5.06297969818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0587420463562</t>
   </si>
   <si>
     <t xml:space="preserve">5.01213788986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616083145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43158149719238</t>
+    <t xml:space="preserve">5.29176664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43158102035522</t>
   </si>
   <si>
     <t xml:space="preserve">5.76205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81713056564331</t>
+    <t xml:space="preserve">5.81713008880615</t>
   </si>
   <si>
     <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93988275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74075412750244</t>
+    <t xml:space="preserve">6.9398832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74075317382812</t>
   </si>
   <si>
     <t xml:space="preserve">6.82125282287598</t>
@@ -2630,97 +2630,97 @@
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09652996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49914121627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45253705978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845546722412</t>
+    <t xml:space="preserve">8.09653091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045406341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303623199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49914073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45253658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5584568977356</t>
   </si>
   <si>
     <t xml:space="preserve">7.62200880050659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77453327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8719801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84232139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67285013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63472032546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011190414429</t>
+    <t xml:space="preserve">7.77453374862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77029657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079622268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87197971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84232234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63471794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011095046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.8253755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85503196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68555974960327</t>
+    <t xml:space="preserve">7.85503339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68556070327759</t>
   </si>
   <si>
     <t xml:space="preserve">7.5245623588562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4779577255249</t>
+    <t xml:space="preserve">7.47795724868774</t>
   </si>
   <si>
     <t xml:space="preserve">7.58811378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56693029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41016864776611</t>
+    <t xml:space="preserve">7.56692934036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41016817092896</t>
   </si>
   <si>
     <t xml:space="preserve">7.28730154037476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22374820709229</t>
+    <t xml:space="preserve">7.22374868392944</t>
   </si>
   <si>
     <t xml:space="preserve">7.32543277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31695890426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985462188721</t>
+    <t xml:space="preserve">7.3169584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985509872437</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2729,49 +2729,49 @@
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15596008300781</t>
+    <t xml:space="preserve">7.15595960617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64319229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727245330811</t>
+    <t xml:space="preserve">7.64319276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727340698242</t>
   </si>
   <si>
     <t xml:space="preserve">7.85926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21515941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23210906982422</t>
+    <t xml:space="preserve">8.21516036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2321081161499</t>
   </si>
   <si>
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668888092041</t>
+    <t xml:space="preserve">8.20668697357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.30837059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79148054122925</t>
+    <t xml:space="preserve">8.14313411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">7.65166568756104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03721523284912</t>
+    <t xml:space="preserve">8.0372142791748</t>
   </si>
   <si>
     <t xml:space="preserve">7.92282199859619</t>
@@ -2780,16 +2780,16 @@
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63460350036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00755786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39734363555908</t>
+    <t xml:space="preserve">8.88033866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63460445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39734268188477</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965435028076</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">8.78712844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544673919678</t>
+    <t xml:space="preserve">8.68544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16844081878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20233631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5582275390625</t>
+    <t xml:space="preserve">9.1684398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55822658538818</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928310394287</t>
+    <t xml:space="preserve">9.04133796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.04981136322021</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">9.71075248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3972282409668</t>
+    <t xml:space="preserve">9.39722919464111</t>
   </si>
   <si>
     <t xml:space="preserve">9.44807052612305</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433300018311</t>
+    <t xml:space="preserve">9.52433204650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.43112373352051</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">9.02747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97554683685303</t>
+    <t xml:space="preserve">8.97554588317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.03613376617432</t>
@@ -2873,34 +2873,34 @@
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0880651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20924091339111</t>
+    <t xml:space="preserve">8.96689128875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08806610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2092399597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386215209961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33907032012939</t>
+    <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.43427753448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63335037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68527984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40831184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47755336761475</t>
+    <t xml:space="preserve">9.63334941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68528079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40831089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47755527496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.32175922393799</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882457733154</t>
+    <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.26117134094238</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">9.31310367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33041381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30444812774658</t>
+    <t xml:space="preserve">9.33041477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3044490814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.34772491455078</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00151252746582</t>
+    <t xml:space="preserve">9.00151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">8.75916481018066</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">8.82840633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05344486236572</t>
+    <t xml:space="preserve">9.05344581604004</t>
   </si>
   <si>
     <t xml:space="preserve">9.20058536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36503505706787</t>
+    <t xml:space="preserve">9.36503601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.41696739196777</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">8.99285888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.252516746521</t>
+    <t xml:space="preserve">9.25251579284668</t>
   </si>
   <si>
     <t xml:space="preserve">9.17461967468262</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706283569336</t>
+    <t xml:space="preserve">8.83706188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84571838378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86302757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78513050079346</t>
+    <t xml:space="preserve">8.84571743011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86302852630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
     <t xml:space="preserve">8.72454357147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63798999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68126583099365</t>
+    <t xml:space="preserve">8.63798904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68126678466797</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">8.44324588775635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36967658996582</t>
+    <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.26581192016602</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">8.23119163513184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28744983673096</t>
+    <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.74185466766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4389181137085</t>
+    <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
     <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42160797119141</t>
+    <t xml:space="preserve">8.42160701751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.3610200881958</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">8.50383281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54278182983398</t>
+    <t xml:space="preserve">8.54278087615967</t>
   </si>
   <si>
     <t xml:space="preserve">8.58605861663818</t>
@@ -3098,31 +3098,31 @@
     <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85901403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93691062927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87632417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749708175659</t>
+    <t xml:space="preserve">7.85901308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93691110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87632322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749755859375</t>
   </si>
   <si>
     <t xml:space="preserve">7.96287631988525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91960048675537</t>
+    <t xml:space="preserve">7.91960000991821</t>
   </si>
   <si>
     <t xml:space="preserve">7.91527271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95854949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96720504760742</t>
+    <t xml:space="preserve">7.95854902267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
     <t xml:space="preserve">7.82439184188843</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">7.53011131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.556077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981784820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39162635803223</t>
+    <t xml:space="preserve">7.55607652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39162731170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.3526782989502</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">7.09734678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16658878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05839729309082</t>
+    <t xml:space="preserve">7.166588306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05839776992798</t>
   </si>
   <si>
     <t xml:space="preserve">7.18390035629272</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">7.33969497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51280117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42191982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37431621551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33104085922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15360641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06272554397583</t>
+    <t xml:space="preserve">7.51280164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42192029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37431669235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33104038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15360689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
     <t xml:space="preserve">7.14927911758423</t>
@@ -3188,28 +3188,28 @@
     <t xml:space="preserve">7.20121002197266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27045297622681</t>
+    <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
     <t xml:space="preserve">7.19255495071411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25747060775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26179790496826</t>
+    <t xml:space="preserve">7.25747013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2617974281311</t>
   </si>
   <si>
     <t xml:space="preserve">7.24448728561401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4046106338501</t>
+    <t xml:space="preserve">7.40461015701294</t>
   </si>
   <si>
     <t xml:space="preserve">7.45654153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31805658340454</t>
+    <t xml:space="preserve">7.3180570602417</t>
   </si>
   <si>
     <t xml:space="preserve">7.41759300231934</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34402322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23583126068115</t>
+    <t xml:space="preserve">7.34402275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23583173751831</t>
   </si>
   <si>
     <t xml:space="preserve">7.14062356948853</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">6.88096380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66458129882812</t>
+    <t xml:space="preserve">6.66458177566528</t>
   </si>
   <si>
     <t xml:space="preserve">6.42223358154297</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">6.42656087875366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40492248535156</t>
+    <t xml:space="preserve">6.40492296218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
@@ -3269,28 +3269,28 @@
     <t xml:space="preserve">6.54340744018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63861656188965</t>
+    <t xml:space="preserve">6.63861560821533</t>
   </si>
   <si>
     <t xml:space="preserve">6.49147510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36164569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43088865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56937313079834</t>
+    <t xml:space="preserve">6.36164665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47849321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43088817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5693736076355</t>
   </si>
   <si>
     <t xml:space="preserve">6.44387197494507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55639028549194</t>
+    <t xml:space="preserve">6.55638980865479</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
@@ -3302,37 +3302,37 @@
     <t xml:space="preserve">6.49580335617065</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21883392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21450567245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10198736190796</t>
+    <t xml:space="preserve">6.21883344650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21450614929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1019868850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.88560438156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20152282714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11497068405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05005550384521</t>
+    <t xml:space="preserve">6.2015233039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11497020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05005502700806</t>
   </si>
   <si>
     <t xml:space="preserve">6.08034896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70817089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60863494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46149492263794</t>
+    <t xml:space="preserve">5.70817041397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60863447189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46149444580078</t>
   </si>
   <si>
     <t xml:space="preserve">5.29704427719116</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237531661987</t>
+    <t xml:space="preserve">5.55237483978271</t>
   </si>
   <si>
     <t xml:space="preserve">5.63460111618042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53506517410278</t>
+    <t xml:space="preserve">5.53506469726562</t>
   </si>
   <si>
     <t xml:space="preserve">5.89425992965698</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">5.83367300033569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87262105941772</t>
+    <t xml:space="preserve">5.87262153625488</t>
   </si>
   <si>
     <t xml:space="preserve">5.81203460693359</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">5.7341365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05438280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08467674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05871057510376</t>
+    <t xml:space="preserve">6.05438327789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08467721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0587100982666</t>
   </si>
   <si>
     <t xml:space="preserve">6.37030172348022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38761186599731</t>
+    <t xml:space="preserve">6.38761234283447</t>
   </si>
   <si>
     <t xml:space="preserve">6.2231616973877</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">6.29673194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37895631790161</t>
+    <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
     <t xml:space="preserve">5.99812316894531</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14526414871216</t>
+    <t xml:space="preserve">6.145263671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.18421220779419</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1236252784729</t>
+    <t xml:space="preserve">6.12362480163574</t>
   </si>
   <si>
     <t xml:space="preserve">6.1755576133728</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34433555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10631418228149</t>
+    <t xml:space="preserve">6.34433507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10631465911865</t>
   </si>
   <si>
     <t xml:space="preserve">6.27900981903076</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">6.38971185684204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42956495285034</t>
+    <t xml:space="preserve">6.42956447601318</t>
   </si>
   <si>
     <t xml:space="preserve">6.3764271736145</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">6.30114984512329</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458190917969</t>
+    <t xml:space="preserve">6.32771825790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27458143234253</t>
   </si>
   <si>
     <t xml:space="preserve">6.34543085098267</t>
@@ -3485,16 +3485,16 @@
     <t xml:space="preserve">6.41627979278564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86277055740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679166793823</t>
+    <t xml:space="preserve">5.86277103424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679119110107</t>
   </si>
   <si>
     <t xml:space="preserve">5.57937431335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71221590042114</t>
+    <t xml:space="preserve">5.7122163772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.40225076675415</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59708642959595</t>
+    <t xml:space="preserve">5.59708595275879</t>
   </si>
   <si>
     <t xml:space="preserve">5.61922645568848</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">5.62808275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63251066207886</t>
+    <t xml:space="preserve">5.63251113891602</t>
   </si>
   <si>
     <t xml:space="preserve">5.80077791213989</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">5.79192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60594272613525</t>
+    <t xml:space="preserve">5.6059422492981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">5.53952169418335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53066539764404</t>
+    <t xml:space="preserve">5.53066492080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.66793584823608</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">5.77863740921021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92476367950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85834217071533</t>
+    <t xml:space="preserve">5.92476415634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85834264755249</t>
   </si>
   <si>
     <t xml:space="preserve">5.40667915344238</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">5.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74321269989014</t>
+    <t xml:space="preserve">5.74321317672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.84948635101318</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">6.07088994979858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16387939453125</t>
+    <t xml:space="preserve">6.16387987136841</t>
   </si>
   <si>
     <t xml:space="preserve">5.96904468536377</t>
@@ -3623,10 +3623,10 @@
     <t xml:space="preserve">6.04432153701782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03546571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02660942077637</t>
+    <t xml:space="preserve">6.03546619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02660894393921</t>
   </si>
   <si>
     <t xml:space="preserve">5.99561262130737</t>
@@ -3641,31 +3641,31 @@
     <t xml:space="preserve">6.01775360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06646203994751</t>
+    <t xml:space="preserve">6.06646251678467</t>
   </si>
   <si>
     <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89819526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61037111282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67236423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73435688018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80963373184204</t>
+    <t xml:space="preserve">5.89819478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61037063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67236375808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73435640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8096342086792</t>
   </si>
   <si>
     <t xml:space="preserve">5.69450378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63693857192993</t>
+    <t xml:space="preserve">5.63693904876709</t>
   </si>
   <si>
     <t xml:space="preserve">5.48195648193359</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">5.39782285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55723333358765</t>
+    <t xml:space="preserve">5.5572338104248</t>
   </si>
   <si>
     <t xml:space="preserve">5.59265851974487</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">5.6546516418457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62365436553955</t>
+    <t xml:space="preserve">5.62365484237671</t>
   </si>
   <si>
     <t xml:space="preserve">5.68121957778931</t>
@@ -3701,19 +3701,19 @@
     <t xml:space="preserve">5.72992849349976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.973473072052</t>
+    <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
     <t xml:space="preserve">6.00889682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22587299346924</t>
+    <t xml:space="preserve">6.2258734703064</t>
   </si>
   <si>
     <t xml:space="preserve">6.31886291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25244140625</t>
+    <t xml:space="preserve">6.25244092941284</t>
   </si>
   <si>
     <t xml:space="preserve">6.17273569107056</t>
@@ -3734,16 +3734,16 @@
     <t xml:space="preserve">6.44727659225464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58897495269775</t>
+    <t xml:space="preserve">6.5889744758606</t>
   </si>
   <si>
     <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42513656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23915719985962</t>
+    <t xml:space="preserve">6.42513608932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23915767669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.35428714752197</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">6.44284868240356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.531409740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668706893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75724172592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79266691207886</t>
+    <t xml:space="preserve">6.53141021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75724220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7926664352417</t>
   </si>
   <si>
     <t xml:space="preserve">6.65539598464966</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">6.64211177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325595855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49155759811401</t>
+    <t xml:space="preserve">6.63325548171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49155712127686</t>
   </si>
   <si>
     <t xml:space="preserve">6.51369762420654</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">6.50926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40299558639526</t>
+    <t xml:space="preserve">6.40299606323242</t>
   </si>
   <si>
     <t xml:space="preserve">6.45613288879395</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">6.46941661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33214712142944</t>
+    <t xml:space="preserve">6.33214664459229</t>
   </si>
   <si>
     <t xml:space="preserve">6.4074239730835</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.0539231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093320846558</t>
+    <t xml:space="preserve">6.96093368530273</t>
   </si>
   <si>
     <t xml:space="preserve">6.98307371139526</t>
@@ -3842,13 +3842,13 @@
     <t xml:space="preserve">7.32846355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63842821121216</t>
+    <t xml:space="preserve">7.63842868804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81998014450073</t>
+    <t xml:space="preserve">7.81998062133789</t>
   </si>
   <si>
     <t xml:space="preserve">7.58529186248779</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">7.19562101364136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24433040618896</t>
+    <t xml:space="preserve">7.24432992935181</t>
   </si>
   <si>
     <t xml:space="preserve">7.20447731018066</t>
@@ -3872,34 +3872,34 @@
     <t xml:space="preserve">7.30189514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52329874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42145252227783</t>
+    <t xml:space="preserve">7.52329921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49230241775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
     <t xml:space="preserve">7.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48787403106689</t>
+    <t xml:space="preserve">7.48787450790405</t>
   </si>
   <si>
     <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10263204574585</t>
+    <t xml:space="preserve">7.10263252258301</t>
   </si>
   <si>
     <t xml:space="preserve">7.3151798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22661781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32403564453125</t>
+    <t xml:space="preserve">7.22661733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32403516769409</t>
   </si>
   <si>
     <t xml:space="preserve">7.35060453414917</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.25318574905396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1779088973999</t>
+    <t xml:space="preserve">7.17790842056274</t>
   </si>
   <si>
     <t xml:space="preserve">7.2753267288208</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">7.30632305145264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547410964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20004940032959</t>
+    <t xml:space="preserve">7.2354736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20004987716675</t>
   </si>
   <si>
     <t xml:space="preserve">6.95207691192627</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451169967651</t>
+    <t xml:space="preserve">6.89451217651367</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3971,10 +3971,10 @@
     <t xml:space="preserve">6.78381013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26204204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761413574219</t>
+    <t xml:space="preserve">7.26204252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25761365890503</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,28 +3983,28 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705995559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12034368515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35945987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17348146438599</t>
+    <t xml:space="preserve">7.10705947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1203441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35946035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17348098754883</t>
   </si>
   <si>
     <t xml:space="preserve">7.31960773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38602828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40374088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39931297302246</t>
+    <t xml:space="preserve">7.38602781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3993124961853</t>
   </si>
   <si>
     <t xml:space="preserve">7.27975511550903</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">7.54543924331665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47459030151367</t>
+    <t xml:space="preserve">7.47458982467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.68271017074585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60300445556641</t>
+    <t xml:space="preserve">7.60300397872925</t>
   </si>
   <si>
     <t xml:space="preserve">7.71370601654053</t>
@@ -68433,7 +68433,7 @@
     </row>
     <row r="2412">
       <c r="A2412" s="1" t="n">
-        <v>45953.6522106481</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2412" t="n">
         <v>259100</v>
@@ -68454,6 +68454,32 @@
         <v>1789</v>
       </c>
       <c r="H2412" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>45954.6511111111</v>
+      </c>
+      <c r="B2413" t="n">
+        <v>295221</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>14.3500003814697</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F2413" t="n">
+        <v>14.6099996566772</v>
+      </c>
+      <c r="G2413" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2413" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="1800">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9603259563446</t>
+    <t xml:space="preserve">2.96032619476318</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">3.13860011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12388038635254</t>
+    <t xml:space="preserve">3.12387990951538</t>
   </si>
   <si>
     <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028080940247</t>
+    <t xml:space="preserve">3.06663608551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0650007724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028057098389</t>
   </si>
   <si>
     <t xml:space="preserve">3.18930172920227</t>
@@ -68,34 +68,34 @@
     <t xml:space="preserve">3.16476845741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17131066322327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16149735450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514231681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168404579163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30051779747009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34140634536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463253974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.437903881073</t>
+    <t xml:space="preserve">3.17131114006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1614978313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205790519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168452262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30051827430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34140706062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43790364265442</t>
   </si>
   <si>
     <t xml:space="preserve">3.39374423027039</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">3.38393092155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33977150917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24000334739685</t>
+    <t xml:space="preserve">3.33977127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24000310897827</t>
   </si>
   <si>
     <t xml:space="preserve">3.14841318130493</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">3.08789825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17294645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18112421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257259368896</t>
+    <t xml:space="preserve">3.1729462146759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752463340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18112397193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257307052612</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0339252948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303674697876</t>
+    <t xml:space="preserve">3.03392553329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303698539734</t>
   </si>
   <si>
     <t xml:space="preserve">3.04373836517334</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">3.12878680229187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23019003868103</t>
+    <t xml:space="preserve">3.23019027709961</t>
   </si>
   <si>
     <t xml:space="preserve">3.2334611415863</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">3.11406683921814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1222448348999</t>
+    <t xml:space="preserve">3.14023542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12224507331848</t>
   </si>
   <si>
     <t xml:space="preserve">3.0911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0829918384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897325515747</t>
+    <t xml:space="preserve">3.08299136161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897373199463</t>
   </si>
   <si>
     <t xml:space="preserve">3.08135604858398</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">3.07481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14677715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13696432113647</t>
+    <t xml:space="preserve">3.14677762985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13696455955505</t>
   </si>
   <si>
     <t xml:space="preserve">3.21383476257324</t>
@@ -197,70 +197,70 @@
     <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36921143531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645502090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51640963554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54094219207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50168991088867</t>
+    <t xml:space="preserve">3.36921072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645525932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5098671913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5164098739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54094266891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50168967247009</t>
   </si>
   <si>
     <t xml:space="preserve">3.47552084922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35612654685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32014465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29724740982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36103320121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575268745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738847732544</t>
+    <t xml:space="preserve">3.35612678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32014489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29724717140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36103343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3757529258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3773889541626</t>
   </si>
   <si>
     <t xml:space="preserve">3.35285568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38556623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061467170715</t>
+    <t xml:space="preserve">3.3855664730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136191368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150345802307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061443328857</t>
   </si>
   <si>
     <t xml:space="preserve">3.4673433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48696947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44280982017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701533317566</t>
+    <t xml:space="preserve">3.48696970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281053543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39701509475708</t>
   </si>
   <si>
     <t xml:space="preserve">3.41337037086487</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">3.488605260849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45916533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50823187828064</t>
+    <t xml:space="preserve">3.45916557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41827726364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50823163986206</t>
   </si>
   <si>
     <t xml:space="preserve">3.557297706604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5785596370697</t>
+    <t xml:space="preserve">3.54584956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57855987548828</t>
   </si>
   <si>
     <t xml:space="preserve">3.60472846031189</t>
@@ -293,46 +293,46 @@
     <t xml:space="preserve">3.56547570228577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59818696975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907551765442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360783576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996335029602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178559303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56711149215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38065958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33813548088074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28743433952332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668709754944</t>
+    <t xml:space="preserve">3.59818649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907504081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725279808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178583145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636401176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5671112537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897864341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355753898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38065981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3381359577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28743386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668662071228</t>
   </si>
   <si>
     <t xml:space="preserve">3.27598524093628</t>
@@ -341,103 +341,103 @@
     <t xml:space="preserve">3.24327445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21874141693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25963020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1549551486969</t>
+    <t xml:space="preserve">3.21874165534973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962996482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495538711548</t>
   </si>
   <si>
     <t xml:space="preserve">3.07644939422607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08462715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1255156993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27107882499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850934028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757588386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846395492554</t>
+    <t xml:space="preserve">3.08462738990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12551593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27107858657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486485481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3675754070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846419334412</t>
   </si>
   <si>
     <t xml:space="preserve">3.30869626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033158302307</t>
+    <t xml:space="preserve">3.24818086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033134460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.48206281661987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54421353340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454200744629</t>
+    <t xml:space="preserve">3.54421377182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454224586487</t>
   </si>
   <si>
     <t xml:space="preserve">3.59655094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57528924942017</t>
+    <t xml:space="preserve">3.57528901100159</t>
   </si>
   <si>
     <t xml:space="preserve">3.58183121681213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63253259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851472854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75192666053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174068450928</t>
+    <t xml:space="preserve">3.63253283500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309338569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851449012756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6407105922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7519268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174092292786</t>
   </si>
   <si>
     <t xml:space="preserve">3.72412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77809548377991</t>
+    <t xml:space="preserve">3.77809596061707</t>
   </si>
   <si>
     <t xml:space="preserve">3.77646064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.791179895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720788955688</t>
+    <t xml:space="preserve">3.79118013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720741271973</t>
   </si>
   <si>
     <t xml:space="preserve">3.90730333328247</t>
@@ -449,94 +449,94 @@
     <t xml:space="preserve">3.99071598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91548156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86314392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89258360862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529439926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641478538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454787254333</t>
+    <t xml:space="preserve">3.91548085212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8631443977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258408546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150884628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454691886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.8516948223114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04305219650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767671585083</t>
+    <t xml:space="preserve">4.04305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618294715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767743110657</t>
   </si>
   <si>
     <t xml:space="preserve">3.86968612670898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81898403167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9138457775116</t>
+    <t xml:space="preserve">3.8189845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384553909302</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165015220642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02669763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398732185364</t>
+    <t xml:space="preserve">4.02669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9939866065979</t>
   </si>
   <si>
     <t xml:space="preserve">3.97272515296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00216436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97926759719849</t>
+    <t xml:space="preserve">4.00216484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97926735877991</t>
   </si>
   <si>
     <t xml:space="preserve">4.00707149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884811401367</t>
+    <t xml:space="preserve">4.01524829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884859085083</t>
   </si>
   <si>
     <t xml:space="preserve">4.08394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16244697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27693462371826</t>
+    <t xml:space="preserve">4.16244745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27693510055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.44048929214478</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">4.41595554351807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33009052276611</t>
+    <t xml:space="preserve">4.33009099960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506771087646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586572647095</t>
+    <t xml:space="preserve">4.59586524963379</t>
   </si>
   <si>
     <t xml:space="preserve">4.76350831985474</t>
@@ -560,46 +560,46 @@
     <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99248361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439615249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710765838623</t>
+    <t xml:space="preserve">4.99248456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8043966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
     <t xml:space="preserve">4.83301830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90661811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96386241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928352355957</t>
+    <t xml:space="preserve">4.90661859512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96386194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928304672241</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337240219116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150501251221</t>
+    <t xml:space="preserve">5.19283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150453567505</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28688049316406</t>
+    <t xml:space="preserve">5.28688144683838</t>
   </si>
   <si>
     <t xml:space="preserve">5.36456918716431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3686580657959</t>
+    <t xml:space="preserve">5.36865854263306</t>
   </si>
   <si>
     <t xml:space="preserve">5.46270132064819</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">5.56901168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5526556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30323696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26643705368042</t>
+    <t xml:space="preserve">5.55265617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30323648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
     <t xml:space="preserve">5.54856729507446</t>
@@ -629,58 +629,58 @@
     <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70803260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80207538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82251930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78572034835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4790563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4872350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46679019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581111907959</t>
+    <t xml:space="preserve">5.70803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709867477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82251977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114240646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816804885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47905731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46678972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581159591675</t>
   </si>
   <si>
     <t xml:space="preserve">5.56083393096924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6430811882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69674682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46144533157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546560287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70500230789185</t>
+    <t xml:space="preserve">5.64308166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69674634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46144580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70500326156616</t>
   </si>
   <si>
     <t xml:space="preserve">5.73802661895752</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">5.78756475448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8040771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84948492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90315103530884</t>
+    <t xml:space="preserve">5.80407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84948539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.10129833221436</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">5.82471704483032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80820465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73389863967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233263015747</t>
+    <t xml:space="preserve">5.80820417404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73389959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233358383179</t>
   </si>
   <si>
     <t xml:space="preserve">5.7793083190918</t>
@@ -731,70 +731,70 @@
     <t xml:space="preserve">5.84535694122314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68849039077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56877613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63069772720337</t>
+    <t xml:space="preserve">5.68849086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56877565383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63069725036621</t>
   </si>
   <si>
     <t xml:space="preserve">5.5770320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5233678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813575744629</t>
+    <t xml:space="preserve">5.52336692810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813480377197</t>
   </si>
   <si>
     <t xml:space="preserve">5.48621463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53162336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639219284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934713363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568244934082</t>
+    <t xml:space="preserve">5.53162288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568292617798</t>
   </si>
   <si>
     <t xml:space="preserve">5.16009616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14771318435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30045127868652</t>
+    <t xml:space="preserve">5.14771223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30045175552368</t>
   </si>
   <si>
     <t xml:space="preserve">5.12294387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1931209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15184020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17248106002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39952516555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74628400802612</t>
+    <t xml:space="preserve">5.19312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15183973312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17248058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3995246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74628353118896</t>
   </si>
   <si>
     <t xml:space="preserve">5.75041198730469</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">5.60592889785767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71325874328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77518033981323</t>
+    <t xml:space="preserve">5.71325922012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977209091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77517986297607</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86599779129028</t>
+    <t xml:space="preserve">5.87012529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86599826812744</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489459991455</t>
+    <t xml:space="preserve">5.89489412307739</t>
   </si>
   <si>
     <t xml:space="preserve">6.04763269424438</t>
@@ -833,88 +833,88 @@
     <t xml:space="preserve">5.93204689025879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86186981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17560386657715</t>
+    <t xml:space="preserve">5.86186933517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827402114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
     <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19211578369141</t>
+    <t xml:space="preserve">6.19211626052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385982513428</t>
+    <t xml:space="preserve">6.18385934829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193822860718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16734790802002</t>
+    <t xml:space="preserve">6.16734743118286</t>
   </si>
   <si>
     <t xml:space="preserve">6.13845062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15083503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98158359527588</t>
+    <t xml:space="preserve">6.1508355140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">6.05176067352295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09717082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909147262573</t>
+    <t xml:space="preserve">6.09717035293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909051895142</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9857120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0889139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87425327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93617486953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9609432220459</t>
+    <t xml:space="preserve">5.98571109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08891439437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87425374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93617534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96094369888306</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222444534302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2292685508728</t>
+    <t xml:space="preserve">6.22926902770996</t>
   </si>
   <si>
     <t xml:space="preserve">6.38200759887695</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">6.88976097106934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85260820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958341598511</t>
+    <t xml:space="preserve">6.8526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958389282227</t>
   </si>
   <si>
     <t xml:space="preserve">6.89801597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7535343170166</t>
+    <t xml:space="preserve">6.82371139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75353479385376</t>
   </si>
   <si>
     <t xml:space="preserve">6.77004671096802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60492324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574069976807</t>
+    <t xml:space="preserve">6.60492420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574165344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.58015489578247</t>
@@ -956,43 +956,43 @@
     <t xml:space="preserve">6.44392824172974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43980073928833</t>
+    <t xml:space="preserve">6.43980026245117</t>
   </si>
   <si>
     <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57189893722534</t>
+    <t xml:space="preserve">6.45631313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5718994140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.65446138381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71638154983521</t>
+    <t xml:space="preserve">6.71638202667236</t>
   </si>
   <si>
     <t xml:space="preserve">6.61318016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061771392822</t>
+    <t xml:space="preserve">6.53061819076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.66684436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4480562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65858793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55538702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62556314468384</t>
+    <t xml:space="preserve">6.44805574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65858888626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55538654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.625563621521</t>
   </si>
   <si>
     <t xml:space="preserve">6.56777095794678</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">6.55125904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60905122756958</t>
+    <t xml:space="preserve">6.6090521812439</t>
   </si>
   <si>
     <t xml:space="preserve">6.7287654876709</t>
@@ -1019,64 +1019,64 @@
     <t xml:space="preserve">6.90214490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748569488525</t>
+    <t xml:space="preserve">6.70812559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6874852180481</t>
   </si>
   <si>
     <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594785690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4718189239502</t>
+    <t xml:space="preserve">6.77417421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47182130813599</t>
   </si>
   <si>
     <t xml:space="preserve">7.46356344223022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64932680130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334707260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6617112159729</t>
+    <t xml:space="preserve">7.64932775497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480585098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7607855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619382858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171169281006</t>
   </si>
   <si>
     <t xml:space="preserve">7.75665712356567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95893335342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590808868408</t>
+    <t xml:space="preserve">7.95893287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590951919556</t>
   </si>
   <si>
     <t xml:space="preserve">7.57914972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28192853927612</t>
+    <t xml:space="preserve">7.28192806243896</t>
   </si>
   <si>
     <t xml:space="preserve">7.40989923477173</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">7.28605651855469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13331699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413492202759</t>
+    <t xml:space="preserve">7.13331747055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241358757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769189834595</t>
+    <t xml:space="preserve">7.46769142150879</t>
   </si>
   <si>
     <t xml:space="preserve">7.57089328765869</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">7.29431247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1787257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38100147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33972263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19936656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011608123779</t>
+    <t xml:space="preserve">7.17872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38100099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33972120285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011560440063</t>
   </si>
   <si>
     <t xml:space="preserve">7.01773118972778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05488395690918</t>
+    <t xml:space="preserve">7.05488443374634</t>
   </si>
   <si>
     <t xml:space="preserve">6.96406650543213</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">6.79481506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74940586090088</t>
+    <t xml:space="preserve">6.74940633773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.68335771560669</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">7.19111061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07965326309204</t>
+    <t xml:space="preserve">7.07965278625488</t>
   </si>
   <si>
     <t xml:space="preserve">6.84022378921509</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">7.05075597763062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2365198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053865432739</t>
+    <t xml:space="preserve">7.23651933670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053960800171</t>
   </si>
   <si>
     <t xml:space="preserve">7.30669689178467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2612886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25715970993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036157608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27780055999756</t>
+    <t xml:space="preserve">7.26128816604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25715923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27779960632324</t>
   </si>
   <si>
     <t xml:space="preserve">8.23138523101807</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40476417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41301918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056873321533</t>
+    <t xml:space="preserve">8.40476512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41302013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.24789810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17359352111816</t>
+    <t xml:space="preserve">8.17359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">8.09103202819824</t>
@@ -1214,28 +1214,28 @@
     <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295124053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20248985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430183410645</t>
+    <t xml:space="preserve">8.14469623565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1529541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20249080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45429992675781</t>
   </si>
   <si>
     <t xml:space="preserve">8.35522842407227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36348533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33046054840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47907066345215</t>
+    <t xml:space="preserve">8.36348438262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33045864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47906970977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.52035140991211</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">9.00746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71024417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070556640625</t>
+    <t xml:space="preserve">8.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408546447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86710929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896152496338</t>
+    <t xml:space="preserve">8.86711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6689624786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.65244960784912</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">8.67721843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42953300476074</t>
+    <t xml:space="preserve">8.42953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74605655670166</t>
+    <t xml:space="preserve">8.74605751037598</t>
   </si>
   <si>
     <t xml:space="preserve">8.7044095993042</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">8.3462381362915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41287422180176</t>
+    <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
     <t xml:space="preserve">8.55447673797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84601306915283</t>
+    <t xml:space="preserve">8.84601402282715</t>
   </si>
   <si>
     <t xml:space="preserve">8.87932968139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57946681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82935333251953</t>
+    <t xml:space="preserve">8.57946586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82935237884521</t>
   </si>
   <si>
     <t xml:space="preserve">8.81269454956055</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86267185211182</t>
+    <t xml:space="preserve">8.8626708984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.72939777374268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5044994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111377716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47118186950684</t>
+    <t xml:space="preserve">8.50449848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47118282318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.45452213287354</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">8.25461196899414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58779525756836</t>
+    <t xml:space="preserve">8.58779621124268</t>
   </si>
   <si>
     <t xml:space="preserve">8.49617099761963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36289691925049</t>
+    <t xml:space="preserve">8.36289596557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.42120361328125</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">8.08802127838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59612655639648</t>
+    <t xml:space="preserve">8.59612560272217</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777256011963</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">7.76733207702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85062742233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323499679565</t>
+    <t xml:space="preserve">7.85062837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323595046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.863121509552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74234390258789</t>
+    <t xml:space="preserve">7.74234294891357</t>
   </si>
   <si>
     <t xml:space="preserve">7.67154216766357</t>
@@ -1412,28 +1412,28 @@
     <t xml:space="preserve">7.72151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59241104125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57158756256104</t>
+    <t xml:space="preserve">7.59241008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57158613204956</t>
   </si>
   <si>
     <t xml:space="preserve">7.82980442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63405847549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229755401611</t>
+    <t xml:space="preserve">7.5465989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6340594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229850769043</t>
   </si>
   <si>
     <t xml:space="preserve">7.79232025146484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61740064620972</t>
+    <t xml:space="preserve">7.61739873886108</t>
   </si>
   <si>
     <t xml:space="preserve">7.71318912506104</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">7.68820095062256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44664287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28838109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14677906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259119033813</t>
+    <t xml:space="preserve">7.44664239883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28838205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14677810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259166717529</t>
   </si>
   <si>
     <t xml:space="preserve">7.47163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66321229934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637241363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1713171005249</t>
+    <t xml:space="preserve">7.66321325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17131614685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.47951126098633</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52948760986328</t>
+    <t xml:space="preserve">8.23378753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52948665618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.0542516708374</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">8.99594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01260280609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00427627563477</t>
+    <t xml:space="preserve">9.01260375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00427532196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.0792407989502</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0959005355835</t>
+    <t xml:space="preserve">9.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09589958190918</t>
   </si>
   <si>
     <t xml:space="preserve">9.02093315124512</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02138328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0838565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15049266815186</t>
+    <t xml:space="preserve">8.02138423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08385562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15049362182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00056076049805</t>
@@ -1550,34 +1550,34 @@
     <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07969093322754</t>
+    <t xml:space="preserve">8.07969188690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.28376579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53781795501709</t>
+    <t xml:space="preserve">8.53781890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.46285152435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60445308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13799858093262</t>
+    <t xml:space="preserve">8.60445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1379976272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.07552528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00472354888916</t>
+    <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01722049713135</t>
+    <t xml:space="preserve">8.01721954345703</t>
   </si>
   <si>
     <t xml:space="preserve">8.26294231414795</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">8.04220771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20047092437744</t>
+    <t xml:space="preserve">8.20046997070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.19214057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09635066986084</t>
+    <t xml:space="preserve">8.09634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.14216327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12550354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17964649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94641923904419</t>
+    <t xml:space="preserve">8.12550449371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17964553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94641733169556</t>
   </si>
   <si>
     <t xml:space="preserve">8.25877666473389</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">7.97557210922241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89227771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81731033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62989377975464</t>
+    <t xml:space="preserve">7.89227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81730937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989473342896</t>
   </si>
   <si>
     <t xml:space="preserve">7.79648494720459</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22129344940186</t>
+    <t xml:space="preserve">8.22129249572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21296501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18380928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630432128906</t>
+    <t xml:space="preserve">8.21296405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18381023406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630527496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.22962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73772716522217</t>
+    <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.43786334991455</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">8.51283073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69607925415039</t>
+    <t xml:space="preserve">8.69608020782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.83768272399902</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">9.37910556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56235599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567356109619</t>
+    <t xml:space="preserve">9.56235694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567451477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.54569625854492</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">9.29580879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65398120880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49571895599365</t>
+    <t xml:space="preserve">9.65398216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">9.17086601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03759288787842</t>
+    <t xml:space="preserve">9.03759384155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.22917366027832</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96262550354004</t>
+    <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
     <t xml:space="preserve">9.13754749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16253566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0709114074707</t>
+    <t xml:space="preserve">9.16253662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07091045379639</t>
   </si>
   <si>
     <t xml:space="preserve">8.56280708312988</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">8.64610385894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592227935791</t>
+    <t xml:space="preserve">9.04592132568359</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">9.10422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94596672058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91264820098877</t>
+    <t xml:space="preserve">8.94596767425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.83797073364258</t>
@@ -1769,37 +1769,37 @@
     <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223747253418</t>
+    <t xml:space="preserve">8.72781372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202133178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70239353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77018260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64307689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5159740447998</t>
+    <t xml:space="preserve">8.702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77018356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51597499847412</t>
   </si>
   <si>
     <t xml:space="preserve">8.48207855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49055290222168</t>
+    <t xml:space="preserve">8.490553855896</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700004577637</t>
+    <t xml:space="preserve">8.42700099945068</t>
   </si>
   <si>
     <t xml:space="preserve">8.30413341522217</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">8.27871322631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28718566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2956600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05839920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10500431060791</t>
+    <t xml:space="preserve">8.28718662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27024078369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29566097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10500335693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397735595703</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">8.3253173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45242309570312</t>
+    <t xml:space="preserve">8.45242118835449</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444839477539</t>
+    <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.66849803924561</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">8.6091833114624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62613010406494</t>
+    <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20244979858398</t>
+    <t xml:space="preserve">8.2024507522583</t>
   </si>
   <si>
     <t xml:space="preserve">8.35921287536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1727933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11771297454834</t>
+    <t xml:space="preserve">8.17279243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11771488189697</t>
   </si>
   <si>
     <t xml:space="preserve">8.03297710418701</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13466167449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96518898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9016375541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995441436768</t>
+    <t xml:space="preserve">8.13466262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96518993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90163660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995393753052</t>
   </si>
   <si>
     <t xml:space="preserve">7.82961177825928</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">7.73640251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72792911529541</t>
+    <t xml:space="preserve">7.72792816162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22787189483643</t>
+    <t xml:space="preserve">8.2532901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
     <t xml:space="preserve">7.7236909866333</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">7.57540321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66014003753662</t>
+    <t xml:space="preserve">7.6601390838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">8.31684494018555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43123817443848</t>
+    <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53292083740234</t>
+    <t xml:space="preserve">8.53291988372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.71934127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46936893463135</t>
+    <t xml:space="preserve">8.46936988830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.89728546142578</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90576076507568</t>
+    <t xml:space="preserve">8.88881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97354793548584</t>
+    <t xml:space="preserve">8.97354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.13042545318604</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37192249298096</t>
+    <t xml:space="preserve">8.37192344665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.49902725219727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76170825958252</t>
+    <t xml:space="preserve">8.7617073059082</t>
   </si>
   <si>
     <t xml:space="preserve">8.81254959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60071086883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139423370361</t>
+    <t xml:space="preserve">8.60070991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139518737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.69392013549805</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">9.02439022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28707122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57517528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47349071502686</t>
+    <t xml:space="preserve">9.28707218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57517433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47349166870117</t>
   </si>
   <si>
     <t xml:space="preserve">9.42264938354492</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">9.3040189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60906982421875</t>
+    <t xml:space="preserve">9.60906887054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.65143775939941</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">9.78701496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83785533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87174987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327743530273</t>
+    <t xml:space="preserve">9.83785629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.871750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327648162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.79548835754395</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">9.82090950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91411972045898</t>
+    <t xml:space="preserve">9.91411876678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.97343349456787</t>
@@ -2105,19 +2105,19 @@
     <t xml:space="preserve">10.1344327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0835905075073</t>
+    <t xml:space="preserve">10.083589553833</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158014297485</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93953990936279</t>
+    <t xml:space="preserve">9.93953895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1768007278442</t>
+    <t xml:space="preserve">10.1768016815186</t>
   </si>
   <si>
     <t xml:space="preserve">10.2276420593262</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">10.1598529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2615375518799</t>
+    <t xml:space="preserve">10.2615365982056</t>
   </si>
   <si>
     <t xml:space="preserve">10.2530632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1683263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1937475204468</t>
+    <t xml:space="preserve">10.168327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1937465667725</t>
   </si>
   <si>
     <t xml:space="preserve">10.0496969223022</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">9.92259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51585960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581703186035</t>
+    <t xml:space="preserve">9.51585865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581693649292</t>
   </si>
   <si>
     <t xml:space="preserve">9.73617267608643</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">9.29554557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16431999206543</t>
+    <t xml:space="preserve">8.16431903839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.32108116149902</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">7.70674419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60082530975342</t>
+    <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
     <t xml:space="preserve">7.39322137832642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29153728485107</t>
+    <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072456359863</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">5.52479124069214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9824800491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08416318893433</t>
+    <t xml:space="preserve">4.98248052597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08416366577148</t>
   </si>
   <si>
     <t xml:space="preserve">5.02484846115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09687376022339</t>
+    <t xml:space="preserve">5.09687328338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.62647390365601</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">4.84690237045288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16042613983154</t>
+    <t xml:space="preserve">5.1604266166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.89774417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76216602325439</t>
+    <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481985092163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41463422775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19008350372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20279407501221</t>
+    <t xml:space="preserve">5.41463470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1900839805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20279455184937</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">5.10111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93163871765137</t>
+    <t xml:space="preserve">4.93163824081421</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129655838013</t>
@@ -2282,25 +2282,25 @@
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663091659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93152379989624</t>
+    <t xml:space="preserve">5.7366304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
     <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70273733139038</t>
+    <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
     <t xml:space="preserve">5.53326463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49513387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87220907211304</t>
+    <t xml:space="preserve">5.49513339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87220859527588</t>
   </si>
   <si>
     <t xml:space="preserve">5.93576097488403</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">6.1009955406189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13065385818481</t>
+    <t xml:space="preserve">6.13065433502197</t>
   </si>
   <si>
     <t xml:space="preserve">5.88068294525146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6773157119751</t>
+    <t xml:space="preserve">5.67731618881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289339065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357818603516</t>
+    <t xml:space="preserve">5.81289386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357866287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">5.91881322860718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03320693969727</t>
+    <t xml:space="preserve">6.03320646286011</t>
   </si>
   <si>
     <t xml:space="preserve">6.35520458221436</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">6.29165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39333534240723</t>
+    <t xml:space="preserve">6.39333581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">6.94835662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91022491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04156732559204</t>
+    <t xml:space="preserve">6.9102258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04156684875488</t>
   </si>
   <si>
     <t xml:space="preserve">7.24916982650757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10088205337524</t>
+    <t xml:space="preserve">7.10088157653809</t>
   </si>
   <si>
     <t xml:space="preserve">7.0034351348877</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71533346176147</t>
+    <t xml:space="preserve">6.71533298492432</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64330673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55009794235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6094126701355</t>
+    <t xml:space="preserve">6.64330720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55009698867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60941219329834</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
@@ -2408,37 +2408,37 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741598129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12641763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15183782577515</t>
+    <t xml:space="preserve">6.28741550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12641716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1518383026123</t>
   </si>
   <si>
     <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31707239151001</t>
+    <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
     <t xml:space="preserve">6.13912725448608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07981204986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04591798782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36367845535278</t>
+    <t xml:space="preserve">6.07981252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04591751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
     <t xml:space="preserve">6.2450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47383499145508</t>
+    <t xml:space="preserve">6.47383451461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.47807168960571</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22386360168457</t>
+    <t xml:space="preserve">6.06286573410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523366928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22386312484741</t>
   </si>
   <si>
     <t xml:space="preserve">6.14336395263672</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">6.07133817672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18149518966675</t>
+    <t xml:space="preserve">6.18149566650391</t>
   </si>
   <si>
     <t xml:space="preserve">6.02049732208252</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">5.99931240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38486194610596</t>
+    <t xml:space="preserve">6.3848614692688</t>
   </si>
   <si>
     <t xml:space="preserve">6.32978391647339</t>
@@ -2486,43 +2486,43 @@
     <t xml:space="preserve">6.3213095664978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23657321929932</t>
+    <t xml:space="preserve">6.23657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">6.19420623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25775814056396</t>
+    <t xml:space="preserve">6.25775766372681</t>
   </si>
   <si>
     <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23233699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30859994888306</t>
+    <t xml:space="preserve">6.232337474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.37215137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63483381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98648834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16019630432129</t>
+    <t xml:space="preserve">6.63483333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.986487865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16019678115845</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73227977752686</t>
+    <t xml:space="preserve">6.97377729415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73228025436401</t>
   </si>
   <si>
     <t xml:space="preserve">6.75346374511719</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">7.0161452293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90175199508667</t>
+    <t xml:space="preserve">6.90175247192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.85938405990601</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10946989059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05439138412476</t>
+    <t xml:space="preserve">6.10946941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0543909072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16031169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09675884246826</t>
+    <t xml:space="preserve">6.16031122207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.21538972854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9484715461731</t>
+    <t xml:space="preserve">5.94847106933594</t>
   </si>
   <si>
     <t xml:space="preserve">6.09252309799194</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563209533691</t>
+    <t xml:space="preserve">5.57563257217407</t>
   </si>
   <si>
     <t xml:space="preserve">5.49089670181274</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787210464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28752994537354</t>
+    <t xml:space="preserve">5.25787258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28753042221069</t>
   </si>
   <si>
     <t xml:space="preserve">5.06297969818115</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">5.76205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81713008880615</t>
+    <t xml:space="preserve">5.81713056564331</t>
   </si>
   <si>
     <t xml:space="preserve">5.83831453323364</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">6.9398832321167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075317382812</t>
+    <t xml:space="preserve">6.74075365066528</t>
   </si>
   <si>
     <t xml:space="preserve">6.82125282287598</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">8.09653091430664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88045406341553</t>
+    <t xml:space="preserve">7.88045310974121</t>
   </si>
   <si>
     <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49914073944092</t>
+    <t xml:space="preserve">7.49914121627808</t>
   </si>
   <si>
     <t xml:space="preserve">7.45253658294678</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">7.5584568977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62200880050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453374862671</t>
+    <t xml:space="preserve">7.62200784683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453279495239</t>
   </si>
   <si>
     <t xml:space="preserve">7.77029657363892</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">7.84232234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6728515625</t>
+    <t xml:space="preserve">7.67285060882568</t>
   </si>
   <si>
     <t xml:space="preserve">7.81266450881958</t>
@@ -2678,34 +2678,34 @@
     <t xml:space="preserve">7.79571723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63471794128418</t>
+    <t xml:space="preserve">7.6347188949585</t>
   </si>
   <si>
     <t xml:space="preserve">7.91011095046997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8253755569458</t>
+    <t xml:space="preserve">7.82537460327148</t>
   </si>
   <si>
     <t xml:space="preserve">7.85503339767456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68556070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5245623588562</t>
+    <t xml:space="preserve">7.68555974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52456188201904</t>
   </si>
   <si>
     <t xml:space="preserve">7.47795724868774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58811378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56692934036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41016817092896</t>
+    <t xml:space="preserve">7.58811473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41016864776611</t>
   </si>
   <si>
     <t xml:space="preserve">7.28730154037476</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">7.22374868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32543277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3169584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985509872437</t>
+    <t xml:space="preserve">7.32543230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31695890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985414505005</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2729,22 +2729,22 @@
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15595960617065</t>
+    <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64319276809692</t>
+    <t xml:space="preserve">7.64319324493408</t>
   </si>
   <si>
     <t xml:space="preserve">7.74911260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53727340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926961898804</t>
+    <t xml:space="preserve">7.53727293014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926866531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.21516036987305</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">8.2321081161499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18550300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20668697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837059020996</t>
+    <t xml:space="preserve">8.18550395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20668792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30836963653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.14313411712646</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">8.0372142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92282199859619</t>
+    <t xml:space="preserve">7.92282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">8.63460445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0075569152832</t>
+    <t xml:space="preserve">8.00755786895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.39734268188477</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">8.78712844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544578552246</t>
+    <t xml:space="preserve">8.68544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1684398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20233535766602</t>
+    <t xml:space="preserve">9.16844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2023344039917</t>
   </si>
   <si>
     <t xml:space="preserve">9.55822658538818</t>
@@ -2816,19 +2816,19 @@
     <t xml:space="preserve">9.60059547424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96507453918457</t>
+    <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21928405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71075248718262</t>
+    <t xml:space="preserve">9.2192850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04981231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7107515335083</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">9.74464702606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72769927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52433204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43112373352051</t>
+    <t xml:space="preserve">9.72770023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52433300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43112277984619</t>
   </si>
   <si>
     <t xml:space="preserve">9.02747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97554588317871</t>
+    <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.03613376617432</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689128875732</t>
+    <t xml:space="preserve">8.96689033508301</t>
   </si>
   <si>
     <t xml:space="preserve">9.08806610107422</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">9.40831089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47755527496338</t>
+    <t xml:space="preserve">9.47755432128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21789455413818</t>
+    <t xml:space="preserve">9.2178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11403179168701</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">9.46889877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26982688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31310367584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33041477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3044490814209</t>
+    <t xml:space="preserve">9.2698278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3131046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33041381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
     <t xml:space="preserve">9.34772491455078</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">8.75916481018066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82840633392334</t>
+    <t xml:space="preserve">8.82840728759766</t>
   </si>
   <si>
     <t xml:space="preserve">9.05344581604004</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">9.36503601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41696739196777</t>
+    <t xml:space="preserve">9.41696834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.16596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99285888671875</t>
+    <t xml:space="preserve">8.99285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.25251579284668</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71588802337646</t>
+    <t xml:space="preserve">8.83706092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71588706970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.77647590637207</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">8.84571743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86302852630615</t>
+    <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
     <t xml:space="preserve">8.78512954711914</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">8.72454357147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63798904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68126678466797</t>
+    <t xml:space="preserve">8.63798999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68126773834229</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26581192016602</t>
+    <t xml:space="preserve">8.26581287384033</t>
   </si>
   <si>
     <t xml:space="preserve">8.19657039642334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23119163513184</t>
+    <t xml:space="preserve">8.23119068145752</t>
   </si>
   <si>
     <t xml:space="preserve">8.28745079040527</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366317749023</t>
+    <t xml:space="preserve">8.63366222381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.67261123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6293363571167</t>
+    <t xml:space="preserve">8.62933540344238</t>
   </si>
   <si>
     <t xml:space="preserve">8.61202430725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59904193878174</t>
+    <t xml:space="preserve">8.59904289245605</t>
   </si>
   <si>
     <t xml:space="preserve">8.50383281707764</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">8.80244159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92825508117676</t>
+    <t xml:space="preserve">7.92825603485107</t>
   </si>
   <si>
     <t xml:space="preserve">7.85901308059692</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">7.93691110610962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87632322311401</t>
+    <t xml:space="preserve">7.87632417678833</t>
   </si>
   <si>
     <t xml:space="preserve">7.99749755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96287631988525</t>
+    <t xml:space="preserve">7.96287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.91960000991821</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">7.95854902267456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96720409393311</t>
+    <t xml:space="preserve">7.96720314025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.82439184188843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65128564834595</t>
+    <t xml:space="preserve">7.65128660202026</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55607652664185</t>
+    <t xml:space="preserve">7.556077003479</t>
   </si>
   <si>
     <t xml:space="preserve">7.49981832504272</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">7.39162731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3526782989502</t>
+    <t xml:space="preserve">7.35267782211304</t>
   </si>
   <si>
     <t xml:space="preserve">7.09734678268433</t>
@@ -3155,25 +3155,25 @@
     <t xml:space="preserve">7.05839776992798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18390035629272</t>
+    <t xml:space="preserve">7.18389987945557</t>
   </si>
   <si>
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969497680664</t>
+    <t xml:space="preserve">7.33969449996948</t>
   </si>
   <si>
     <t xml:space="preserve">7.51280164718628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42192029953003</t>
+    <t xml:space="preserve">7.42192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">7.37431669235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33104038238525</t>
+    <t xml:space="preserve">7.3310399055481</t>
   </si>
   <si>
     <t xml:space="preserve">7.15360689163208</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927911758423</t>
+    <t xml:space="preserve">7.14927864074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.20121002197266</t>
@@ -3194,22 +3194,22 @@
     <t xml:space="preserve">7.19255495071411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25747013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2617974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24448728561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40461015701294</t>
+    <t xml:space="preserve">7.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24448680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40460968017578</t>
   </si>
   <si>
     <t xml:space="preserve">7.45654153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3180570602417</t>
+    <t xml:space="preserve">7.31805658340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.41759300231934</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34402275085449</t>
+    <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
     <t xml:space="preserve">7.23583173751831</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">7.14062356948853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07138061523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02377700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01944875717163</t>
+    <t xml:space="preserve">7.07138109207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02377653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01944923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.88961935043335</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">6.66458177566528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42223358154297</t>
+    <t xml:space="preserve">6.42223310470581</t>
   </si>
   <si>
     <t xml:space="preserve">6.4698371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42656087875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40492296218872</t>
+    <t xml:space="preserve">6.42656135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">6.63861560821533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49147510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36164665222168</t>
+    <t xml:space="preserve">6.4914755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36164617538452</t>
   </si>
   <si>
     <t xml:space="preserve">6.47849321365356</t>
@@ -3296,25 +3296,25 @@
     <t xml:space="preserve">6.75978994369507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56504535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49580335617065</t>
+    <t xml:space="preserve">6.56504583358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4958028793335</t>
   </si>
   <si>
     <t xml:space="preserve">6.21883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21450614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1019868850708</t>
+    <t xml:space="preserve">6.21450567245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10198736190796</t>
   </si>
   <si>
     <t xml:space="preserve">5.88560438156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2015233039856</t>
+    <t xml:space="preserve">6.20152282714844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11497020721436</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">5.70817041397095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60863447189331</t>
+    <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
     <t xml:space="preserve">5.46149444580078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29704427719116</t>
+    <t xml:space="preserve">5.297043800354</t>
   </si>
   <si>
     <t xml:space="preserve">5.53073740005493</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237483978271</t>
+    <t xml:space="preserve">5.55237531661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.63460111618042</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">5.85098361968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05438327789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08467721939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0587100982666</t>
+    <t xml:space="preserve">5.73413705825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05438280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08467674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.37030172348022</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">6.145263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18421220779419</t>
+    <t xml:space="preserve">6.18421268463135</t>
   </si>
   <si>
     <t xml:space="preserve">6.34000778198242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19286823272705</t>
+    <t xml:space="preserve">6.19286775588989</t>
   </si>
   <si>
     <t xml:space="preserve">6.12362480163574</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">6.26211023330688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30105876922607</t>
+    <t xml:space="preserve">6.30105924606323</t>
   </si>
   <si>
     <t xml:space="preserve">6.45685434341431</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4828200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51744174957275</t>
+    <t xml:space="preserve">6.48281955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51744222640991</t>
   </si>
   <si>
     <t xml:space="preserve">6.34433507919312</t>
@@ -3473,19 +3473,19 @@
     <t xml:space="preserve">6.30114984512329</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32771825790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34543085098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41627979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86277103424072</t>
+    <t xml:space="preserve">6.32771873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27458190917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34543037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4162802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86277055740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.67679119110107</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">5.59708595275879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61922645568848</t>
+    <t xml:space="preserve">5.61922693252563</t>
   </si>
   <si>
     <t xml:space="preserve">5.62808275222778</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">5.81406211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6059422492981</t>
+    <t xml:space="preserve">5.79192209243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60594272613525</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">5.66793584823608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72107267379761</t>
+    <t xml:space="preserve">5.72107219696045</t>
   </si>
   <si>
     <t xml:space="preserve">5.88933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77863740921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92476415634155</t>
+    <t xml:space="preserve">5.77863788604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92476367950439</t>
   </si>
   <si>
     <t xml:space="preserve">5.85834264755249</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">6.07531833648682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07974624633789</t>
+    <t xml:space="preserve">6.07974672317505</t>
   </si>
   <si>
     <t xml:space="preserve">5.95576047897339</t>
@@ -3611,22 +3611,22 @@
     <t xml:space="preserve">6.14616775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18159198760986</t>
+    <t xml:space="preserve">6.18159246444702</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27015399932861</t>
+    <t xml:space="preserve">6.27015352249146</t>
   </si>
   <si>
     <t xml:space="preserve">6.04432153701782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03546619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02660894393921</t>
+    <t xml:space="preserve">6.03546571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02660942077637</t>
   </si>
   <si>
     <t xml:space="preserve">5.99561262130737</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">5.89819478988647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61037063598633</t>
+    <t xml:space="preserve">5.61037015914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.67236375808716</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">5.73435640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8096342086792</t>
+    <t xml:space="preserve">5.80963373184204</t>
   </si>
   <si>
     <t xml:space="preserve">5.69450378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63693904876709</t>
+    <t xml:space="preserve">5.63693857192993</t>
   </si>
   <si>
     <t xml:space="preserve">5.48195648193359</t>
@@ -3686,16 +3686,16 @@
     <t xml:space="preserve">5.68564796447754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86719846725464</t>
+    <t xml:space="preserve">5.8671989440918</t>
   </si>
   <si>
     <t xml:space="preserve">5.6546516418457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62365484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121957778931</t>
+    <t xml:space="preserve">5.62365436553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68122005462646</t>
   </si>
   <si>
     <t xml:space="preserve">5.72992849349976</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">6.00889682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2258734703064</t>
+    <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
     <t xml:space="preserve">6.31886291503906</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">6.17273569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08417463302612</t>
+    <t xml:space="preserve">6.08417415618896</t>
   </si>
   <si>
     <t xml:space="preserve">6.06203413009644</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">6.29672193527222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44727659225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5889744758606</t>
+    <t xml:space="preserve">6.4472770690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
     <t xml:space="preserve">6.4738450050354</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">6.42513608932495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915767669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428714752197</t>
+    <t xml:space="preserve">6.23915719985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428762435913</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">6.7926664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539598464966</t>
+    <t xml:space="preserve">6.65539646148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.54912233352661</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">6.49598550796509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64211177825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325548171997</t>
+    <t xml:space="preserve">6.64211225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325500488281</t>
   </si>
   <si>
     <t xml:space="preserve">6.49155712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51369762420654</t>
+    <t xml:space="preserve">6.5136981010437</t>
   </si>
   <si>
     <t xml:space="preserve">6.50926971435547</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.36314296722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46941661834717</t>
+    <t xml:space="preserve">6.46941709518433</t>
   </si>
   <si>
     <t xml:space="preserve">6.33214664459229</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">6.4074239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55355072021484</t>
+    <t xml:space="preserve">6.55355024337769</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425228118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9476490020752</t>
+    <t xml:space="preserve">6.94764852523804</t>
   </si>
   <si>
     <t xml:space="preserve">6.92993688583374</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.0539231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093368530273</t>
+    <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
     <t xml:space="preserve">6.98307371139526</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">7.06720685958862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32846355438232</t>
+    <t xml:space="preserve">7.32846307754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.63842868804932</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81998062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58529186248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2487587928772</t>
+    <t xml:space="preserve">7.81997966766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58529138565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
     <t xml:space="preserve">7.2089056968689</t>
@@ -3863,16 +3863,16 @@
     <t xml:space="preserve">7.19562101364136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24432992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20447731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30189514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52329921722412</t>
+    <t xml:space="preserve">7.24433040618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20447778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3018946647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52329874038696</t>
   </si>
   <si>
     <t xml:space="preserve">7.49230241775513</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.34617567062378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48787450790405</t>
+    <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
     <t xml:space="preserve">7.34174776077271</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">7.10263252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3151798248291</t>
+    <t xml:space="preserve">7.31517934799194</t>
   </si>
   <si>
     <t xml:space="preserve">7.22661733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32403516769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35060453414917</t>
+    <t xml:space="preserve">7.32403564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35060405731201</t>
   </si>
   <si>
     <t xml:space="preserve">7.25318574905396</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">7.17790842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2753267288208</t>
+    <t xml:space="preserve">7.27532625198364</t>
   </si>
   <si>
     <t xml:space="preserve">7.29303884506226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41259717941284</t>
+    <t xml:space="preserve">7.41259670257568</t>
   </si>
   <si>
     <t xml:space="preserve">7.44802093505859</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">7.30632305145264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2354736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20004987716675</t>
+    <t xml:space="preserve">7.23547410964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">6.95207691192627</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451217651367</t>
+    <t xml:space="preserve">6.89451265335083</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">6.84580326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81480693817139</t>
+    <t xml:space="preserve">6.81480741500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.81037855148315</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">7.26204252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25761365890503</t>
+    <t xml:space="preserve">7.25761413574219</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">7.10705947875977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1203441619873</t>
+    <t xml:space="preserve">7.12034368515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
@@ -3998,28 +3998,28 @@
     <t xml:space="preserve">7.31960773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38602781295776</t>
+    <t xml:space="preserve">7.38602828979492</t>
   </si>
   <si>
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3993124961853</t>
+    <t xml:space="preserve">7.39931201934814</t>
   </si>
   <si>
     <t xml:space="preserve">7.27975511550903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45687770843506</t>
+    <t xml:space="preserve">7.45687818527222</t>
   </si>
   <si>
     <t xml:space="preserve">7.54543924331665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68271017074585</t>
+    <t xml:space="preserve">7.47458934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68270921707153</t>
   </si>
   <si>
     <t xml:space="preserve">7.60300397872925</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">7.81506776809692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79683017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88802051544189</t>
+    <t xml:space="preserve">7.79682922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">8.07040309906006</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">7.90169954299927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74211454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80138969421387</t>
+    <t xml:space="preserve">7.74211502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80138921737671</t>
   </si>
   <si>
     <t xml:space="preserve">7.95185470581055</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">7.94273519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09776020050049</t>
+    <t xml:space="preserve">8.09775924682617</t>
   </si>
   <si>
     <t xml:space="preserve">8.22086811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30293846130371</t>
+    <t xml:space="preserve">8.30293941497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.45340538024902</t>
@@ -4085,28 +4085,28 @@
     <t xml:space="preserve">8.13423633575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03392601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09320068359375</t>
+    <t xml:space="preserve">8.03392696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09319972991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.03848552703857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70563793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7193169593811</t>
+    <t xml:space="preserve">7.70563840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71931743621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.78771066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75579357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73299598693848</t>
+    <t xml:space="preserve">7.75579404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73299551010132</t>
   </si>
   <si>
     <t xml:space="preserve">7.71475791931152</t>
@@ -4118,16 +4118,16 @@
     <t xml:space="preserve">7.60988855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45030355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56885290145874</t>
+    <t xml:space="preserve">7.45030403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56885242462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55517292022705</t>
+    <t xml:space="preserve">7.55517339706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.59164953231812</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">7.50501823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54149484634399</t>
+    <t xml:space="preserve">7.45942354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54149532318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.60076904296875</t>
@@ -4157,34 +4157,37 @@
     <t xml:space="preserve">7.55061340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53237628936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69651937484741</t>
+    <t xml:space="preserve">7.53237581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828178405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69651889801025</t>
   </si>
   <si>
     <t xml:space="preserve">7.65548372268677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64636516571045</t>
+    <t xml:space="preserve">7.64636468887329</t>
   </si>
   <si>
     <t xml:space="preserve">7.48678016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41838693618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33175563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38191080093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40470790863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52781581878662</t>
+    <t xml:space="preserve">7.4183874130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3317551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.381911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40470838546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52781629562378</t>
   </si>
   <si>
     <t xml:space="preserve">7.39102935791016</t>
@@ -4193,10 +4196,10 @@
     <t xml:space="preserve">7.29527902603149</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24056434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26792192459106</t>
+    <t xml:space="preserve">7.24056482315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26792144775391</t>
   </si>
   <si>
     <t xml:space="preserve">7.25880289077759</t>
@@ -4205,7 +4208,7 @@
     <t xml:space="preserve">7.06274175643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08553981781006</t>
+    <t xml:space="preserve">7.08554029464722</t>
   </si>
   <si>
     <t xml:space="preserve">7.01258707046509</t>
@@ -4268,7 +4271,7 @@
     <t xml:space="preserve">6.6797399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54751300811768</t>
+    <t xml:space="preserve">6.54751253128052</t>
   </si>
   <si>
     <t xml:space="preserve">6.50191783905029</t>
@@ -4301,19 +4304,19 @@
     <t xml:space="preserve">6.67062091827393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60222768783569</t>
+    <t xml:space="preserve">6.60222721099854</t>
   </si>
   <si>
     <t xml:space="preserve">6.59310865402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52927446365356</t>
+    <t xml:space="preserve">6.52927494049072</t>
   </si>
   <si>
     <t xml:space="preserve">6.43808364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69341850280762</t>
+    <t xml:space="preserve">6.69341897964478</t>
   </si>
   <si>
     <t xml:space="preserve">6.75725221633911</t>
@@ -4322,10 +4325,10 @@
     <t xml:space="preserve">6.50647735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37880992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28761863708496</t>
+    <t xml:space="preserve">6.37880945205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28761911392212</t>
   </si>
   <si>
     <t xml:space="preserve">6.45176219940186</t>
@@ -4334,7 +4337,7 @@
     <t xml:space="preserve">6.47911977767944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58398914337158</t>
+    <t xml:space="preserve">6.58398962020874</t>
   </si>
   <si>
     <t xml:space="preserve">6.97155094146729</t>
@@ -4352,7 +4355,7 @@
     <t xml:space="preserve">7.03994417190552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03538513183594</t>
+    <t xml:space="preserve">7.03538465499878</t>
   </si>
   <si>
     <t xml:space="preserve">7.06730175018311</t>
@@ -4361,7 +4364,7 @@
     <t xml:space="preserve">7.21320724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18129062652588</t>
+    <t xml:space="preserve">7.18129014968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.28615999221802</t>
@@ -4370,16 +4373,16 @@
     <t xml:space="preserve">7.29983901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2360053062439</t>
+    <t xml:space="preserve">7.23600482940674</t>
   </si>
   <si>
     <t xml:space="preserve">7.20408821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96097230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86066341400146</t>
+    <t xml:space="preserve">7.96097278594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86066293716431</t>
   </si>
   <si>
     <t xml:space="preserve">7.97921180725098</t>
@@ -4394,34 +4397,34 @@
     <t xml:space="preserve">7.97009229660034</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05672359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98377084732056</t>
+    <t xml:space="preserve">8.05672454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">8.28926086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31661891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20263004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29837989807129</t>
+    <t xml:space="preserve">8.31661796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20262908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29838085174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.25278472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26646327972412</t>
+    <t xml:space="preserve">8.2664623260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.32117748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08408069610596</t>
+    <t xml:space="preserve">8.08408164978027</t>
   </si>
   <si>
     <t xml:space="preserve">8.04304504394531</t>
@@ -4433,13 +4436,13 @@
     <t xml:space="preserve">8.04760456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20718955993652</t>
+    <t xml:space="preserve">8.20718860626221</t>
   </si>
   <si>
     <t xml:space="preserve">8.16615295410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06128311157227</t>
+    <t xml:space="preserve">8.06128406524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.16159343719482</t>
@@ -4466,7 +4469,7 @@
     <t xml:space="preserve">8.34397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38957023620605</t>
+    <t xml:space="preserve">8.38957118988037</t>
   </si>
   <si>
     <t xml:space="preserve">8.37589263916016</t>
@@ -4478,10 +4481,10 @@
     <t xml:space="preserve">8.2755823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44884586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32573699951172</t>
+    <t xml:space="preserve">8.44884490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32573795318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.57195281982422</t>
@@ -4496,7 +4499,7 @@
     <t xml:space="preserve">8.64034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53547668457031</t>
+    <t xml:space="preserve">8.535475730896</t>
   </si>
   <si>
     <t xml:space="preserve">8.62666797637939</t>
@@ -4532,13 +4535,13 @@
     <t xml:space="preserve">8.43516635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54459476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68138217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79081153869629</t>
+    <t xml:space="preserve">8.54459571838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68138313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79081249237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.84552574157715</t>
@@ -4571,37 +4574,37 @@
     <t xml:space="preserve">8.23910522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01112747192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93817567825317</t>
+    <t xml:space="preserve">8.01112842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93817520141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.93361568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85154390335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68284130096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06584358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14335536956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12055778503418</t>
+    <t xml:space="preserve">7.85154342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594921112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6828408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.065842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17071342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14335632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12055683135986</t>
   </si>
   <si>
     <t xml:space="preserve">8.13879585266113</t>
@@ -4616,7 +4619,7 @@
     <t xml:space="preserve">8.50811958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67226409912109</t>
+    <t xml:space="preserve">8.67226314544678</t>
   </si>
   <si>
     <t xml:space="preserve">8.75433540344238</t>
@@ -53683,7 +53686,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1844" t="s">
-        <v>1338</v>
+        <v>1382</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -53709,7 +53712,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1845" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -53735,7 +53738,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1846" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -53761,7 +53764,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G1847" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -53813,7 +53816,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53839,7 +53842,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1850" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -53865,7 +53868,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1851" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -53891,7 +53894,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1852" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -53917,7 +53920,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1853" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -53969,7 +53972,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G1855" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -53995,7 +53998,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1856" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -54021,7 +54024,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G1857" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54047,7 +54050,7 @@
         <v>8</v>
       </c>
       <c r="G1858" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -54073,7 +54076,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1859" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -54099,7 +54102,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1860" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54125,7 +54128,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1861" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -54151,7 +54154,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1862" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -54177,7 +54180,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1863" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -54203,7 +54206,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1864" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -54229,7 +54232,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1865" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -54255,7 +54258,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54281,7 +54284,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1867" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -54307,7 +54310,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -54333,7 +54336,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1869" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -54359,7 +54362,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1870" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54385,7 +54388,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1871" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -54411,7 +54414,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -54437,7 +54440,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1873" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -54463,7 +54466,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1874" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -54489,7 +54492,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -54515,7 +54518,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1876" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -54541,7 +54544,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1877" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -54567,7 +54570,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -54593,7 +54596,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G1879" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -54619,7 +54622,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1880" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -54645,7 +54648,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G1881" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -54671,7 +54674,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1882" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -54697,7 +54700,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1883" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -54723,7 +54726,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1884" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -54749,7 +54752,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1885" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -54775,7 +54778,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1886" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -54801,7 +54804,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1887" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -54827,7 +54830,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1888" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -54853,7 +54856,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1889" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -54879,7 +54882,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -54905,7 +54908,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G1891" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54931,7 +54934,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1892" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -54957,7 +54960,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -54983,7 +54986,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1894" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -55009,7 +55012,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -55035,7 +55038,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -55061,7 +55064,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1897" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -55087,7 +55090,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1898" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -55113,7 +55116,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1899" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -55139,7 +55142,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -55165,7 +55168,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1901" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -55191,7 +55194,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1902" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -55217,7 +55220,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1903" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -55243,7 +55246,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1904" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55269,7 +55272,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1905" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -55295,7 +55298,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1906" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55321,7 +55324,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1907" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -55347,7 +55350,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -55373,7 +55376,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1909" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -55399,7 +55402,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G1910" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -55425,7 +55428,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1911" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -55451,7 +55454,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1912" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -55477,7 +55480,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -55503,7 +55506,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1914" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -55529,7 +55532,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1915" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -55555,7 +55558,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1916" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -55581,7 +55584,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1917" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -55607,7 +55610,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1918" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -55633,7 +55636,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1919" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -55659,7 +55662,7 @@
         <v>7.75</v>
       </c>
       <c r="G1920" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -55685,7 +55688,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1921" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -55711,7 +55714,7 @@
         <v>7.875</v>
       </c>
       <c r="G1922" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55737,7 +55740,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1923" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -55763,7 +55766,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1924" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -55789,7 +55792,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1925" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -55815,7 +55818,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -55841,7 +55844,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -55867,7 +55870,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1928" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -55893,7 +55896,7 @@
         <v>8</v>
       </c>
       <c r="G1929" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -55919,7 +55922,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1930" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -55945,7 +55948,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1931" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -55971,7 +55974,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1932" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55997,7 +56000,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1933" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56049,7 +56052,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1935" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -56101,7 +56104,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -56153,7 +56156,7 @@
         <v>8.75</v>
       </c>
       <c r="G1939" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -56179,7 +56182,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1940" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -56205,7 +56208,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -56231,7 +56234,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -56257,7 +56260,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -56309,7 +56312,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1945" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -56335,7 +56338,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1946" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -56361,7 +56364,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -56387,7 +56390,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -56413,7 +56416,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1949" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -56439,7 +56442,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -56465,7 +56468,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1951" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -56491,7 +56494,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1952" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -56517,7 +56520,7 @@
         <v>9.125</v>
       </c>
       <c r="G1953" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -56543,7 +56546,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G1954" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -56569,7 +56572,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1955" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -56595,7 +56598,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1956" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -56621,7 +56624,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1957" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56673,7 +56676,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1959" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56699,7 +56702,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1960" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56725,7 +56728,7 @@
         <v>9</v>
       </c>
       <c r="G1961" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56751,7 +56754,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56777,7 +56780,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56803,7 +56806,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1964" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56829,7 +56832,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1965" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56855,7 +56858,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1966" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56881,7 +56884,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G1967" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56907,7 +56910,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G1968" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56933,7 +56936,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1969" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56959,7 +56962,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1970" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56985,7 +56988,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1971" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57011,7 +57014,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1972" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57037,7 +57040,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57063,7 +57066,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G1974" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57089,7 +57092,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1975" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57115,7 +57118,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1976" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57141,7 +57144,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57167,7 +57170,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1978" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57193,7 +57196,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1979" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57245,7 +57248,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1981" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57271,7 +57274,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G1982" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57297,7 +57300,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1983" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57323,7 +57326,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G1984" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57349,7 +57352,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1985" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57375,7 +57378,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57401,7 +57404,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1987" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57427,7 +57430,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1988" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57453,7 +57456,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1989" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57479,7 +57482,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1990" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57505,7 +57508,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1991" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57531,7 +57534,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G1992" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57557,7 +57560,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1993" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57583,7 +57586,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1994" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57609,7 +57612,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57635,7 +57638,7 @@
         <v>8.75</v>
       </c>
       <c r="G1996" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57661,7 +57664,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1997" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57687,7 +57690,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57713,7 +57716,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1999" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57739,7 +57742,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57765,7 +57768,7 @@
         <v>9.25</v>
       </c>
       <c r="G2001" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57791,7 +57794,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2002" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57817,7 +57820,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2003" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57843,7 +57846,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2004" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57869,7 +57872,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57895,7 +57898,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G2006" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57921,7 +57924,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2007" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57947,7 +57950,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G2008" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57973,7 +57976,7 @@
         <v>9.375</v>
       </c>
       <c r="G2009" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57999,7 +58002,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2010" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58025,7 +58028,7 @@
         <v>9.73499965667725</v>
       </c>
       <c r="G2011" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58051,7 +58054,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2012" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58077,7 +58080,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2013" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58129,7 +58132,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2015" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58155,7 +58158,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2016" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58181,7 +58184,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G2017" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58207,7 +58210,7 @@
         <v>9</v>
       </c>
       <c r="G2018" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58259,7 +58262,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2020" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58285,7 +58288,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G2021" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58311,7 +58314,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58337,7 +58340,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2023" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58389,7 +58392,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2025" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58415,7 +58418,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2026" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58441,7 +58444,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G2027" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58467,7 +58470,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58545,7 +58548,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58571,7 +58574,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G2032" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58597,7 +58600,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2033" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58623,7 +58626,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58649,7 +58652,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2035" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58675,7 +58678,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G2036" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58701,7 +58704,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G2037" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58727,7 +58730,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G2038" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58753,7 +58756,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G2039" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58779,7 +58782,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58805,7 +58808,7 @@
         <v>9.25</v>
       </c>
       <c r="G2041" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58831,7 +58834,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58857,7 +58860,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G2043" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58883,7 +58886,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2044" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58909,7 +58912,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58935,7 +58938,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2046" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58961,7 +58964,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2047" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58987,7 +58990,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2048" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59013,7 +59016,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2049" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59039,7 +59042,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2050" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59065,7 +59068,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G2051" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59091,7 +59094,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2052" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59117,7 +59120,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59143,7 +59146,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2054" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59169,7 +59172,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59195,7 +59198,7 @@
         <v>9.125</v>
       </c>
       <c r="G2056" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59221,7 +59224,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G2057" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59247,7 +59250,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2058" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59273,7 +59276,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2059" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59299,7 +59302,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2060" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59325,7 +59328,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2061" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59351,7 +59354,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2062" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59377,7 +59380,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2063" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59403,7 +59406,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2064" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59429,7 +59432,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2065" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59455,7 +59458,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G2066" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59481,7 +59484,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G2067" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59507,7 +59510,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2068" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59533,7 +59536,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2069" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59559,7 +59562,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G2070" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59585,7 +59588,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59611,7 +59614,7 @@
         <v>9.5</v>
       </c>
       <c r="G2072" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59637,7 +59640,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2073" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59663,7 +59666,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2074" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59689,7 +59692,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59715,7 +59718,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2076" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59741,7 +59744,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2077" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59767,7 +59770,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59793,7 +59796,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2079" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59819,7 +59822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2080" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59845,7 +59848,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2081" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59871,7 +59874,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2082" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59897,7 +59900,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2083" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59923,7 +59926,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2084" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59949,7 +59952,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59975,7 +59978,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2086" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60001,7 +60004,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2087" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60027,7 +60030,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2088" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60053,7 +60056,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G2089" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60079,7 +60082,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2090" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60105,7 +60108,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2091" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60131,7 +60134,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G2092" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60157,7 +60160,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2093" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60183,7 +60186,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60209,7 +60212,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2095" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60235,7 +60238,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2096" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60261,7 +60264,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2097" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60287,7 +60290,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2098" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60313,7 +60316,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G2099" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60339,7 +60342,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2100" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60365,7 +60368,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G2101" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60391,7 +60394,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G2102" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60417,7 +60420,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2103" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60443,7 +60446,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2104" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60469,7 +60472,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2105" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60495,7 +60498,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2106" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60521,7 +60524,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2107" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60547,7 +60550,7 @@
         <v>8.875</v>
       </c>
       <c r="G2108" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60573,7 +60576,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2109" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60599,7 +60602,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2110" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60625,7 +60628,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G2111" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60651,7 +60654,7 @@
         <v>9.125</v>
       </c>
       <c r="G2112" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60677,7 +60680,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2113" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60703,7 +60706,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G2114" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60729,7 +60732,7 @@
         <v>9.25</v>
       </c>
       <c r="G2115" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60755,7 +60758,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2116" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60781,7 +60784,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2117" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60807,7 +60810,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2118" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60833,7 +60836,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2119" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60859,7 +60862,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2120" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60885,7 +60888,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2121" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60911,7 +60914,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60937,7 +60940,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60963,7 +60966,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60989,7 +60992,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G2125" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61015,7 +61018,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G2126" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61041,7 +61044,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2127" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61067,7 +61070,7 @@
         <v>9.25</v>
       </c>
       <c r="G2128" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61093,7 +61096,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2129" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61119,7 +61122,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G2130" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61145,7 +61148,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2131" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61171,7 +61174,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G2132" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61197,7 +61200,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2133" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61223,7 +61226,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2134" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61249,7 +61252,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2135" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61275,7 +61278,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2136" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61301,7 +61304,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G2137" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61327,7 +61330,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G2138" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61353,7 +61356,7 @@
         <v>9.25</v>
       </c>
       <c r="G2139" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61379,7 +61382,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61405,7 +61408,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2141" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61431,7 +61434,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2142" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61457,7 +61460,7 @@
         <v>9.375</v>
       </c>
       <c r="G2143" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61483,7 +61486,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2144" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61509,7 +61512,7 @@
         <v>9.375</v>
       </c>
       <c r="G2145" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61535,7 +61538,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2146" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61561,7 +61564,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2147" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61587,7 +61590,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61613,7 +61616,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2149" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61639,7 +61642,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2150" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61665,7 +61668,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2151" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61691,7 +61694,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2152" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61717,7 +61720,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61743,7 +61746,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2154" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61769,7 +61772,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2155" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61795,7 +61798,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G2156" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61821,7 +61824,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2157" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61847,7 +61850,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61873,7 +61876,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2159" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61899,7 +61902,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61925,7 +61928,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2161" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61951,7 +61954,7 @@
         <v>9.625</v>
       </c>
       <c r="G2162" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61977,7 +61980,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G2163" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62003,7 +62006,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G2164" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62029,7 +62032,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G2165" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62055,7 +62058,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2166" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62081,7 +62084,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G2167" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62107,7 +62110,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62133,7 +62136,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G2169" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62159,7 +62162,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G2170" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62185,7 +62188,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2171" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62211,7 +62214,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2172" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62237,7 +62240,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2173" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62263,7 +62266,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2174" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62289,7 +62292,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2175" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62315,7 +62318,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62341,7 +62344,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G2177" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62367,7 +62370,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G2178" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62393,7 +62396,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2179" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62419,7 +62422,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2180" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62445,7 +62448,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2181" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62471,7 +62474,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G2182" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62497,7 +62500,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2183" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62523,7 +62526,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2184" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62549,7 +62552,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2185" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62575,7 +62578,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2186" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62601,7 +62604,7 @@
         <v>10.5</v>
       </c>
       <c r="G2187" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62627,7 +62630,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2188" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62653,7 +62656,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62679,7 +62682,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2190" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62705,7 +62708,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2191" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62731,7 +62734,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2192" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62757,7 +62760,7 @@
         <v>10.25</v>
       </c>
       <c r="G2193" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62783,7 +62786,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2194" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62809,7 +62812,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2195" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62835,7 +62838,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2196" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62861,7 +62864,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2197" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62887,7 +62890,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2198" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62913,7 +62916,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2199" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62939,7 +62942,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2200" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62965,7 +62968,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2201" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62991,7 +62994,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2202" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63017,7 +63020,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63043,7 +63046,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2204" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63069,7 +63072,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63095,7 +63098,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2206" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63121,7 +63124,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2207" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63147,7 +63150,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2208" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63173,7 +63176,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2209" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63199,7 +63202,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2210" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63225,7 +63228,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2211" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63251,7 +63254,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G2212" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63277,7 +63280,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G2213" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63303,7 +63306,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2214" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63329,7 +63332,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2215" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63355,7 +63358,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2216" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63381,7 +63384,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2217" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63407,7 +63410,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2218" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63433,7 +63436,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2219" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63459,7 +63462,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2220" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63485,7 +63488,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2221" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63511,7 +63514,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2222" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63537,7 +63540,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63563,7 +63566,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63589,7 +63592,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2225" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63615,7 +63618,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2226" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63641,7 +63644,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2227" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63667,7 +63670,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2228" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63693,7 +63696,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2229" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63719,7 +63722,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2230" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63745,7 +63748,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2231" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63771,7 +63774,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2232" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63797,7 +63800,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2233" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63823,7 +63826,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2234" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63849,7 +63852,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63875,7 +63878,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2236" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63901,7 +63904,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2237" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63927,7 +63930,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2238" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63953,7 +63956,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2239" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63979,7 +63982,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2240" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64005,7 +64008,7 @@
         <v>11.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64031,7 +64034,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2242" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64057,7 +64060,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64083,7 +64086,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2244" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64109,7 +64112,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2245" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64135,7 +64138,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2246" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64161,7 +64164,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G2247" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64187,7 +64190,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2248" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64213,7 +64216,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64239,7 +64242,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G2250" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64265,7 +64268,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2251" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64291,7 +64294,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G2252" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64317,7 +64320,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2253" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64343,7 +64346,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2254" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64369,7 +64372,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2255" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64395,7 +64398,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2256" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64421,7 +64424,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2257" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64447,7 +64450,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2258" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64473,7 +64476,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64499,7 +64502,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2260" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64525,7 +64528,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2261" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64551,7 +64554,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2262" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64577,7 +64580,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64603,7 +64606,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64629,7 +64632,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G2265" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64655,7 +64658,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2266" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64681,7 +64684,7 @@
         <v>12</v>
       </c>
       <c r="G2267" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64707,7 +64710,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2268" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64733,7 +64736,7 @@
         <v>12</v>
       </c>
       <c r="G2269" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64759,7 +64762,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2270" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64785,7 +64788,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2271" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64811,7 +64814,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G2272" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64837,7 +64840,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G2273" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64863,7 +64866,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2274" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64889,7 +64892,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2275" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64915,7 +64918,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G2276" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64941,7 +64944,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2277" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64967,7 +64970,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64993,7 +64996,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2279" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65019,7 +65022,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65045,7 +65048,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2281" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65071,7 +65074,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2282" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65097,7 +65100,7 @@
         <v>11.25</v>
       </c>
       <c r="G2283" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65123,7 +65126,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2284" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65149,7 +65152,7 @@
         <v>11.5</v>
       </c>
       <c r="G2285" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65175,7 +65178,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2286" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65201,7 +65204,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2287" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65227,7 +65230,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2288" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65253,7 +65256,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2289" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65279,7 +65282,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2290" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65305,7 +65308,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2291" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65331,7 +65334,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2292" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65357,7 +65360,7 @@
         <v>12.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65383,7 +65386,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G2294" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65409,7 +65412,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2295" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65435,7 +65438,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2296" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65461,7 +65464,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2297" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65487,7 +65490,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2298" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65513,7 +65516,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65539,7 +65542,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65565,7 +65568,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G2301" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65591,7 +65594,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G2302" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65617,7 +65620,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G2303" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65643,7 +65646,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2304" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65669,7 +65672,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65695,7 +65698,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G2306" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65721,7 +65724,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2307" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65747,7 +65750,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G2308" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65773,7 +65776,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2309" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65799,7 +65802,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2310" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65825,7 +65828,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2311" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65851,7 +65854,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2312" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65877,7 +65880,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G2313" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65903,7 +65906,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2314" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65929,7 +65932,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2315" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65955,7 +65958,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2316" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65981,7 +65984,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2317" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66007,7 +66010,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2318" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66033,7 +66036,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2319" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66059,7 +66062,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2320" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66085,7 +66088,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2321" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66111,7 +66114,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G2322" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66137,7 +66140,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2323" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66163,7 +66166,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66189,7 +66192,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2325" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66215,7 +66218,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2326" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66241,7 +66244,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2327" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66267,7 +66270,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2328" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66293,7 +66296,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66319,7 +66322,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2330" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66345,7 +66348,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66371,7 +66374,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2332" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66397,7 +66400,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2333" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66423,7 +66426,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2334" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66449,7 +66452,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2335" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66475,7 +66478,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2336" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66501,7 +66504,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2337" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66527,7 +66530,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66553,7 +66556,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G2339" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66579,7 +66582,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2340" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66605,7 +66608,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66631,7 +66634,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66657,7 +66660,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2343" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66683,7 +66686,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2344" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66709,7 +66712,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2345" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66735,7 +66738,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2346" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66761,7 +66764,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66787,7 +66790,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G2348" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66813,7 +66816,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G2349" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66839,7 +66842,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2350" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66865,7 +66868,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66891,7 +66894,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66917,7 +66920,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G2353" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66943,7 +66946,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G2354" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66969,7 +66972,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G2355" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66995,7 +66998,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G2356" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67021,7 +67024,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67047,7 +67050,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2358" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67073,7 +67076,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2359" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2360" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2361" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2362" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G2363" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2365" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2366" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2367" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2368" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2369" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G2371" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2372" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G2373" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G2375" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G2376" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67541,7 +67544,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2378" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2380" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G2382" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G2383" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67723,7 +67726,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G2384" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2385" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G2386" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2387" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2388" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67853,7 +67856,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2389" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2390" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67905,7 +67908,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2392" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67957,7 +67960,7 @@
         <v>14.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68009,7 +68012,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G2395" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68061,7 +68064,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2397" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68087,7 +68090,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2398" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68113,7 +68116,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68139,7 +68142,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2400" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68165,7 +68168,7 @@
         <v>14.25</v>
       </c>
       <c r="G2401" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68191,7 +68194,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G2402" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68217,7 +68220,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G2403" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68243,7 +68246,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2404" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68269,7 +68272,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2405" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68295,7 +68298,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2406" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68321,7 +68324,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G2407" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68347,7 +68350,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G2408" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68373,7 +68376,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68399,7 +68402,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G2410" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68425,7 +68428,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G2411" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68451,7 +68454,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68459,7 +68462,7 @@
     </row>
     <row r="2413">
       <c r="A2413" s="1" t="n">
-        <v>45954.6511111111</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2413" t="n">
         <v>295221</v>
@@ -68477,9 +68480,35 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G2413" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2413" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>45957.6912384259</v>
+      </c>
+      <c r="B2414" t="n">
+        <v>255284</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>14.7299995422363</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>14.539999961853</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>14.6099996566772</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>14.6199998855591</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H2414" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -47,31 +47,31 @@
     <t xml:space="preserve">3.13860011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12387990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06663608551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0650007724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930172920227</t>
+    <t xml:space="preserve">3.12388038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588955879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06663632392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028128623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930196762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.16476845741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17131114006042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1614978313446</t>
+    <t xml:space="preserve">3.17131066322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16149735450745</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205790519714</t>
@@ -89,58 +89,58 @@
     <t xml:space="preserve">3.30051827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34140706062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790364265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39374423027039</t>
+    <t xml:space="preserve">3.34140682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463253974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.437903881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39374446868896</t>
   </si>
   <si>
     <t xml:space="preserve">3.38393092155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33977127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24000310897827</t>
+    <t xml:space="preserve">3.33977150917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
     <t xml:space="preserve">3.14841318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0306544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1729462146759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752463340759</t>
+    <t xml:space="preserve">3.03065466880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08789777755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17294645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752439498901</t>
   </si>
   <si>
     <t xml:space="preserve">3.18112397193909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19257307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19911503791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03392553329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373836517334</t>
+    <t xml:space="preserve">3.19257283210754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19911456108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0339252948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373860359192</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878680229187</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">3.2334611415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2252836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11406683921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14023542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12224507331848</t>
+    <t xml:space="preserve">3.22528314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11406707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14023566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12224435806274</t>
   </si>
   <si>
     <t xml:space="preserve">3.0911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897373199463</t>
+    <t xml:space="preserve">3.08299160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897349357605</t>
   </si>
   <si>
     <t xml:space="preserve">3.08135604858398</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">3.1042537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07481384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14677762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13696455955505</t>
+    <t xml:space="preserve">3.07481408119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14677786827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13696432113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.21383476257324</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36921072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645525932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5098671913147</t>
+    <t xml:space="preserve">3.36921095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986695289612</t>
   </si>
   <si>
     <t xml:space="preserve">3.5164098739624</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54094266891479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50168967247009</t>
+    <t xml:space="preserve">3.50168943405151</t>
   </si>
   <si>
     <t xml:space="preserve">3.47552084922791</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.32014489173889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724717140198</t>
+    <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
     <t xml:space="preserve">3.36103343963623</t>
@@ -236,88 +236,88 @@
     <t xml:space="preserve">3.3773889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3855664730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136191368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150345802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4673433303833</t>
+    <t xml:space="preserve">3.35285544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38556623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150321960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061467170715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46734356880188</t>
   </si>
   <si>
     <t xml:space="preserve">3.48696970939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44281053543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701509475708</t>
+    <t xml:space="preserve">3.44281077384949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3970148563385</t>
   </si>
   <si>
     <t xml:space="preserve">3.41337037086487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.488605260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41827726364136</t>
+    <t xml:space="preserve">3.48860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41827702522278</t>
   </si>
   <si>
     <t xml:space="preserve">3.50823163986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.557297706604</t>
+    <t xml:space="preserve">3.55729794502258</t>
   </si>
   <si>
     <t xml:space="preserve">3.54584956169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57855987548828</t>
+    <t xml:space="preserve">3.57856035232544</t>
   </si>
   <si>
     <t xml:space="preserve">3.60472846031189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59818649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907504081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725279808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996311187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636401176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5671112537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897864341736</t>
+    <t xml:space="preserve">3.56547594070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818625450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360831260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6472532749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178511619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636448860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897912025452</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355753898621</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">3.38065981864929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3381359577179</t>
+    <t xml:space="preserve">3.33813571929932</t>
   </si>
   <si>
     <t xml:space="preserve">3.28743386268616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32668662071228</t>
+    <t xml:space="preserve">3.32668685913086</t>
   </si>
   <si>
     <t xml:space="preserve">3.27598524093628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24327445030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21874165534973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25962996482849</t>
+    <t xml:space="preserve">3.2432746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21874141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962972640991</t>
   </si>
   <si>
     <t xml:space="preserve">3.15495538711548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07644939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462738990784</t>
+    <t xml:space="preserve">3.07644963264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462715148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.12551593780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27107858657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850910186768</t>
+    <t xml:space="preserve">3.27107882499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850934028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.33486485481262</t>
@@ -380,61 +380,61 @@
     <t xml:space="preserve">3.24818086624146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31033134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48206281661987</t>
+    <t xml:space="preserve">3.31033158302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48206305503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.54421377182007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61454224586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528901100159</t>
+    <t xml:space="preserve">3.61454176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655117988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528877258301</t>
   </si>
   <si>
     <t xml:space="preserve">3.58183121681213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309338569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851449012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6407105922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7519268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174092292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809596061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77646064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118013381958</t>
+    <t xml:space="preserve">3.63253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309267044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64071083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435555458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75192666053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7617404460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412323951721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809548377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646040916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118037223816</t>
   </si>
   <si>
     <t xml:space="preserve">3.73720741271973</t>
@@ -443,91 +443,91 @@
     <t xml:space="preserve">3.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79445123672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91548085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8631443977356</t>
+    <t xml:space="preserve">3.79445099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071621894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91548109054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314392089844</t>
   </si>
   <si>
     <t xml:space="preserve">3.89258408546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92529487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150884628296</t>
+    <t xml:space="preserve">3.92529463768005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641478538513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150813102722</t>
   </si>
   <si>
     <t xml:space="preserve">3.96454691886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8516948223114</t>
+    <t xml:space="preserve">3.85169529914856</t>
   </si>
   <si>
     <t xml:space="preserve">4.04305267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96618294715881</t>
+    <t xml:space="preserve">3.96618270874023</t>
   </si>
   <si>
     <t xml:space="preserve">3.88767743110657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86968612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165015220642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02669715881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9939866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272515296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00216484069824</t>
+    <t xml:space="preserve">3.86968636512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898427009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.941650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02669763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398684501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272562980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0021653175354</t>
   </si>
   <si>
     <t xml:space="preserve">4.0561375617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97926735877991</t>
+    <t xml:space="preserve">3.97926712036133</t>
   </si>
   <si>
     <t xml:space="preserve">4.00707149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01524829864502</t>
+    <t xml:space="preserve">4.01524877548218</t>
   </si>
   <si>
     <t xml:space="preserve">4.04141712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08884859085083</t>
+    <t xml:space="preserve">4.08884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">4.08394193649292</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">4.27693510055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048929214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595554351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009099960327</t>
+    <t xml:space="preserve">4.44048881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595602035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009004592896</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506771087646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78804159164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99248456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8043966293335</t>
+    <t xml:space="preserve">4.59586572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78804111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99248361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439710617065</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710718154907</t>
@@ -572,58 +572,58 @@
     <t xml:space="preserve">4.83301830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90661859512329</t>
+    <t xml:space="preserve">4.90661764144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.96386194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02928304672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03337240219116</t>
+    <t xml:space="preserve">5.02928352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03337287902832</t>
   </si>
   <si>
     <t xml:space="preserve">5.19283723831177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13150453567505</t>
+    <t xml:space="preserve">5.13150501251221</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28688144683838</t>
+    <t xml:space="preserve">5.28688097000122</t>
   </si>
   <si>
     <t xml:space="preserve">5.36456918716431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36865854263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56492280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56901168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55265617370605</t>
+    <t xml:space="preserve">5.3686580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56492328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56901073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5526556968689</t>
   </si>
   <si>
     <t xml:space="preserve">5.30323648452759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26643657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54856729507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354400634766</t>
+    <t xml:space="preserve">5.26643705368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54856634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.601722240448</t>
@@ -635,34 +635,34 @@
     <t xml:space="preserve">5.75709867477417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80207490921021</t>
+    <t xml:space="preserve">5.80207586288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.82251977920532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85114240646362</t>
+    <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43816804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48723411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46678972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581159591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083393096924</t>
+    <t xml:space="preserve">5.4381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4790563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48723459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46679067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5608344078064</t>
   </si>
   <si>
     <t xml:space="preserve">5.64308166503906</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">5.46144580841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290363311768</t>
+    <t xml:space="preserve">5.57290410995483</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546607971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70500326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73802661895752</t>
+    <t xml:space="preserve">5.705002784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73802709579468</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756475448608</t>
@@ -695,31 +695,31 @@
     <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10129833221436</t>
+    <t xml:space="preserve">5.90315103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1012978553772</t>
   </si>
   <si>
     <t xml:space="preserve">5.84122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80820417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73389959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133810043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233358383179</t>
+    <t xml:space="preserve">5.82471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80820512771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73389911651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75866794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233263015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.7793083190918</t>
@@ -728,67 +728,67 @@
     <t xml:space="preserve">5.77105188369751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84535694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68849086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56877565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63069725036621</t>
+    <t xml:space="preserve">5.84535789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68849039077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56877613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63069772720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.5770320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52336692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568292617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009616851807</t>
+    <t xml:space="preserve">5.52336740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813528060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621416091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934808731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568197250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009664535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30045175552368</t>
+    <t xml:space="preserve">5.30045127868652</t>
   </si>
   <si>
     <t xml:space="preserve">5.12294387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15183973312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17248058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998893737793</t>
+    <t xml:space="preserve">5.19312143325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17248010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
     <t xml:space="preserve">5.3995246887207</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">5.75041198730469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60592889785767</t>
+    <t xml:space="preserve">5.60592842102051</t>
   </si>
   <si>
     <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72977209091187</t>
+    <t xml:space="preserve">5.72977113723755</t>
   </si>
   <si>
     <t xml:space="preserve">5.77517986297607</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87012529373169</t>
+    <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.86599826812744</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489412307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04763269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86186933517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827402114868</t>
+    <t xml:space="preserve">5.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0476336479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204736709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86186981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827306747437</t>
   </si>
   <si>
     <t xml:space="preserve">6.10955476760864</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17973184585571</t>
+    <t xml:space="preserve">6.1797308921814</t>
   </si>
   <si>
     <t xml:space="preserve">6.19211626052856</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">6.16734743118286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1508355140686</t>
+    <t xml:space="preserve">6.13845109939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083456039429</t>
   </si>
   <si>
     <t xml:space="preserve">5.98158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05176067352295</t>
+    <t xml:space="preserve">6.05176162719727</t>
   </si>
   <si>
     <t xml:space="preserve">6.09717035293579</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">6.18798780441284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15909051895142</t>
+    <t xml:space="preserve">6.15909147262573</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98571109771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08891439437866</t>
+    <t xml:space="preserve">5.9857120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0889139175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140604019165</t>
@@ -908,49 +908,49 @@
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96094369888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00222444534302</t>
+    <t xml:space="preserve">5.96094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00222396850586</t>
   </si>
   <si>
     <t xml:space="preserve">6.22926902770996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38200759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976097106934</t>
+    <t xml:space="preserve">6.38200712203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976144790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.8526086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75353479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004671096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015489578247</t>
+    <t xml:space="preserve">6.81958436965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7535343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492372512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015441894531</t>
   </si>
   <si>
     <t xml:space="preserve">6.44392824172974</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">6.43980026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52649021148682</t>
+    <t xml:space="preserve">6.52648973464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.45631313323975</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">6.5718994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65446138381958</t>
+    <t xml:space="preserve">6.65446043014526</t>
   </si>
   <si>
     <t xml:space="preserve">6.71638202667236</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">6.61318016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44805574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65858888626099</t>
+    <t xml:space="preserve">6.53061771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44805669784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65858840942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.625563621521</t>
+    <t xml:space="preserve">6.62556409835815</t>
   </si>
   <si>
     <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125904083252</t>
+    <t xml:space="preserve">6.50584936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125856399536</t>
   </si>
   <si>
     <t xml:space="preserve">6.6090521812439</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">6.7287654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84847974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75766277313232</t>
+    <t xml:space="preserve">6.84848070144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75766229629517</t>
   </si>
   <si>
     <t xml:space="preserve">6.90214490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6874852180481</t>
+    <t xml:space="preserve">6.70812511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47182130813599</t>
+    <t xml:space="preserve">6.77417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47182083129883</t>
   </si>
   <si>
     <t xml:space="preserve">7.46356344223022</t>
@@ -1049,31 +1049,31 @@
     <t xml:space="preserve">7.64932775497437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95480585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7607855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334659576416</t>
+    <t xml:space="preserve">7.95480442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334564208984</t>
   </si>
   <si>
     <t xml:space="preserve">7.80619382858276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66171169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665712356567</t>
+    <t xml:space="preserve">7.66171073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665760040283</t>
   </si>
   <si>
     <t xml:space="preserve">7.95893287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92590951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57914972305298</t>
+    <t xml:space="preserve">7.92590856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915019989014</t>
   </si>
   <si>
     <t xml:space="preserve">7.28192806243896</t>
@@ -1082,73 +1082,73 @@
     <t xml:space="preserve">7.40989923477173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2241358757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41402626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769142150879</t>
+    <t xml:space="preserve">7.28605604171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41402530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769189834595</t>
   </si>
   <si>
     <t xml:space="preserve">7.57089328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872619628906</t>
+    <t xml:space="preserve">7.29431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872667312622</t>
   </si>
   <si>
     <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38100099563599</t>
+    <t xml:space="preserve">7.38100147247314</t>
   </si>
   <si>
     <t xml:space="preserve">7.33972120285034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19936752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011560440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01773118972778</t>
+    <t xml:space="preserve">7.1993670463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011655807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01773023605347</t>
   </si>
   <si>
     <t xml:space="preserve">7.05488443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79481506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335771560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79068756103516</t>
+    <t xml:space="preserve">6.96406745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.790687084198</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965278625488</t>
+    <t xml:space="preserve">7.19111013412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965183258057</t>
   </si>
   <si>
     <t xml:space="preserve">6.84022378921509</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">7.05075597763062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23651933670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053960800171</t>
+    <t xml:space="preserve">7.2365198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053913116455</t>
   </si>
   <si>
     <t xml:space="preserve">7.30669689178467</t>
@@ -1169,79 +1169,79 @@
     <t xml:space="preserve">7.26128816604614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25715923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036109924316</t>
+    <t xml:space="preserve">7.25715970993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036157608032</t>
   </si>
   <si>
     <t xml:space="preserve">7.27779960632324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23138523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12405586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476512908936</t>
+    <t xml:space="preserve">8.2313871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12405776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476608276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.62768173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41302013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17359256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09103202819824</t>
+    <t xml:space="preserve">8.41302108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1405668258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789905548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17359447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09103012084961</t>
   </si>
   <si>
     <t xml:space="preserve">8.19836139678955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18184852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14469623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1529541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20249080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45429992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33045864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47906970977783</t>
+    <t xml:space="preserve">8.18184947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20661640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14469718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20248985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430088043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33045959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47907257080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.52035140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280471801758</t>
+    <t xml:space="preserve">8.79280376434326</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">8.71024322509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82582855224609</t>
+    <t xml:space="preserve">8.82582950592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86711025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6689624786377</t>
+    <t xml:space="preserve">8.83408451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86710929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896152496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.65244960784912</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">8.67721843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42953205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74605751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7044095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77104663848877</t>
+    <t xml:space="preserve">8.42953395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67109203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74605655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70441150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77104568481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.75438690185547</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">8.24628257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30875492095947</t>
+    <t xml:space="preserve">8.30875396728516</t>
   </si>
   <si>
     <t xml:space="preserve">8.3462381362915</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87932968139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57946586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82935237884521</t>
+    <t xml:space="preserve">8.55447864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87933158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57946681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
     <t xml:space="preserve">8.81269454956055</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8626708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50449848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47118282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45452213287354</t>
+    <t xml:space="preserve">8.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5044994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111377716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47118186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45452117919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.25461196899414</t>
@@ -1346,109 +1346,109 @@
     <t xml:space="preserve">8.58779621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49617099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36289596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42120361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21712875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59612560272217</t>
+    <t xml:space="preserve">8.49617004394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42120456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21712970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08802032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12133884429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78815507888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323595046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.863121509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234294891357</t>
+    <t xml:space="preserve">8.16298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12134075164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78815603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323499679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312103271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234342575073</t>
   </si>
   <si>
     <t xml:space="preserve">7.67154216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62572908401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72151947021484</t>
+    <t xml:space="preserve">7.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145042419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">7.59241008758545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57158613204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82980442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5465989112854</t>
+    <t xml:space="preserve">7.57158708572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82980346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54659843444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.6340594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84229850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79232025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61739873886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68820095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44664239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28838205337524</t>
+    <t xml:space="preserve">7.84229755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.792320728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71319055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6882004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44664287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28838109970093</t>
   </si>
   <si>
     <t xml:space="preserve">7.14677810668945</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">8.17131614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32957744598389</t>
+    <t xml:space="preserve">8.47951221466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3295783996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.20463562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23378753662109</t>
+    <t xml:space="preserve">8.23378849029541</t>
   </si>
   <si>
     <t xml:space="preserve">8.37955570220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52948665618896</t>
+    <t xml:space="preserve">8.52948760986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.0542516708374</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.01260375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00427532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0792407989502</t>
+    <t xml:space="preserve">9.00427436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07923984527588</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">9.09589958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02093315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02926349639893</t>
+    <t xml:space="preserve">9.0209321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02926254272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02138423919678</t>
+    <t xml:space="preserve">8.57113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02138328552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.08385562896729</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">8.15049362182617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00056076049805</t>
+    <t xml:space="preserve">8.00055980682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.354567527771</t>
@@ -1541,31 +1541,31 @@
     <t xml:space="preserve">7.9839015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82563924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99223041534424</t>
+    <t xml:space="preserve">7.82563877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9922308921814</t>
   </si>
   <si>
     <t xml:space="preserve">8.27127170562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07969188690186</t>
+    <t xml:space="preserve">8.07969093322754</t>
   </si>
   <si>
     <t xml:space="preserve">8.28376579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46285152435303</t>
+    <t xml:space="preserve">8.53781795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46285247802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1379976272583</t>
+    <t xml:space="preserve">8.13799858093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.07552528381348</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01721954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26294231414795</t>
+    <t xml:space="preserve">7.54243278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01721858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26294136047363</t>
   </si>
   <si>
     <t xml:space="preserve">8.04220771789551</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">8.14216327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12550449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17964553833008</t>
+    <t xml:space="preserve">8.12550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17964649200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.94641733169556</t>
@@ -1610,25 +1610,25 @@
     <t xml:space="preserve">8.25877666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227676391602</t>
+    <t xml:space="preserve">7.9755711555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8922758102417</t>
   </si>
   <si>
     <t xml:space="preserve">7.81730937957764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62989473342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129249572754</t>
+    <t xml:space="preserve">7.62989377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129440307617</t>
   </si>
   <si>
     <t xml:space="preserve">8.32541370391846</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">8.21296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630527496338</t>
+    <t xml:space="preserve">8.18381118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630718231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.22962379455566</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">8.43786334991455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38788604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62944316864014</t>
+    <t xml:space="preserve">8.38788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62944412231445</t>
   </si>
   <si>
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51283073425293</t>
+    <t xml:space="preserve">8.5128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">8.69608020782471</t>
@@ -1670,31 +1670,31 @@
     <t xml:space="preserve">8.83768272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77937507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87100124359131</t>
+    <t xml:space="preserve">8.77937698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87100028991699</t>
   </si>
   <si>
     <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37910556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56235694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54569625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39576435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28747940063477</t>
+    <t xml:space="preserve">9.37910461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56235599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54569721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39576530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28748035430908</t>
   </si>
   <si>
     <t xml:space="preserve">9.29580879211426</t>
@@ -1703,46 +1703,46 @@
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571990966797</t>
+    <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03759384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22917366027832</t>
+    <t xml:space="preserve">9.66231060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.229172706604</t>
   </si>
   <si>
     <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96262645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13754749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16253662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07091045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56280708312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64610385894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592132568359</t>
+    <t xml:space="preserve">8.96262741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0709114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56280517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64610290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592227935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258201599121</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">9.10422992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94596767425537</t>
+    <t xml:space="preserve">8.94596672058105</t>
   </si>
   <si>
     <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83797073364258</t>
+    <t xml:space="preserve">8.83797168731689</t>
   </si>
   <si>
     <t xml:space="preserve">8.65155124664307</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781372070312</t>
+    <t xml:space="preserve">8.72781467437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98202133178711</t>
+    <t xml:space="preserve">8.98202228546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.702392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77018356323242</t>
+    <t xml:space="preserve">8.77018260955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.6430778503418</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">8.51597499847412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48207855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.490553855896</t>
+    <t xml:space="preserve">8.48207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49055290222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700099945068</t>
+    <t xml:space="preserve">8.427001953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.30413341522217</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">8.2617654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34226512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39310550689697</t>
+    <t xml:space="preserve">8.34226417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39310741424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.33379173278809</t>
@@ -1820,43 +1820,43 @@
     <t xml:space="preserve">8.31260776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27871322631836</t>
+    <t xml:space="preserve">8.27871417999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.28718662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024078369141</t>
+    <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.29566097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839824676514</t>
+    <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
     <t xml:space="preserve">8.10500335693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19397735595703</t>
+    <t xml:space="preserve">8.19397640228271</t>
   </si>
   <si>
     <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3253173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45242118835449</t>
+    <t xml:space="preserve">8.44394969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32531642913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444744110107</t>
+    <t xml:space="preserve">8.52444648742676</t>
   </si>
   <si>
     <t xml:space="preserve">8.66849803924561</t>
@@ -1874,43 +1874,43 @@
     <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57528877258301</t>
+    <t xml:space="preserve">8.57528972625732</t>
   </si>
   <si>
     <t xml:space="preserve">8.2024507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35921287536621</t>
+    <t xml:space="preserve">8.35921192169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.17279243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11771488189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03297710418701</t>
+    <t xml:space="preserve">8.11771392822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03297805786133</t>
   </si>
   <si>
     <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13466262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96518993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961177825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640251159668</t>
+    <t xml:space="preserve">8.13466167449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9651894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9016375541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640203475952</t>
   </si>
   <si>
     <t xml:space="preserve">7.72792816162109</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">8.2363452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2532901763916</t>
+    <t xml:space="preserve">8.25329113006592</t>
   </si>
   <si>
     <t xml:space="preserve">8.22787094116211</t>
@@ -1928,70 +1928,70 @@
     <t xml:space="preserve">7.7236909866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95671606063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540321350098</t>
+    <t xml:space="preserve">7.95671510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113838195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945524215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540273666382</t>
   </si>
   <si>
     <t xml:space="preserve">7.6601390838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71098184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66002559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41429138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684494018555</t>
+    <t xml:space="preserve">7.71098136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66002655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41429042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684398651123</t>
   </si>
   <si>
     <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19821262359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24058246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21939754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53291988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71934127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46936988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89728546142578</t>
+    <t xml:space="preserve">8.42276477813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19821357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24058151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21939849853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46513175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71934032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46936893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89728736877441</t>
   </si>
   <si>
     <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575981140137</t>
+    <t xml:space="preserve">8.88881206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575885772705</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270660400391</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">8.13042545318604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22363471984863</t>
+    <t xml:space="preserve">8.22363376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37192344665527</t>
+    <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.49902725219727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7617073059082</t>
+    <t xml:space="preserve">8.76170825958252</t>
   </si>
   <si>
     <t xml:space="preserve">8.81254959106445</t>
@@ -2024,34 +2024,34 @@
     <t xml:space="preserve">8.60070991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54139518737793</t>
+    <t xml:space="preserve">8.54139423370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.69392013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67697143554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85491847991943</t>
+    <t xml:space="preserve">8.67697238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02439022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28707218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57517433166504</t>
+    <t xml:space="preserve">9.28707122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57517623901367</t>
   </si>
   <si>
     <t xml:space="preserve">9.47349166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42264938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3040189743042</t>
+    <t xml:space="preserve">9.42265129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401802062988</t>
   </si>
   <si>
     <t xml:space="preserve">9.60906887054443</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76159477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78701496124268</t>
+    <t xml:space="preserve">9.76159381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78701400756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.83785629272461</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">9.871750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86327648162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79548835754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82090950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91411876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97343349456787</t>
+    <t xml:space="preserve">9.86327838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79548931121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82090854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91411781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9734354019165</t>
   </si>
   <si>
     <t xml:space="preserve">10.0242757797241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083589553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0158014297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93953895568848</t>
+    <t xml:space="preserve">10.1344318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0835905075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0158023834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93953990936279</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666437149048</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">10.1768016815186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1598529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2615365982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.168327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1937465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496969223022</t>
+    <t xml:space="preserve">10.2276411056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1598539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2615356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530641555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1683263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1937484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496959686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.82938289642334</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">9.92259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51585865020752</t>
+    <t xml:space="preserve">9.51585960388184</t>
   </si>
   <si>
     <t xml:space="preserve">10.0581693649292</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54975509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29554557800293</t>
+    <t xml:space="preserve">9.64296436309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54975318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.16431903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32108116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01603126525879</t>
+    <t xml:space="preserve">8.32108020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01603221893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.00332069396973</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39322137832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153776168823</t>
+    <t xml:space="preserve">7.39322185516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153728485107</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072456359863</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">6.71109580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61364936828613</t>
+    <t xml:space="preserve">6.61364889144897</t>
   </si>
   <si>
     <t xml:space="preserve">5.6137638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52479124069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98248052597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484846115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09687328338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62647390365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80865716934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50784349441528</t>
+    <t xml:space="preserve">5.52479076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9824800491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08416318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09687423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62647438049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59258031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50784397125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.26210927963257</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">5.1604266166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89774417877197</t>
+    <t xml:space="preserve">4.89774465560913</t>
   </si>
   <si>
     <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27481985092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41463470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1900839805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20279455184937</t>
+    <t xml:space="preserve">5.27481937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19008350372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20279407501221</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">5.10111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93163824081421</t>
+    <t xml:space="preserve">4.93163919448853</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129655838013</t>
@@ -2282,19 +2282,19 @@
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7366304397583</t>
+    <t xml:space="preserve">5.73663139343262</t>
   </si>
   <si>
     <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07557535171509</t>
+    <t xml:space="preserve">6.07557582855225</t>
   </si>
   <si>
     <t xml:space="preserve">5.70273685455322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53326463699341</t>
+    <t xml:space="preserve">5.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49513339996338</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">5.87220859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93576097488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13065433502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88068294525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67731618881226</t>
+    <t xml:space="preserve">5.93576049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10099601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13065385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88068246841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6773157119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.87644577026367</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">5.81289386749268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75357866287231</t>
+    <t xml:space="preserve">5.75357818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65189504623413</t>
+    <t xml:space="preserve">5.65189552307129</t>
   </si>
   <si>
     <t xml:space="preserve">6.05015468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91881322860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03320646286011</t>
+    <t xml:space="preserve">5.91881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03320741653442</t>
   </si>
   <si>
     <t xml:space="preserve">6.35520458221436</t>
@@ -2348,19 +2348,19 @@
     <t xml:space="preserve">6.29165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39333581924438</t>
+    <t xml:space="preserve">6.39333534240723</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835662841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9102258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04156684875488</t>
+    <t xml:space="preserve">6.94835710525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04156637191772</t>
   </si>
   <si>
     <t xml:space="preserve">7.24916982650757</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">7.10088157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0034351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70685863494873</t>
+    <t xml:space="preserve">7.00343561172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
     <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71533298492432</t>
+    <t xml:space="preserve">6.71533250808716</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">6.55009698867798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60941219329834</t>
+    <t xml:space="preserve">6.6094126701355</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912725448608</t>
+    <t xml:space="preserve">6.13912773132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981252670288</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2450475692749</t>
+    <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
     <t xml:space="preserve">6.47383451461792</t>
@@ -2447,55 +2447,55 @@
     <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286573410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22386312484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14336395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08404874801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95270872116089</t>
+    <t xml:space="preserve">6.06286525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22386360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14336442947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0840482711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95270824432373</t>
   </si>
   <si>
     <t xml:space="preserve">6.07133817672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18149566650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02049732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931240081787</t>
+    <t xml:space="preserve">6.18149614334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02049684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931287765503</t>
   </si>
   <si>
     <t xml:space="preserve">6.3848614692688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32978391647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3213095664978</t>
+    <t xml:space="preserve">6.32978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32130908966064</t>
   </si>
   <si>
     <t xml:space="preserve">6.23657369613647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19420623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25775766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27470541000366</t>
+    <t xml:space="preserve">6.19420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25775814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2747049331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.232337474823</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37215137481689</t>
+    <t xml:space="preserve">6.37215185165405</t>
   </si>
   <si>
     <t xml:space="preserve">6.63483333587646</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">6.986487865448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019678115845</t>
+    <t xml:space="preserve">7.16019725799561</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377729415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73228025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75346374511719</t>
+    <t xml:space="preserve">6.97377777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73227977752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75346422195435</t>
   </si>
   <si>
     <t xml:space="preserve">7.0161452293396</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">6.90175247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85938405990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79583215713501</t>
+    <t xml:space="preserve">6.85938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79583263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10946941375732</t>
+    <t xml:space="preserve">6.10946989059448</t>
   </si>
   <si>
     <t xml:space="preserve">6.0543909072876</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21538972854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94847106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09252309799194</t>
+    <t xml:space="preserve">6.2153902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9484715461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09252262115479</t>
   </si>
   <si>
     <t xml:space="preserve">6.00778675079346</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563257217407</t>
+    <t xml:space="preserve">5.57563304901123</t>
   </si>
   <si>
     <t xml:space="preserve">5.49089670181274</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28753042221069</t>
+    <t xml:space="preserve">5.25787210464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28752994537354</t>
   </si>
   <si>
     <t xml:space="preserve">5.06297969818115</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">5.01213788986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176664352417</t>
+    <t xml:space="preserve">5.29176616668701</t>
   </si>
   <si>
     <t xml:space="preserve">5.40616035461426</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">5.43158102035522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76205158233643</t>
+    <t xml:space="preserve">5.76205205917358</t>
   </si>
   <si>
     <t xml:space="preserve">5.81713056564331</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9398832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74075365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82125282287598</t>
+    <t xml:space="preserve">6.93988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74075317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82125329971313</t>
   </si>
   <si>
     <t xml:space="preserve">7.04580307006836</t>
@@ -2639,76 +2639,76 @@
     <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49914121627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45253658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5584568977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200784683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079622268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87197971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67285060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6347188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011095046997</t>
+    <t xml:space="preserve">7.49914169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45253610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845594406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77029705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87197923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8423228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67284917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8126654624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7957181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63471937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011047363281</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537460327148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85503339767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68555974960327</t>
+    <t xml:space="preserve">7.8550329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68556070327759</t>
   </si>
   <si>
     <t xml:space="preserve">7.52456188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47795724868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58811473846436</t>
+    <t xml:space="preserve">7.47795677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5881142616272</t>
   </si>
   <si>
     <t xml:space="preserve">7.56693077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41016864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730154037476</t>
+    <t xml:space="preserve">7.41016817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730201721191</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374868392944</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">7.32543230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31695890426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985414505005</t>
+    <t xml:space="preserve">7.31695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985366821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2732,49 +2732,49 @@
     <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63895606994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727293014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21516036987305</t>
+    <t xml:space="preserve">7.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74911308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21516132354736</t>
   </si>
   <si>
     <t xml:space="preserve">8.2321081161499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18550395965576</t>
+    <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
     <t xml:space="preserve">8.20668792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30836963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14313411712646</t>
+    <t xml:space="preserve">8.30837059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14313507080078</t>
   </si>
   <si>
     <t xml:space="preserve">7.79148006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65166568756104</t>
+    <t xml:space="preserve">7.65166616439819</t>
   </si>
   <si>
     <t xml:space="preserve">8.0372142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92282104492188</t>
+    <t xml:space="preserve">7.92282152175903</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
@@ -2786,19 +2786,19 @@
     <t xml:space="preserve">8.63460445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00755786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39734268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965435028076</t>
+    <t xml:space="preserve">8.0075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3973445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.78712844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544673919678</t>
+    <t xml:space="preserve">8.68544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">9.16844081878662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55822658538818</t>
+    <t xml:space="preserve">9.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5582275390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2192850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7107515335083</t>
+    <t xml:space="preserve">9.04133892059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04981136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71075248718262</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.44807052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196411132812</t>
+    <t xml:space="preserve">9.48196506500244</t>
   </si>
   <si>
     <t xml:space="preserve">9.69380474090576</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">9.74464702606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72770023345947</t>
+    <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.52433300018311</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">9.03613376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91495895385742</t>
+    <t xml:space="preserve">8.91496086120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689033508301</t>
+    <t xml:space="preserve">8.96689128875732</t>
   </si>
   <si>
     <t xml:space="preserve">9.08806610107422</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43427753448486</t>
+    <t xml:space="preserve">9.43427658081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.63334941864014</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40831089019775</t>
+    <t xml:space="preserve">9.40831184387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.47755432128906</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11403179168701</t>
+    <t xml:space="preserve">9.21789646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1140308380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.04478931427002</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">9.46889877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2698278427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3131046295166</t>
+    <t xml:space="preserve">9.26982879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31310367584229</t>
   </si>
   <si>
     <t xml:space="preserve">9.33041381835938</t>
@@ -2951,25 +2951,25 @@
     <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00151348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75916481018066</t>
+    <t xml:space="preserve">9.00151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75916385650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05344581604004</t>
+    <t xml:space="preserve">9.05344486236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.20058536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36503601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41696834564209</t>
+    <t xml:space="preserve">9.36503505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41696739196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.16596412658691</t>
@@ -2978,10 +2978,10 @@
     <t xml:space="preserve">8.99285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25251579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17461967468262</t>
+    <t xml:space="preserve">9.252516746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1746187210083</t>
   </si>
   <si>
     <t xml:space="preserve">8.94958114624023</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">8.83706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71588706970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77647590637207</t>
+    <t xml:space="preserve">8.71588802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77647495269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.98420238494873</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395568847656</t>
+    <t xml:space="preserve">8.66395664215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84571743011475</t>
+    <t xml:space="preserve">8.84571838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.86302757263184</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72454357147217</t>
+    <t xml:space="preserve">8.72454261779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.63798999786377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68126773834229</t>
+    <t xml:space="preserve">8.68126678466797</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44324588775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3696756362915</t>
+    <t xml:space="preserve">8.44324684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36967658996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.26581287384033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19657039642334</t>
+    <t xml:space="preserve">8.19656944274902</t>
   </si>
   <si>
     <t xml:space="preserve">8.23119068145752</t>
@@ -3047,55 +3047,55 @@
     <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74185466766357</t>
+    <t xml:space="preserve">8.74185371398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42160701751709</t>
+    <t xml:space="preserve">8.39131450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.3610200881958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47353935241699</t>
+    <t xml:space="preserve">8.47354030609131</t>
   </si>
   <si>
     <t xml:space="preserve">8.63366222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67261123657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62933540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59904289245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50383281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81975078582764</t>
+    <t xml:space="preserve">8.67261219024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62933444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59904193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50383186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5427827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58605766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81975173950195</t>
   </si>
   <si>
     <t xml:space="preserve">8.80244159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92825603485107</t>
+    <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
     <t xml:space="preserve">7.85901308059692</t>
@@ -3104,31 +3104,31 @@
     <t xml:space="preserve">7.93691110610962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87632417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96287727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91960000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527271270752</t>
+    <t xml:space="preserve">7.87632369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96287775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91959953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527318954468</t>
   </si>
   <si>
     <t xml:space="preserve">7.95854902267456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96720314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82439184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128660202026</t>
+    <t xml:space="preserve">7.96720409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128612518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011131286621</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">7.09734678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.166588306427</t>
+    <t xml:space="preserve">7.16658878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.05839776992798</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51280164718628</t>
+    <t xml:space="preserve">7.33969497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51280117034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.42192077636719</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">7.37431669235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3310399055481</t>
+    <t xml:space="preserve">7.33104038238525</t>
   </si>
   <si>
     <t xml:space="preserve">7.15360689163208</t>
@@ -3182,31 +3182,31 @@
     <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20121002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27045249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19255495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26179790496826</t>
+    <t xml:space="preserve">7.14927816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2012095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27045202255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19255542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25747013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2617974281311</t>
   </si>
   <si>
     <t xml:space="preserve">7.24448680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40460968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654153823853</t>
+    <t xml:space="preserve">7.40461015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654106140137</t>
   </si>
   <si>
     <t xml:space="preserve">7.31805658340454</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36566162109375</t>
+    <t xml:space="preserve">7.36566114425659</t>
   </si>
   <si>
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583173751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14062356948853</t>
+    <t xml:space="preserve">7.23583126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14062309265137</t>
   </si>
   <si>
     <t xml:space="preserve">7.07138109207153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02377653121948</t>
+    <t xml:space="preserve">7.02377605438232</t>
   </si>
   <si>
     <t xml:space="preserve">7.01944923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88961935043335</t>
+    <t xml:space="preserve">6.88961982727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.91991281509399</t>
@@ -3266,16 +3266,16 @@
     <t xml:space="preserve">6.5131139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54340744018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63861560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4914755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36164617538452</t>
+    <t xml:space="preserve">6.54340791702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63861608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49147605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36164569854736</t>
   </si>
   <si>
     <t xml:space="preserve">6.47849321365356</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">6.5693736076355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44387197494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55638980865479</t>
+    <t xml:space="preserve">6.44387149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55639028549194</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">6.56504583358765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4958028793335</t>
+    <t xml:space="preserve">6.49580335617065</t>
   </si>
   <si>
     <t xml:space="preserve">6.21883344650269</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">6.11497020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05005502700806</t>
+    <t xml:space="preserve">6.05005550384521</t>
   </si>
   <si>
     <t xml:space="preserve">6.08034896850586</t>
@@ -3332,31 +3332,31 @@
     <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46149444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.297043800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53073740005493</t>
+    <t xml:space="preserve">5.46149492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29704427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53073692321777</t>
   </si>
   <si>
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460111618042</t>
+    <t xml:space="preserve">5.55237579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460063934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89425992965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367300033569</t>
+    <t xml:space="preserve">5.89425945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367252349854</t>
   </si>
   <si>
     <t xml:space="preserve">5.87262153625488</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73413705825806</t>
+    <t xml:space="preserve">5.8509840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7341365814209</t>
   </si>
   <si>
     <t xml:space="preserve">6.05438280105591</t>
@@ -3380,37 +3380,37 @@
     <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37030172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38761234283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2231616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29673194885254</t>
+    <t xml:space="preserve">6.37030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38761186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316122055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29673147201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99812316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15391874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1106424331665</t>
+    <t xml:space="preserve">5.99812269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1539192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11064195632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.145263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18421268463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34000778198242</t>
+    <t xml:space="preserve">6.18421220779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34000825881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.19286775588989</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">6.12362480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1755576133728</t>
+    <t xml:space="preserve">6.17555713653564</t>
   </si>
   <si>
     <t xml:space="preserve">6.26211023330688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30105924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45685434341431</t>
+    <t xml:space="preserve">6.30105972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45685386657715</t>
   </si>
   <si>
     <t xml:space="preserve">6.24479961395264</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48281955718994</t>
+    <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.51744222640991</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">6.19044828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1284556388855</t>
+    <t xml:space="preserve">6.12845516204834</t>
   </si>
   <si>
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971185684204</t>
+    <t xml:space="preserve">6.38971138000488</t>
   </si>
   <si>
     <t xml:space="preserve">6.42956447601318</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">5.57937431335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7122163772583</t>
+    <t xml:space="preserve">5.71221590042114</t>
   </si>
   <si>
     <t xml:space="preserve">5.40225076675415</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59708595275879</t>
+    <t xml:space="preserve">5.59708642959595</t>
   </si>
   <si>
     <t xml:space="preserve">5.61922693252563</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">5.63251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80077791213989</t>
+    <t xml:space="preserve">5.80077838897705</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">5.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60594272613525</t>
+    <t xml:space="preserve">5.6059422492981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66793584823608</t>
+    <t xml:space="preserve">5.53952121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66793537139893</t>
   </si>
   <si>
     <t xml:space="preserve">5.72107219696045</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">5.40667915344238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57494592666626</t>
+    <t xml:space="preserve">5.57494640350342</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74321317672729</t>
+    <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
     <t xml:space="preserve">5.84948635101318</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">5.76092529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84063053131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07088994979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16387987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904468536377</t>
+    <t xml:space="preserve">5.84063005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07089042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.07531833648682</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">6.07974672317505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95576047897339</t>
+    <t xml:space="preserve">5.95576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.97790050506592</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">6.14616775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18159246444702</t>
+    <t xml:space="preserve">6.18159198760986</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99561262130737</t>
+    <t xml:space="preserve">6.02660989761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99561309814453</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">6.01775360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06646251678467</t>
+    <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89819478988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61037015914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67236375808716</t>
+    <t xml:space="preserve">5.89819526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61037063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67236423492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.73435640335083</t>
@@ -3695,25 +3695,25 @@
     <t xml:space="preserve">5.62365436553955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68122005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72992849349976</t>
+    <t xml:space="preserve">5.68121957778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7299280166626</t>
   </si>
   <si>
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00889682769775</t>
+    <t xml:space="preserve">6.00889730453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31886291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25244092941284</t>
+    <t xml:space="preserve">6.3188624382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25244140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.17273569107056</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">6.06203413009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22144460678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29672193527222</t>
+    <t xml:space="preserve">6.22144508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29672241210938</t>
   </si>
   <si>
     <t xml:space="preserve">6.4472770690918</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42513608932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23915719985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428762435913</t>
+    <t xml:space="preserve">6.42513656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23915672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428714752197</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">6.53141021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668754577637</t>
+    <t xml:space="preserve">6.60668706893921</t>
   </si>
   <si>
     <t xml:space="preserve">6.75724220275879</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">6.7926664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539646148682</t>
+    <t xml:space="preserve">6.65539598464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.54912233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52255344390869</t>
+    <t xml:space="preserve">6.52255392074585</t>
   </si>
   <si>
     <t xml:space="preserve">6.53583812713623</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">6.64211225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325500488281</t>
+    <t xml:space="preserve">6.63325548171997</t>
   </si>
   <si>
     <t xml:space="preserve">6.49155712127686</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">6.92993688583374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0539231300354</t>
+    <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
     <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98307371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06720685958862</t>
+    <t xml:space="preserve">6.98307418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06720733642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.32846307754517</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997966766357</t>
+    <t xml:space="preserve">7.81998014450073</t>
   </si>
   <si>
     <t xml:space="preserve">7.58529138565063</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2089056968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19562101364136</t>
+    <t xml:space="preserve">7.20890617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19562149047852</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20447778701782</t>
+    <t xml:space="preserve">7.20447731018066</t>
   </si>
   <si>
     <t xml:space="preserve">7.3018946647644</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34617567062378</t>
+    <t xml:space="preserve">7.34617614746094</t>
   </si>
   <si>
     <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34174776077271</t>
+    <t xml:space="preserve">7.34174728393555</t>
   </si>
   <si>
     <t xml:space="preserve">7.10263252258301</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">7.22661733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32403564453125</t>
+    <t xml:space="preserve">7.32403612136841</t>
   </si>
   <si>
     <t xml:space="preserve">7.35060405731201</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">7.17790842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27532625198364</t>
+    <t xml:space="preserve">7.2753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">7.29303884506226</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">7.44802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48344564437866</t>
+    <t xml:space="preserve">7.48344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.36388778686523</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">6.95207691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74838542938232</t>
+    <t xml:space="preserve">6.74838590621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.00078582763672</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451265335083</t>
+    <t xml:space="preserve">6.89451217651367</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">6.84580326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81037855148315</t>
+    <t xml:space="preserve">6.81480693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81037902832031</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">7.26204252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25761413574219</t>
+    <t xml:space="preserve">7.25761365890503</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12034368515015</t>
+    <t xml:space="preserve">7.10705900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1203441619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39931201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27975511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45687818527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54543924331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47458934783936</t>
+    <t xml:space="preserve">7.3993124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27975463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45687770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54543972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47458982467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.68270921707153</t>
@@ -68488,7 +68488,7 @@
     </row>
     <row r="2414">
       <c r="A2414" s="1" t="n">
-        <v>45957.6912384259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2414" t="n">
         <v>255284</v>
@@ -68509,6 +68509,32 @@
         <v>1763</v>
       </c>
       <c r="H2414" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>45958.6912384259</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>195970</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>14.5600004196167</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>14.6300001144409</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2415" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="1803">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13859963417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12387990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588932037354</t>
+    <t xml:space="preserve">3.13859987258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1238796710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588955879211</t>
   </si>
   <si>
     <t xml:space="preserve">3.06663632392883</t>
@@ -59,70 +59,70 @@
     <t xml:space="preserve">3.06500053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05028057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16476893424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17131090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1614978313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822625160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514231681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168404579163</t>
+    <t xml:space="preserve">3.05028080940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930220603943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1647686958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17131066322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16149759292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205790519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168428421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.30051827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34140682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463230133057</t>
+    <t xml:space="preserve">3.34140706062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463253974915</t>
   </si>
   <si>
     <t xml:space="preserve">3.43790364265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39374423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393092155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977150917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24000334739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14841318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0306544303894</t>
+    <t xml:space="preserve">3.39374375343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393068313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24000310897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14841341972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03065466880798</t>
   </si>
   <si>
     <t xml:space="preserve">3.08789825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17294645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10752463340759</t>
+    <t xml:space="preserve">3.1729462146759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
     <t xml:space="preserve">3.18112421035767</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">3.19911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03392577171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373860359192</t>
+    <t xml:space="preserve">3.03392553329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303722381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0437388420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.12878680229187</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">3.2252836227417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11406707763672</t>
+    <t xml:space="preserve">3.1140673160553</t>
   </si>
   <si>
     <t xml:space="preserve">3.14023542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1222448348999</t>
+    <t xml:space="preserve">3.12224459648132</t>
   </si>
   <si>
     <t xml:space="preserve">3.0911693572998</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">3.11897325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08135581016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1042537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07481408119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14677762985229</t>
+    <t xml:space="preserve">3.08135604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425353050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07481360435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
     <t xml:space="preserve">3.13696455955505</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">3.21383476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16640424728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10916066169739</t>
+    <t xml:space="preserve">3.16640400886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.36921072006226</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.54094266891479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50168943405151</t>
+    <t xml:space="preserve">3.50168967247009</t>
   </si>
   <si>
     <t xml:space="preserve">3.47552108764648</t>
@@ -221,85 +221,85 @@
     <t xml:space="preserve">3.35612678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32014465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29724717140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36103320121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738871574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35285568237305</t>
+    <t xml:space="preserve">3.32014489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29724740982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36103367805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37575340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3773889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35285592079163</t>
   </si>
   <si>
     <t xml:space="preserve">3.38556623458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43136143684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061419487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4673433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281029701233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337037086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4591658115387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41827726364136</t>
+    <t xml:space="preserve">3.43136119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150298118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46734356880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3970148563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337060928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488605260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916604995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41827654838562</t>
   </si>
   <si>
     <t xml:space="preserve">3.50823187828064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.557297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584956169128</t>
+    <t xml:space="preserve">3.55729794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584908485413</t>
   </si>
   <si>
     <t xml:space="preserve">3.57856011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60472822189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547570228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5981867313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360855102539</t>
+    <t xml:space="preserve">3.60472846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907480239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360831260681</t>
   </si>
   <si>
     <t xml:space="preserve">3.64725303649902</t>
@@ -308,46 +308,46 @@
     <t xml:space="preserve">3.67996311187744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67178559303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5671112537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355753898621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38065958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3381359577179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28743410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668709754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27598571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2432746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21874165534973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25962948799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495538711548</t>
+    <t xml:space="preserve">3.67178535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636448860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897864341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355730056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38065981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33813548088074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28743386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27598547935486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24327445030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21874117851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25963020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495586395264</t>
   </si>
   <si>
     <t xml:space="preserve">3.07644963264465</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">3.1255156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27107906341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850934028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486485481262</t>
+    <t xml:space="preserve">3.27107858657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850957870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486461639404</t>
   </si>
   <si>
     <t xml:space="preserve">3.3675754070282</t>
@@ -374,55 +374,55 @@
     <t xml:space="preserve">3.40846419334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30869579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818110466003</t>
+    <t xml:space="preserve">3.30869626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818062782288</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206305503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454224586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253307342529</t>
+    <t xml:space="preserve">3.48206353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421401023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528901100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183073997498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253283500671</t>
   </si>
   <si>
     <t xml:space="preserve">3.60309338569641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66851449012756</t>
+    <t xml:space="preserve">3.66851496696472</t>
   </si>
   <si>
     <t xml:space="preserve">3.64071083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6161777973175</t>
+    <t xml:space="preserve">3.61617732048035</t>
   </si>
   <si>
     <t xml:space="preserve">3.62435531616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75192737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174092292786</t>
+    <t xml:space="preserve">3.75192713737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174020767212</t>
   </si>
   <si>
     <t xml:space="preserve">3.72412300109863</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.77645993232727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79118037223816</t>
+    <t xml:space="preserve">3.791179895401</t>
   </si>
   <si>
     <t xml:space="preserve">3.73720765113831</t>
@@ -443,91 +443,91 @@
     <t xml:space="preserve">3.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79445099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91548109054565</t>
+    <t xml:space="preserve">3.79445123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91548156738281</t>
   </si>
   <si>
     <t xml:space="preserve">3.86314415931702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89258456230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529439926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150884628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454763412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04305362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618294715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8189845085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94164967536926</t>
+    <t xml:space="preserve">3.89258360862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9252941608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440585136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454787254333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8516948223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767695426941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968588829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898403167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94164991378784</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99398708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00216436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0561375617981</t>
+    <t xml:space="preserve">3.99398589134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9727246761322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00216484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05613803863525</t>
   </si>
   <si>
     <t xml:space="preserve">3.97926759719849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00707149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884859085083</t>
+    <t xml:space="preserve">4.00707197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">4.08394193649292</t>
@@ -539,76 +539,76 @@
     <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048881530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595602035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009052276611</t>
+    <t xml:space="preserve">4.44048929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595649719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009004592896</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506771087646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76350879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78804111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99248313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8043966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710765838623</t>
+    <t xml:space="preserve">4.59586477279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76350784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99248361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
     <t xml:space="preserve">4.83301877975464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90661811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96386194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03337287902832</t>
+    <t xml:space="preserve">4.90661764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928304672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03337240219116</t>
   </si>
   <si>
     <t xml:space="preserve">5.19283723831177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13150501251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830396652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688144683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865854263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270227432251</t>
+    <t xml:space="preserve">5.13150453567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688097000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3686580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.56492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56901121139526</t>
+    <t xml:space="preserve">5.56901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">5.55265617370605</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">5.30323648452759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2664361000061</t>
+    <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
     <t xml:space="preserve">5.54856729507446</t>
@@ -626,40 +626,40 @@
     <t xml:space="preserve">5.59354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.601722240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70803260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709819793701</t>
+    <t xml:space="preserve">5.60172271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70803213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709867477417</t>
   </si>
   <si>
     <t xml:space="preserve">5.80207586288452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82251930236816</t>
+    <t xml:space="preserve">5.82251977920532</t>
   </si>
   <si>
     <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78572034835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4381685256958</t>
+    <t xml:space="preserve">5.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816804885864</t>
   </si>
   <si>
     <t xml:space="preserve">5.4790563583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48723411560059</t>
+    <t xml:space="preserve">5.48723459243774</t>
   </si>
   <si>
     <t xml:space="preserve">5.46679019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60581064224243</t>
+    <t xml:space="preserve">5.60581111907959</t>
   </si>
   <si>
     <t xml:space="preserve">5.56083393096924</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">5.64308166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69674634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46144580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290363311768</t>
+    <t xml:space="preserve">5.69674682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4614462852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290410995483</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546560287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70500326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73802709579468</t>
+    <t xml:space="preserve">5.70500230789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73802757263184</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756475448608</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">5.80407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948587417603</t>
+    <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315008163452</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">6.1012978553772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84122896194458</t>
+    <t xml:space="preserve">5.84122848510742</t>
   </si>
   <si>
     <t xml:space="preserve">5.82471704483032</t>
@@ -710,34 +710,34 @@
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389863967896</t>
+    <t xml:space="preserve">5.73389911651611</t>
   </si>
   <si>
     <t xml:space="preserve">5.75866746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133762359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7793083190918</t>
+    <t xml:space="preserve">5.65133810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233263015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77930784225464</t>
   </si>
   <si>
     <t xml:space="preserve">5.77105188369751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8453574180603</t>
+    <t xml:space="preserve">5.84535694122314</t>
   </si>
   <si>
     <t xml:space="preserve">5.68849039077759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56877660751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63069820404053</t>
+    <t xml:space="preserve">5.56877613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63069725036621</t>
   </si>
   <si>
     <t xml:space="preserve">5.5770320892334</t>
@@ -749,52 +749,52 @@
     <t xml:space="preserve">5.54813528060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48621463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162336349487</t>
+    <t xml:space="preserve">5.48621416091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162384033203</t>
   </si>
   <si>
     <t xml:space="preserve">5.55639219284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32934713363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568292617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009616851807</t>
+    <t xml:space="preserve">5.32934761047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009664535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.14771270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30045175552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1931209564209</t>
+    <t xml:space="preserve">5.30045127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19312143325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.10230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15183973312378</t>
+    <t xml:space="preserve">5.1518406867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.17248058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34998798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39952564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74628305435181</t>
+    <t xml:space="preserve">5.34998750686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3995246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74628400802612</t>
   </si>
   <si>
     <t xml:space="preserve">5.75041198730469</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72977161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77517938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76692342758179</t>
+    <t xml:space="preserve">5.72977113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77517986297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76692390441895</t>
   </si>
   <si>
     <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599779129028</t>
+    <t xml:space="preserve">5.86599731445312</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">5.89489412307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04763269424438</t>
+    <t xml:space="preserve">6.04763317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.93204689025879</t>
@@ -836,31 +836,31 @@
     <t xml:space="preserve">5.86186981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95268678665161</t>
+    <t xml:space="preserve">5.95268726348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.97332811355591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10955429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17560338973999</t>
+    <t xml:space="preserve">6.06827306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10955476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17560386657715</t>
   </si>
   <si>
     <t xml:space="preserve">6.17973136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19211578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21275568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18385934829712</t>
+    <t xml:space="preserve">6.19211626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21275663375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18385887145996</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193822860718</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">6.16734743118286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13845014572144</t>
+    <t xml:space="preserve">6.13845062255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.1508355140686</t>
@@ -878,43 +878,43 @@
     <t xml:space="preserve">5.98158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05176115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09716987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798780441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06001806259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9857120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08891344070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140651702881</t>
+    <t xml:space="preserve">6.05176162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09717035293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909147262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06001710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98571252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0889139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140556335449</t>
   </si>
   <si>
     <t xml:space="preserve">5.87425374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93617486953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96094369888306</t>
+    <t xml:space="preserve">5.93617534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9609432220459</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22926902770996</t>
+    <t xml:space="preserve">6.22926807403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.38200759887695</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">6.64207649230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88976144790649</t>
+    <t xml:space="preserve">6.88976097106934</t>
   </si>
   <si>
     <t xml:space="preserve">6.8526086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81958293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004671096802</t>
+    <t xml:space="preserve">6.81958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75353479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004623413086</t>
   </si>
   <si>
     <t xml:space="preserve">6.60492372512817</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">6.44392824172974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43980026245117</t>
+    <t xml:space="preserve">6.43980073928833</t>
   </si>
   <si>
     <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4563136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65446090698242</t>
+    <t xml:space="preserve">6.45631265640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57189846038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65446043014526</t>
   </si>
   <si>
     <t xml:space="preserve">6.71638202667236</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">6.61318016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53061771392822</t>
+    <t xml:space="preserve">6.53061819076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.66684484481812</t>
@@ -989,37 +989,37 @@
     <t xml:space="preserve">6.65858888626099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55538654327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62556314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777095794678</t>
+    <t xml:space="preserve">6.55538702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.625563621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777048110962</t>
   </si>
   <si>
     <t xml:space="preserve">6.50584983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5512580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7287654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84848022460938</t>
+    <t xml:space="preserve">6.55125856399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72876596450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84848070144653</t>
   </si>
   <si>
     <t xml:space="preserve">6.75766277313232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90214490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70812559127808</t>
+    <t xml:space="preserve">6.90214538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70812511444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.68748569488525</t>
@@ -1028,91 +1028,91 @@
     <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4346661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705295562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594738006592</t>
+    <t xml:space="preserve">6.77417421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594785690308</t>
   </si>
   <si>
     <t xml:space="preserve">7.47182035446167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46356344223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078510284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334564208984</t>
+    <t xml:space="preserve">7.46356391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932775497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334659576416</t>
   </si>
   <si>
     <t xml:space="preserve">7.80619382858276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66171073913574</t>
+    <t xml:space="preserve">7.6617112159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.75665760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95893478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57914924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28192710876465</t>
+    <t xml:space="preserve">7.95893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915067672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28192853927612</t>
   </si>
   <si>
     <t xml:space="preserve">7.40989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28605604171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41402673721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57089471817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872667312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
+    <t xml:space="preserve">7.28605651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241358757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41402626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769142150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57089376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787257194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.38100147247314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33972263336182</t>
+    <t xml:space="preserve">7.33972215652466</t>
   </si>
   <si>
     <t xml:space="preserve">7.1993670463562</t>
@@ -1121,73 +1121,73 @@
     <t xml:space="preserve">7.03011560440063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01773118972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406698226929</t>
+    <t xml:space="preserve">7.01773166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488538742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406650543213</t>
   </si>
   <si>
     <t xml:space="preserve">6.7948145866394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74940633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335771560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79068756103516</t>
+    <t xml:space="preserve">6.7494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.790687084198</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1911096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84022378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05075645446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23651885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053865432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128816604614</t>
+    <t xml:space="preserve">7.19111108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965135574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8402247428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05075550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23652029037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669641494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128673553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.25715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36036157608032</t>
+    <t xml:space="preserve">7.36036205291748</t>
   </si>
   <si>
     <t xml:space="preserve">7.2778000831604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23138523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12405490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768173217773</t>
+    <t xml:space="preserve">8.23138618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12405776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768077850342</t>
   </si>
   <si>
     <t xml:space="preserve">8.41302108764648</t>
@@ -1196,58 +1196,58 @@
     <t xml:space="preserve">8.14056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24789810180664</t>
+    <t xml:space="preserve">8.24789905548096</t>
   </si>
   <si>
     <t xml:space="preserve">8.17359256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09103202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18184947967529</t>
+    <t xml:space="preserve">8.09103107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19835948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18184852600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20248985290527</t>
+    <t xml:space="preserve">8.14469718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20248889923096</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430088043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348438262939</t>
+    <t xml:space="preserve">8.35522842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348533630371</t>
   </si>
   <si>
     <t xml:space="preserve">8.33045959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47907066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52035140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79280471801758</t>
+    <t xml:space="preserve">8.47907161712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52035045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79280376434326</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71024322509766</t>
+    <t xml:space="preserve">8.71024227142334</t>
   </si>
   <si>
     <t xml:space="preserve">8.82582855224609</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86710929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65244960784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721748352051</t>
+    <t xml:space="preserve">8.83408451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86711025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6689624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721939086914</t>
   </si>
   <si>
     <t xml:space="preserve">8.42953491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67109107971191</t>
+    <t xml:space="preserve">8.67109203338623</t>
   </si>
   <si>
     <t xml:space="preserve">8.74605655670166</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">8.7044095993042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104568481445</t>
+    <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
     <t xml:space="preserve">8.75438690185547</t>
@@ -1295,22 +1295,22 @@
     <t xml:space="preserve">8.30875492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34623908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41287422180176</t>
+    <t xml:space="preserve">8.3462381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
     <t xml:space="preserve">8.55447769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84601211547852</t>
+    <t xml:space="preserve">8.84601306915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.87933158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57946681976318</t>
+    <t xml:space="preserve">8.57946586608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.82935333251953</t>
@@ -1319,34 +1319,34 @@
     <t xml:space="preserve">8.81269454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82102394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86267280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50450038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111377716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47118091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45452117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58779621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49617099761963</t>
+    <t xml:space="preserve">8.82102298736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5044994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47118282318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45452308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49617004394531</t>
   </si>
   <si>
     <t xml:space="preserve">8.36289691925049</t>
@@ -1355,22 +1355,22 @@
     <t xml:space="preserve">8.42120361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21712970733643</t>
+    <t xml:space="preserve">8.21713066101074</t>
   </si>
   <si>
     <t xml:space="preserve">8.08802032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59612464904785</t>
+    <t xml:space="preserve">8.59612369537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777351379395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12133884429932</t>
+    <t xml:space="preserve">8.16298770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12133979797363</t>
   </si>
   <si>
     <t xml:space="preserve">7.99639558792114</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">7.92142963409424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78815650939941</t>
+    <t xml:space="preserve">7.78815603256226</t>
   </si>
   <si>
     <t xml:space="preserve">8.02554893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733160018921</t>
+    <t xml:space="preserve">7.76733303070068</t>
   </si>
   <si>
     <t xml:space="preserve">7.85062789916992</t>
@@ -1394,43 +1394,43 @@
     <t xml:space="preserve">7.61323499679565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86312103271484</t>
+    <t xml:space="preserve">7.86312198638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.74234294891357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67154169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145137786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.721519947052</t>
+    <t xml:space="preserve">7.67154264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">7.59241056442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57158613204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82980394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5465989112854</t>
+    <t xml:space="preserve">7.57158660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54659986495972</t>
   </si>
   <si>
     <t xml:space="preserve">7.6340594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84229803085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79232025146484</t>
+    <t xml:space="preserve">7.84229850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.792320728302</t>
   </si>
   <si>
     <t xml:space="preserve">7.6173996925354</t>
@@ -1439,25 +1439,25 @@
     <t xml:space="preserve">7.71318960189819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74650859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68820095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44664287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28838157653809</t>
+    <t xml:space="preserve">7.74650812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6882004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44664335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2883825302124</t>
   </si>
   <si>
     <t xml:space="preserve">7.14677858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19259166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163200378418</t>
+    <t xml:space="preserve">7.19259119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163248062134</t>
   </si>
   <si>
     <t xml:space="preserve">7.66321229934692</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">8.04637241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17131805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47951126098633</t>
+    <t xml:space="preserve">8.1713171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47951030731201</t>
   </si>
   <si>
     <t xml:space="preserve">8.3295783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20463562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955570220947</t>
+    <t xml:space="preserve">8.20463466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23378944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.52948760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05425262451172</t>
+    <t xml:space="preserve">9.0542516708374</t>
   </si>
   <si>
     <t xml:space="preserve">8.99594402313232</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">9.01260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00427341461182</t>
+    <t xml:space="preserve">9.00427436828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07923984527588</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09589958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02093410491943</t>
+    <t xml:space="preserve">9.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0959005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02093315124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02926349639893</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113742828369</t>
+    <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.02138423919678</t>
@@ -1532,76 +1532,76 @@
     <t xml:space="preserve">8.15049362182617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00055980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354567527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9839015007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99223136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07969188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28376483917236</t>
+    <t xml:space="preserve">8.00056076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35456657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98390054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563972473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9922308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27126979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07969093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28376579284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.53781795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46285152435303</t>
+    <t xml:space="preserve">8.46285247802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13799858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552528381348</t>
+    <t xml:space="preserve">8.1379976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552623748779</t>
   </si>
   <si>
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243278503418</t>
+    <t xml:space="preserve">7.5424337387085</t>
   </si>
   <si>
     <t xml:space="preserve">8.01721858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26294326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04220867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20046997070312</t>
+    <t xml:space="preserve">8.26294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04220676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20047092437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.19214057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09634971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14216327667236</t>
+    <t xml:space="preserve">8.09635066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14216232299805</t>
   </si>
   <si>
     <t xml:space="preserve">8.12550449371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17964649200439</t>
+    <t xml:space="preserve">8.17964553833008</t>
   </si>
   <si>
     <t xml:space="preserve">7.94641733169556</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">8.25877571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227533340454</t>
+    <t xml:space="preserve">7.97557210922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227676391602</t>
   </si>
   <si>
     <t xml:space="preserve">7.81730937957764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648590087891</t>
+    <t xml:space="preserve">7.62989330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648447036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.75483798980713</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">8.21296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962379455566</t>
+    <t xml:space="preserve">8.18381118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962474822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43786334991455</t>
+    <t xml:space="preserve">8.43786430358887</t>
   </si>
   <si>
     <t xml:space="preserve">8.38788509368896</t>
@@ -1658,58 +1658,58 @@
     <t xml:space="preserve">8.62944316864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37122631072998</t>
+    <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.5128288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768177032471</t>
+    <t xml:space="preserve">8.69608020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768272399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.77937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87100219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237869262695</t>
+    <t xml:space="preserve">8.87100028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237773895264</t>
   </si>
   <si>
     <t xml:space="preserve">9.37910556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56235599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54569625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39576435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28748035430908</t>
+    <t xml:space="preserve">9.56235504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54569721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39576530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28747940063477</t>
   </si>
   <si>
     <t xml:space="preserve">9.29580879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65398120880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49571990966797</t>
+    <t xml:space="preserve">9.65398216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411739349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231155395508</t>
+    <t xml:space="preserve">9.66231250762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.17086601257324</t>
@@ -1718,31 +1718,31 @@
     <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.229172706604</t>
+    <t xml:space="preserve">9.22917366027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96262741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13754749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07091045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56280612945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64610481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592227935791</t>
+    <t xml:space="preserve">8.96262645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16253662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0709114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56280708312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64610290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592132568359</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258106231689</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">8.83797168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223747253418</t>
+    <t xml:space="preserve">8.65155220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202228546143</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">8.70239353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77018356323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64307880401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5159740447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48207855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.490553855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38039588928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42700004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30413341522217</t>
+    <t xml:space="preserve">8.77018260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51597499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48208045959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49055290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38039684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.427001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.26176643371582</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">8.33379173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31260776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27871322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28718662261963</t>
+    <t xml:space="preserve">8.31260681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27871227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.287184715271</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29566097259521</t>
+    <t xml:space="preserve">8.2956600189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839920043945</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">8.10500431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19397735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44394874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32531642913818</t>
+    <t xml:space="preserve">8.19397640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75323390960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44394779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253173828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43971061706543</t>
+    <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
     <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849899291992</t>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">8.44818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60918426513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62613105773926</t>
+    <t xml:space="preserve">8.6091833114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62613010406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20244979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35921192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17279243469238</t>
+    <t xml:space="preserve">8.20245170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35921287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1727933883667</t>
   </si>
   <si>
     <t xml:space="preserve">8.11771488189697</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">8.03297805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89739942550659</t>
+    <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
     <t xml:space="preserve">8.13466167449951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96518898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640298843384</t>
+    <t xml:space="preserve">7.96518850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90163850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640251159668</t>
   </si>
   <si>
     <t xml:space="preserve">7.72792863845825</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">8.2363452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329303741455</t>
+    <t xml:space="preserve">8.25329208374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.22787094116211</t>
@@ -1928,40 +1928,40 @@
     <t xml:space="preserve">7.72369146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95671558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540273666382</t>
+    <t xml:space="preserve">7.95671606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540321350098</t>
   </si>
   <si>
     <t xml:space="preserve">7.66013956069946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71098184585571</t>
+    <t xml:space="preserve">7.7109808921814</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41429138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31684494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43123817443848</t>
+    <t xml:space="preserve">8.4142894744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31684303283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19821357727051</t>
+    <t xml:space="preserve">8.19821262359619</t>
   </si>
   <si>
     <t xml:space="preserve">8.24058246612549</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">8.21939754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46513175964355</t>
+    <t xml:space="preserve">8.46513271331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71934032440186</t>
+    <t xml:space="preserve">8.71934127807617</t>
   </si>
   <si>
     <t xml:space="preserve">8.46936893463135</t>
@@ -1985,19 +1985,19 @@
     <t xml:space="preserve">8.8972864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01591777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8888111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97354888916016</t>
+    <t xml:space="preserve">9.01591682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88881206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97354793548584</t>
   </si>
   <si>
     <t xml:space="preserve">8.13042545318604</t>
@@ -2006,25 +2006,25 @@
     <t xml:space="preserve">8.22363376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18974018096924</t>
+    <t xml:space="preserve">8.18973922729492</t>
   </si>
   <si>
     <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49902725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76170825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81255054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60070896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139614105225</t>
+    <t xml:space="preserve">8.49902629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7617073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81254959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60071086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139423370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.69391918182373</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02439117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28707218170166</t>
+    <t xml:space="preserve">9.02438926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28707122802734</t>
   </si>
   <si>
     <t xml:space="preserve">9.57517528533936</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">9.47349166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401802062988</t>
+    <t xml:space="preserve">9.42264938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401992797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.60906887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53280735015869</t>
+    <t xml:space="preserve">9.65143871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53280639648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.63449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75311946868896</t>
+    <t xml:space="preserve">9.56670093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159477233887</t>
@@ -2081,34 +2081,34 @@
     <t xml:space="preserve">9.83785629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.871750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79548931121826</t>
+    <t xml:space="preserve">9.87174987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79548835754395</t>
   </si>
   <si>
     <t xml:space="preserve">9.82090950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91411781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97343444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1344318389893</t>
+    <t xml:space="preserve">9.91411876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9734354019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1344327926636</t>
   </si>
   <si>
     <t xml:space="preserve">10.0835905075073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0158023834229</t>
+    <t xml:space="preserve">10.0158014297485</t>
   </si>
   <si>
     <t xml:space="preserve">9.93953895568848</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">10.0666437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1768007278442</t>
+    <t xml:space="preserve">10.1768016815186</t>
   </si>
   <si>
     <t xml:space="preserve">10.2276420593262</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">10.1598529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2615365982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530641555786</t>
+    <t xml:space="preserve">10.2615356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25306224823</t>
   </si>
   <si>
     <t xml:space="preserve">10.1683263778687</t>
@@ -2138,49 +2138,49 @@
     <t xml:space="preserve">10.1937475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0496969223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82938289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94801330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.998854637146</t>
+    <t xml:space="preserve">10.0496959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82938385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94801235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99885559082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.92259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51585960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73617172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8463306427002</t>
+    <t xml:space="preserve">9.51586055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73617267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.64296340942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54975509643555</t>
+    <t xml:space="preserve">9.54975318908691</t>
   </si>
   <si>
     <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16431999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01603221893311</t>
+    <t xml:space="preserve">8.16431903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01603126525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.00332069396973</t>
@@ -2189,64 +2189,64 @@
     <t xml:space="preserve">7.70674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322185516357</t>
+    <t xml:space="preserve">7.60082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322090148926</t>
   </si>
   <si>
     <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99072456359863</t>
+    <t xml:space="preserve">6.99072504043579</t>
   </si>
   <si>
     <t xml:space="preserve">6.71109580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61364936828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61376428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5247917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9824800491333</t>
+    <t xml:space="preserve">6.61364889144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6137638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52479076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
     <t xml:space="preserve">5.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02484846115112</t>
+    <t xml:space="preserve">5.02484798431396</t>
   </si>
   <si>
     <t xml:space="preserve">5.09687376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62647390365601</t>
+    <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50784349441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26210975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84690237045288</t>
+    <t xml:space="preserve">5.80865716934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50784397125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26210927963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84690284729004</t>
   </si>
   <si>
     <t xml:space="preserve">5.16042613983154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89774465560913</t>
+    <t xml:space="preserve">4.89774417877197</t>
   </si>
   <si>
     <t xml:space="preserve">4.76216650009155</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">5.41463422775269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1900839805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20279407501221</t>
+    <t xml:space="preserve">5.19008350372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20279359817505</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466283798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10111093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93163871765137</t>
+    <t xml:space="preserve">5.16466236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10111045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93163919448853</t>
   </si>
   <si>
     <t xml:space="preserve">4.96129655838013</t>
@@ -2282,28 +2282,28 @@
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9315242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70273733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53326511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49513339996338</t>
+    <t xml:space="preserve">5.73663091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93152379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70273637771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53326463699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49513292312622</t>
   </si>
   <si>
     <t xml:space="preserve">5.87220859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93576097488403</t>
+    <t xml:space="preserve">5.93576049804688</t>
   </si>
   <si>
     <t xml:space="preserve">6.10099601745605</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">5.67731618881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87644529342651</t>
+    <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.81289386749268</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">5.75357818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66460561752319</t>
+    <t xml:space="preserve">5.66460514068604</t>
   </si>
   <si>
     <t xml:space="preserve">5.65189504623413</t>
@@ -2336,64 +2336,64 @@
     <t xml:space="preserve">6.05015420913696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03320693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3552041053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29165267944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39333581924438</t>
+    <t xml:space="preserve">5.91881418228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03320741653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35520458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2916522026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39333486557007</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9102258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04156684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24916982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088205337524</t>
+    <t xml:space="preserve">6.94835662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04156637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24917078018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088109970093</t>
   </si>
   <si>
     <t xml:space="preserve">7.00343561172485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70685863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5755181312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71533298492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69838523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64330720901489</t>
+    <t xml:space="preserve">6.70685911178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57551860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71533250808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72804355621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69838571548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64330673217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.55009746551514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60941219329834</t>
+    <t xml:space="preserve">6.60941314697266</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14760112762451</t>
+    <t xml:space="preserve">6.14760160446167</t>
   </si>
   <si>
     <t xml:space="preserve">6.28741598129272</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">6.15183782577515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01625967025757</t>
+    <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912677764893</t>
+    <t xml:space="preserve">6.13912773132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981252670288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591798782349</t>
+    <t xml:space="preserve">6.04591751098633</t>
   </si>
   <si>
     <t xml:space="preserve">6.36367797851562</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">6.2450475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47383451461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807168960571</t>
+    <t xml:space="preserve">6.47383499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807216644287</t>
   </si>
   <si>
     <t xml:space="preserve">6.27046871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286525726318</t>
+    <t xml:space="preserve">6.06286478042603</t>
   </si>
   <si>
     <t xml:space="preserve">6.10523271560669</t>
@@ -2459,25 +2459,25 @@
     <t xml:space="preserve">6.14336442947388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08404874801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95270824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07133817672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18149614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02049732208252</t>
+    <t xml:space="preserve">6.0840482711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95270776748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07133865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18149566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02049684524536</t>
   </si>
   <si>
     <t xml:space="preserve">5.99931240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3848614692688</t>
+    <t xml:space="preserve">6.38486194610596</t>
   </si>
   <si>
     <t xml:space="preserve">6.32978343963623</t>
@@ -2486,34 +2486,34 @@
     <t xml:space="preserve">6.32131004333496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23657417297363</t>
+    <t xml:space="preserve">6.23657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">6.19420576095581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25775718688965</t>
+    <t xml:space="preserve">6.25775814056396</t>
   </si>
   <si>
     <t xml:space="preserve">6.2747049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.232337474823</t>
+    <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
     <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37215137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483285903931</t>
+    <t xml:space="preserve">6.37215185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.986487865448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019678115845</t>
+    <t xml:space="preserve">7.16019630432129</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01614475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90175199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85938405990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79583263397217</t>
+    <t xml:space="preserve">7.0161452293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90175294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79583215713501</t>
   </si>
   <si>
     <t xml:space="preserve">6.44417762756348</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">6.10946989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05439138412476</t>
+    <t xml:space="preserve">6.0543909072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168128967285</t>
@@ -2555,28 +2555,28 @@
     <t xml:space="preserve">6.16031122207642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09675931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2153902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94847106933594</t>
+    <t xml:space="preserve">6.09676027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21538972854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
     <t xml:space="preserve">6.09252309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0077862739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90610361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57563257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089670181274</t>
+    <t xml:space="preserve">6.00778722763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90610313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57563304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49089622497559</t>
   </si>
   <si>
     <t xml:space="preserve">5.60105323791504</t>
@@ -2585,25 +2585,25 @@
     <t xml:space="preserve">5.46547555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25787210464478</t>
+    <t xml:space="preserve">5.25787258148193</t>
   </si>
   <si>
     <t xml:space="preserve">5.28753042221069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06297969818115</t>
+    <t xml:space="preserve">5.06297922134399</t>
   </si>
   <si>
     <t xml:space="preserve">5.05874252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01213836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29176616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616083145142</t>
+    <t xml:space="preserve">5.0121374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29176664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616035461426</t>
   </si>
   <si>
     <t xml:space="preserve">5.43158102035522</t>
@@ -2615,112 +2615,112 @@
     <t xml:space="preserve">5.81713056564331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831453323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9398832321167</t>
+    <t xml:space="preserve">5.83831405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
     <t xml:space="preserve">6.74075317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82125329971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04580354690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09652996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88045358657837</t>
+    <t xml:space="preserve">6.82125282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0458025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09653091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88045310974121</t>
   </si>
   <si>
     <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49914169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45253658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624502182007</t>
+    <t xml:space="preserve">7.49914073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4525351524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624454498291</t>
   </si>
   <si>
     <t xml:space="preserve">7.55845642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62200880050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029752731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87197971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8126654624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571771621704</t>
+    <t xml:space="preserve">7.62200832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453422546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77029705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8719801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84232187271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67285013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79571723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.63471937179565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91011095046997</t>
+    <t xml:space="preserve">7.91011142730713</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537460327148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8550329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68555974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5245623588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47795677185059</t>
+    <t xml:space="preserve">7.85503387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68556070327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52456188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47795724868774</t>
   </si>
   <si>
     <t xml:space="preserve">7.58811378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56693029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41016864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28730201721191</t>
+    <t xml:space="preserve">7.56693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4101676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28730154037476</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32543230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985414505005</t>
+    <t xml:space="preserve">7.32543182373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31695890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985366821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64319372177124</t>
+    <t xml:space="preserve">7.63895702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64319276809692</t>
   </si>
   <si>
     <t xml:space="preserve">7.74911260604858</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">7.53727245330811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85926961898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21516036987305</t>
+    <t xml:space="preserve">7.85926914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21516132354736</t>
   </si>
   <si>
     <t xml:space="preserve">8.2321081161499</t>
@@ -2765,22 +2765,22 @@
     <t xml:space="preserve">8.14313507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79148054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65166521072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03721523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92282104492188</t>
+    <t xml:space="preserve">7.79148006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65166616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03721618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92282152175903</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033866882324</t>
+    <t xml:space="preserve">8.88033771514893</t>
   </si>
   <si>
     <t xml:space="preserve">8.63460350036621</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">8.00755786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3973445892334</t>
+    <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965339660645</t>
@@ -2798,25 +2798,25 @@
     <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544578552246</t>
+    <t xml:space="preserve">8.68544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16844081878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60059642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96507453918457</t>
+    <t xml:space="preserve">9.16844177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60059547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96507549285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133796691895</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">9.21928310394287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04981231689453</t>
+    <t xml:space="preserve">9.04981136322021</t>
   </si>
   <si>
     <t xml:space="preserve">9.71075248718262</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">9.39722919464111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44806957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48196315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69380474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.041223526001</t>
+    <t xml:space="preserve">9.44807052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48196506500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69380569458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0412244796753</t>
   </si>
   <si>
     <t xml:space="preserve">9.74464702606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72769927978516</t>
+    <t xml:space="preserve">9.72769832611084</t>
   </si>
   <si>
     <t xml:space="preserve">9.52433300018311</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03613471984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91495895385742</t>
+    <t xml:space="preserve">9.0361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91496086120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">8.96689128875732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08806610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20924091339111</t>
+    <t xml:space="preserve">9.0880651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2092399597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386215209961</t>
@@ -2891,34 +2891,34 @@
     <t xml:space="preserve">9.43427658081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63334941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68527984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40831089019775</t>
+    <t xml:space="preserve">9.63335037231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68528079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40831184387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.47755432128906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32175922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21789646148682</t>
+    <t xml:space="preserve">9.3217601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.1140308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0447883605957</t>
+    <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26117134094238</t>
+    <t xml:space="preserve">9.26117038726807</t>
   </si>
   <si>
     <t xml:space="preserve">9.51217555999756</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">9.2698278427124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3131046295166</t>
+    <t xml:space="preserve">9.31310272216797</t>
   </si>
   <si>
     <t xml:space="preserve">9.33041381835938</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">9.1226863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10537719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00151348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75916481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82840728759766</t>
+    <t xml:space="preserve">9.10537624359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75916385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82840633392334</t>
   </si>
   <si>
     <t xml:space="preserve">9.05344486236572</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">8.99285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.252516746521</t>
+    <t xml:space="preserve">9.25251579284668</t>
   </si>
   <si>
     <t xml:space="preserve">9.1746187210083</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">8.94958114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83706092834473</t>
+    <t xml:space="preserve">8.83706188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77647590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98420238494873</t>
+    <t xml:space="preserve">8.77647495269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98420143127441</t>
   </si>
   <si>
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95823764801025</t>
+    <t xml:space="preserve">8.6639575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.84571743011475</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78512954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72454452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63798904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68126773834229</t>
+    <t xml:space="preserve">8.78513050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72454261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63798999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68126583099365</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44324588775635</t>
+    <t xml:space="preserve">8.44324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">8.36967658996582</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">8.26581287384033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19656944274902</t>
+    <t xml:space="preserve">8.19657039642334</t>
   </si>
   <si>
     <t xml:space="preserve">8.23119163513184</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131355285645</t>
+    <t xml:space="preserve">8.39131450653076</t>
   </si>
   <si>
     <t xml:space="preserve">8.42160797119141</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">8.47354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67261219024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62933444976807</t>
+    <t xml:space="preserve">8.63366222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67261123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62933540344238</t>
   </si>
   <si>
     <t xml:space="preserve">8.61202430725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59904289245605</t>
+    <t xml:space="preserve">8.59904193878174</t>
   </si>
   <si>
     <t xml:space="preserve">8.50383186340332</t>
@@ -3092,31 +3092,31 @@
     <t xml:space="preserve">8.81975078582764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80244064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92825603485107</t>
+    <t xml:space="preserve">8.80244159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
     <t xml:space="preserve">7.85901308059692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93691205978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87632417678833</t>
+    <t xml:space="preserve">7.93691110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87632369995117</t>
   </si>
   <si>
     <t xml:space="preserve">7.99749755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96287727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91960000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527271270752</t>
+    <t xml:space="preserve">7.9628758430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91960048675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527223587036</t>
   </si>
   <si>
     <t xml:space="preserve">7.95854902267456</t>
@@ -3125,55 +3125,55 @@
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53011131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55607652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981880187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39162731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3526782989502</t>
+    <t xml:space="preserve">7.82439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128564834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53011226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55607748031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981784820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39162683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35267782211304</t>
   </si>
   <si>
     <t xml:space="preserve">7.09734678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.166588306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05839824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18389987945557</t>
+    <t xml:space="preserve">7.16658878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05839776992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18390035629272</t>
   </si>
   <si>
     <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33969497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51280164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42192029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37431716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3310399055481</t>
+    <t xml:space="preserve">7.33969449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51280117034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42191982269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37431669235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33104038238525</t>
   </si>
   <si>
     <t xml:space="preserve">7.15360641479492</t>
@@ -3182,28 +3182,28 @@
     <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2012095451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27045249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19255542755127</t>
+    <t xml:space="preserve">7.14927864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20121002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27045297622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19255590438843</t>
   </si>
   <si>
     <t xml:space="preserve">7.25746965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26179790496826</t>
+    <t xml:space="preserve">7.26179838180542</t>
   </si>
   <si>
     <t xml:space="preserve">7.24448680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40460968017578</t>
+    <t xml:space="preserve">7.4046106338501</t>
   </si>
   <si>
     <t xml:space="preserve">7.45654153823853</t>
@@ -3212,49 +3212,49 @@
     <t xml:space="preserve">7.3180570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41759252548218</t>
+    <t xml:space="preserve">7.41759300231934</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36566162109375</t>
+    <t xml:space="preserve">7.36566114425659</t>
   </si>
   <si>
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583173751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14062309265137</t>
+    <t xml:space="preserve">7.23583126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14062356948853</t>
   </si>
   <si>
     <t xml:space="preserve">7.07138109207153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02377653121948</t>
+    <t xml:space="preserve">7.02377605438232</t>
   </si>
   <si>
     <t xml:space="preserve">7.01944875717163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88961935043335</t>
+    <t xml:space="preserve">6.88961982727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.91991281509399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88096380233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66458177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42223358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4698371887207</t>
+    <t xml:space="preserve">6.8809642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66458129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42223310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46983766555786</t>
   </si>
   <si>
     <t xml:space="preserve">6.42656135559082</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">6.5131139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54340791702271</t>
+    <t xml:space="preserve">6.54340744018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.63861560821533</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">6.4914755821228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36164617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47849273681641</t>
+    <t xml:space="preserve">6.36164569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47849321365356</t>
   </si>
   <si>
     <t xml:space="preserve">6.43088817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5693736076355</t>
+    <t xml:space="preserve">6.56937313079834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44387149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55639028549194</t>
+    <t xml:space="preserve">6.5563907623291</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
@@ -3314,13 +3314,13 @@
     <t xml:space="preserve">5.88560438156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20152282714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1149697303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05005502700806</t>
+    <t xml:space="preserve">6.2015233039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11497068405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05005550384521</t>
   </si>
   <si>
     <t xml:space="preserve">6.08034896850586</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46149444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.297043800354</t>
+    <t xml:space="preserve">5.4614953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29704427719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.53073740005493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55670356750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55237531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460111618042</t>
+    <t xml:space="preserve">5.55670309066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55237579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460063934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506469726562</t>
@@ -3368,28 +3368,28 @@
     <t xml:space="preserve">5.85098361968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73413705825806</t>
+    <t xml:space="preserve">5.7341365814209</t>
   </si>
   <si>
     <t xml:space="preserve">6.05438327789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08467674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05871057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37030172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38761234283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2231616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29673194885254</t>
+    <t xml:space="preserve">6.08467626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0587100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38761186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316122055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29673147201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.37895679473877</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">6.1539192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11064195632935</t>
+    <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.14526319503784</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">6.18421268463135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34000778198242</t>
+    <t xml:space="preserve">6.34000825881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12362480163574</t>
+    <t xml:space="preserve">6.1236252784729</t>
   </si>
   <si>
     <t xml:space="preserve">6.1755576133728</t>
@@ -3425,19 +3425,19 @@
     <t xml:space="preserve">6.26211023330688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30105972290039</t>
+    <t xml:space="preserve">6.30105924606323</t>
   </si>
   <si>
     <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24479961395264</t>
+    <t xml:space="preserve">6.24480009078979</t>
   </si>
   <si>
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48281955718994</t>
+    <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.51744174957275</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">6.19044828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1284556388855</t>
+    <t xml:space="preserve">6.12845516204834</t>
   </si>
   <si>
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971185684204</t>
+    <t xml:space="preserve">6.38971138000488</t>
   </si>
   <si>
     <t xml:space="preserve">6.42956447601318</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">5.57937431335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7122163772583</t>
+    <t xml:space="preserve">5.71221590042114</t>
   </si>
   <si>
     <t xml:space="preserve">5.40225076675415</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59708595275879</t>
+    <t xml:space="preserve">5.59708642959595</t>
   </si>
   <si>
     <t xml:space="preserve">5.61922693252563</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">5.63251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80077791213989</t>
+    <t xml:space="preserve">5.80077838897705</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">5.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60594272613525</t>
+    <t xml:space="preserve">5.6059422492981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66793584823608</t>
+    <t xml:space="preserve">5.53952121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66793537139893</t>
   </si>
   <si>
     <t xml:space="preserve">5.72107219696045</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">5.40667915344238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57494592666626</t>
+    <t xml:space="preserve">5.57494640350342</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74321317672729</t>
+    <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
     <t xml:space="preserve">5.84948635101318</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">5.76092529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84063053131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07088994979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16387987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904468536377</t>
+    <t xml:space="preserve">5.84063005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07089042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.07531833648682</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">6.07974672317505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95576047897339</t>
+    <t xml:space="preserve">5.95576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.97790050506592</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">6.14616775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18159246444702</t>
+    <t xml:space="preserve">6.18159198760986</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99561262130737</t>
+    <t xml:space="preserve">6.02660989761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99561309814453</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">6.01775360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06646251678467</t>
+    <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89819478988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61037015914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67236375808716</t>
+    <t xml:space="preserve">5.89819526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61037063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67236423492432</t>
   </si>
   <si>
     <t xml:space="preserve">5.73435640335083</t>
@@ -3695,25 +3695,25 @@
     <t xml:space="preserve">5.62365436553955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68122005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72992849349976</t>
+    <t xml:space="preserve">5.68121957778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7299280166626</t>
   </si>
   <si>
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00889682769775</t>
+    <t xml:space="preserve">6.00889730453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31886291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25244092941284</t>
+    <t xml:space="preserve">6.3188624382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25244140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.17273569107056</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">6.06203413009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22144460678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29672193527222</t>
+    <t xml:space="preserve">6.22144508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29672241210938</t>
   </si>
   <si>
     <t xml:space="preserve">6.4472770690918</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42513608932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23915719985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428762435913</t>
+    <t xml:space="preserve">6.42513656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23915672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428714752197</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">6.53141021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668754577637</t>
+    <t xml:space="preserve">6.60668706893921</t>
   </si>
   <si>
     <t xml:space="preserve">6.75724220275879</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">6.7926664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539646148682</t>
+    <t xml:space="preserve">6.65539598464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.54912233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52255344390869</t>
+    <t xml:space="preserve">6.52255392074585</t>
   </si>
   <si>
     <t xml:space="preserve">6.53583812713623</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">6.64211225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325500488281</t>
+    <t xml:space="preserve">6.63325548171997</t>
   </si>
   <si>
     <t xml:space="preserve">6.49155712127686</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">6.92993688583374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0539231300354</t>
+    <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
     <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98307371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06720685958862</t>
+    <t xml:space="preserve">6.98307418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06720733642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.32846307754517</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997966766357</t>
+    <t xml:space="preserve">7.81998014450073</t>
   </si>
   <si>
     <t xml:space="preserve">7.58529138565063</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2089056968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19562101364136</t>
+    <t xml:space="preserve">7.20890617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19562149047852</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20447778701782</t>
+    <t xml:space="preserve">7.20447731018066</t>
   </si>
   <si>
     <t xml:space="preserve">7.3018946647644</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34617567062378</t>
+    <t xml:space="preserve">7.34617614746094</t>
   </si>
   <si>
     <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34174776077271</t>
+    <t xml:space="preserve">7.34174728393555</t>
   </si>
   <si>
     <t xml:space="preserve">7.10263252258301</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">7.22661733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32403564453125</t>
+    <t xml:space="preserve">7.32403612136841</t>
   </si>
   <si>
     <t xml:space="preserve">7.35060405731201</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">7.17790842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27532625198364</t>
+    <t xml:space="preserve">7.2753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">7.29303884506226</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">7.44802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48344564437866</t>
+    <t xml:space="preserve">7.48344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.36388778686523</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">6.95207691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74838542938232</t>
+    <t xml:space="preserve">6.74838590621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.00078582763672</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451265335083</t>
+    <t xml:space="preserve">6.89451217651367</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">6.84580326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81037855148315</t>
+    <t xml:space="preserve">6.81480693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81037902832031</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">7.26204252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25761413574219</t>
+    <t xml:space="preserve">7.25761365890503</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12034368515015</t>
+    <t xml:space="preserve">7.10705900192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1203441619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39931201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27975511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45687818527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54543924331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47458934783936</t>
+    <t xml:space="preserve">7.3993124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27975463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45687770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54543972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47458982467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.68270921707153</t>
@@ -5418,6 +5418,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.3900003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6999998092651</t>
   </si>
 </sst>
 </file>
@@ -68572,7 +68575,7 @@
     </row>
     <row r="2417">
       <c r="A2417" s="1" t="n">
-        <v>45960.6910763889</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2417" t="n">
         <v>381169</v>
@@ -68593,6 +68596,32 @@
         <v>1801</v>
       </c>
       <c r="H2417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>45961.6909837963</v>
+      </c>
+      <c r="B2418" t="n">
+        <v>270923</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>15.710000038147</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>15.2399997711182</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>15.3699998855591</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>15.6999998092651</v>
+      </c>
+      <c r="G2418" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H2418" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -44,76 +44,76 @@
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13859987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1238796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10588955879211</t>
+    <t xml:space="preserve">3.13860011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12387990951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10588979721069</t>
   </si>
   <si>
     <t xml:space="preserve">3.06663632392883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06500053405762</t>
+    <t xml:space="preserve">3.0650007724762</t>
   </si>
   <si>
     <t xml:space="preserve">3.05028080940247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18930220603943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647686958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17131066322327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16149759292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205790519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168428421021</t>
+    <t xml:space="preserve">3.18930172920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17131114006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16149735450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822625160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514183998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168452262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.30051827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34140706062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43463253974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790364265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39374375343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393068313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24000310897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14841341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03065466880798</t>
+    <t xml:space="preserve">3.34140682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43463230133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43790411949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39374446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393092155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24000334739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14841294288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0306544303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.08789825439453</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18112421035767</t>
+    <t xml:space="preserve">3.18112397193909</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257283210754</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">3.19911479949951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03392553329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0437388420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12878680229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23019051551819</t>
+    <t xml:space="preserve">3.0339252948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303698539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12878656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23019003868103</t>
   </si>
   <si>
     <t xml:space="preserve">3.2334611415863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2252836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1140673160553</t>
+    <t xml:space="preserve">3.22528386116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11406707763672</t>
   </si>
   <si>
     <t xml:space="preserve">3.14023542404175</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">3.12224459648132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0911693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897325515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135604858398</t>
+    <t xml:space="preserve">3.09116911888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08299160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897349357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135581016541</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425353050232</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13696455955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16640400886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10916042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36921072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42645502090454</t>
+    <t xml:space="preserve">3.13696432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16640424728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10916018486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36921095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42645454406738</t>
   </si>
   <si>
     <t xml:space="preserve">3.50986742973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5164098739624</t>
+    <t xml:space="preserve">3.51640963554382</t>
   </si>
   <si>
     <t xml:space="preserve">3.54094266891479</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">3.50168967247009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47552108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35612678527832</t>
+    <t xml:space="preserve">3.47552132606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3561270236969</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014489173889</t>
@@ -227,70 +227,70 @@
     <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36103367805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3773889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35285592079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38556623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150298118591</t>
+    <t xml:space="preserve">3.36103320121765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3757529258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738871574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35285544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38556575775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136143684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150274276733</t>
   </si>
   <si>
     <t xml:space="preserve">3.47061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46734356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696970939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281005859375</t>
+    <t xml:space="preserve">3.46734309196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281029701233</t>
   </si>
   <si>
     <t xml:space="preserve">3.3970148563385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41337060928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.488605260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41827654838562</t>
+    <t xml:space="preserve">3.41337037086487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4591658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4182767868042</t>
   </si>
   <si>
     <t xml:space="preserve">3.50823187828064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55729794502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57856011390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547617912292</t>
+    <t xml:space="preserve">3.55729842185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57855987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547594070435</t>
   </si>
   <si>
     <t xml:space="preserve">3.59818649291992</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">3.63907480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66360831260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996311187744</t>
+    <t xml:space="preserve">3.66360878944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725279808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996335029602</t>
   </si>
   <si>
     <t xml:space="preserve">3.67178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60636448860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56711101531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897864341736</t>
+    <t xml:space="preserve">3.60636425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5671112537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46897888183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355730056763</t>
@@ -326,31 +326,31 @@
     <t xml:space="preserve">3.38065981864929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33813548088074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28743386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27598547935486</t>
+    <t xml:space="preserve">3.33813571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28743362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668709754944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2759850025177</t>
   </si>
   <si>
     <t xml:space="preserve">3.24327445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21874117851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25963020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07644963264465</t>
+    <t xml:space="preserve">3.21874165534973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07644939422607</t>
   </si>
   <si>
     <t xml:space="preserve">3.08462738990784</t>
@@ -362,85 +362,85 @@
     <t xml:space="preserve">3.27107858657837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31850957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3675754070282</t>
+    <t xml:space="preserve">3.31850934028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486485481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36757564544678</t>
   </si>
   <si>
     <t xml:space="preserve">3.40846419334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30869626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818062782288</t>
+    <t xml:space="preserve">3.30869603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818086624146</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421401023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655046463013</t>
+    <t xml:space="preserve">3.48206329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421377182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454224586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655094146729</t>
   </si>
   <si>
     <t xml:space="preserve">3.57528901100159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58183073997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309338569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851496696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617732048035</t>
+    <t xml:space="preserve">3.58183145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309290885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64071035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617755889893</t>
   </si>
   <si>
     <t xml:space="preserve">3.62435531616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75192713737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809548377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77645993232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.791179895401</t>
+    <t xml:space="preserve">3.75192737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809572219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118013381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.73720765113831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90730333328247</t>
+    <t xml:space="preserve">3.90730285644531</t>
   </si>
   <si>
     <t xml:space="preserve">3.79445123672485</t>
@@ -452,61 +452,61 @@
     <t xml:space="preserve">3.91548156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86314415931702</t>
+    <t xml:space="preserve">3.86314392089844</t>
   </si>
   <si>
     <t xml:space="preserve">3.89258360862732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9252941608429</t>
+    <t xml:space="preserve">3.92529487609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.88440585136414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86641502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454787254333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8516948223114</t>
+    <t xml:space="preserve">3.86641478538513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169577598572</t>
   </si>
   <si>
     <t xml:space="preserve">4.04305267333984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767695426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968588829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898403167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384530067444</t>
+    <t xml:space="preserve">3.96618318557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8189845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138457775116</t>
   </si>
   <si>
     <t xml:space="preserve">3.94164991378784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02669763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99398589134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9727246761322</t>
+    <t xml:space="preserve">4.02669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99398732185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272515296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.00216484069824</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">4.05613803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97926759719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01524877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08394193649292</t>
+    <t xml:space="preserve">3.97926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141664505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884859085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08394145965576</t>
   </si>
   <si>
     <t xml:space="preserve">4.16244745254517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.44048929214478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41595649719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009004592896</t>
+    <t xml:space="preserve">4.41595602035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009052276611</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506771087646</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">4.76350784301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78804063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99248361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439710617065</t>
+    <t xml:space="preserve">4.78804159164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9924840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8043966293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83301877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90661764144897</t>
+    <t xml:space="preserve">4.8330192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90661811828613</t>
   </si>
   <si>
     <t xml:space="preserve">4.96386241912842</t>
@@ -599,43 +599,43 @@
     <t xml:space="preserve">5.36456918716431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3686580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56492233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56901168823242</t>
+    <t xml:space="preserve">5.36865758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56492328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56901121139526</t>
   </si>
   <si>
     <t xml:space="preserve">5.55265617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30323648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26643657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54856729507446</t>
+    <t xml:space="preserve">5.30323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26643705368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54856634140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.59354496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60172271728516</t>
+    <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
     <t xml:space="preserve">5.70803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75709867477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80207586288452</t>
+    <t xml:space="preserve">5.75709819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80207538604736</t>
   </si>
   <si>
     <t xml:space="preserve">5.82251977920532</t>
@@ -644,25 +644,25 @@
     <t xml:space="preserve">5.85114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4790563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48723459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46679019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083393096924</t>
+    <t xml:space="preserve">5.78572082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43816900253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47905683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4872350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46678972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581159591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083345413208</t>
   </si>
   <si>
     <t xml:space="preserve">5.64308166503906</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">5.4614462852478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290410995483</t>
+    <t xml:space="preserve">5.57290458679199</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546560287476</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">5.73802757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80407667160034</t>
+    <t xml:space="preserve">5.78756427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8040771484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1012978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84122848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471704483032</t>
+    <t xml:space="preserve">5.90315055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10129737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84122943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75866746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65133810043335</t>
+    <t xml:space="preserve">5.73389863967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65133762359619</t>
   </si>
   <si>
     <t xml:space="preserve">5.81233263015747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77930784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77105188369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84535694122314</t>
+    <t xml:space="preserve">5.7793083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77105236053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8453574180603</t>
   </si>
   <si>
     <t xml:space="preserve">5.68849039077759</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63069725036621</t>
+    <t xml:space="preserve">5.63069772720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.5770320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52336740493774</t>
+    <t xml:space="preserve">5.52336692810059</t>
   </si>
   <si>
     <t xml:space="preserve">5.54813528060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48621416091919</t>
+    <t xml:space="preserve">5.48621463775635</t>
   </si>
   <si>
     <t xml:space="preserve">5.53162384033203</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">5.32934761047363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771270751953</t>
+    <t xml:space="preserve">5.27568292617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.30045127868652</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">5.12294340133667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19312143325806</t>
+    <t xml:space="preserve">5.1931209564209</t>
   </si>
   <si>
     <t xml:space="preserve">5.10230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1518406867981</t>
+    <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17248058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34998750686646</t>
+    <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
     <t xml:space="preserve">5.3995246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74628400802612</t>
+    <t xml:space="preserve">5.74628353118896</t>
   </si>
   <si>
     <t xml:space="preserve">5.75041198730469</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72977113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77517986297607</t>
+    <t xml:space="preserve">5.72977161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77518033981323</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599731445312</t>
+    <t xml:space="preserve">5.86599779129028</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489412307739</t>
+    <t xml:space="preserve">5.89489507675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.04763317108154</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">6.06827306747437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10955476760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17560386657715</t>
+    <t xml:space="preserve">6.10955429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
     <t xml:space="preserve">6.17973136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19211626052856</t>
+    <t xml:space="preserve">6.19211578369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275663375854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385887145996</t>
+    <t xml:space="preserve">6.18385982513428</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193822860718</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">6.16734743118286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1508355140686</t>
+    <t xml:space="preserve">6.13845109939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083503723145</t>
   </si>
   <si>
     <t xml:space="preserve">5.98158407211304</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">6.05176162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09717035293579</t>
+    <t xml:space="preserve">6.09716987609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.18798732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15909147262573</t>
+    <t xml:space="preserve">6.15909099578857</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001710891724</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">6.0889139175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91140556335449</t>
+    <t xml:space="preserve">5.91140604019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.87425374984741</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">5.93617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9609432220459</t>
+    <t xml:space="preserve">5.96094417572021</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222396850586</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">6.64207649230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88976097106934</t>
+    <t xml:space="preserve">6.88976144790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.8526086807251</t>
@@ -935,70 +935,70 @@
     <t xml:space="preserve">6.89801645278931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82371234893799</t>
+    <t xml:space="preserve">6.82371187210083</t>
   </si>
   <si>
     <t xml:space="preserve">6.75353479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77004623413086</t>
+    <t xml:space="preserve">6.7700457572937</t>
   </si>
   <si>
     <t xml:space="preserve">6.60492372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69574117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392824172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43980073928833</t>
+    <t xml:space="preserve">6.69574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43980026245117</t>
   </si>
   <si>
     <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45631265640259</t>
+    <t xml:space="preserve">6.45631217956543</t>
   </si>
   <si>
     <t xml:space="preserve">6.57189846038818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65446043014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71638202667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61318016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53061819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66684484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44805669784546</t>
+    <t xml:space="preserve">6.65446090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71638154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61317920684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53061771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66684436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44805717468262</t>
   </si>
   <si>
     <t xml:space="preserve">6.65858888626099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55538702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.625563621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50584983825684</t>
+    <t xml:space="preserve">6.55538654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62556409835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50584936141968</t>
   </si>
   <si>
     <t xml:space="preserve">6.55125856399536</t>
@@ -1007,43 +1007,43 @@
     <t xml:space="preserve">6.60905170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72876596450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84848070144653</t>
+    <t xml:space="preserve">6.7287654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84848022460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.75766277313232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90214538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70812511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748569488525</t>
+    <t xml:space="preserve">6.90214443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70812559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6874852180481</t>
   </si>
   <si>
     <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705152511597</t>
+    <t xml:space="preserve">6.77417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705200195312</t>
   </si>
   <si>
     <t xml:space="preserve">7.47594785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47182035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356391906738</t>
+    <t xml:space="preserve">7.4718189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356344223022</t>
   </si>
   <si>
     <t xml:space="preserve">7.64932775497437</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">7.95480537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76078367233276</t>
+    <t xml:space="preserve">7.76078414916992</t>
   </si>
   <si>
     <t xml:space="preserve">7.84334659576416</t>
@@ -1064,55 +1064,55 @@
     <t xml:space="preserve">7.6617112159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75665760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57915067672729</t>
+    <t xml:space="preserve">7.75665712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915115356445</t>
   </si>
   <si>
     <t xml:space="preserve">7.28192853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2241358757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41402626037598</t>
+    <t xml:space="preserve">7.40989923477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331747055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41402578353882</t>
   </si>
   <si>
     <t xml:space="preserve">7.46769142150879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57089376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29431200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1787257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38100147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33972215652466</t>
+    <t xml:space="preserve">7.57089328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38100242614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33972120285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.1993670463562</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">7.01773166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05488538742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7948145866394</t>
+    <t xml:space="preserve">7.0548849105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406602859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79481363296509</t>
   </si>
   <si>
     <t xml:space="preserve">6.7494068145752</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">7.25303173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19111108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07965135574341</t>
+    <t xml:space="preserve">7.19111061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07965087890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.8402247428894</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">7.05075550079346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23652029037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053817749023</t>
+    <t xml:space="preserve">7.2365198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053913116455</t>
   </si>
   <si>
     <t xml:space="preserve">7.30669641494751</t>
@@ -1169,43 +1169,43 @@
     <t xml:space="preserve">7.26128673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25715923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2778000831604</t>
+    <t xml:space="preserve">7.2571587562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27779960632324</t>
   </si>
   <si>
     <t xml:space="preserve">8.23138618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12405776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41302108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056777954102</t>
+    <t xml:space="preserve">8.12405681610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6276798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41302013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.24789905548096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17359256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09103107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19835948944092</t>
+    <t xml:space="preserve">8.17359352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09103202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19836139678955</t>
   </si>
   <si>
     <t xml:space="preserve">8.18184852600098</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295219421387</t>
+    <t xml:space="preserve">8.14469528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295124053955</t>
   </si>
   <si>
     <t xml:space="preserve">8.20248889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430088043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348533630371</t>
+    <t xml:space="preserve">8.45430278778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348342895508</t>
   </si>
   <si>
     <t xml:space="preserve">8.33045959472656</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">8.52035045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79280376434326</t>
+    <t xml:space="preserve">8.79280471801758</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82582855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070652008057</t>
+    <t xml:space="preserve">8.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070747375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.83408451080322</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">8.86711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6689624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42953491210938</t>
+    <t xml:space="preserve">8.66896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65244960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42953395843506</t>
   </si>
   <si>
     <t xml:space="preserve">8.67109203338623</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">8.74605655670166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7044095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77104663848877</t>
+    <t xml:space="preserve">8.70440864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77104568481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.75438690185547</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">8.24628257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30875492095947</t>
+    <t xml:space="preserve">8.30875396728516</t>
   </si>
   <si>
     <t xml:space="preserve">8.3462381362915</t>
@@ -1310,22 +1310,22 @@
     <t xml:space="preserve">8.87933158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57946586608887</t>
+    <t xml:space="preserve">8.5794677734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269454956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82102298736572</t>
+    <t xml:space="preserve">8.81269359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.86267185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72939777374268</t>
+    <t xml:space="preserve">8.72939872741699</t>
   </si>
   <si>
     <t xml:space="preserve">8.5044994354248</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">8.47118282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461196899414</t>
+    <t xml:space="preserve">8.45452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461101531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.58779525756836</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">8.36289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42120361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21713066101074</t>
+    <t xml:space="preserve">8.42120456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21712875366211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08802032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59612369537354</t>
+    <t xml:space="preserve">8.59612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777351379395</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639558792114</t>
+    <t xml:space="preserve">8.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.92142963409424</t>
@@ -1385,31 +1385,31 @@
     <t xml:space="preserve">8.02554893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733303070068</t>
+    <t xml:space="preserve">7.76733255386353</t>
   </si>
   <si>
     <t xml:space="preserve">7.85062789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61323499679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572908401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72152042388916</t>
+    <t xml:space="preserve">7.61323547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234342575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6715407371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572813034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145137786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72151947021484</t>
   </si>
   <si>
     <t xml:space="preserve">7.59241056442261</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">7.82980251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54659986495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6340594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229850769043</t>
+    <t xml:space="preserve">7.54659938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229755401611</t>
   </si>
   <si>
     <t xml:space="preserve">7.792320728302</t>
@@ -1436,55 +1436,55 @@
     <t xml:space="preserve">7.6173996925354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71318960189819</t>
+    <t xml:space="preserve">7.71319055557251</t>
   </si>
   <si>
     <t xml:space="preserve">7.74650812149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6882004737854</t>
+    <t xml:space="preserve">7.68820095062256</t>
   </si>
   <si>
     <t xml:space="preserve">7.44664335250854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2883825302124</t>
+    <t xml:space="preserve">7.28838157653809</t>
   </si>
   <si>
     <t xml:space="preserve">7.14677858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19259119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321229934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637241363525</t>
+    <t xml:space="preserve">7.19259071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637336730957</t>
   </si>
   <si>
     <t xml:space="preserve">8.1713171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3295783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463466644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378944396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52948760986328</t>
+    <t xml:space="preserve">8.47951221466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23379039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5294885635376</t>
   </si>
   <si>
     <t xml:space="preserve">9.0542516708374</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">8.99594402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01260471343994</t>
+    <t xml:space="preserve">9.01260375976562</t>
   </si>
   <si>
     <t xml:space="preserve">9.00427436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07923984527588</t>
+    <t xml:space="preserve">9.0792407989502</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255836486816</t>
+    <t xml:space="preserve">9.11255931854248</t>
   </si>
   <si>
     <t xml:space="preserve">9.0959005355835</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">9.02926349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66276168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57113647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02138423919678</t>
+    <t xml:space="preserve">8.66276264190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02138519287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.08385562896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15049362182617</t>
+    <t xml:space="preserve">8.15049266815186</t>
   </si>
   <si>
     <t xml:space="preserve">8.00056076049805</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">8.35456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98390054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82563972473145</t>
+    <t xml:space="preserve">7.9839015007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563877105713</t>
   </si>
   <si>
     <t xml:space="preserve">7.9922308921814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27126979827881</t>
+    <t xml:space="preserve">8.27127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.07969093322754</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">8.46285247802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60445404052734</t>
+    <t xml:space="preserve">8.60445499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.1379976272583</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">8.20047092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19214057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09635066986084</t>
+    <t xml:space="preserve">8.19214153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.14216232299805</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">8.12550449371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17964553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94641733169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25877571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97557210922241</t>
+    <t xml:space="preserve">8.17964744567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94641828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9755711555481</t>
   </si>
   <si>
     <t xml:space="preserve">7.89227676391602</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">7.62989330291748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79648447036743</t>
+    <t xml:space="preserve">7.79648542404175</t>
   </si>
   <si>
     <t xml:space="preserve">7.75483798980713</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21296405792236</t>
+    <t xml:space="preserve">8.21296501159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.18381118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19630718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962474822998</t>
+    <t xml:space="preserve">8.1963062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962379455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43786430358887</t>
+    <t xml:space="preserve">8.43786239624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944316864014</t>
+    <t xml:space="preserve">8.62944412231445</t>
   </si>
   <si>
     <t xml:space="preserve">8.3712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
+    <t xml:space="preserve">8.51282978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69607925415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.83768272399902</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">8.77937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37910556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56235504150391</t>
+    <t xml:space="preserve">8.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37910652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56235599517822</t>
   </si>
   <si>
     <t xml:space="preserve">9.59567546844482</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">9.28747940063477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29580879211426</t>
+    <t xml:space="preserve">9.29580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35411739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66231250762939</t>
+    <t xml:space="preserve">9.35411643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66231155395508</t>
   </si>
   <si>
     <t xml:space="preserve">9.17086601257324</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">9.22917366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27082061767578</t>
+    <t xml:space="preserve">9.2708215713501</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13754844665527</t>
+    <t xml:space="preserve">9.13754940032959</t>
   </si>
   <si>
     <t xml:space="preserve">9.16253662109375</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">9.0709114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56280708312988</t>
+    <t xml:space="preserve">8.56280612945557</t>
   </si>
   <si>
     <t xml:space="preserve">8.64610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06258106231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10422992706299</t>
+    <t xml:space="preserve">9.04592227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06258201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10422897338867</t>
   </si>
   <si>
     <t xml:space="preserve">8.94596767425537</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">8.83797168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781372070312</t>
+    <t xml:space="preserve">8.65155124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781467437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.59223651885986</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">8.6430778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597499847412</t>
+    <t xml:space="preserve">8.5159740447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.48208045959473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49055290222168</t>
+    <t xml:space="preserve">8.490553855896</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039684295654</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26176643371582</t>
+    <t xml:space="preserve">8.2617654800415</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39310646057129</t>
+    <t xml:space="preserve">8.39310741424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.33379173278809</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">8.31260681152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27871227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.287184715271</t>
+    <t xml:space="preserve">8.27871322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28718566894531</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023983001709</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394779205322</t>
+    <t xml:space="preserve">8.44394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.3253173828125</t>
@@ -1859,28 +1859,28 @@
     <t xml:space="preserve">8.52444744110107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849803924561</t>
+    <t xml:space="preserve">8.66849708557129</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44818496704102</t>
+    <t xml:space="preserve">8.44818592071533</t>
   </si>
   <si>
     <t xml:space="preserve">8.6091833114624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62613010406494</t>
+    <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20245170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35921287536621</t>
+    <t xml:space="preserve">8.2024507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35921192169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727933883667</t>
@@ -1889,31 +1889,31 @@
     <t xml:space="preserve">8.11771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03297805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89740037918091</t>
+    <t xml:space="preserve">8.03297901153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89740133285522</t>
   </si>
   <si>
     <t xml:space="preserve">8.13466167449951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96518850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90163850784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792863845825</t>
+    <t xml:space="preserve">7.9651894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9016375541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72369146347046</t>
+    <t xml:space="preserve">7.72369194030762</t>
   </si>
   <si>
     <t xml:space="preserve">7.95671606063843</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">7.71945476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66013956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7109808921814</t>
+    <t xml:space="preserve">7.57540369033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66014003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
     <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4142894744873</t>
+    <t xml:space="preserve">8.41429042816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.31684303283691</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42276382446289</t>
+    <t xml:space="preserve">8.42276477813721</t>
   </si>
   <si>
     <t xml:space="preserve">8.19821262359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24058246612549</t>
+    <t xml:space="preserve">8.24058151245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.21939754486084</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71934127807617</t>
+    <t xml:space="preserve">8.71934032440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.46936893463135</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">8.88881206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90575981140137</t>
+    <t xml:space="preserve">8.90576076507568</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270755767822</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">8.97354793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13042545318604</t>
+    <t xml:space="preserve">8.13042449951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.22363376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18973922729492</t>
+    <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
     <t xml:space="preserve">8.37192249298096</t>
@@ -2015,22 +2015,22 @@
     <t xml:space="preserve">8.49902629852295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7617073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81254959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60071086883545</t>
+    <t xml:space="preserve">8.76170825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81255054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60070991516113</t>
   </si>
   <si>
     <t xml:space="preserve">8.54139423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697143554688</t>
+    <t xml:space="preserve">8.69392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697238922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.85491752624512</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">9.02438926696777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28707122802734</t>
+    <t xml:space="preserve">9.28707218170166</t>
   </si>
   <si>
     <t xml:space="preserve">9.57517528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349166870117</t>
+    <t xml:space="preserve">9.47349262237549</t>
   </si>
   <si>
     <t xml:space="preserve">9.42264938354492</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">9.30401992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60906887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65143871307373</t>
+    <t xml:space="preserve">9.60906982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65143775939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.53280639648438</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76159477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78701496124268</t>
+    <t xml:space="preserve">9.76159381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78701400756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.83785629272461</t>
@@ -2096,55 +2096,55 @@
     <t xml:space="preserve">9.91411876678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9734354019165</t>
+    <t xml:space="preserve">9.97343444824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0835905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0158014297485</t>
+    <t xml:space="preserve">10.1344337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0835914611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0158023834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.93953895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0666437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1768016815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1598529815674</t>
+    <t xml:space="preserve">10.0666446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1768007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2276411056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1598539352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.2615356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.25306224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1683263778687</t>
+    <t xml:space="preserve">10.2530632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.168327331543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1937475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0496959686279</t>
+    <t xml:space="preserve">10.0496969223022</t>
   </si>
   <si>
     <t xml:space="preserve">9.82938385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94801235198975</t>
+    <t xml:space="preserve">9.94801330566406</t>
   </si>
   <si>
     <t xml:space="preserve">9.99885559082031</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">9.92259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51586055755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0581693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73617267608643</t>
+    <t xml:space="preserve">9.51585960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0581703186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73617362976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.84632968902588</t>
@@ -2180,25 +2180,25 @@
     <t xml:space="preserve">8.32108020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01603126525879</t>
+    <t xml:space="preserve">8.01603221893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60082483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322090148926</t>
+    <t xml:space="preserve">7.7067437171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6008243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322137832642</t>
   </si>
   <si>
     <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99072504043579</t>
+    <t xml:space="preserve">6.99072456359863</t>
   </si>
   <si>
     <t xml:space="preserve">6.71109580993652</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484798431396</t>
+    <t xml:space="preserve">5.08416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484846115112</t>
   </si>
   <si>
     <t xml:space="preserve">5.09687376022339</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80865716934204</t>
+    <t xml:space="preserve">5.59258031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80865669250488</t>
   </si>
   <si>
     <t xml:space="preserve">5.50784397125244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210927963257</t>
+    <t xml:space="preserve">5.26210975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690284729004</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20279359817505</t>
+    <t xml:space="preserve">5.20279407501221</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">5.73663091659546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93152379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07557582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70273637771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53326463699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49513292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87220859527588</t>
+    <t xml:space="preserve">5.9315242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70273685455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53326511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49513339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8722095489502</t>
   </si>
   <si>
     <t xml:space="preserve">5.93576049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10099601745605</t>
+    <t xml:space="preserve">6.10099649429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.13065385818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88068246841431</t>
+    <t xml:space="preserve">5.88068294525146</t>
   </si>
   <si>
     <t xml:space="preserve">5.67731618881226</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289386749268</t>
+    <t xml:space="preserve">5.81289434432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.75357818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66460514068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65189504623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05015420913696</t>
+    <t xml:space="preserve">5.66460561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65189552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05015516281128</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881418228149</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">6.03320741653442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35520458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2916522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39333486557007</t>
+    <t xml:space="preserve">6.3552041053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29165267944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39333534240723</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835662841797</t>
+    <t xml:space="preserve">6.94835710525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.91022539138794</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">7.04156637191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24917078018188</t>
+    <t xml:space="preserve">7.24916982650757</t>
   </si>
   <si>
     <t xml:space="preserve">7.10088109970093</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57551860809326</t>
+    <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
     <t xml:space="preserve">6.71533250808716</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">6.55009746551514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60941314697266</t>
+    <t xml:space="preserve">6.6094126701355</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3255467414856</t>
+    <t xml:space="preserve">6.32554721832275</t>
   </si>
   <si>
     <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14760160446167</t>
+    <t xml:space="preserve">6.14760065078735</t>
   </si>
   <si>
     <t xml:space="preserve">6.28741598129272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12641716003418</t>
+    <t xml:space="preserve">6.12641763687134</t>
   </si>
   <si>
     <t xml:space="preserve">6.15183782577515</t>
@@ -2423,43 +2423,43 @@
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912773132324</t>
+    <t xml:space="preserve">6.13912725448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981252670288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36367797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2450475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47383499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807216644287</t>
+    <t xml:space="preserve">6.04591798782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36367750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24504709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47383451461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807168960571</t>
   </si>
   <si>
     <t xml:space="preserve">6.27046871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22386312484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14336442947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0840482711792</t>
+    <t xml:space="preserve">6.06286525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22386360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14336395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08404874801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.95270776748657</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">6.02049684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99931240081787</t>
+    <t xml:space="preserve">5.99931287765503</t>
   </si>
   <si>
     <t xml:space="preserve">6.38486194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32978343963623</t>
+    <t xml:space="preserve">6.32978391647339</t>
   </si>
   <si>
     <t xml:space="preserve">6.32131004333496</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">6.25775814056396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2747049331665</t>
+    <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.23233699798584</t>
@@ -2504,22 +2504,22 @@
     <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37215185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483333587646</t>
+    <t xml:space="preserve">6.37215089797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483285903931</t>
   </si>
   <si>
     <t xml:space="preserve">6.986487865448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019630432129</t>
+    <t xml:space="preserve">7.16019678115845</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377729415894</t>
+    <t xml:space="preserve">6.97377681732178</t>
   </si>
   <si>
     <t xml:space="preserve">6.73228025436401</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0161452293396</t>
+    <t xml:space="preserve">7.01614475250244</t>
   </si>
   <si>
     <t xml:space="preserve">6.90175294876099</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10946989059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0543909072876</t>
+    <t xml:space="preserve">6.10947036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05439138412476</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168128967285</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">5.9484715461731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09252309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00778722763062</t>
+    <t xml:space="preserve">6.09252262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00778675079346</t>
   </si>
   <si>
     <t xml:space="preserve">5.90610313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57563304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60105323791504</t>
+    <t xml:space="preserve">5.57563257217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4908971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">5.28753042221069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06297922134399</t>
+    <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
     <t xml:space="preserve">5.05874252319336</t>
@@ -2606,25 +2606,25 @@
     <t xml:space="preserve">5.40616035461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43158102035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76205158233643</t>
+    <t xml:space="preserve">5.43158149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76205205917358</t>
   </si>
   <si>
     <t xml:space="preserve">5.81713056564331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831405639648</t>
+    <t xml:space="preserve">5.83831453323364</t>
   </si>
   <si>
     <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82125282287598</t>
+    <t xml:space="preserve">6.74075365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82125234603882</t>
   </si>
   <si>
     <t xml:space="preserve">7.0458025932312</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">7.88045310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53303623199463</t>
+    <t xml:space="preserve">7.53303527832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.49914073944092</t>
@@ -2645,49 +2645,49 @@
     <t xml:space="preserve">7.4525351524353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62624454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77453422546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77029705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8719801902771</t>
+    <t xml:space="preserve">7.62624502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200784683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77453327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77029752731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87197923660278</t>
   </si>
   <si>
     <t xml:space="preserve">7.84232187271118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67285013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266450881958</t>
+    <t xml:space="preserve">7.67284917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8126654624939</t>
   </si>
   <si>
     <t xml:space="preserve">7.79571723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63471937179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011142730713</t>
+    <t xml:space="preserve">7.6347188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011047363281</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537460327148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85503387451172</t>
+    <t xml:space="preserve">7.8550329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.68556070327759</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">7.52456188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47795724868774</t>
+    <t xml:space="preserve">7.47795677185059</t>
   </si>
   <si>
     <t xml:space="preserve">7.58811378479004</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">7.4101676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28730154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22374868392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32543182373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31695890426636</t>
+    <t xml:space="preserve">7.28730201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22374820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32543230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3169584274292</t>
   </si>
   <si>
     <t xml:space="preserve">7.18985366821289</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">7.06275033950806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1813817024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15596008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63895702362061</t>
+    <t xml:space="preserve">7.18138074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15596055984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
     <t xml:space="preserve">7.64319276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74911260604858</t>
+    <t xml:space="preserve">7.74911308288574</t>
   </si>
   <si>
     <t xml:space="preserve">7.53727245330811</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">7.85926914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21516132354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2321081161499</t>
+    <t xml:space="preserve">8.21516036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23210716247559</t>
   </si>
   <si>
     <t xml:space="preserve">8.18550300598145</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">8.20668792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30837059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79148006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65166616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03721618652344</t>
+    <t xml:space="preserve">8.30837154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14313411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79147911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65166521072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03721523284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.92282152175903</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033771514893</t>
+    <t xml:space="preserve">8.88033866882324</t>
   </si>
   <si>
     <t xml:space="preserve">8.63460350036621</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78712940216064</t>
+    <t xml:space="preserve">8.93965435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78712844848633</t>
   </si>
   <si>
     <t xml:space="preserve">8.68544673919678</t>
@@ -2813,28 +2813,28 @@
     <t xml:space="preserve">9.5582275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60059547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96507549285889</t>
+    <t xml:space="preserve">9.60059642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133796691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21928310394287</t>
+    <t xml:space="preserve">9.21928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.04981136322021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71075248718262</t>
+    <t xml:space="preserve">9.71075344085693</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44807052612305</t>
+    <t xml:space="preserve">9.44806957244873</t>
   </si>
   <si>
     <t xml:space="preserve">9.48196506500244</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">10.0412244796753</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74464702606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72769832611084</t>
+    <t xml:space="preserve">9.74464797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.52433300018311</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0361328125</t>
+    <t xml:space="preserve">9.03613376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.91496086120605</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689128875732</t>
+    <t xml:space="preserve">8.96689224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.0880651473999</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">9.33906936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43427658081055</t>
+    <t xml:space="preserve">9.43427753448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.63335037231445</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">9.3217601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2178955078125</t>
+    <t xml:space="preserve">9.21789455413818</t>
   </si>
   <si>
     <t xml:space="preserve">9.1140308380127</t>
@@ -2915,49 +2915,49 @@
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26117038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51217555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46889877319336</t>
+    <t xml:space="preserve">9.01882457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26117134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51217460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46889972686768</t>
   </si>
   <si>
     <t xml:space="preserve">9.2698278427124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31310272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33041381835938</t>
+    <t xml:space="preserve">9.31310367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33041477203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34772491455078</t>
+    <t xml:space="preserve">9.3477258682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.1313419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1226863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10537624359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00151252746582</t>
+    <t xml:space="preserve">9.12268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10537719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">8.75916385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82840633392334</t>
+    <t xml:space="preserve">8.82840728759766</t>
   </si>
   <si>
     <t xml:space="preserve">9.05344486236572</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">9.36503505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41696739196777</t>
+    <t xml:space="preserve">9.41696834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.16596412658691</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">9.25251579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1746187210083</t>
+    <t xml:space="preserve">9.17461967468262</t>
   </si>
   <si>
     <t xml:space="preserve">8.94958114624023</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">8.77647495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98420143127441</t>
+    <t xml:space="preserve">8.98420238494873</t>
   </si>
   <si>
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6639575958252</t>
+    <t xml:space="preserve">8.66395664215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84571743011475</t>
+    <t xml:space="preserve">8.84571838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78513050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72454261779785</t>
+    <t xml:space="preserve">8.78512954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72454357147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.63798999786377</t>
@@ -3029,31 +3029,31 @@
     <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44324684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36967658996582</t>
+    <t xml:space="preserve">8.44324588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3696756362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.26581287384033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23119163513184</t>
+    <t xml:space="preserve">8.19656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23119068145752</t>
   </si>
   <si>
     <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74185466766357</t>
+    <t xml:space="preserve">8.74185562133789</t>
   </si>
   <si>
     <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131450653076</t>
+    <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
     <t xml:space="preserve">8.42160797119141</t>
@@ -3062,37 +3062,37 @@
     <t xml:space="preserve">8.3610200881958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47354030609131</t>
+    <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
     <t xml:space="preserve">8.63366222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67261123657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62933540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59904193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50383186340332</t>
+    <t xml:space="preserve">8.67261219024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62933444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59904098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50383281707764</t>
   </si>
   <si>
     <t xml:space="preserve">8.54278182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58605766296387</t>
+    <t xml:space="preserve">8.58605861663818</t>
   </si>
   <si>
     <t xml:space="preserve">8.81975078582764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80244159698486</t>
+    <t xml:space="preserve">8.80244064331055</t>
   </si>
   <si>
     <t xml:space="preserve">7.92825508117676</t>
@@ -3107,37 +3107,37 @@
     <t xml:space="preserve">7.87632369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99749755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9628758430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91960048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95854902267456</t>
+    <t xml:space="preserve">7.99749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96287679672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91959953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527318954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95854806900024</t>
   </si>
   <si>
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128564834595</t>
+    <t xml:space="preserve">7.82439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128612518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55607748031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981784820557</t>
+    <t xml:space="preserve">7.556077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981832504272</t>
   </si>
   <si>
     <t xml:space="preserve">7.39162683486938</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">7.35267782211304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09734678268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16658878326416</t>
+    <t xml:space="preserve">7.09734630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.166588306427</t>
   </si>
   <si>
     <t xml:space="preserve">7.05839776992798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18390035629272</t>
+    <t xml:space="preserve">7.18389987945557</t>
   </si>
   <si>
     <t xml:space="preserve">7.11032962799072</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">7.33969449996948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51280117034912</t>
+    <t xml:space="preserve">7.51280164718628</t>
   </si>
   <si>
     <t xml:space="preserve">7.42191982269287</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">7.37431669235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33104038238525</t>
+    <t xml:space="preserve">7.3310399055481</t>
   </si>
   <si>
     <t xml:space="preserve">7.15360641479492</t>
@@ -3182,40 +3182,40 @@
     <t xml:space="preserve">7.06272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14927864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20121002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27045297622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19255590438843</t>
+    <t xml:space="preserve">7.14927816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2012095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27045249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19255542755127</t>
   </si>
   <si>
     <t xml:space="preserve">7.25746965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26179838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24448680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4046106338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654153823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3180570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700607299805</t>
+    <t xml:space="preserve">7.26179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2444863319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40461015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31805658340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41759252548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700654983521</t>
   </si>
   <si>
     <t xml:space="preserve">7.36566114425659</t>
@@ -3224,28 +3224,28 @@
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583126068115</t>
+    <t xml:space="preserve">7.23583078384399</t>
   </si>
   <si>
     <t xml:space="preserve">7.14062356948853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07138109207153</t>
+    <t xml:space="preserve">7.07138061523438</t>
   </si>
   <si>
     <t xml:space="preserve">7.02377605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01944875717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91991281509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8809642791748</t>
+    <t xml:space="preserve">7.01944828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88961935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91991329193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88096380233765</t>
   </si>
   <si>
     <t xml:space="preserve">6.66458129882812</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">6.42656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40492296218872</t>
+    <t xml:space="preserve">6.40492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">6.36164569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47849321365356</t>
+    <t xml:space="preserve">6.47849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">6.43088817596436</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">6.44387149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5563907623291</t>
+    <t xml:space="preserve">6.55639028549194</t>
   </si>
   <si>
     <t xml:space="preserve">6.75978994369507</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">6.21883344650269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21450567245483</t>
+    <t xml:space="preserve">6.21450614929199</t>
   </si>
   <si>
     <t xml:space="preserve">6.10198736190796</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">6.2015233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11497068405151</t>
+    <t xml:space="preserve">6.11497020721436</t>
   </si>
   <si>
     <t xml:space="preserve">6.05005550384521</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">6.08034896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70817041397095</t>
+    <t xml:space="preserve">5.70817089080811</t>
   </si>
   <si>
     <t xml:space="preserve">5.60863494873047</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">5.53073740005493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55670309066772</t>
+    <t xml:space="preserve">5.55670356750488</t>
   </si>
   <si>
     <t xml:space="preserve">5.55237579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63460063934326</t>
+    <t xml:space="preserve">5.63460111618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506469726562</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85098361968994</t>
+    <t xml:space="preserve">5.8509840965271</t>
   </si>
   <si>
     <t xml:space="preserve">5.7341365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05438327789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08467626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0587100982666</t>
+    <t xml:space="preserve">6.05438280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08467674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.37030124664307</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99812316894531</t>
+    <t xml:space="preserve">5.99812364578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.1539192199707</t>
@@ -3404,22 +3404,22 @@
     <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14526319503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18421268463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34000825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19286823272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1236252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1755576133728</t>
+    <t xml:space="preserve">6.145263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18421220779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19286775588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12362480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17555713653564</t>
   </si>
   <si>
     <t xml:space="preserve">6.26211023330688</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24480009078979</t>
+    <t xml:space="preserve">6.24479961395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.11929798126221</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34433507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10631465911865</t>
+    <t xml:space="preserve">6.34433555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10631418228149</t>
   </si>
   <si>
     <t xml:space="preserve">6.27900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19044828414917</t>
+    <t xml:space="preserve">6.19044780731201</t>
   </si>
   <si>
     <t xml:space="preserve">6.12845516204834</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">6.27458190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34543037414551</t>
+    <t xml:space="preserve">6.34543085098267</t>
   </si>
   <si>
     <t xml:space="preserve">6.4162802696228</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">5.86277055740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67679119110107</t>
+    <t xml:space="preserve">5.67679166793823</t>
   </si>
   <si>
     <t xml:space="preserve">5.57937431335449</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">5.40225076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65022325515747</t>
+    <t xml:space="preserve">5.65022373199463</t>
   </si>
   <si>
     <t xml:space="preserve">5.59708642959595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61922693252563</t>
+    <t xml:space="preserve">5.61922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.62808275222778</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">5.81406211853027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79192209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6059422492981</t>
+    <t xml:space="preserve">5.79192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60594177246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">5.88933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77863788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92476367950439</t>
+    <t xml:space="preserve">5.77863740921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92476415634155</t>
   </si>
   <si>
     <t xml:space="preserve">5.85834264755249</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">5.74321269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84948635101318</t>
+    <t xml:space="preserve">5.84948682785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.94690418243408</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">5.96904420852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07531833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07974672317505</t>
+    <t xml:space="preserve">6.07531881332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07974624633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.95576000213623</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660989761353</t>
+    <t xml:space="preserve">6.02660942077637</t>
   </si>
   <si>
     <t xml:space="preserve">5.99561309814453</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">5.96018838882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95133209228516</t>
+    <t xml:space="preserve">5.95133256912231</t>
   </si>
   <si>
     <t xml:space="preserve">6.01775360107422</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">6.06646203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8760552406311</t>
+    <t xml:space="preserve">5.87605571746826</t>
   </si>
   <si>
     <t xml:space="preserve">5.89819526672363</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">5.61037063598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67236423492432</t>
+    <t xml:space="preserve">5.67236375808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.73435640335083</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">5.5572338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59265851974487</t>
+    <t xml:space="preserve">5.59265804290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.68564796447754</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">5.8671989440918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6546516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62365436553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68121957778931</t>
+    <t xml:space="preserve">5.65465116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62365484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68121910095215</t>
   </si>
   <si>
     <t xml:space="preserve">5.7299280166626</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3188624382019</t>
+    <t xml:space="preserve">6.31886291503906</t>
   </si>
   <si>
     <t xml:space="preserve">6.25244140625</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">6.17273569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08417415618896</t>
+    <t xml:space="preserve">6.08417463302612</t>
   </si>
   <si>
     <t xml:space="preserve">6.06203413009644</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">6.29672241210938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4472770690918</t>
+    <t xml:space="preserve">6.44727659225464</t>
   </si>
   <si>
     <t xml:space="preserve">6.58897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4738450050354</t>
+    <t xml:space="preserve">6.47384452819824</t>
   </si>
   <si>
     <t xml:space="preserve">6.42513656616211</t>
@@ -3758,22 +3758,22 @@
     <t xml:space="preserve">6.53141021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668706893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75724220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7926664352417</t>
+    <t xml:space="preserve">6.60668754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75724172592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79266691207886</t>
   </si>
   <si>
     <t xml:space="preserve">6.65539598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54912233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52255392074585</t>
+    <t xml:space="preserve">6.54912185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52255344390869</t>
   </si>
   <si>
     <t xml:space="preserve">6.53583812713623</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">6.63325548171997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49155712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5136981010437</t>
+    <t xml:space="preserve">6.49155759811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51369762420654</t>
   </si>
   <si>
     <t xml:space="preserve">6.50926971435547</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">6.4074239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55355024337769</t>
+    <t xml:space="preserve">6.55355072021484</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425228118896</t>
@@ -3830,34 +3830,34 @@
     <t xml:space="preserve">7.05392265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96093320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98307418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06720733642578</t>
+    <t xml:space="preserve">6.96093368530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98307371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06720685958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.32846307754517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63842868804932</t>
+    <t xml:space="preserve">7.63842916488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81998014450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58529138565063</t>
+    <t xml:space="preserve">7.81997919082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58529186248779</t>
   </si>
   <si>
     <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20890617370605</t>
+    <t xml:space="preserve">7.2089056968689</t>
   </si>
   <si>
     <t xml:space="preserve">7.19562149047852</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">7.3018946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52329874038696</t>
+    <t xml:space="preserve">7.5232982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.49230241775513</t>
@@ -3881,34 +3881,34 @@
     <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34617614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48787403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34174728393555</t>
+    <t xml:space="preserve">7.34617567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48787450790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
     <t xml:space="preserve">7.10263252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31517934799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22661733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32403612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35060405731201</t>
+    <t xml:space="preserve">7.3151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32403564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35060358047485</t>
   </si>
   <si>
     <t xml:space="preserve">7.25318574905396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17790842056274</t>
+    <t xml:space="preserve">7.1779088973999</t>
   </si>
   <si>
     <t xml:space="preserve">7.2753267288208</t>
@@ -3917,13 +3917,13 @@
     <t xml:space="preserve">7.29303884506226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41259670257568</t>
+    <t xml:space="preserve">7.41259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">7.44802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48344612121582</t>
+    <t xml:space="preserve">7.48344564437866</t>
   </si>
   <si>
     <t xml:space="preserve">7.36388778686523</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">7.20004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95207691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74838590621948</t>
+    <t xml:space="preserve">6.95207738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74838542938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.00078582763672</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">7.17348098754883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31960773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38602828979492</t>
+    <t xml:space="preserve">7.31960821151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38602876663208</t>
   </si>
   <si>
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3993124961853</t>
+    <t xml:space="preserve">7.39931201934814</t>
   </si>
   <si>
     <t xml:space="preserve">7.27975463867188</t>
@@ -4013,22 +4013,22 @@
     <t xml:space="preserve">7.45687770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54543972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47458982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68270921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60300397872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67828130722046</t>
+    <t xml:space="preserve">7.54543924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47458934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68270969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60300445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71370649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67828178405762</t>
   </si>
   <si>
     <t xml:space="preserve">7.85610342025757</t>
@@ -4160,9 +4160,6 @@
     <t xml:space="preserve">7.53237581253052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67828178405762</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.69651889801025</t>
   </si>
   <si>
@@ -5421,6 +5418,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.6999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -53695,7 +53695,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1844" t="s">
-        <v>1382</v>
+        <v>1338</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -53721,7 +53721,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1845" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -53747,7 +53747,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1846" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -53773,7 +53773,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G1847" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -53825,7 +53825,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53851,7 +53851,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1850" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -53877,7 +53877,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1851" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -53903,7 +53903,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1852" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -53929,7 +53929,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1853" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -53981,7 +53981,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G1855" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -54007,7 +54007,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1856" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -54033,7 +54033,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G1857" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54059,7 +54059,7 @@
         <v>8</v>
       </c>
       <c r="G1858" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -54085,7 +54085,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1859" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -54111,7 +54111,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1860" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54137,7 +54137,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1861" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -54163,7 +54163,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1862" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -54189,7 +54189,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1863" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -54215,7 +54215,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1864" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -54241,7 +54241,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1865" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -54267,7 +54267,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54293,7 +54293,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1867" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -54319,7 +54319,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -54345,7 +54345,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1869" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -54371,7 +54371,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1870" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54397,7 +54397,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1871" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -54423,7 +54423,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -54449,7 +54449,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G1873" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -54475,7 +54475,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1874" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -54501,7 +54501,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -54527,7 +54527,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1876" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -54553,7 +54553,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1877" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -54579,7 +54579,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -54605,7 +54605,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G1879" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -54631,7 +54631,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1880" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -54657,7 +54657,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G1881" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -54683,7 +54683,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1882" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -54709,7 +54709,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1883" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -54735,7 +54735,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1884" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -54761,7 +54761,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1885" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -54787,7 +54787,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1886" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -54813,7 +54813,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1887" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -54839,7 +54839,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1888" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -54865,7 +54865,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1889" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -54891,7 +54891,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -54917,7 +54917,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G1891" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54943,7 +54943,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1892" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -54969,7 +54969,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -54995,7 +54995,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1894" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -55021,7 +55021,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -55047,7 +55047,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -55073,7 +55073,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1897" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -55099,7 +55099,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1898" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -55125,7 +55125,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1899" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -55151,7 +55151,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -55177,7 +55177,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1901" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -55203,7 +55203,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1902" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -55229,7 +55229,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1903" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -55255,7 +55255,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1904" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55281,7 +55281,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1905" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -55307,7 +55307,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1906" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55333,7 +55333,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1907" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -55359,7 +55359,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -55385,7 +55385,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1909" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -55411,7 +55411,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G1910" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -55437,7 +55437,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1911" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -55463,7 +55463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1912" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -55489,7 +55489,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G1913" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -55515,7 +55515,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1914" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -55541,7 +55541,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1915" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -55567,7 +55567,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1916" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -55593,7 +55593,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1917" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -55619,7 +55619,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1918" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -55645,7 +55645,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1919" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -55671,7 +55671,7 @@
         <v>7.75</v>
       </c>
       <c r="G1920" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -55697,7 +55697,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1921" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -55723,7 +55723,7 @@
         <v>7.875</v>
       </c>
       <c r="G1922" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55749,7 +55749,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1923" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -55775,7 +55775,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1924" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -55801,7 +55801,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1925" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -55827,7 +55827,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -55853,7 +55853,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1927" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -55879,7 +55879,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1928" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -55905,7 +55905,7 @@
         <v>8</v>
       </c>
       <c r="G1929" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -55931,7 +55931,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1930" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -55957,7 +55957,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1931" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -55983,7 +55983,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1932" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -56009,7 +56009,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1933" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56061,7 +56061,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1935" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -56113,7 +56113,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -56165,7 +56165,7 @@
         <v>8.75</v>
       </c>
       <c r="G1939" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -56191,7 +56191,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1940" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -56217,7 +56217,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -56243,7 +56243,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -56269,7 +56269,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1943" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -56321,7 +56321,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1945" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -56347,7 +56347,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1946" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -56373,7 +56373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -56399,7 +56399,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -56425,7 +56425,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1949" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -56451,7 +56451,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -56477,7 +56477,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1951" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -56503,7 +56503,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1952" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -56529,7 +56529,7 @@
         <v>9.125</v>
       </c>
       <c r="G1953" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -56555,7 +56555,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G1954" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -56581,7 +56581,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G1955" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -56607,7 +56607,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1956" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -56633,7 +56633,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1957" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56685,7 +56685,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1959" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56711,7 +56711,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1960" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56737,7 +56737,7 @@
         <v>9</v>
       </c>
       <c r="G1961" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56763,7 +56763,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56789,7 +56789,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56815,7 +56815,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1964" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56841,7 +56841,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1965" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56867,7 +56867,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1966" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56893,7 +56893,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G1967" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56919,7 +56919,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G1968" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56945,7 +56945,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1969" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56971,7 +56971,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1970" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56997,7 +56997,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1971" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57023,7 +57023,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1972" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57049,7 +57049,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57075,7 +57075,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G1974" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57101,7 +57101,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1975" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57127,7 +57127,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1976" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57153,7 +57153,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57179,7 +57179,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1978" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57205,7 +57205,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1979" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57257,7 +57257,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1981" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57283,7 +57283,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G1982" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57309,7 +57309,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G1983" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57335,7 +57335,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G1984" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57361,7 +57361,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1985" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57387,7 +57387,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57413,7 +57413,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1987" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57439,7 +57439,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1988" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57465,7 +57465,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1989" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57491,7 +57491,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1990" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57517,7 +57517,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1991" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57543,7 +57543,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G1992" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57569,7 +57569,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1993" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57595,7 +57595,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1994" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57621,7 +57621,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57647,7 +57647,7 @@
         <v>8.75</v>
       </c>
       <c r="G1996" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57673,7 +57673,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1997" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57699,7 +57699,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G1998" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57725,7 +57725,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1999" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57751,7 +57751,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57777,7 +57777,7 @@
         <v>9.25</v>
       </c>
       <c r="G2001" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57803,7 +57803,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2002" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57829,7 +57829,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2003" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57855,7 +57855,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2004" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57881,7 +57881,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57907,7 +57907,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G2006" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57933,7 +57933,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2007" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57959,7 +57959,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G2008" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57985,7 +57985,7 @@
         <v>9.375</v>
       </c>
       <c r="G2009" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58011,7 +58011,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2010" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58037,7 +58037,7 @@
         <v>9.73499965667725</v>
       </c>
       <c r="G2011" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58063,7 +58063,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2012" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58089,7 +58089,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2013" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58141,7 +58141,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2015" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58167,7 +58167,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2016" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58193,7 +58193,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G2017" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58219,7 +58219,7 @@
         <v>9</v>
       </c>
       <c r="G2018" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58271,7 +58271,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2020" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58297,7 +58297,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G2021" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58323,7 +58323,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G2022" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58349,7 +58349,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2023" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58401,7 +58401,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2025" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58427,7 +58427,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2026" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58453,7 +58453,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G2027" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58479,7 +58479,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58557,7 +58557,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2031" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58583,7 +58583,7 @@
         <v>8.84500026702881</v>
       </c>
       <c r="G2032" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58609,7 +58609,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2033" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58635,7 +58635,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2034" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58661,7 +58661,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2035" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58687,7 +58687,7 @@
         <v>8.86499977111816</v>
       </c>
       <c r="G2036" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58713,7 +58713,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G2037" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58739,7 +58739,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G2038" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58765,7 +58765,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G2039" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58791,7 +58791,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58817,7 +58817,7 @@
         <v>9.25</v>
       </c>
       <c r="G2041" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58843,7 +58843,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58869,7 +58869,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G2043" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58895,7 +58895,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2044" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58921,7 +58921,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58947,7 +58947,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2046" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58973,7 +58973,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2047" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58999,7 +58999,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2048" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59025,7 +59025,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2049" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59051,7 +59051,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2050" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59077,7 +59077,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G2051" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59103,7 +59103,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2052" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59129,7 +59129,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59155,7 +59155,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2054" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59181,7 +59181,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59207,7 +59207,7 @@
         <v>9.125</v>
       </c>
       <c r="G2056" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59233,7 +59233,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G2057" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59259,7 +59259,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2058" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59285,7 +59285,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2059" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59311,7 +59311,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2060" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59337,7 +59337,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G2061" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59363,7 +59363,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2062" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59389,7 +59389,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2063" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59415,7 +59415,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2064" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59441,7 +59441,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2065" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59467,7 +59467,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G2066" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59493,7 +59493,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G2067" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59519,7 +59519,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G2068" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59545,7 +59545,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2069" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59571,7 +59571,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G2070" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59597,7 +59597,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2071" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59623,7 +59623,7 @@
         <v>9.5</v>
       </c>
       <c r="G2072" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59649,7 +59649,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2073" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59675,7 +59675,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2074" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59701,7 +59701,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59727,7 +59727,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2076" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59753,7 +59753,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2077" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59779,7 +59779,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59805,7 +59805,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2079" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59831,7 +59831,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2080" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59857,7 +59857,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2081" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59883,7 +59883,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2082" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59909,7 +59909,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2083" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59935,7 +59935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2084" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59961,7 +59961,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59987,7 +59987,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2086" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60013,7 +60013,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2087" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60039,7 +60039,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G2088" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60065,7 +60065,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G2089" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60091,7 +60091,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G2090" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60117,7 +60117,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2091" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60143,7 +60143,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G2092" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60169,7 +60169,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2093" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60195,7 +60195,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60221,7 +60221,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2095" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60247,7 +60247,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2096" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60273,7 +60273,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2097" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60299,7 +60299,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2098" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60325,7 +60325,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G2099" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60351,7 +60351,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G2100" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60377,7 +60377,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G2101" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60403,7 +60403,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G2102" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60429,7 +60429,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G2103" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60455,7 +60455,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2104" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60481,7 +60481,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2105" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60507,7 +60507,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2106" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60533,7 +60533,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2107" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60559,7 +60559,7 @@
         <v>8.875</v>
       </c>
       <c r="G2108" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60585,7 +60585,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2109" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60611,7 +60611,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2110" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60637,7 +60637,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G2111" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60663,7 +60663,7 @@
         <v>9.125</v>
       </c>
       <c r="G2112" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60689,7 +60689,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2113" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60715,7 +60715,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G2114" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60741,7 +60741,7 @@
         <v>9.25</v>
       </c>
       <c r="G2115" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60767,7 +60767,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2116" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60793,7 +60793,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2117" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60819,7 +60819,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2118" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60845,7 +60845,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G2119" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60871,7 +60871,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2120" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60897,7 +60897,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2121" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60923,7 +60923,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60949,7 +60949,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60975,7 +60975,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61001,7 +61001,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G2125" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61027,7 +61027,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G2126" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61053,7 +61053,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2127" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61079,7 +61079,7 @@
         <v>9.25</v>
       </c>
       <c r="G2128" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61105,7 +61105,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2129" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61131,7 +61131,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G2130" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61157,7 +61157,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G2131" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61183,7 +61183,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G2132" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61209,7 +61209,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2133" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61235,7 +61235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2134" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61261,7 +61261,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2135" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61287,7 +61287,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G2136" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61313,7 +61313,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G2137" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61339,7 +61339,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G2138" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61365,7 +61365,7 @@
         <v>9.25</v>
       </c>
       <c r="G2139" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61391,7 +61391,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61417,7 +61417,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2141" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61443,7 +61443,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2142" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61469,7 +61469,7 @@
         <v>9.375</v>
       </c>
       <c r="G2143" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61495,7 +61495,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2144" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61521,7 +61521,7 @@
         <v>9.375</v>
       </c>
       <c r="G2145" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61547,7 +61547,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2146" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61573,7 +61573,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2147" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61599,7 +61599,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61625,7 +61625,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2149" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61651,7 +61651,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2150" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61677,7 +61677,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2151" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61703,7 +61703,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2152" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61729,7 +61729,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61755,7 +61755,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2154" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61781,7 +61781,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2155" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61807,7 +61807,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G2156" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61833,7 +61833,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2157" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61859,7 +61859,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G2158" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61885,7 +61885,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G2159" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61911,7 +61911,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61937,7 +61937,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2161" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61963,7 +61963,7 @@
         <v>9.625</v>
       </c>
       <c r="G2162" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61989,7 +61989,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G2163" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62015,7 +62015,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G2164" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62041,7 +62041,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G2165" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62067,7 +62067,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2166" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62093,7 +62093,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G2167" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62119,7 +62119,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62145,7 +62145,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G2169" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62171,7 +62171,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G2170" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62197,7 +62197,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2171" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62223,7 +62223,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2172" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62249,7 +62249,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2173" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62275,7 +62275,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2174" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62301,7 +62301,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2175" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62327,7 +62327,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62353,7 +62353,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G2177" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62379,7 +62379,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G2178" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62405,7 +62405,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2179" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62431,7 +62431,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2180" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62457,7 +62457,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2181" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62483,7 +62483,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G2182" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62509,7 +62509,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2183" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62535,7 +62535,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2184" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62561,7 +62561,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2185" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62587,7 +62587,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2186" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62613,7 +62613,7 @@
         <v>10.5</v>
       </c>
       <c r="G2187" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62639,7 +62639,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2188" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62665,7 +62665,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62691,7 +62691,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2190" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62717,7 +62717,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2191" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62743,7 +62743,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2192" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62769,7 +62769,7 @@
         <v>10.25</v>
       </c>
       <c r="G2193" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62795,7 +62795,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2194" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62821,7 +62821,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2195" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62847,7 +62847,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2196" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62873,7 +62873,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2197" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62899,7 +62899,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2198" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62925,7 +62925,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2199" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62951,7 +62951,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2200" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62977,7 +62977,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2201" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63003,7 +63003,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2202" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63029,7 +63029,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G2203" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63055,7 +63055,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2204" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63081,7 +63081,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G2205" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63107,7 +63107,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2206" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63133,7 +63133,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2207" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63159,7 +63159,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2208" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63185,7 +63185,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G2209" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63211,7 +63211,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2210" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63237,7 +63237,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2211" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63263,7 +63263,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G2212" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63289,7 +63289,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G2213" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63315,7 +63315,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G2214" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63341,7 +63341,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2215" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63367,7 +63367,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2216" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63393,7 +63393,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2217" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63419,7 +63419,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G2218" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63445,7 +63445,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2219" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63471,7 +63471,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2220" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63497,7 +63497,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2221" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63523,7 +63523,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2222" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63549,7 +63549,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63575,7 +63575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2224" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63601,7 +63601,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2225" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63627,7 +63627,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2226" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63653,7 +63653,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2227" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63679,7 +63679,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2228" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63705,7 +63705,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2229" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63731,7 +63731,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2230" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63757,7 +63757,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2231" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63783,7 +63783,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2232" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63809,7 +63809,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2233" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63835,7 +63835,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2234" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63861,7 +63861,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2235" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63887,7 +63887,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2236" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63913,7 +63913,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2237" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63939,7 +63939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2238" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63965,7 +63965,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2239" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63991,7 +63991,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2240" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64017,7 +64017,7 @@
         <v>11.5</v>
       </c>
       <c r="G2241" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64043,7 +64043,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2242" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64069,7 +64069,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64095,7 +64095,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2244" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64121,7 +64121,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2245" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64147,7 +64147,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2246" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64173,7 +64173,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G2247" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64199,7 +64199,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2248" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64225,7 +64225,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64251,7 +64251,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G2250" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64277,7 +64277,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2251" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64303,7 +64303,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G2252" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64329,7 +64329,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2253" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64355,7 +64355,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2254" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64381,7 +64381,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2255" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64407,7 +64407,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2256" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64433,7 +64433,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2257" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64459,7 +64459,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2258" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64485,7 +64485,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64511,7 +64511,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2260" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64537,7 +64537,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2261" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64563,7 +64563,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2262" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64589,7 +64589,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64615,7 +64615,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64641,7 +64641,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G2265" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64667,7 +64667,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2266" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64693,7 +64693,7 @@
         <v>12</v>
       </c>
       <c r="G2267" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64719,7 +64719,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2268" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64745,7 +64745,7 @@
         <v>12</v>
       </c>
       <c r="G2269" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64771,7 +64771,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2270" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64797,7 +64797,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2271" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64823,7 +64823,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G2272" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64849,7 +64849,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G2273" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64875,7 +64875,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2274" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64901,7 +64901,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2275" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64927,7 +64927,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G2276" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64953,7 +64953,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2277" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64979,7 +64979,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65005,7 +65005,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2279" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65031,7 +65031,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65057,7 +65057,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2281" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65083,7 +65083,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2282" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65109,7 +65109,7 @@
         <v>11.25</v>
       </c>
       <c r="G2283" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65135,7 +65135,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2284" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65161,7 +65161,7 @@
         <v>11.5</v>
       </c>
       <c r="G2285" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65187,7 +65187,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2286" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65213,7 +65213,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2287" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65239,7 +65239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2288" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65265,7 +65265,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2289" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65291,7 +65291,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2290" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65317,7 +65317,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2291" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65343,7 +65343,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2292" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65369,7 +65369,7 @@
         <v>12.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65395,7 +65395,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G2294" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65421,7 +65421,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2295" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65447,7 +65447,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2296" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65473,7 +65473,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2297" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65499,7 +65499,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2298" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65525,7 +65525,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65551,7 +65551,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65577,7 +65577,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G2301" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65603,7 +65603,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G2302" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65629,7 +65629,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G2303" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65655,7 +65655,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2304" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65681,7 +65681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65707,7 +65707,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G2306" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65733,7 +65733,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2307" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65759,7 +65759,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G2308" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65785,7 +65785,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2309" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65811,7 +65811,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2310" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65837,7 +65837,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2311" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65863,7 +65863,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2312" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65889,7 +65889,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G2313" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65915,7 +65915,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2314" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65941,7 +65941,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2315" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65967,7 +65967,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2316" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65993,7 +65993,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G2317" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66019,7 +66019,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2318" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66045,7 +66045,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G2319" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66071,7 +66071,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2320" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66097,7 +66097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2321" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66123,7 +66123,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G2322" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66149,7 +66149,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G2323" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66175,7 +66175,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G2324" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66201,7 +66201,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2325" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66227,7 +66227,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2326" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66253,7 +66253,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2327" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66279,7 +66279,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2328" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66305,7 +66305,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66331,7 +66331,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2330" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66357,7 +66357,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66383,7 +66383,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2332" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66409,7 +66409,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G2333" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66435,7 +66435,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2334" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66461,7 +66461,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2335" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66487,7 +66487,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G2336" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66513,7 +66513,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2337" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66539,7 +66539,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66565,7 +66565,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G2339" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66591,7 +66591,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2340" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66617,7 +66617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2341" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66643,7 +66643,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66669,7 +66669,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2343" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66695,7 +66695,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2344" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66721,7 +66721,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2345" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66747,7 +66747,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2346" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66773,7 +66773,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66799,7 +66799,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G2348" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66825,7 +66825,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G2349" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66851,7 +66851,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2350" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66877,7 +66877,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66903,7 +66903,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66929,7 +66929,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G2353" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66955,7 +66955,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G2354" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66981,7 +66981,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G2355" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67007,7 +67007,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G2356" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67033,7 +67033,7 @@
         <v>14</v>
       </c>
       <c r="G2357" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67059,7 +67059,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2358" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67085,7 +67085,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2359" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67111,7 +67111,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2360" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67137,7 +67137,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2361" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67163,7 +67163,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2362" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67189,7 +67189,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G2363" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67215,7 +67215,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67241,7 +67241,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2365" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67267,7 +67267,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2366" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67293,7 +67293,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G2367" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67319,7 +67319,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2368" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67345,7 +67345,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2369" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67371,7 +67371,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67397,7 +67397,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G2371" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67423,7 +67423,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2372" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67449,7 +67449,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G2373" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67475,7 +67475,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G2374" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67501,7 +67501,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G2375" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67527,7 +67527,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G2376" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67553,7 +67553,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67579,7 +67579,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2378" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67605,7 +67605,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67631,7 +67631,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2380" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67657,7 +67657,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67683,7 +67683,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G2382" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67709,7 +67709,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G2383" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67735,7 +67735,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G2384" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67761,7 +67761,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2385" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67787,7 +67787,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G2386" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67813,7 +67813,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G2387" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67839,7 +67839,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2388" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67865,7 +67865,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2389" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67891,7 +67891,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2390" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67917,7 +67917,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67943,7 +67943,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2392" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67969,7 +67969,7 @@
         <v>14.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67995,7 +67995,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G2394" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68021,7 +68021,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G2395" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68047,7 +68047,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2396" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68073,7 +68073,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2397" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68099,7 +68099,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G2398" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68125,7 +68125,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68151,7 +68151,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2400" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68177,7 +68177,7 @@
         <v>14.25</v>
       </c>
       <c r="G2401" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68203,7 +68203,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G2402" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68229,7 +68229,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G2403" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68255,7 +68255,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2404" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68281,7 +68281,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2405" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68307,7 +68307,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2406" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68333,7 +68333,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G2407" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68359,7 +68359,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G2408" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68385,7 +68385,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68411,7 +68411,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G2410" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68437,7 +68437,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G2411" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68463,7 +68463,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68489,7 +68489,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G2413" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68515,7 +68515,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2414" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68541,7 +68541,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68567,7 +68567,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G2416" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68593,7 +68593,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G2417" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68601,7 +68601,7 @@
     </row>
     <row r="2418">
       <c r="A2418" s="1" t="n">
-        <v>45961.6909837963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2418" t="n">
         <v>270923</v>
@@ -68619,9 +68619,35 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2418" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H2418" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>45964.6911805556</v>
+      </c>
+      <c r="B2419" t="n">
+        <v>232007</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>15.8800001144409</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>15.6499996185303</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>15.8999996185303</v>
+      </c>
+      <c r="G2419" t="s">
         <v>1802</v>
       </c>
-      <c r="H2418" t="s">
+      <c r="H2419" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1806">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032619476318</t>
+    <t xml:space="preserve">2.9603259563446</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">3.13860011100769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12387990951538</t>
+    <t xml:space="preserve">3.12388014793396</t>
   </si>
   <si>
     <t xml:space="preserve">3.10588908195496</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">3.06663656234741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06500053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028104782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647686958313</t>
+    <t xml:space="preserve">3.06500005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028080940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476845741272</t>
   </si>
   <si>
     <t xml:space="preserve">3.17131066322327</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">3.15822625160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14514183998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15168404579163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30051827430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34140729904175</t>
+    <t xml:space="preserve">3.14514231681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15168428421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30051851272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34140706062317</t>
   </si>
   <si>
     <t xml:space="preserve">3.43463253974915</t>
@@ -98,34 +98,34 @@
     <t xml:space="preserve">3.43790364265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39374423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393068313599</t>
+    <t xml:space="preserve">3.39374470710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393115997314</t>
   </si>
   <si>
     <t xml:space="preserve">3.33977127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24000334739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14841341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03065466880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08789801597595</t>
+    <t xml:space="preserve">3.24000358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14841318130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0306544303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08789825439453</t>
   </si>
   <si>
     <t xml:space="preserve">3.1729462146759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10752487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18112397193909</t>
+    <t xml:space="preserve">3.10752463340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18112421035767</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257283210754</t>
@@ -134,49 +134,49 @@
     <t xml:space="preserve">3.19911503791809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03392505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12878680229187</t>
+    <t xml:space="preserve">3.0339252948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373860359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12878704071045</t>
   </si>
   <si>
     <t xml:space="preserve">3.23019051551819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2334611415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22528338432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1140673160553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14023566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12224459648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09116959571838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897373199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135581016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425400733948</t>
+    <t xml:space="preserve">3.23346138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2252836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11406707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14023590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1222448348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08299160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897349357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1042537689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.07481384277344</t>
@@ -185,76 +185,76 @@
     <t xml:space="preserve">3.14677762985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13696455955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21383476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16640448570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10916042327881</t>
+    <t xml:space="preserve">3.13696432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21383452415466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16640400886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10916066169739</t>
   </si>
   <si>
     <t xml:space="preserve">3.36921095848083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42645478248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5098671913147</t>
+    <t xml:space="preserve">3.42645502090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50986742973328</t>
   </si>
   <si>
     <t xml:space="preserve">3.5164098739624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54094266891479</t>
+    <t xml:space="preserve">3.54094243049622</t>
   </si>
   <si>
     <t xml:space="preserve">3.50168967247009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47552061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35612678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32014489173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29724740982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36103343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37575316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738919258118</t>
+    <t xml:space="preserve">3.47552108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35612630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32014465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29724717140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36103320121765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37575268745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738847732544</t>
   </si>
   <si>
     <t xml:space="preserve">3.35285568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38556575775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136096000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150274276733</t>
+    <t xml:space="preserve">3.38556623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136191368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150298118591</t>
   </si>
   <si>
     <t xml:space="preserve">3.47061467170715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46734356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696970939636</t>
+    <t xml:space="preserve">3.4673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696994781494</t>
   </si>
   <si>
     <t xml:space="preserve">3.44281029701233</t>
@@ -263,31 +263,31 @@
     <t xml:space="preserve">3.3970148563385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41337037086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860502243042</t>
+    <t xml:space="preserve">3.41337060928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488605260849</t>
   </si>
   <si>
     <t xml:space="preserve">3.45916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41827702522278</t>
+    <t xml:space="preserve">3.4182767868042</t>
   </si>
   <si>
     <t xml:space="preserve">3.50823187828064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.557297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57855987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472822189331</t>
+    <t xml:space="preserve">3.55729794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57856035232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472869873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.56547570228577</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">3.5981867313385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6390745639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360831260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725279808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6799635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636425018311</t>
+    <t xml:space="preserve">3.63907480239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725208282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67996335029602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178559303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636377334595</t>
   </si>
   <si>
     <t xml:space="preserve">3.56711149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46897912025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40355730056763</t>
+    <t xml:space="preserve">3.46897864341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40355777740479</t>
   </si>
   <si>
     <t xml:space="preserve">3.38065958023071</t>
@@ -329,88 +329,88 @@
     <t xml:space="preserve">3.33813571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28743386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27598571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2432746887207</t>
+    <t xml:space="preserve">3.28743410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668709754944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27598547935486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24327445030212</t>
   </si>
   <si>
     <t xml:space="preserve">3.21874141693115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25962972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495538711548</t>
+    <t xml:space="preserve">3.25962996482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1549551486969</t>
   </si>
   <si>
     <t xml:space="preserve">3.07644963264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08462738990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1255156993866</t>
+    <t xml:space="preserve">3.08462715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12551593780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.27107858657837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31850957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486461639404</t>
+    <t xml:space="preserve">3.31850934028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486485481262</t>
   </si>
   <si>
     <t xml:space="preserve">3.3675754070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40846395492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30869626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818134307861</t>
+    <t xml:space="preserve">3.40846419334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30869579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818086624146</t>
   </si>
   <si>
     <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48206353187561</t>
+    <t xml:space="preserve">3.48206305503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.54421377182007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61454153060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528877258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183121681213</t>
+    <t xml:space="preserve">3.61454224586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528901100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183073997498</t>
   </si>
   <si>
     <t xml:space="preserve">3.63253283500671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60309290885925</t>
+    <t xml:space="preserve">3.60309362411499</t>
   </si>
   <si>
     <t xml:space="preserve">3.66851449012756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64071083068848</t>
+    <t xml:space="preserve">3.64071106910706</t>
   </si>
   <si>
     <t xml:space="preserve">3.61617732048035</t>
@@ -419,85 +419,85 @@
     <t xml:space="preserve">3.62435507774353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75192737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7617404460907</t>
+    <t xml:space="preserve">3.7519268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174068450928</t>
   </si>
   <si>
     <t xml:space="preserve">3.72412300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77809548377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77646017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118061065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720788955688</t>
+    <t xml:space="preserve">3.77809619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646040916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79117965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720741271973</t>
   </si>
   <si>
     <t xml:space="preserve">3.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79445123672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071574211121</t>
+    <t xml:space="preserve">3.7944507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071550369263</t>
   </si>
   <si>
     <t xml:space="preserve">3.91548109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86314415931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89258408546448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9252941608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440632820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655609130859</t>
+    <t xml:space="preserve">3.86314392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258456230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529439926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641430854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655656814575</t>
   </si>
   <si>
     <t xml:space="preserve">3.86150884628296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96454787254333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8516948223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.043053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767695426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86968564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898427009583</t>
+    <t xml:space="preserve">3.96454739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305267333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86968588829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81898474693298</t>
   </si>
   <si>
     <t xml:space="preserve">3.91384482383728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94164991378784</t>
+    <t xml:space="preserve">3.94165062904358</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">3.97272515296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00216484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00707101821899</t>
+    <t xml:space="preserve">4.00216436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97926759719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00707197189331</t>
   </si>
   <si>
     <t xml:space="preserve">4.01524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08394145965576</t>
+    <t xml:space="preserve">4.04141807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0839409828186</t>
   </si>
   <si>
     <t xml:space="preserve">4.16244745254517</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048929214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595649719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37506723403931</t>
+    <t xml:space="preserve">4.44048881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37506818771362</t>
   </si>
   <si>
     <t xml:space="preserve">4.59586524963379</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78804111480713</t>
+    <t xml:space="preserve">4.78804159164429</t>
   </si>
   <si>
     <t xml:space="preserve">4.99248361587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80439710617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710813522339</t>
+    <t xml:space="preserve">4.8043966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710765838623</t>
   </si>
   <si>
     <t xml:space="preserve">4.83301877975464</t>
@@ -578,76 +578,76 @@
     <t xml:space="preserve">4.9638614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02928352355957</t>
+    <t xml:space="preserve">5.02928447723389</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337240219116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283723831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150405883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688097000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46270132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56492233276367</t>
+    <t xml:space="preserve">5.19283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830396652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688144683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36865854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46270084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56492185592651</t>
   </si>
   <si>
     <t xml:space="preserve">5.56901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55265617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30323696136475</t>
+    <t xml:space="preserve">5.55265665054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30323648452759</t>
   </si>
   <si>
     <t xml:space="preserve">5.26643657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5485668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354543685913</t>
+    <t xml:space="preserve">5.54856729507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354400634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.60172271728516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70803213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75709867477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80207586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82252025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114145278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816804885864</t>
+    <t xml:space="preserve">5.70803308486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75709819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82251977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114240646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78572034835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">5.47905683517456</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">5.48723459243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46679019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581064224243</t>
+    <t xml:space="preserve">5.46679067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581111907959</t>
   </si>
   <si>
     <t xml:space="preserve">5.56083393096924</t>
@@ -671,40 +671,40 @@
     <t xml:space="preserve">5.69674634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4614462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546560287476</t>
+    <t xml:space="preserve">5.46144580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546607971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.705002784729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73802757263184</t>
+    <t xml:space="preserve">5.73802661895752</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756475448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8040771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84948587417603</t>
+    <t xml:space="preserve">5.80407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
     <t xml:space="preserve">5.90315008163452</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10129737854004</t>
+    <t xml:space="preserve">6.10129833221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.84122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82471656799316</t>
+    <t xml:space="preserve">5.82471704483032</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820465087891</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">5.75866746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133810043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233310699463</t>
+    <t xml:space="preserve">5.65133714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233263015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.7793083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77105188369751</t>
+    <t xml:space="preserve">5.77105140686035</t>
   </si>
   <si>
     <t xml:space="preserve">5.8453574180603</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.68849039077759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56877613067627</t>
+    <t xml:space="preserve">5.56877660751343</t>
   </si>
   <si>
     <t xml:space="preserve">5.63069772720337</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">5.5770320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52336740493774</t>
+    <t xml:space="preserve">5.5233678817749</t>
   </si>
   <si>
     <t xml:space="preserve">5.54813528060913</t>
@@ -755,61 +755,61 @@
     <t xml:space="preserve">5.53162384033203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32934761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27568197250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30045127868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294340133667</t>
+    <t xml:space="preserve">5.55639171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32934808731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27568244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30045175552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294387817383</t>
   </si>
   <si>
     <t xml:space="preserve">5.1931209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10230302810669</t>
+    <t xml:space="preserve">5.10230398178101</t>
   </si>
   <si>
     <t xml:space="preserve">5.15184020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17248010635376</t>
+    <t xml:space="preserve">5.17248058319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.34998798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39952564239502</t>
+    <t xml:space="preserve">5.39952516555786</t>
   </si>
   <si>
     <t xml:space="preserve">5.74628353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75041198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592889785767</t>
+    <t xml:space="preserve">5.75041151046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592937469482</t>
   </si>
   <si>
     <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72977113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77518033981323</t>
+    <t xml:space="preserve">5.72977161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77517986297607</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
@@ -818,40 +818,40 @@
     <t xml:space="preserve">5.87012624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599731445312</t>
+    <t xml:space="preserve">5.86599779129028</t>
   </si>
   <si>
     <t xml:space="preserve">5.94443082809448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89489412307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04763317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86187028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06827306747437</t>
+    <t xml:space="preserve">5.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04763269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86186933517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06827354431152</t>
   </si>
   <si>
     <t xml:space="preserve">6.10955429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17560386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17973136901855</t>
+    <t xml:space="preserve">6.17560338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
     <t xml:space="preserve">6.19211626052856</t>
@@ -866,88 +866,88 @@
     <t xml:space="preserve">6.12193822860718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1673469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15083408355713</t>
+    <t xml:space="preserve">6.16734743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13845014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083503723145</t>
   </si>
   <si>
     <t xml:space="preserve">5.98158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05176162719727</t>
+    <t xml:space="preserve">6.05176115036011</t>
   </si>
   <si>
     <t xml:space="preserve">6.09716987609863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18798685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15909051895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06001758575439</t>
+    <t xml:space="preserve">6.18798780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15909099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06001806259155</t>
   </si>
   <si>
     <t xml:space="preserve">5.98571252822876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08891439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87425327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93617534637451</t>
+    <t xml:space="preserve">6.0889139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87425374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93617486953735</t>
   </si>
   <si>
     <t xml:space="preserve">5.96094369888306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00222396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22926902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207696914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8526086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89801645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82371234893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75353527069092</t>
+    <t xml:space="preserve">6.00222492218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85260915756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89801692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7535343170166</t>
   </si>
   <si>
     <t xml:space="preserve">6.77004671096802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60492420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574117660522</t>
+    <t xml:space="preserve">6.60492324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574069976807</t>
   </si>
   <si>
     <t xml:space="preserve">6.58015537261963</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">6.44392824172974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43980026245117</t>
+    <t xml:space="preserve">6.43979978561401</t>
   </si>
   <si>
     <t xml:space="preserve">6.52649021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5718994140625</t>
+    <t xml:space="preserve">6.45631313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57189893722534</t>
   </si>
   <si>
     <t xml:space="preserve">6.65446090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71638202667236</t>
+    <t xml:space="preserve">6.71638154983521</t>
   </si>
   <si>
     <t xml:space="preserve">6.61318016052246</t>
@@ -980,43 +980,43 @@
     <t xml:space="preserve">6.53061771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66684436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44805669784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65858840942383</t>
+    <t xml:space="preserve">6.66684484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44805717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65858888626099</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.625563621521</t>
+    <t xml:space="preserve">6.62556266784668</t>
   </si>
   <si>
     <t xml:space="preserve">6.56777095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50585031509399</t>
+    <t xml:space="preserve">6.50584983825684</t>
   </si>
   <si>
     <t xml:space="preserve">6.55125856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6090521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72876596450806</t>
+    <t xml:space="preserve">6.60905170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7287654876709</t>
   </si>
   <si>
     <t xml:space="preserve">6.84848070144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75766229629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90214490890503</t>
+    <t xml:space="preserve">6.75766277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90214443206787</t>
   </si>
   <si>
     <t xml:space="preserve">6.70812559127808</t>
@@ -1028,49 +1028,49 @@
     <t xml:space="preserve">6.71225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77417469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594785690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47182035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7607855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590856552124</t>
+    <t xml:space="preserve">6.77417516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43466711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47181987762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356344223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932775497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.843346118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66171026229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665807723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590808868408</t>
   </si>
   <si>
     <t xml:space="preserve">7.57914972305298</t>
@@ -1082,64 +1082,64 @@
     <t xml:space="preserve">7.40989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28605556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413492202759</t>
+    <t xml:space="preserve">7.28605604171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1333179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241358757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46769189834595</t>
+    <t xml:space="preserve">7.46769142150879</t>
   </si>
   <si>
     <t xml:space="preserve">7.57089424133301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872667312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
+    <t xml:space="preserve">7.29431295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890422821045</t>
   </si>
   <si>
     <t xml:space="preserve">7.38100099563599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1993670463562</t>
+    <t xml:space="preserve">7.33972215652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936656951904</t>
   </si>
   <si>
     <t xml:space="preserve">7.03011608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01773071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79481506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74940633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68335723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79068803787231</t>
+    <t xml:space="preserve">7.01773118972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406698226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7948145866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68335819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79068756103516</t>
   </si>
   <si>
     <t xml:space="preserve">7.25303173065186</t>
@@ -1148,43 +1148,43 @@
     <t xml:space="preserve">7.19111013412476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07965230941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84022426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05075597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2365198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128768920898</t>
+    <t xml:space="preserve">7.07965278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84022378921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05075645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23651933670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669641494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128816604614</t>
   </si>
   <si>
     <t xml:space="preserve">7.25715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36036157608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27780055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23138618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12405490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476608276367</t>
+    <t xml:space="preserve">7.36036205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2778000831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23138523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12405586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476417541504</t>
   </si>
   <si>
     <t xml:space="preserve">8.62768077850342</t>
@@ -1193,40 +1193,40 @@
     <t xml:space="preserve">8.41302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1405668258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789905548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17359256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09103107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19836139678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18184852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20661640167236</t>
+    <t xml:space="preserve">8.14056777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17359352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09103202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18184947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20661735534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.14469528198242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15295219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20248985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430183410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522937774658</t>
+    <t xml:space="preserve">8.15295314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20249080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430088043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522842407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.36348533630371</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">8.33046054840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47907161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52035236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79280567169189</t>
+    <t xml:space="preserve">8.47907066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52035140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79280471801758</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
@@ -1250,43 +1250,43 @@
     <t xml:space="preserve">8.71024322509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82582855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83408451080322</t>
+    <t xml:space="preserve">8.82582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">8.86711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66896343231201</t>
+    <t xml:space="preserve">8.66896057128906</t>
   </si>
   <si>
     <t xml:space="preserve">8.65244960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67721748352051</t>
+    <t xml:space="preserve">8.67721843719482</t>
   </si>
   <si>
     <t xml:space="preserve">8.42953395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67109203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74605751037598</t>
+    <t xml:space="preserve">8.67109107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74605655670166</t>
   </si>
   <si>
     <t xml:space="preserve">8.70440864562988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75438594818115</t>
+    <t xml:space="preserve">8.77104663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75438690185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.24628257751465</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">8.8793306350708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57946681976318</t>
+    <t xml:space="preserve">8.57946586608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269359588623</t>
+    <t xml:space="preserve">8.81269454956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.82102394104004</t>
@@ -1325,28 +1325,28 @@
     <t xml:space="preserve">8.86267280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72939872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50449848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111377716064</t>
+    <t xml:space="preserve">8.72939777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50450038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">8.47118186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58779621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49617004394531</t>
+    <t xml:space="preserve">8.45452117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49617099761963</t>
   </si>
   <si>
     <t xml:space="preserve">8.36289691925049</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">8.21712875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08802127838135</t>
+    <t xml:space="preserve">8.08802032470703</t>
   </si>
   <si>
     <t xml:space="preserve">8.59612560272217</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">8.63777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16298675537109</t>
+    <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
     <t xml:space="preserve">8.12133884429932</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">7.99639558792114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92142963409424</t>
+    <t xml:space="preserve">7.9214301109314</t>
   </si>
   <si>
     <t xml:space="preserve">7.78815603256226</t>
@@ -1385,73 +1385,73 @@
     <t xml:space="preserve">8.02554893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74234247207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67154264450073</t>
+    <t xml:space="preserve">7.76733160018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062742233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323499679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.863121509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74234294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67154169082642</t>
   </si>
   <si>
     <t xml:space="preserve">7.62572908401489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87145137786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72151899337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57158660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82980442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54659795761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63405990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.792320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68820142745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44664287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28838109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14677810668945</t>
+    <t xml:space="preserve">7.87145185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72151947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57158613204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82980346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5465989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79232025146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6173996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71318960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68820095062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44664239883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28838205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14677858352661</t>
   </si>
   <si>
     <t xml:space="preserve">7.19259166717529</t>
@@ -1460,37 +1460,37 @@
     <t xml:space="preserve">7.47163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66321325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637241363525</t>
+    <t xml:space="preserve">7.66321229934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637145996094</t>
   </si>
   <si>
     <t xml:space="preserve">8.17131805419922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951221466064</t>
+    <t xml:space="preserve">8.47951030731201</t>
   </si>
   <si>
     <t xml:space="preserve">8.3295783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20463562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378849029541</t>
+    <t xml:space="preserve">8.20463466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">8.37955570220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52948760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0542516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99594497680664</t>
+    <t xml:space="preserve">8.52948665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05425262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99594402313232</t>
   </si>
   <si>
     <t xml:space="preserve">9.01260375976562</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">9.0792407989502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80436325073242</t>
+    <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.11255836486816</t>
@@ -1511,79 +1511,79 @@
     <t xml:space="preserve">9.09589958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02093315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02926254272461</t>
+    <t xml:space="preserve">9.02093410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02926349639893</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113647460938</t>
+    <t xml:space="preserve">8.57113742828369</t>
   </si>
   <si>
     <t xml:space="preserve">8.02138423919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08385467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15049266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00056076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35456657409668</t>
+    <t xml:space="preserve">8.08385562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15049362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00055980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354567527771</t>
   </si>
   <si>
     <t xml:space="preserve">7.98390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82563877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9922308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27127170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07969093322754</t>
+    <t xml:space="preserve">7.8256402015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99223136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27127075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07969188690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.28376579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53781795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46285247802734</t>
+    <t xml:space="preserve">8.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46285152435303</t>
   </si>
   <si>
     <t xml:space="preserve">8.60445404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13799953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00472450256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54243421554565</t>
+    <t xml:space="preserve">8.13799858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00472545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54243326187134</t>
   </si>
   <si>
     <t xml:space="preserve">8.01721858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26294136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04220771789551</t>
+    <t xml:space="preserve">8.26294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04220867156982</t>
   </si>
   <si>
     <t xml:space="preserve">8.20047092437744</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">8.19214153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09635066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14216232299805</t>
+    <t xml:space="preserve">8.09634971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14216327667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.12550449371338</t>
@@ -1610,58 +1610,58 @@
     <t xml:space="preserve">8.25877666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557210922241</t>
+    <t xml:space="preserve">7.9755711555481</t>
   </si>
   <si>
     <t xml:space="preserve">7.8922758102417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81730890274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62989330291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648447036743</t>
+    <t xml:space="preserve">7.81731033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62989473342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648590087891</t>
   </si>
   <si>
     <t xml:space="preserve">7.75483798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22129535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541465759277</t>
+    <t xml:space="preserve">8.22129440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541370391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.21296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19630527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22962474822998</t>
+    <t xml:space="preserve">8.18380928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19630432128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22962379455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43786430358887</t>
+    <t xml:space="preserve">8.43786334991455</t>
   </si>
   <si>
     <t xml:space="preserve">8.38788604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3712272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51282978057861</t>
+    <t xml:space="preserve">8.62944221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37122631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">8.69608020782471</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">8.83768177032471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77937602996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87100124359131</t>
+    <t xml:space="preserve">8.77937507629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87100219726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37910652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56235599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567546844482</t>
+    <t xml:space="preserve">9.37910556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56235694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567451477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.54569625854492</t>
@@ -1697,37 +1697,37 @@
     <t xml:space="preserve">9.28748035430908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29580974578857</t>
+    <t xml:space="preserve">9.29580879211426</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35411643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66231060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03759384155273</t>
+    <t xml:space="preserve">9.49571990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35411739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66231250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.22917366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2708215713501</t>
+    <t xml:space="preserve">9.27082061767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13754940032959</t>
+    <t xml:space="preserve">9.13754749298096</t>
   </si>
   <si>
     <t xml:space="preserve">9.16253662109375</t>
@@ -1739,91 +1739,91 @@
     <t xml:space="preserve">8.56280612945557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64610385894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04592037200928</t>
+    <t xml:space="preserve">8.64610481262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04592227935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.06258106231689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10422897338867</t>
+    <t xml:space="preserve">9.10422992706299</t>
   </si>
   <si>
     <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91264820098877</t>
+    <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.83797168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65155124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376216888428</t>
+    <t xml:space="preserve">8.65155029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376312255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59223556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98202323913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70239353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77018260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6430778503418</t>
+    <t xml:space="preserve">8.72781372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59223747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98202228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77018356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64307880401611</t>
   </si>
   <si>
     <t xml:space="preserve">8.5159740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48207950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49055290222168</t>
+    <t xml:space="preserve">8.48207855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.490553855896</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039588928223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700099945068</t>
+    <t xml:space="preserve">8.42700004577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.30413341522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2617654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34226417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39310741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33379173278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31260776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27871417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28718566894531</t>
+    <t xml:space="preserve">8.26176643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34226512908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39310646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33379077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31260871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27871322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28718662261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023983001709</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">8.29566097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10500335693359</t>
+    <t xml:space="preserve">8.05840015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10500431060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397735595703</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">8.32531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45242214202881</t>
+    <t xml:space="preserve">8.45242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52444648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66849899291992</t>
+    <t xml:space="preserve">8.52444744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">8.6091833114624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62613105773926</t>
+    <t xml:space="preserve">8.62613010406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528877258301</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35921096801758</t>
+    <t xml:space="preserve">8.35921287536621</t>
   </si>
   <si>
     <t xml:space="preserve">8.17279243469238</t>
@@ -1889,67 +1889,67 @@
     <t xml:space="preserve">8.11771488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03297805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89740037918091</t>
+    <t xml:space="preserve">8.03297710418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89739942550659</t>
   </si>
   <si>
     <t xml:space="preserve">8.13466167449951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96518993377686</t>
+    <t xml:space="preserve">7.96518898010254</t>
   </si>
   <si>
     <t xml:space="preserve">7.9016375541687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79995441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961273193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792816162109</t>
+    <t xml:space="preserve">7.79995393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640298843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792863845825</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25329113006592</t>
+    <t xml:space="preserve">8.25329208374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7236909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671606063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6601390838623</t>
+    <t xml:space="preserve">7.72369146347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671510696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113790512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66013956069946</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66002559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41429138183594</t>
+    <t xml:space="preserve">8.66002464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41429042816162</t>
   </si>
   <si>
     <t xml:space="preserve">8.31684398651123</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">8.19821357727051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21939849853516</t>
+    <t xml:space="preserve">8.24058246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21939754486084</t>
   </si>
   <si>
     <t xml:space="preserve">8.46513175964355</t>
@@ -1976,25 +1976,25 @@
     <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71934127807617</t>
+    <t xml:space="preserve">8.71934032440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.46936893463135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89728736877441</t>
+    <t xml:space="preserve">8.89728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">9.01591777801514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88881206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92270755767822</t>
+    <t xml:space="preserve">8.8888111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92270660400391</t>
   </si>
   <si>
     <t xml:space="preserve">8.97354888916016</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49902629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76170921325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81254959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60070896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54139423370361</t>
+    <t xml:space="preserve">8.49902820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76170825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81255054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60070991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54139614105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.69392013549805</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02439022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28707122802734</t>
+    <t xml:space="preserve">9.02439117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28707218170166</t>
   </si>
   <si>
     <t xml:space="preserve">9.57517528533936</t>
@@ -2048,37 +2048,37 @@
     <t xml:space="preserve">9.47349166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42265033721924</t>
+    <t xml:space="preserve">9.42264938354492</t>
   </si>
   <si>
     <t xml:space="preserve">9.30401802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60906791687012</t>
+    <t xml:space="preserve">9.60906887054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.6514368057251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53280544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63448905944824</t>
+    <t xml:space="preserve">9.53280639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63449001312256</t>
   </si>
   <si>
     <t xml:space="preserve">9.56670093536377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75312042236328</t>
+    <t xml:space="preserve">9.75311946868896</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78701400756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83785724639893</t>
+    <t xml:space="preserve">9.78701496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83785629272461</t>
   </si>
   <si>
     <t xml:space="preserve">9.871750831604</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">9.86327743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79548931121826</t>
+    <t xml:space="preserve">9.79548835754395</t>
   </si>
   <si>
     <t xml:space="preserve">9.82090950012207</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">9.91411876678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9734354019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242757797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083589553833</t>
+    <t xml:space="preserve">9.97343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0242767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1344318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0835905075073</t>
   </si>
   <si>
     <t xml:space="preserve">10.0158023834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93953990936279</t>
+    <t xml:space="preserve">9.93953895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666437149048</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">10.1598529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2615356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530641555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1683263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1937484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496959686279</t>
+    <t xml:space="preserve">10.2615375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.168327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1937475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496969223022</t>
   </si>
   <si>
     <t xml:space="preserve">9.82938289642334</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">9.94801330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99885559082031</t>
+    <t xml:space="preserve">9.998854637146</t>
   </si>
   <si>
     <t xml:space="preserve">9.92259311676025</t>
@@ -2165,19 +2165,19 @@
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54975318908691</t>
+    <t xml:space="preserve">9.64296436309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54975509643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.29554653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16431903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108020782471</t>
+    <t xml:space="preserve">8.16431999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108116149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603221893311</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">7.70674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6008243560791</t>
+    <t xml:space="preserve">7.60082483291626</t>
   </si>
   <si>
     <t xml:space="preserve">7.39322185516357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29153728485107</t>
+    <t xml:space="preserve">7.29153776168823</t>
   </si>
   <si>
     <t xml:space="preserve">6.99072504043579</t>
@@ -2216,43 +2216,43 @@
     <t xml:space="preserve">4.9824800491333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09687423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62647438049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59258031845093</t>
+    <t xml:space="preserve">5.08416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484846115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09687376022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62647390365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59257984161377</t>
   </si>
   <si>
     <t xml:space="preserve">5.80865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50784397125244</t>
+    <t xml:space="preserve">5.50784349441528</t>
   </si>
   <si>
     <t xml:space="preserve">5.26210927963257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84690284729004</t>
+    <t xml:space="preserve">4.84690237045288</t>
   </si>
   <si>
     <t xml:space="preserve">5.16042613983154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89774465560913</t>
+    <t xml:space="preserve">4.89774417877197</t>
   </si>
   <si>
     <t xml:space="preserve">4.76216650009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27481889724731</t>
+    <t xml:space="preserve">5.27481985092163</t>
   </si>
   <si>
     <t xml:space="preserve">5.41463422775269</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20279407501221</t>
+    <t xml:space="preserve">5.20279455184937</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">4.96129655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33837175369263</t>
+    <t xml:space="preserve">5.33837223052979</t>
   </si>
   <si>
     <t xml:space="preserve">5.73663091659546</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70273685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53326511383057</t>
+    <t xml:space="preserve">5.70273733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53326463699341</t>
   </si>
   <si>
     <t xml:space="preserve">5.49513339996338</t>
@@ -2306,70 +2306,70 @@
     <t xml:space="preserve">5.93576097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10099601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13065385818481</t>
+    <t xml:space="preserve">6.1009955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13065433502197</t>
   </si>
   <si>
     <t xml:space="preserve">5.88068246841431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6773157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87644577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81289339065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357818603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66460514068604</t>
+    <t xml:space="preserve">5.67731618881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87644529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81289386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357866287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66460561752319</t>
   </si>
   <si>
     <t xml:space="preserve">5.65189552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015468597412</t>
+    <t xml:space="preserve">6.05015420913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03320741653442</t>
+    <t xml:space="preserve">6.03320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">6.35520458221436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2916522026062</t>
+    <t xml:space="preserve">6.29165267944336</t>
   </si>
   <si>
     <t xml:space="preserve">6.39333581924438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79159498214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94835710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91022539138794</t>
+    <t xml:space="preserve">6.79159545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94835662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9102258682251</t>
   </si>
   <si>
     <t xml:space="preserve">7.04156684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00343608856201</t>
+    <t xml:space="preserve">7.24916982650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0034351348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.70685911178589</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71533250808716</t>
+    <t xml:space="preserve">6.71533298492432</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">6.64330673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55009746551514</t>
+    <t xml:space="preserve">6.55009698867798</t>
   </si>
   <si>
     <t xml:space="preserve">6.6094126701355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33401966094971</t>
+    <t xml:space="preserve">6.33402013778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.3255467414856</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741550445557</t>
+    <t xml:space="preserve">6.28741598129272</t>
   </si>
   <si>
     <t xml:space="preserve">6.12641716003418</t>
@@ -2417,46 +2417,46 @@
     <t xml:space="preserve">6.1518383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01626062393188</t>
+    <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912773132324</t>
+    <t xml:space="preserve">6.13912677764893</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981252670288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591751098633</t>
+    <t xml:space="preserve">6.04591798782349</t>
   </si>
   <si>
     <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24504709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47383499145508</t>
+    <t xml:space="preserve">6.2450475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47383451461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.47807168960571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27046823501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06286525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523271560669</t>
+    <t xml:space="preserve">6.27046871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06286573410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523319244385</t>
   </si>
   <si>
     <t xml:space="preserve">6.22386312484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336442947388</t>
+    <t xml:space="preserve">6.14336395263672</t>
   </si>
   <si>
     <t xml:space="preserve">6.08404874801636</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">6.02049684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99931287765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38486194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32978296279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32130908966064</t>
+    <t xml:space="preserve">5.99931240081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3848614692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32131004333496</t>
   </si>
   <si>
     <t xml:space="preserve">6.23657369613647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25775814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2747049331665</t>
+    <t xml:space="preserve">6.19420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25775718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27470541000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.23233699798584</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">6.3085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37215185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483285903931</t>
+    <t xml:space="preserve">6.37215137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.986487865448</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97377777099609</t>
+    <t xml:space="preserve">6.97377729415894</t>
   </si>
   <si>
     <t xml:space="preserve">6.73227977752686</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">7.0161452293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90175247192383</t>
+    <t xml:space="preserve">6.90175199508667</t>
   </si>
   <si>
     <t xml:space="preserve">6.85938405990601</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">6.79583263397217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44417762756348</t>
+    <t xml:space="preserve">6.44417810440063</t>
   </si>
   <si>
     <t xml:space="preserve">6.10946989059448</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">6.21538972854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9484715461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09252309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00778675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90610313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57563304901123</t>
+    <t xml:space="preserve">5.94847106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09252262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0077862739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90610361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57563257217407</t>
   </si>
   <si>
     <t xml:space="preserve">5.49089670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6010537147522</t>
+    <t xml:space="preserve">5.60105323791504</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2588,49 +2588,49 @@
     <t xml:space="preserve">5.25787210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28752994537354</t>
+    <t xml:space="preserve">5.28753042221069</t>
   </si>
   <si>
     <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0587420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01213788986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29176616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616035461426</t>
+    <t xml:space="preserve">5.05874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01213836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29176664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616083145142</t>
   </si>
   <si>
     <t xml:space="preserve">5.43158102035522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76205205917358</t>
+    <t xml:space="preserve">5.76205158233643</t>
   </si>
   <si>
     <t xml:space="preserve">5.81713056564331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83831405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93988275527954</t>
+    <t xml:space="preserve">5.83831453323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9398832321167</t>
   </si>
   <si>
     <t xml:space="preserve">6.74075317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82125282287598</t>
+    <t xml:space="preserve">6.82125329971313</t>
   </si>
   <si>
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09653091430664</t>
+    <t xml:space="preserve">8.09652996063232</t>
   </si>
   <si>
     <t xml:space="preserve">7.88045406341553</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49914169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45253658294678</t>
+    <t xml:space="preserve">7.49914121627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45253610610962</t>
   </si>
   <si>
     <t xml:space="preserve">7.62624502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55845642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62200784683228</t>
+    <t xml:space="preserve">7.5584568977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62200880050659</t>
   </si>
   <si>
     <t xml:space="preserve">7.77453279495239</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">7.77029752731323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87197923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8423228263855</t>
+    <t xml:space="preserve">7.85079526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87197971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84232139587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.67285013198853</t>
@@ -2675,22 +2675,22 @@
     <t xml:space="preserve">7.8126654624939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7957181930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6347188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011047363281</t>
+    <t xml:space="preserve">7.79571723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63471937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011095046997</t>
   </si>
   <si>
     <t xml:space="preserve">7.82537460327148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8550329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68556070327759</t>
+    <t xml:space="preserve">7.85503244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68555927276611</t>
   </si>
   <si>
     <t xml:space="preserve">7.52456188201904</t>
@@ -2699,16 +2699,16 @@
     <t xml:space="preserve">7.47795677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5881142616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56693124771118</t>
+    <t xml:space="preserve">7.58811378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56693029403687</t>
   </si>
   <si>
     <t xml:space="preserve">7.41016864776611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28730154037476</t>
+    <t xml:space="preserve">7.28730201721191</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374868392944</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">7.32543230056763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31695890426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18985366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06275033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18138122558594</t>
+    <t xml:space="preserve">7.31695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18985414505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06275081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1813817024231</t>
   </si>
   <si>
     <t xml:space="preserve">7.15596008300781</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64319276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21516132354736</t>
+    <t xml:space="preserve">7.64319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727293014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21516036987305</t>
   </si>
   <si>
     <t xml:space="preserve">8.2321081161499</t>
@@ -2756,25 +2756,25 @@
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668697357178</t>
+    <t xml:space="preserve">8.20668792724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.30837059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14313411712646</t>
+    <t xml:space="preserve">8.14313507080078</t>
   </si>
   <si>
     <t xml:space="preserve">7.79148006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65166616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03721523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92282152175903</t>
+    <t xml:space="preserve">7.65166521072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
@@ -2786,19 +2786,19 @@
     <t xml:space="preserve">8.63460445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0075569152832</t>
+    <t xml:space="preserve">8.00755786895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965435028076</t>
+    <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.78712940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544673919678</t>
+    <t xml:space="preserve">8.68544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">9.55822658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60059547424316</t>
+    <t xml:space="preserve">9.60059642791748</t>
   </si>
   <si>
     <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04981136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71075248718262</t>
+    <t xml:space="preserve">9.04133796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04981231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7107515335083</t>
   </si>
   <si>
     <t xml:space="preserve">9.39722919464111</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">9.44807052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69380569458008</t>
+    <t xml:space="preserve">9.48196315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69380474090576</t>
   </si>
   <si>
     <t xml:space="preserve">10.041223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74464797973633</t>
+    <t xml:space="preserve">9.74464702606201</t>
   </si>
   <si>
     <t xml:space="preserve">9.72769927978516</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">8.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03613376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91496086120605</t>
+    <t xml:space="preserve">9.03613471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91495895385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">9.08806610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2092399597168</t>
+    <t xml:space="preserve">9.20924091339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.24386215209961</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">9.63334941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68528079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40831184387207</t>
+    <t xml:space="preserve">9.68527984619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40831089019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.47755432128906</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">9.1140308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04478931427002</t>
+    <t xml:space="preserve">9.0447883605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.01882362365723</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">9.46889877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26982879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31310367584229</t>
+    <t xml:space="preserve">9.2698278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3131046295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.33041381835938</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">9.1313419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12268733978271</t>
+    <t xml:space="preserve">9.1226863861084</t>
   </si>
   <si>
     <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00151252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75916385650635</t>
+    <t xml:space="preserve">9.00151348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75916481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840728759766</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">8.71588802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77647495269775</t>
+    <t xml:space="preserve">8.77647590637207</t>
   </si>
   <si>
     <t xml:space="preserve">8.98420238494873</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95823669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84571838378906</t>
+    <t xml:space="preserve">8.66395568847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95823764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84571743011475</t>
   </si>
   <si>
     <t xml:space="preserve">8.86302757263184</t>
@@ -3017,19 +3017,19 @@
     <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72454261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63798999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68126678466797</t>
+    <t xml:space="preserve">8.72454452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63798904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68126773834229</t>
   </si>
   <si>
     <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44324684143066</t>
+    <t xml:space="preserve">8.44324588775635</t>
   </si>
   <si>
     <t xml:space="preserve">8.36967658996582</t>
@@ -3041,19 +3041,19 @@
     <t xml:space="preserve">8.19656944274902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23119068145752</t>
+    <t xml:space="preserve">8.23119163513184</t>
   </si>
   <si>
     <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74185371398926</t>
+    <t xml:space="preserve">8.74185466766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.43891906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131450653076</t>
+    <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
     <t xml:space="preserve">8.42160797119141</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">8.47354030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63366222381592</t>
+    <t xml:space="preserve">8.63366317749023</t>
   </si>
   <si>
     <t xml:space="preserve">8.67261219024658</t>
@@ -3074,49 +3074,49 @@
     <t xml:space="preserve">8.62933444976807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59904193878174</t>
+    <t xml:space="preserve">8.61202430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59904289245605</t>
   </si>
   <si>
     <t xml:space="preserve">8.50383186340332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5427827835083</t>
+    <t xml:space="preserve">8.54278182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.58605766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81975173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80244159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92825508117676</t>
+    <t xml:space="preserve">8.81975078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80244064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92825603485107</t>
   </si>
   <si>
     <t xml:space="preserve">7.85901308059692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93691110610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87632369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99749851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96287775039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91959953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91527318954468</t>
+    <t xml:space="preserve">7.93691205978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87632417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96287727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91960000991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91527271270752</t>
   </si>
   <si>
     <t xml:space="preserve">7.95854902267456</t>
@@ -3125,34 +3125,34 @@
     <t xml:space="preserve">7.96720409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65128612518311</t>
+    <t xml:space="preserve">7.82439184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65128707885742</t>
   </si>
   <si>
     <t xml:space="preserve">7.53011131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.556077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49981832504272</t>
+    <t xml:space="preserve">7.55607652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49981880187988</t>
   </si>
   <si>
     <t xml:space="preserve">7.39162731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35267782211304</t>
+    <t xml:space="preserve">7.3526782989502</t>
   </si>
   <si>
     <t xml:space="preserve">7.09734678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16658878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05839776992798</t>
+    <t xml:space="preserve">7.166588306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05839824676514</t>
   </si>
   <si>
     <t xml:space="preserve">7.18389987945557</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">7.33969497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51280117034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42192077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37431669235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33104038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15360689163208</t>
+    <t xml:space="preserve">7.51280164718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42192029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37431716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3310399055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15360641479492</t>
   </si>
   <si>
     <t xml:space="preserve">7.06272506713867</t>
@@ -3188,43 +3188,43 @@
     <t xml:space="preserve">7.2012095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27045202255249</t>
+    <t xml:space="preserve">7.27045249938965</t>
   </si>
   <si>
     <t xml:space="preserve">7.19255542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25747013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2617974281311</t>
+    <t xml:space="preserve">7.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26179790496826</t>
   </si>
   <si>
     <t xml:space="preserve">7.24448680877686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40461015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654106140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31805658340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41759300231934</t>
+    <t xml:space="preserve">7.40460968017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654153823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3180570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41759252548218</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36566114425659</t>
+    <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
     <t xml:space="preserve">7.34402227401733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23583126068115</t>
+    <t xml:space="preserve">7.23583173751831</t>
   </si>
   <si>
     <t xml:space="preserve">7.14062309265137</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">7.07138109207153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02377605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01944923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88961982727051</t>
+    <t xml:space="preserve">7.02377653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01944875717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88961935043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.91991281509399</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">6.66458177566528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42223310470581</t>
+    <t xml:space="preserve">6.42223358154297</t>
   </si>
   <si>
     <t xml:space="preserve">6.4698371887207</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">6.42656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40492248535156</t>
+    <t xml:space="preserve">6.40492296218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">6.54340791702271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63861608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49147605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36164569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47849321365356</t>
+    <t xml:space="preserve">6.63861560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4914755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36164617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">6.43088817596436</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">6.20152282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11497020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05005550384521</t>
+    <t xml:space="preserve">6.1149697303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05005502700806</t>
   </si>
   <si>
     <t xml:space="preserve">6.08034896850586</t>
@@ -3332,28 +3332,28 @@
     <t xml:space="preserve">5.60863494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46149492263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29704427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53073692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55670309066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55237579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460063934326</t>
+    <t xml:space="preserve">5.46149444580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.297043800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53073740005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55670356750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55237531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460111618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89425945281982</t>
+    <t xml:space="preserve">5.89425992965698</t>
   </si>
   <si>
     <t xml:space="preserve">5.83367252349854</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8509840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05438280105591</t>
+    <t xml:space="preserve">5.85098361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73413705825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05438327789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.08467674255371</t>
@@ -3380,22 +3380,22 @@
     <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37030124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38761186599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316122055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29673147201538</t>
+    <t xml:space="preserve">6.37030172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38761234283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2231616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29673194885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.37895679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99812269210815</t>
+    <t xml:space="preserve">5.99812316894531</t>
   </si>
   <si>
     <t xml:space="preserve">6.1539192199707</t>
@@ -3404,22 +3404,22 @@
     <t xml:space="preserve">6.11064195632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.145263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18421220779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34000825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19286775588989</t>
+    <t xml:space="preserve">6.14526319503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18421268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
     <t xml:space="preserve">6.12362480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17555713653564</t>
+    <t xml:space="preserve">6.1755576133728</t>
   </si>
   <si>
     <t xml:space="preserve">6.26211023330688</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">6.30105972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45685386657715</t>
+    <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
     <t xml:space="preserve">6.24479961395264</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4828200340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51744222640991</t>
+    <t xml:space="preserve">6.48281955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
     <t xml:space="preserve">6.34433507919312</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">6.19044828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12845516204834</t>
+    <t xml:space="preserve">6.1284556388855</t>
   </si>
   <si>
     <t xml:space="preserve">6.3498592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38971138000488</t>
+    <t xml:space="preserve">6.38971185684204</t>
   </si>
   <si>
     <t xml:space="preserve">6.42956447601318</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">5.57937431335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71221590042114</t>
+    <t xml:space="preserve">5.7122163772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.40225076675415</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">5.65022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59708642959595</t>
+    <t xml:space="preserve">5.59708595275879</t>
   </si>
   <si>
     <t xml:space="preserve">5.61922693252563</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">5.63251113891602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80077838897705</t>
+    <t xml:space="preserve">5.80077791213989</t>
   </si>
   <si>
     <t xml:space="preserve">5.81406211853027</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">5.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6059422492981</t>
+    <t xml:space="preserve">5.60594272613525</t>
   </si>
   <si>
     <t xml:space="preserve">5.5085244178772</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">5.51295280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53952121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53066444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66793537139893</t>
+    <t xml:space="preserve">5.53952169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53066492080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66793584823608</t>
   </si>
   <si>
     <t xml:space="preserve">5.72107219696045</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">5.40667915344238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57494640350342</t>
+    <t xml:space="preserve">5.57494592666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.74764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74321269989014</t>
+    <t xml:space="preserve">5.74321317672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.84948635101318</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">5.76092529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84063005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07089042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904420852661</t>
+    <t xml:space="preserve">5.84063053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07088994979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16387987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904468536377</t>
   </si>
   <si>
     <t xml:space="preserve">6.07531833648682</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">6.07974672317505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95576000213623</t>
+    <t xml:space="preserve">5.95576047897339</t>
   </si>
   <si>
     <t xml:space="preserve">5.97790050506592</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">6.14616775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18159198760986</t>
+    <t xml:space="preserve">6.18159246444702</t>
   </si>
   <si>
     <t xml:space="preserve">6.1550235748291</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">6.03546571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02660989761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99561309814453</t>
+    <t xml:space="preserve">6.02660942077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99561262130737</t>
   </si>
   <si>
     <t xml:space="preserve">5.96018838882446</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">6.01775360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06646203994751</t>
+    <t xml:space="preserve">6.06646251678467</t>
   </si>
   <si>
     <t xml:space="preserve">5.8760552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89819526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67236423492432</t>
+    <t xml:space="preserve">5.89819478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61037015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67236375808716</t>
   </si>
   <si>
     <t xml:space="preserve">5.73435640335083</t>
@@ -3695,25 +3695,25 @@
     <t xml:space="preserve">5.62365436553955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68121957778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7299280166626</t>
+    <t xml:space="preserve">5.68122005462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72992849349976</t>
   </si>
   <si>
     <t xml:space="preserve">5.97347259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00889730453491</t>
+    <t xml:space="preserve">6.00889682769775</t>
   </si>
   <si>
     <t xml:space="preserve">6.22587299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3188624382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25244140625</t>
+    <t xml:space="preserve">6.31886291503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25244092941284</t>
   </si>
   <si>
     <t xml:space="preserve">6.17273569107056</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">6.06203413009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22144508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29672241210938</t>
+    <t xml:space="preserve">6.22144460678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29672193527222</t>
   </si>
   <si>
     <t xml:space="preserve">6.4472770690918</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">6.4738450050354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42513656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23915672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35428714752197</t>
+    <t xml:space="preserve">6.42513608932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23915719985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35428762435913</t>
   </si>
   <si>
     <t xml:space="preserve">6.43842029571533</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">6.53141021728516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668706893921</t>
+    <t xml:space="preserve">6.60668754577637</t>
   </si>
   <si>
     <t xml:space="preserve">6.75724220275879</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">6.7926664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65539598464966</t>
+    <t xml:space="preserve">6.65539646148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.54912233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52255392074585</t>
+    <t xml:space="preserve">6.52255344390869</t>
   </si>
   <si>
     <t xml:space="preserve">6.53583812713623</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">6.64211225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325548171997</t>
+    <t xml:space="preserve">6.63325500488281</t>
   </si>
   <si>
     <t xml:space="preserve">6.49155712127686</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">6.92993688583374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05392265319824</t>
+    <t xml:space="preserve">7.0539231300354</t>
   </si>
   <si>
     <t xml:space="preserve">6.96093320846558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98307418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06720733642578</t>
+    <t xml:space="preserve">6.98307371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06720685958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.32846307754517</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">7.58971977233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81998014450073</t>
+    <t xml:space="preserve">7.81997966766357</t>
   </si>
   <si>
     <t xml:space="preserve">7.58529138565063</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">7.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20890617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19562149047852</t>
+    <t xml:space="preserve">7.2089056968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19562101364136</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20447731018066</t>
+    <t xml:space="preserve">7.20447778701782</t>
   </si>
   <si>
     <t xml:space="preserve">7.3018946647644</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">7.42145299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34617614746094</t>
+    <t xml:space="preserve">7.34617567062378</t>
   </si>
   <si>
     <t xml:space="preserve">7.48787403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34174728393555</t>
+    <t xml:space="preserve">7.34174776077271</t>
   </si>
   <si>
     <t xml:space="preserve">7.10263252258301</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">7.22661733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32403612136841</t>
+    <t xml:space="preserve">7.32403564453125</t>
   </si>
   <si>
     <t xml:space="preserve">7.35060405731201</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">7.17790842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2753267288208</t>
+    <t xml:space="preserve">7.27532625198364</t>
   </si>
   <si>
     <t xml:space="preserve">7.29303884506226</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">7.44802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48344612121582</t>
+    <t xml:space="preserve">7.48344564437866</t>
   </si>
   <si>
     <t xml:space="preserve">7.36388778686523</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">6.95207691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74838590621948</t>
+    <t xml:space="preserve">6.74838542938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.00078582763672</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">6.76167011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89451217651367</t>
+    <t xml:space="preserve">6.89451265335083</t>
   </si>
   <si>
     <t xml:space="preserve">6.68639278411865</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">6.84580326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81480693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81037902832031</t>
+    <t xml:space="preserve">6.81480741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81037855148315</t>
   </si>
   <si>
     <t xml:space="preserve">6.78381013870239</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">7.26204252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25761365890503</t>
+    <t xml:space="preserve">7.25761413574219</t>
   </si>
   <si>
     <t xml:space="preserve">7.22218942642212</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">7.23990201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10705900192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1203441619873</t>
+    <t xml:space="preserve">7.10705947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12034368515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.35946035385132</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">7.40374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3993124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27975463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45687770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54543972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47458982467651</t>
+    <t xml:space="preserve">7.39931201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27975511550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45687818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54543924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47458934783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.68270921707153</t>
@@ -5427,6 +5427,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.7200002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7299995422363</t>
   </si>
 </sst>
 </file>
@@ -68659,7 +68662,7 @@
     </row>
     <row r="2420">
       <c r="A2420" s="1" t="n">
-        <v>45965.6912615741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2420" t="n">
         <v>194193</v>
@@ -68680,6 +68683,32 @@
         <v>1804</v>
       </c>
       <c r="H2420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>45966.6911574074</v>
+      </c>
+      <c r="B2421" t="n">
+        <v>180577</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>15.8500003814697</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>15.5799999237061</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>15.6199998855591</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>15.7299995422363</v>
+      </c>
+      <c r="G2421" t="s">
+        <v>1805</v>
+      </c>
+      <c r="H2421" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032571792603</t>
+    <t xml:space="preserve">2.96032619476318</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13859987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1238796710968</t>
+    <t xml:space="preserve">3.13860011100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12388014793396</t>
   </si>
   <si>
     <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06663656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05028080940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18930172920227</t>
+    <t xml:space="preserve">3.06663584709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0650007724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05028104782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18930149078369</t>
   </si>
   <si>
     <t xml:space="preserve">3.1647686958313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17131090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16149735450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13205790519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15822649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514207839966</t>
+    <t xml:space="preserve">3.17131066322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16149759292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15822672843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514231681824</t>
   </si>
   <si>
     <t xml:space="preserve">3.15168428421021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30051827430725</t>
+    <t xml:space="preserve">3.30051803588867</t>
   </si>
   <si>
     <t xml:space="preserve">3.34140682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463230133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790340423584</t>
+    <t xml:space="preserve">3.43463277816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43790411949158</t>
   </si>
   <si>
     <t xml:space="preserve">3.39374423027039</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">3.38393068313599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33977103233337</t>
+    <t xml:space="preserve">3.33977150917053</t>
   </si>
   <si>
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841294288635</t>
+    <t xml:space="preserve">3.14841341972351</t>
   </si>
   <si>
     <t xml:space="preserve">3.0306544303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08789825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17294645309448</t>
+    <t xml:space="preserve">3.08789801597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1729462146759</t>
   </si>
   <si>
     <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18112421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257259368896</t>
+    <t xml:space="preserve">3.18112397193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257283210754</t>
   </si>
   <si>
     <t xml:space="preserve">3.19911503791809</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">3.03392553329468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99303722381592</t>
+    <t xml:space="preserve">2.99303698539734</t>
   </si>
   <si>
     <t xml:space="preserve">3.04373860359192</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">3.12878656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23018980026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2334611415863</t>
+    <t xml:space="preserve">3.23019027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23346138000488</t>
   </si>
   <si>
     <t xml:space="preserve">3.2252836227417</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">3.11406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12224459648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0911693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08299160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897349357605</t>
+    <t xml:space="preserve">3.14023566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12224435806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09116911888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08299136161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897325515747</t>
   </si>
   <si>
     <t xml:space="preserve">3.08135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1042537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07481408119202</t>
+    <t xml:space="preserve">3.10425353050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">3.14677762985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13696432113647</t>
+    <t xml:space="preserve">3.13696455955505</t>
   </si>
   <si>
     <t xml:space="preserve">3.21383476257324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16640448570251</t>
+    <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
     <t xml:space="preserve">3.10916018486023</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">3.42645478248596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50986766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51641011238098</t>
+    <t xml:space="preserve">3.50986742973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51640963554382</t>
   </si>
   <si>
     <t xml:space="preserve">3.54094266891479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50169014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47552084922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3561270236969</t>
+    <t xml:space="preserve">3.50168967247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47552108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35612678527832</t>
   </si>
   <si>
     <t xml:space="preserve">3.32014465332031</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.29724740982056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36103343963623</t>
+    <t xml:space="preserve">3.36103367805481</t>
   </si>
   <si>
     <t xml:space="preserve">3.37575316429138</t>
@@ -236,124 +236,124 @@
     <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35285615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38556623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43136119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51150321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061419487</t>
+    <t xml:space="preserve">3.35285592079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38556599617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43136167526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51150298118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061443328857</t>
   </si>
   <si>
     <t xml:space="preserve">3.4673433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48697018623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44281005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39701461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337037086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860573768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4591658115387</t>
+    <t xml:space="preserve">3.48696994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44281029701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39701509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337084770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916604995728</t>
   </si>
   <si>
     <t xml:space="preserve">3.41827702522278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50823211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55729842185974</t>
+    <t xml:space="preserve">3.50823163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55729818344116</t>
   </si>
   <si>
     <t xml:space="preserve">3.54584932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57855939865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60472822189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56547594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5981867313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63907408714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66360807418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64725208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67996382713318</t>
+    <t xml:space="preserve">3.57855987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60472869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56547617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59818625450134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63907504081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66360831260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64725255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6799635887146</t>
   </si>
   <si>
     <t xml:space="preserve">3.67178559303284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60636425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56711101531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46897864341736</t>
+    <t xml:space="preserve">3.60636377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5671112537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4689793586731</t>
   </si>
   <si>
     <t xml:space="preserve">3.40355753898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38065981864929</t>
+    <t xml:space="preserve">3.38065934181213</t>
   </si>
   <si>
     <t xml:space="preserve">3.33813548088074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28743410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32668662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27598524093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24327421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21874117851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25962996482849</t>
+    <t xml:space="preserve">3.28743386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32668709754944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27598547935486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24327492713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21874141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25963020324707</t>
   </si>
   <si>
     <t xml:space="preserve">3.15495538711548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07644963264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08462738990784</t>
+    <t xml:space="preserve">3.07644939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08462715148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.12551546096802</t>
@@ -365,187 +365,187 @@
     <t xml:space="preserve">3.31850957870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33486461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36757588386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846371650696</t>
+    <t xml:space="preserve">3.33486485481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3675754070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846395492554</t>
   </si>
   <si>
     <t xml:space="preserve">3.30869603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033158302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48206281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54421329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454224586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655070304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528948783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183073997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309290885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66851425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64071083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61617708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62435507774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75192761421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76174020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77809572219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77645969390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118037223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720765113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90730404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7944507598877</t>
+    <t xml:space="preserve">3.24818110466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48206305503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54421424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66851496696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64071035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61617732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62435555458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7519268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76173973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77809548377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77646017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118084907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90730333328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79445123672485</t>
   </si>
   <si>
     <t xml:space="preserve">3.99071598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91548109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8631443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8925838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529463768005</t>
+    <t xml:space="preserve">3.91548156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86314368247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258408546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529511451721</t>
   </si>
   <si>
     <t xml:space="preserve">3.88440632820129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655680656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86150908470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454787254333</t>
+    <t xml:space="preserve">3.86641502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454691886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.85169506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04305267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618270874023</t>
+    <t xml:space="preserve">4.043053150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618294715881</t>
   </si>
   <si>
     <t xml:space="preserve">3.88767719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86968612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81898403167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91384482383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165015220642</t>
+    <t xml:space="preserve">3.86968564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8189845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91384530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94164991378784</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99398684501648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272443771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00216484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0561375617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97926712036133</t>
+    <t xml:space="preserve">3.99398708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0021653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05613708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97926759719849</t>
   </si>
   <si>
     <t xml:space="preserve">4.00707149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08394241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16244745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27693510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44048976898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009052276611</t>
+    <t xml:space="preserve">4.01524877548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0839409828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16244792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27693557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44048929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595649719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009004592896</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506723403931</t>
@@ -557,49 +557,49 @@
     <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78804111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99248361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80439615249634</t>
+    <t xml:space="preserve">4.78804159164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99248456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8043966293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.83710765838623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83301830291748</t>
+    <t xml:space="preserve">4.83301877975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.90661811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928352355957</t>
+    <t xml:space="preserve">4.96386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928400039673</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150501251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36865758895874</t>
+    <t xml:space="preserve">5.19283676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150453567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830396652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688097000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3686580657959</t>
   </si>
   <si>
     <t xml:space="preserve">5.46270132064819</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">5.56901168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5526556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30323696136475</t>
+    <t xml:space="preserve">5.55265617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30323648452759</t>
   </si>
   <si>
     <t xml:space="preserve">5.26643705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5485668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60172176361084</t>
+    <t xml:space="preserve">5.54856634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.601722240448</t>
   </si>
   <si>
     <t xml:space="preserve">5.70803213119507</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">5.75709819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80207586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82251977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78572034835815</t>
+    <t xml:space="preserve">5.80207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82252025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114240646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.785719871521</t>
   </si>
   <si>
     <t xml:space="preserve">5.43816804885864</t>
@@ -656,34 +656,34 @@
     <t xml:space="preserve">5.48723459243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46679067611694</t>
+    <t xml:space="preserve">5.46678972244263</t>
   </si>
   <si>
     <t xml:space="preserve">5.60581111907959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56083393096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64308166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69674634933472</t>
+    <t xml:space="preserve">5.56083297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64308214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69674682617188</t>
   </si>
   <si>
     <t xml:space="preserve">5.46144580841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57290410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65546607971191</t>
+    <t xml:space="preserve">5.57290363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65546560287476</t>
   </si>
   <si>
     <t xml:space="preserve">5.70500230789185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73802709579468</t>
+    <t xml:space="preserve">5.73802757263184</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756427764893</t>
@@ -695,37 +695,37 @@
     <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10129833221436</t>
+    <t xml:space="preserve">5.90315055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1012978553772</t>
   </si>
   <si>
     <t xml:space="preserve">5.84122896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82471656799316</t>
+    <t xml:space="preserve">5.82471609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73389959335327</t>
+    <t xml:space="preserve">5.73389863967896</t>
   </si>
   <si>
     <t xml:space="preserve">5.75866746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133762359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81233310699463</t>
+    <t xml:space="preserve">5.65133714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81233263015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.7793083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77105140686035</t>
+    <t xml:space="preserve">5.77105188369751</t>
   </si>
   <si>
     <t xml:space="preserve">5.8453574180603</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.68849039077759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56877565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63069725036621</t>
+    <t xml:space="preserve">5.56877517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63069677352905</t>
   </si>
   <si>
     <t xml:space="preserve">5.57703256607056</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">5.5233678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54813575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162384033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55639219284058</t>
+    <t xml:space="preserve">5.54813528060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621416091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55639171600342</t>
   </si>
   <si>
     <t xml:space="preserve">5.32934761047363</t>
@@ -764,103 +764,103 @@
     <t xml:space="preserve">5.27568244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009712219238</t>
+    <t xml:space="preserve">5.16009569168091</t>
   </si>
   <si>
     <t xml:space="preserve">5.14771270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30045080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12294340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518406867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17248058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998750686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39952564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74628353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041151046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72977113723755</t>
+    <t xml:space="preserve">5.30045127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12294387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1931209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10230255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17248106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3995246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74628305435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041246414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72977161407471</t>
   </si>
   <si>
     <t xml:space="preserve">5.77518033981323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76692342758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87012672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86599779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94443082809448</t>
+    <t xml:space="preserve">5.76692390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86599731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94443130493164</t>
   </si>
   <si>
     <t xml:space="preserve">5.89489412307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0476336479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93204736709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86186981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332763671875</t>
+    <t xml:space="preserve">6.04763269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93204689025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86187028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332811355591</t>
   </si>
   <si>
     <t xml:space="preserve">6.06827306747437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1095552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17560386657715</t>
+    <t xml:space="preserve">6.10955429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17560338973999</t>
   </si>
   <si>
     <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19211530685425</t>
+    <t xml:space="preserve">6.19211578369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.21275615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18385982513428</t>
+    <t xml:space="preserve">6.18385934829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.12193822860718</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">6.16734743118286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15083503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98158407211304</t>
+    <t xml:space="preserve">6.13845157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15083456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98158311843872</t>
   </si>
   <si>
     <t xml:space="preserve">6.05176115036011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09716987609863</t>
+    <t xml:space="preserve">6.09717082977295</t>
   </si>
   <si>
     <t xml:space="preserve">6.18798732757568</t>
@@ -893,37 +893,37 @@
     <t xml:space="preserve">6.06001758575439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9857120513916</t>
+    <t xml:space="preserve">5.98571157455444</t>
   </si>
   <si>
     <t xml:space="preserve">6.0889139175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91140604019165</t>
+    <t xml:space="preserve">5.91140651702881</t>
   </si>
   <si>
     <t xml:space="preserve">5.87425374984741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93617534637451</t>
+    <t xml:space="preserve">5.93617582321167</t>
   </si>
   <si>
     <t xml:space="preserve">5.9609432220459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00222444534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38200712203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64207696914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88976144790649</t>
+    <t xml:space="preserve">6.00222396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2292685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38200759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64207601547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88976097106934</t>
   </si>
   <si>
     <t xml:space="preserve">6.85260915756226</t>
@@ -932,40 +932,40 @@
     <t xml:space="preserve">6.81958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89801645278931</t>
+    <t xml:space="preserve">6.89801692962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.82371187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75353527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004671096802</t>
+    <t xml:space="preserve">6.7535343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77004718780518</t>
   </si>
   <si>
     <t xml:space="preserve">6.60492324829102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69574069976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015537261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392776489258</t>
+    <t xml:space="preserve">6.69574117660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015489578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392871856689</t>
   </si>
   <si>
     <t xml:space="preserve">6.43980073928833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52649021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631265640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57189846038818</t>
+    <t xml:space="preserve">6.52649068832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5718994140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.65446090698242</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">6.6131796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5306191444397</t>
+    <t xml:space="preserve">6.53061819076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.66684484481812</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">6.44805669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65858840942383</t>
+    <t xml:space="preserve">6.65858793258667</t>
   </si>
   <si>
     <t xml:space="preserve">6.55538702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.625563621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50584936141968</t>
+    <t xml:space="preserve">6.62556409835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777143478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50584983825684</t>
   </si>
   <si>
     <t xml:space="preserve">6.55125856399536</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">6.6090521812439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7287654876709</t>
+    <t xml:space="preserve">6.72876596450806</t>
   </si>
   <si>
     <t xml:space="preserve">6.84848022460938</t>
@@ -1019,118 +1019,118 @@
     <t xml:space="preserve">6.90214490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7122540473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77417516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47594833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4718189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356344223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84334707260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80619478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66171073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75665807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95893287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57915067672729</t>
+    <t xml:space="preserve">6.70812559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748617172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71225357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77417421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4346661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47594738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47181987762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932775497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480585098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76078510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84334802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80619382858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6617112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75665712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95893239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57915019989014</t>
   </si>
   <si>
     <t xml:space="preserve">7.28192758560181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40989923477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605699539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331699371338</t>
+    <t xml:space="preserve">7.40989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331842422485</t>
   </si>
   <si>
     <t xml:space="preserve">7.22413492202759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41402578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46769142150879</t>
+    <t xml:space="preserve">7.41402673721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46769189834595</t>
   </si>
   <si>
     <t xml:space="preserve">7.57089328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38100147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33972263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1993670463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01773118972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05488443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96406698226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79481506347656</t>
+    <t xml:space="preserve">7.29431200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1787257194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890375137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3810019493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33972072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011560440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01773166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05488395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96406650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79481554031372</t>
   </si>
   <si>
     <t xml:space="preserve">6.7494068145752</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">6.68335723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79068803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25303173065186</t>
+    <t xml:space="preserve">6.790687084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25303077697754</t>
   </si>
   <si>
     <t xml:space="preserve">7.19111108779907</t>
@@ -1151,52 +1151,52 @@
     <t xml:space="preserve">7.07965230941772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84022378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05075597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2365198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053817749023</t>
+    <t xml:space="preserve">6.84022331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05075550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23651933670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053960800171</t>
   </si>
   <si>
     <t xml:space="preserve">7.30669641494751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26128768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2571587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36036109924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27779960632324</t>
+    <t xml:space="preserve">7.26128816604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25715923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36036157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2778000831604</t>
   </si>
   <si>
     <t xml:space="preserve">8.2313871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12405490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40476512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62768077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41302013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14056777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789905548096</t>
+    <t xml:space="preserve">8.12405681610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62768173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41302108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14056873321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789810180664</t>
   </si>
   <si>
     <t xml:space="preserve">8.17359352111816</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">8.09103202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19836139678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18184757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14469623565674</t>
+    <t xml:space="preserve">8.19836235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18184947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20661640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14469718933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.15295219421387</t>
@@ -1226,43 +1226,43 @@
     <t xml:space="preserve">8.45430183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35522937774658</t>
+    <t xml:space="preserve">8.35522842407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.36348438262939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33046054840088</t>
+    <t xml:space="preserve">8.33045959472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52035045623779</t>
+    <t xml:space="preserve">8.52035236358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.79280376434326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0074634552002</t>
+    <t xml:space="preserve">9.00746440887451</t>
   </si>
   <si>
     <t xml:space="preserve">8.71024322509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82582950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66070556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83408451080322</t>
+    <t xml:space="preserve">8.82582855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66070652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">8.86711025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6689624786377</t>
+    <t xml:space="preserve">8.66896152496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.6524486541748</t>
@@ -1280,34 +1280,34 @@
     <t xml:space="preserve">8.74605751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70441055297852</t>
+    <t xml:space="preserve">8.70440864562988</t>
   </si>
   <si>
     <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75438690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24628257751465</t>
+    <t xml:space="preserve">8.75438594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24628353118896</t>
   </si>
   <si>
     <t xml:space="preserve">8.30875492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3462381362915</t>
+    <t xml:space="preserve">8.34623718261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87933158874512</t>
+    <t xml:space="preserve">8.55447769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8460111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8793306350708</t>
   </si>
   <si>
     <t xml:space="preserve">8.57946586608887</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">8.82935428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81269550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82102298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86267280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50450038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62111377716064</t>
+    <t xml:space="preserve">8.81269359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82102394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5044994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">8.47118186950684</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">8.45452213287354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25461196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58779621124268</t>
+    <t xml:space="preserve">8.25461292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58779525756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.49617004394531</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">8.36289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42120456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21712970733643</t>
+    <t xml:space="preserve">8.42120361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21712875366211</t>
   </si>
   <si>
     <t xml:space="preserve">8.08802032470703</t>
@@ -1364,136 +1364,136 @@
     <t xml:space="preserve">8.59612560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63777351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16298580169678</t>
+    <t xml:space="preserve">8.63777256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
     <t xml:space="preserve">8.12133979797363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99639558792114</t>
+    <t xml:space="preserve">7.99639654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.92142915725708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78815603256226</t>
+    <t xml:space="preserve">7.78815650939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.02554988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76733160018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6132345199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.863121509552</t>
+    <t xml:space="preserve">7.76733112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062742233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323499679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312198638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.74234342575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67154264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62572956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87145185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72152042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57158803939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82980442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54659795761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63405752182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229755401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79232025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6173996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650859832764</t>
+    <t xml:space="preserve">7.67154312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62572860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87145233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72151851654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5715856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82980394363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54659843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6340594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229946136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71319055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650764465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.68819999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44664335250854</t>
+    <t xml:space="preserve">7.44664287567139</t>
   </si>
   <si>
     <t xml:space="preserve">7.28838109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14677906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259166717529</t>
+    <t xml:space="preserve">7.14677858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259119033813</t>
   </si>
   <si>
     <t xml:space="preserve">7.47163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66321277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04637336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1713171005249</t>
+    <t xml:space="preserve">7.66321182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04637241363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17131805419922</t>
   </si>
   <si>
     <t xml:space="preserve">8.47951126098633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3295783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463466644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955570220947</t>
+    <t xml:space="preserve">8.32957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23378849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955665588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.5294885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0542516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01260471343994</t>
+    <t xml:space="preserve">9.05425071716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99594593048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01260375976562</t>
   </si>
   <si>
     <t xml:space="preserve">9.00427436828613</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0959005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0209321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02926254272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66276264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57113647460938</t>
+    <t xml:space="preserve">9.11255931854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09589862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02093410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02926445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66276168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57113742828369</t>
   </si>
   <si>
     <t xml:space="preserve">8.02138423919678</t>
@@ -1529,34 +1529,34 @@
     <t xml:space="preserve">8.0838565826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15049266815186</t>
+    <t xml:space="preserve">8.15049362182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00055980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.354567527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98390054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9922308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07969093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28376579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53781700134277</t>
+    <t xml:space="preserve">8.35456657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98390197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99223041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27127170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07969188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28376483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53781890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.46285152435303</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">8.13799858093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07552623748779</t>
+    <t xml:space="preserve">8.07552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243278503418</t>
+    <t xml:space="preserve">7.54243326187134</t>
   </si>
   <si>
     <t xml:space="preserve">8.01721954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26294326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04220771789551</t>
+    <t xml:space="preserve">8.26294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04220867156982</t>
   </si>
   <si>
     <t xml:space="preserve">8.20046997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19214153289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09634971618652</t>
+    <t xml:space="preserve">8.19214057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09635066986084</t>
   </si>
   <si>
     <t xml:space="preserve">8.14216327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12550354003906</t>
+    <t xml:space="preserve">8.12550449371338</t>
   </si>
   <si>
     <t xml:space="preserve">8.17964553833008</t>
@@ -1607,64 +1607,64 @@
     <t xml:space="preserve">7.94641733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2587776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97557258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227676391602</t>
+    <t xml:space="preserve">8.25877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97557163238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8922758102417</t>
   </si>
   <si>
     <t xml:space="preserve">7.81731033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62989473342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483846664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541370391846</t>
+    <t xml:space="preserve">7.62989377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541275024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.21296501159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18381023406982</t>
+    <t xml:space="preserve">8.18381118774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.19630527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22962379455566</t>
+    <t xml:space="preserve">8.22962284088135</t>
   </si>
   <si>
     <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43786334991455</t>
+    <t xml:space="preserve">8.43786239624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62944316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37122821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51282978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69608020782471</t>
+    <t xml:space="preserve">8.62944412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3712272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51283073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69607925415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.83768272399902</t>
@@ -1676,55 +1676,55 @@
     <t xml:space="preserve">8.87100028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51237773895264</t>
+    <t xml:space="preserve">9.51237869262695</t>
   </si>
   <si>
     <t xml:space="preserve">9.37910556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56235504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59567451477051</t>
+    <t xml:space="preserve">9.56235599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59567546844482</t>
   </si>
   <si>
     <t xml:space="preserve">9.54569721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39576435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28747940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29580879211426</t>
+    <t xml:space="preserve">9.39576530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28748035430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571990966797</t>
+    <t xml:space="preserve">9.49571895599365</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66231060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17086505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03759288787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.229172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27082061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96262741088867</t>
+    <t xml:space="preserve">9.66231155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17086601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03759384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22917366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
     <t xml:space="preserve">9.13754749298096</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">8.56280708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64610195159912</t>
+    <t xml:space="preserve">8.64610290527344</t>
   </si>
   <si>
     <t xml:space="preserve">9.04592227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06258201599121</t>
+    <t xml:space="preserve">9.06258106231689</t>
   </si>
   <si>
     <t xml:space="preserve">9.10422992706299</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">8.91264915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83797168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65155220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781467437744</t>
+    <t xml:space="preserve">8.83797073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65155124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781372070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.59223747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98202228546143</t>
+    <t xml:space="preserve">8.98202323913574</t>
   </si>
   <si>
     <t xml:space="preserve">8.70239353179932</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">8.6430778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5159740447998</t>
+    <t xml:space="preserve">8.51597499847412</t>
   </si>
   <si>
     <t xml:space="preserve">8.48207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.490553855896</t>
+    <t xml:space="preserve">8.49055290222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.38039684295654</t>
@@ -1805,28 +1805,28 @@
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2617654800415</t>
+    <t xml:space="preserve">8.26176643371582</t>
   </si>
   <si>
     <t xml:space="preserve">8.34226512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39310741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33379077911377</t>
+    <t xml:space="preserve">8.39310646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33379173278809</t>
   </si>
   <si>
     <t xml:space="preserve">8.31260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27871227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28718662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023792266846</t>
+    <t xml:space="preserve">8.27871322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28718566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023887634277</t>
   </si>
   <si>
     <t xml:space="preserve">8.2956600189209</t>
@@ -1835,43 +1835,43 @@
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500431060791</t>
+    <t xml:space="preserve">8.10500335693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.19397735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75323486328125</t>
+    <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44394779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3253173828125</t>
+    <t xml:space="preserve">8.32531833648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.45242214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43971061706543</t>
+    <t xml:space="preserve">8.43971157073975</t>
   </si>
   <si>
     <t xml:space="preserve">8.52444839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56681632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44818496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60918235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62613010406494</t>
+    <t xml:space="preserve">8.66849708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56681537628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44818592071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6091833114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.57528877258301</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">8.20244979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35921096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11771392822266</t>
+    <t xml:space="preserve">8.35921192169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17279243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11771488189697</t>
   </si>
   <si>
     <t xml:space="preserve">8.03297805786133</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13466167449951</t>
+    <t xml:space="preserve">8.13466262817383</t>
   </si>
   <si>
     <t xml:space="preserve">7.9651894569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9016375541687</t>
+    <t xml:space="preserve">7.90163660049438</t>
   </si>
   <si>
     <t xml:space="preserve">7.79995441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82961177825928</t>
+    <t xml:space="preserve">7.82961130142212</t>
   </si>
   <si>
     <t xml:space="preserve">7.73640203475952</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">8.25329208374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22787189483643</t>
+    <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
     <t xml:space="preserve">7.72369146347046</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">7.95671653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82113790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945476531982</t>
+    <t xml:space="preserve">7.82113695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945571899414</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66014051437378</t>
+    <t xml:space="preserve">7.66013956069946</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">8.41429042816162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31684494018555</t>
+    <t xml:space="preserve">8.31684398651123</t>
   </si>
   <si>
     <t xml:space="preserve">8.43123817443848</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">8.19821357727051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24058246612549</t>
+    <t xml:space="preserve">8.24058151245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.21939849853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46513271331787</t>
+    <t xml:space="preserve">8.46513175964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.53292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71933937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46936893463135</t>
+    <t xml:space="preserve">8.71934127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46936798095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.8972864151001</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">9.01591682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8888111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575981140137</t>
+    <t xml:space="preserve">8.88881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575885772705</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97354793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13042545318604</t>
+    <t xml:space="preserve">8.97354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13042449951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.22363471984863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18973922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37192249298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49902725219727</t>
+    <t xml:space="preserve">8.18974018096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37192153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49902629852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.76170825958252</t>
@@ -2024,19 +2024,19 @@
     <t xml:space="preserve">8.60070991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5413932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697143554688</t>
+    <t xml:space="preserve">8.54139518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69391822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697238922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.85491752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02439022064209</t>
+    <t xml:space="preserve">9.02438926696777</t>
   </si>
   <si>
     <t xml:space="preserve">9.28707218170166</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">9.57517528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47349166870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42264938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3040189743042</t>
+    <t xml:space="preserve">9.47349262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42264842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401802062988</t>
   </si>
   <si>
     <t xml:space="preserve">9.60906887054443</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">9.65143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53280544281006</t>
+    <t xml:space="preserve">9.53280735015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.63448905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56670093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7531213760376</t>
+    <t xml:space="preserve">9.56669998168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75311946868896</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159477233887</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">9.78701591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83785629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87174987792969</t>
+    <t xml:space="preserve">9.83785438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.871750831604</t>
   </si>
   <si>
     <t xml:space="preserve">9.86327743530273</t>
@@ -2114,31 +2114,31 @@
     <t xml:space="preserve">9.93953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0666437149048</t>
+    <t xml:space="preserve">10.0666446685791</t>
   </si>
   <si>
     <t xml:space="preserve">10.1768007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2276420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1598529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2615365982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1683254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1937484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496959686279</t>
+    <t xml:space="preserve">10.2276430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1598539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2615356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530641555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1683263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1937475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496950149536</t>
   </si>
   <si>
     <t xml:space="preserve">9.82938289642334</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">9.998854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92259407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51585960388184</t>
+    <t xml:space="preserve">9.92259216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51585865020752</t>
   </si>
   <si>
     <t xml:space="preserve">10.0581703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73617267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8463306427002</t>
+    <t xml:space="preserve">9.73617362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.64296436309814</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">9.54975414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29554653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16431903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108116149902</t>
+    <t xml:space="preserve">9.29554557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16431999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108020782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00331974029541</t>
+    <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
     <t xml:space="preserve">7.70674514770508</t>
@@ -2192,40 +2192,40 @@
     <t xml:space="preserve">7.6008243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39322185516357</t>
+    <t xml:space="preserve">7.39322233200073</t>
   </si>
   <si>
     <t xml:space="preserve">7.29153728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99072408676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71109580993652</t>
+    <t xml:space="preserve">6.99072504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71109533309937</t>
   </si>
   <si>
     <t xml:space="preserve">6.61364936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6137638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52479124069214</t>
+    <t xml:space="preserve">5.61376333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5247917175293</t>
   </si>
   <si>
     <t xml:space="preserve">4.9824800491333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08416271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02484798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09687423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62647390365601</t>
+    <t xml:space="preserve">5.08416318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02484750747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09687376022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62647485733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">5.50784349441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26210927963257</t>
+    <t xml:space="preserve">5.26210975646973</t>
   </si>
   <si>
     <t xml:space="preserve">4.84690237045288</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">4.89774417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76216602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27481985092163</t>
+    <t xml:space="preserve">4.76216650009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27481937408447</t>
   </si>
   <si>
     <t xml:space="preserve">5.41463422775269</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">5.19008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20279359817505</t>
+    <t xml:space="preserve">5.20279407501221</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2276,106 +2276,106 @@
     <t xml:space="preserve">4.93163871765137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96129703521729</t>
+    <t xml:space="preserve">4.96129608154297</t>
   </si>
   <si>
     <t xml:space="preserve">5.33837175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73663139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93152379989624</t>
+    <t xml:space="preserve">5.73663091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9315242767334</t>
   </si>
   <si>
     <t xml:space="preserve">6.07557535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70273685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53326463699341</t>
+    <t xml:space="preserve">5.70273637771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49513339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87220907211304</t>
+    <t xml:space="preserve">5.87220859527588</t>
   </si>
   <si>
     <t xml:space="preserve">5.93576049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13065338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88068246841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67731523513794</t>
+    <t xml:space="preserve">6.10099601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13065433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88068294525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6773157119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289339065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357818603516</t>
+    <t xml:space="preserve">5.81289386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357866287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65189552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05015468597412</t>
+    <t xml:space="preserve">5.65189504623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05015420913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.91881370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03320693969727</t>
+    <t xml:space="preserve">6.03320741653442</t>
   </si>
   <si>
     <t xml:space="preserve">6.3552041053772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29165267944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39333534240723</t>
+    <t xml:space="preserve">6.2916522026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39333581924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.79159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94835662841797</t>
+    <t xml:space="preserve">6.94835710525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.91022491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04156732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24916982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088205337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00343561172485</t>
+    <t xml:space="preserve">7.04156637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24917078018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088157653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0034351348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57551860809326</t>
+    <t xml:space="preserve">6.5755181312561</t>
   </si>
   <si>
     <t xml:space="preserve">6.71533298492432</t>
@@ -2384,13 +2384,13 @@
     <t xml:space="preserve">6.72804307937622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69838523864746</t>
+    <t xml:space="preserve">6.69838571548462</t>
   </si>
   <si>
     <t xml:space="preserve">6.64330720901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55009794235229</t>
+    <t xml:space="preserve">6.55009746551514</t>
   </si>
   <si>
     <t xml:space="preserve">6.6094126701355</t>
@@ -2399,43 +2399,43 @@
     <t xml:space="preserve">6.33402013778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32554721832275</t>
+    <t xml:space="preserve">6.3255467414856</t>
   </si>
   <si>
     <t xml:space="preserve">6.18573236465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14760065078735</t>
+    <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">6.28741550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12641716003418</t>
+    <t xml:space="preserve">6.12641668319702</t>
   </si>
   <si>
     <t xml:space="preserve">6.1518383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01626014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13912725448608</t>
+    <t xml:space="preserve">6.01626062393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31707334518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13912677764893</t>
   </si>
   <si>
     <t xml:space="preserve">6.07981204986572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04591798782349</t>
+    <t xml:space="preserve">6.04591846466064</t>
   </si>
   <si>
     <t xml:space="preserve">6.36367893218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2450475692749</t>
+    <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
     <t xml:space="preserve">6.47383451461792</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523271560669</t>
+    <t xml:space="preserve">6.06286573410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523319244385</t>
   </si>
   <si>
     <t xml:space="preserve">6.22386360168457</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">6.08404874801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95270872116089</t>
+    <t xml:space="preserve">5.95270824432373</t>
   </si>
   <si>
     <t xml:space="preserve">6.07133865356445</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">6.18149518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02049684524536</t>
+    <t xml:space="preserve">6.0204963684082</t>
   </si>
   <si>
     <t xml:space="preserve">5.99931287765503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32978391647339</t>
+    <t xml:space="preserve">6.38486194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32978343963623</t>
   </si>
   <si>
     <t xml:space="preserve">6.32131004333496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23657417297363</t>
+    <t xml:space="preserve">6.23657464981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.19420623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25775814056396</t>
+    <t xml:space="preserve">6.25775861740112</t>
   </si>
   <si>
     <t xml:space="preserve">6.2747049331665</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3085994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37215185165405</t>
+    <t xml:space="preserve">6.30859994888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37215137481689</t>
   </si>
   <si>
     <t xml:space="preserve">6.63483381271362</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">6.98648834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29577350616455</t>
+    <t xml:space="preserve">7.16019678115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29577398300171</t>
   </si>
   <si>
     <t xml:space="preserve">6.97377777099609</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">6.73227977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75346422195435</t>
+    <t xml:space="preserve">6.75346374511719</t>
   </si>
   <si>
     <t xml:space="preserve">7.0161452293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90175199508667</t>
+    <t xml:space="preserve">6.90175247192383</t>
   </si>
   <si>
     <t xml:space="preserve">6.85938405990601</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">6.44417715072632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10947036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05439138412476</t>
+    <t xml:space="preserve">6.10946989059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0543909072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168081283569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16031169891357</t>
+    <t xml:space="preserve">6.16031122207642</t>
   </si>
   <si>
     <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21538972854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94847106933594</t>
+    <t xml:space="preserve">6.2153902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94847059249878</t>
   </si>
   <si>
     <t xml:space="preserve">6.09252309799194</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">6.00778675079346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90610313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57563209533691</t>
+    <t xml:space="preserve">5.90610265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57563257217407</t>
   </si>
   <si>
     <t xml:space="preserve">5.49089622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60105419158936</t>
+    <t xml:space="preserve">5.60105323791504</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">5.25787210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28752946853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06297969818115</t>
+    <t xml:space="preserve">5.28752994537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06297922134399</t>
   </si>
   <si>
     <t xml:space="preserve">5.05874252319336</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">5.01213788986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40616035461426</t>
+    <t xml:space="preserve">5.29176712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40616083145142</t>
   </si>
   <si>
     <t xml:space="preserve">5.43158149719238</t>
@@ -2621,22 +2621,22 @@
     <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82125329971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04580354690552</t>
+    <t xml:space="preserve">6.74075412750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82125282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.09652996063232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88045406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53303623199463</t>
+    <t xml:space="preserve">7.88045310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53303527832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.49914121627808</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">7.62624549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55845642089844</t>
+    <t xml:space="preserve">7.55845546722412</t>
   </si>
   <si>
     <t xml:space="preserve">7.62200880050659</t>
@@ -2660,43 +2660,43 @@
     <t xml:space="preserve">7.77029609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079574584961</t>
+    <t xml:space="preserve">7.85079669952393</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67285108566284</t>
+    <t xml:space="preserve">7.84232139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67285013198853</t>
   </si>
   <si>
     <t xml:space="preserve">7.81266498565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79571771621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63471841812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011095046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82537460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8550329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68556070327759</t>
+    <t xml:space="preserve">7.79571676254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63472032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8253755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85503196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68555974960327</t>
   </si>
   <si>
     <t xml:space="preserve">7.5245623588562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47795724868774</t>
+    <t xml:space="preserve">7.4779577255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.58811378479004</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">7.56693029403687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41016817092896</t>
+    <t xml:space="preserve">7.41016864776611</t>
   </si>
   <si>
     <t xml:space="preserve">7.28730154037476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22374868392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32543325424194</t>
+    <t xml:space="preserve">7.22374820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32543277740479</t>
   </si>
   <si>
     <t xml:space="preserve">7.31695890426636</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">7.18985462188721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0627498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1813817024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15595960617065</t>
+    <t xml:space="preserve">7.06275033950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18138122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15596008300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
@@ -2738,28 +2738,28 @@
     <t xml:space="preserve">7.64319229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21516132354736</t>
+    <t xml:space="preserve">7.74911212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727245330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.23210906982422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18550205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20668792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837154388428</t>
+    <t xml:space="preserve">8.18550300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20668888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30837059020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.14313507080078</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">7.79148054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65166664123535</t>
+    <t xml:space="preserve">7.65166568756104</t>
   </si>
   <si>
     <t xml:space="preserve">8.03721523284912</t>
@@ -2786,19 +2786,19 @@
     <t xml:space="preserve">8.63460350036621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0075569152832</t>
+    <t xml:space="preserve">8.00755786895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.39734363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965530395508</t>
+    <t xml:space="preserve">8.93965435028076</t>
   </si>
   <si>
     <t xml:space="preserve">8.78712844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68544578552246</t>
+    <t xml:space="preserve">8.68544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">9.20233631134033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55822658538818</t>
+    <t xml:space="preserve">9.5582275390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.60059547424316</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">9.21928310394287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0498104095459</t>
+    <t xml:space="preserve">9.04981136322021</t>
   </si>
   <si>
     <t xml:space="preserve">9.71075248718262</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.44807052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48196506500244</t>
+    <t xml:space="preserve">9.48196411132812</t>
   </si>
   <si>
     <t xml:space="preserve">9.69380474090576</t>
@@ -2849,16 +2849,16 @@
     <t xml:space="preserve">9.74464702606201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72769832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52433204650879</t>
+    <t xml:space="preserve">9.72769927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52433300018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.43112373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02748012542725</t>
+    <t xml:space="preserve">9.02747917175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.97554683685303</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">9.03613376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91495990753174</t>
+    <t xml:space="preserve">8.91495895385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">8.96689224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08806610107422</t>
+    <t xml:space="preserve">9.0880651473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.20924091339111</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">9.24386215209961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33906936645508</t>
+    <t xml:space="preserve">9.33907032012939</t>
   </si>
   <si>
     <t xml:space="preserve">9.43427753448486</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">9.63335037231445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68528079986572</t>
+    <t xml:space="preserve">9.68527984619141</t>
   </si>
   <si>
     <t xml:space="preserve">9.40831184387207</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1140308380127</t>
+    <t xml:space="preserve">9.21789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11403179168701</t>
   </si>
   <si>
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882362365723</t>
+    <t xml:space="preserve">9.01882457733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.26117134094238</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">9.31310367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33041477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3044490814209</t>
+    <t xml:space="preserve">9.33041381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
     <t xml:space="preserve">9.34772491455078</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">9.12268733978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10537624359131</t>
+    <t xml:space="preserve">9.10537719726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.00151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75916385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82840728759766</t>
+    <t xml:space="preserve">8.75916481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82840633392334</t>
   </si>
   <si>
     <t xml:space="preserve">9.05344486236572</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">9.36503505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41696834564209</t>
+    <t xml:space="preserve">9.41696739196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.16596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99285793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25251579284668</t>
+    <t xml:space="preserve">8.99285888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.252516746521</t>
   </si>
   <si>
     <t xml:space="preserve">9.17461967468262</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">8.98420238494873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69857692718506</t>
+    <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
     <t xml:space="preserve">8.66395568847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95823764801025</t>
+    <t xml:space="preserve">8.95823669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.84571838378906</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">8.68126583099365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73319911956787</t>
+    <t xml:space="preserve">8.73319816589355</t>
   </si>
   <si>
     <t xml:space="preserve">8.44324588775635</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">8.4389181137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39131450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42160701751709</t>
+    <t xml:space="preserve">8.39131355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42160797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.3610200881958</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">8.67261123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62933540344238</t>
+    <t xml:space="preserve">8.6293363571167</t>
   </si>
   <si>
     <t xml:space="preserve">8.61202430725098</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">8.50383281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54278087615967</t>
+    <t xml:space="preserve">8.54278182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.58605861663818</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">7.92825508117676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85901308059692</t>
+    <t xml:space="preserve">7.85901403427124</t>
   </si>
   <si>
     <t xml:space="preserve">7.93691062927246</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">7.87632417678833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99749803543091</t>
+    <t xml:space="preserve">7.99749708175659</t>
   </si>
   <si>
     <t xml:space="preserve">7.96287631988525</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">7.91527271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9585485458374</t>
+    <t xml:space="preserve">7.95854949951172</t>
   </si>
   <si>
     <t xml:space="preserve">7.96720504760742</t>
@@ -3137,28 +3137,28 @@
     <t xml:space="preserve">7.556077003479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49981832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39162683486938</t>
+    <t xml:space="preserve">7.49981784820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39162635803223</t>
   </si>
   <si>
     <t xml:space="preserve">7.3526782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09734630584717</t>
+    <t xml:space="preserve">7.09734678268433</t>
   </si>
   <si>
     <t xml:space="preserve">7.16658878326416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05839776992798</t>
+    <t xml:space="preserve">7.05839729309082</t>
   </si>
   <si>
     <t xml:space="preserve">7.18390035629272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11033010482788</t>
+    <t xml:space="preserve">7.11032962799072</t>
   </si>
   <si>
     <t xml:space="preserve">7.33969497680664</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">7.51280117034912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42192029953003</t>
+    <t xml:space="preserve">7.42191982269287</t>
   </si>
   <si>
     <t xml:space="preserve">7.37431621551514</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">7.14927911758423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2012095451355</t>
+    <t xml:space="preserve">7.20121002197266</t>
   </si>
   <si>
     <t xml:space="preserve">7.27045297622681</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">7.19255495071411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25747013092041</t>
+    <t xml:space="preserve">7.25747060775757</t>
   </si>
   <si>
     <t xml:space="preserve">7.26179790496826</t>
@@ -3203,37 +3203,37 @@
     <t xml:space="preserve">7.24448728561401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40461015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45654106140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3180570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41759252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700559616089</t>
+    <t xml:space="preserve">7.4046106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45654153823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31805658340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700607299805</t>
   </si>
   <si>
     <t xml:space="preserve">7.36566162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34402227401733</t>
+    <t xml:space="preserve">7.34402322769165</t>
   </si>
   <si>
     <t xml:space="preserve">7.23583126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14062309265137</t>
+    <t xml:space="preserve">7.14062356948853</t>
   </si>
   <si>
     <t xml:space="preserve">7.07138061523438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02377653121948</t>
+    <t xml:space="preserve">7.02377700805664</t>
   </si>
   <si>
     <t xml:space="preserve">7.01944875717163</t>
@@ -3254,46 +3254,46 @@
     <t xml:space="preserve">6.42223358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46983766555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42656135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40492296218872</t>
+    <t xml:space="preserve">6.4698371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42656087875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">6.5131139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54340791702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63861608505249</t>
+    <t xml:space="preserve">6.54340744018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63861656188965</t>
   </si>
   <si>
     <t xml:space="preserve">6.49147510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36164617538452</t>
+    <t xml:space="preserve">6.36164569854736</t>
   </si>
   <si>
     <t xml:space="preserve">6.47849273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43088817596436</t>
+    <t xml:space="preserve">6.43088865280151</t>
   </si>
   <si>
     <t xml:space="preserve">6.56937313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44387149810791</t>
+    <t xml:space="preserve">6.44387197494507</t>
   </si>
   <si>
     <t xml:space="preserve">6.55639028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75979042053223</t>
+    <t xml:space="preserve">6.75978994369507</t>
   </si>
   <si>
     <t xml:space="preserve">6.56504535675049</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">6.21450567245483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1019868850708</t>
+    <t xml:space="preserve">6.10198736190796</t>
   </si>
   <si>
     <t xml:space="preserve">5.88560438156128</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">6.20152282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11497020721436</t>
+    <t xml:space="preserve">6.11497068405151</t>
   </si>
   <si>
     <t xml:space="preserve">6.05005550384521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0803484916687</t>
+    <t xml:space="preserve">6.08034896850586</t>
   </si>
   <si>
     <t xml:space="preserve">5.70817089080811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60863447189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46149444580078</t>
+    <t xml:space="preserve">5.60863494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46149492263794</t>
   </si>
   <si>
     <t xml:space="preserve">5.29704427719116</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">5.55670309066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55237483978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460159301758</t>
+    <t xml:space="preserve">5.55237531661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460111618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.53506517410278</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">5.81203460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85098314285278</t>
+    <t xml:space="preserve">5.85098361968994</t>
   </si>
   <si>
     <t xml:space="preserve">5.7341365814209</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">6.05871057510376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37030124664307</t>
+    <t xml:space="preserve">6.37030172348022</t>
   </si>
   <si>
     <t xml:space="preserve">6.38761186599731</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">6.2231616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29673147201538</t>
+    <t xml:space="preserve">6.29673194885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.37895631790161</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">6.1106424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.145263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18421268463135</t>
+    <t xml:space="preserve">6.14526414871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18421220779419</t>
   </si>
   <si>
     <t xml:space="preserve">6.34000778198242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19286775588989</t>
+    <t xml:space="preserve">6.19286823272705</t>
   </si>
   <si>
     <t xml:space="preserve">6.1236252784729</t>
@@ -3422,31 +3422,31 @@
     <t xml:space="preserve">6.1755576133728</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26210975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30105924606323</t>
+    <t xml:space="preserve">6.26211023330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30105876922607</t>
   </si>
   <si>
     <t xml:space="preserve">6.45685434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24480009078979</t>
+    <t xml:space="preserve">6.24479961395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.11929798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48282051086426</t>
+    <t xml:space="preserve">6.4828200340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.51744174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34433603286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10631465911865</t>
+    <t xml:space="preserve">6.34433555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10631418228149</t>
   </si>
   <si>
     <t xml:space="preserve">6.27900981903076</t>
@@ -5426,7 +5426,7 @@
     <t xml:space="preserve">15.7200002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5900001525879</t>
+    <t xml:space="preserve">15.6700000762939</t>
   </si>
 </sst>
 </file>
@@ -68685,22 +68685,22 @@
     </row>
     <row r="2421">
       <c r="A2421" s="1" t="n">
-        <v>45967.6911805556</v>
+        <v>45968.6910185185</v>
       </c>
       <c r="B2421" t="n">
-        <v>163392</v>
+        <v>135250</v>
       </c>
       <c r="C2421" t="n">
-        <v>15.8199996948242</v>
+        <v>15.7700004577637</v>
       </c>
       <c r="D2421" t="n">
         <v>15.5900001525879</v>
       </c>
       <c r="E2421" t="n">
-        <v>15.7399997711182</v>
+        <v>15.5900001525879</v>
       </c>
       <c r="F2421" t="n">
-        <v>15.5900001525879</v>
+        <v>15.6700000762939</v>
       </c>
       <c r="G2421" t="s">
         <v>1804</v>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1808">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96032619476318</t>
+    <t xml:space="preserve">2.9603259563446</t>
   </si>
   <si>
     <t xml:space="preserve">TGYM.MI</t>
@@ -53,64 +53,64 @@
     <t xml:space="preserve">3.10588932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06663584709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0650007724762</t>
+    <t xml:space="preserve">3.06663656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500053405762</t>
   </si>
   <si>
     <t xml:space="preserve">3.05028104782104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18930149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647686958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17131066322327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16149759292603</t>
+    <t xml:space="preserve">3.18930196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17131090164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1614978313446</t>
   </si>
   <si>
     <t xml:space="preserve">3.13205766677856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15822672843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14514231681824</t>
+    <t xml:space="preserve">3.15822649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14514207839966</t>
   </si>
   <si>
     <t xml:space="preserve">3.15168428421021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30051803588867</t>
+    <t xml:space="preserve">3.30051827430725</t>
   </si>
   <si>
     <t xml:space="preserve">3.34140682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43463277816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43790411949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39374423027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393068313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33977150917053</t>
+    <t xml:space="preserve">3.43463253974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43790364265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39374446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393092155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33977174758911</t>
   </si>
   <si>
     <t xml:space="preserve">3.24000334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14841341972351</t>
+    <t xml:space="preserve">3.14841294288635</t>
   </si>
   <si>
     <t xml:space="preserve">3.0306544303894</t>
@@ -119,61 +119,61 @@
     <t xml:space="preserve">3.08789801597595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1729462146759</t>
+    <t xml:space="preserve">3.17294645309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.10752487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18112397193909</t>
+    <t xml:space="preserve">3.18112421035767</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257283210754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19911503791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03392553329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99303698539734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04373860359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12878656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23019027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23346138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2252836227417</t>
+    <t xml:space="preserve">3.19911479949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03392577171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99303674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12878680229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23019003868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2334611415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22528314590454</t>
   </si>
   <si>
     <t xml:space="preserve">3.11406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14023566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12224435806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09116911888123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08299136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11897325515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08135604858398</t>
+    <t xml:space="preserve">3.14023542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12224459648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08299160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11897349357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08135581016541</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425353050232</t>
@@ -182,28 +182,28 @@
     <t xml:space="preserve">3.07481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14677762985229</t>
+    <t xml:space="preserve">3.14677786827087</t>
   </si>
   <si>
     <t xml:space="preserve">3.13696455955505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21383476257324</t>
+    <t xml:space="preserve">3.21383452415466</t>
   </si>
   <si>
     <t xml:space="preserve">3.16640424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10916018486023</t>
+    <t xml:space="preserve">3.10916042327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.36921095848083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42645478248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50986742973328</t>
+    <t xml:space="preserve">3.42645525932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5098671913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.51640963554382</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.50168967247009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47552108764648</t>
+    <t xml:space="preserve">3.47552084922791</t>
   </si>
   <si>
     <t xml:space="preserve">3.35612678527832</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.32014465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29724740982056</t>
+    <t xml:space="preserve">3.29724717140198</t>
   </si>
   <si>
     <t xml:space="preserve">3.36103367805481</t>
@@ -233,43 +233,43 @@
     <t xml:space="preserve">3.37575316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37738871574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35285592079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38556599617004</t>
+    <t xml:space="preserve">3.37738847732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35285520553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38556623458862</t>
   </si>
   <si>
     <t xml:space="preserve">3.43136167526245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51150298118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47061443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4673433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48696994781494</t>
+    <t xml:space="preserve">3.51150274276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47061467170715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46734285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48696947097778</t>
   </si>
   <si>
     <t xml:space="preserve">3.44281029701233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39701509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41337084770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48860549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45916604995728</t>
+    <t xml:space="preserve">3.39701461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41337013244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.488605260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45916557312012</t>
   </si>
   <si>
     <t xml:space="preserve">3.41827702522278</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">3.50823163986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55729818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584932327271</t>
+    <t xml:space="preserve">3.557297706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584908485413</t>
   </si>
   <si>
     <t xml:space="preserve">3.57855987548828</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.56547617912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59818625450134</t>
+    <t xml:space="preserve">3.5981867313385</t>
   </si>
   <si>
     <t xml:space="preserve">3.63907504081726</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">3.64725255966187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6799635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67178559303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60636377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5671112537384</t>
+    <t xml:space="preserve">3.67996311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67178583145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60636448860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56711173057556</t>
   </si>
   <si>
     <t xml:space="preserve">3.4689793586731</t>
@@ -323,196 +323,196 @@
     <t xml:space="preserve">3.40355753898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38065934181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33813548088074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28743386268616</t>
+    <t xml:space="preserve">3.38065981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33813524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28743362426758</t>
   </si>
   <si>
     <t xml:space="preserve">3.32668709754944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27598547935486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24327492713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21874141693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25963020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15495538711548</t>
+    <t xml:space="preserve">3.27598524093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2432746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21874117851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25962972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15495562553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.07644939422607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08462715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12551546096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27107858657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31850957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33486485481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3675754070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40846395492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30869603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24818110466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31033182144165</t>
+    <t xml:space="preserve">3.08462738990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1255156993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27107906341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31850910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33486461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36757564544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40846419334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30869579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24818086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31033158302307</t>
   </si>
   <si>
     <t xml:space="preserve">3.48206305503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54421424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61454176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59655046463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57528924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63253259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60309314727783</t>
+    <t xml:space="preserve">3.54421353340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59655070304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57528948783875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58183121681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63253235816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60309338569641</t>
   </si>
   <si>
     <t xml:space="preserve">3.66851496696472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64071035385132</t>
+    <t xml:space="preserve">3.64071083068848</t>
   </si>
   <si>
     <t xml:space="preserve">3.61617732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62435555458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7519268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76173973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72412276268005</t>
+    <t xml:space="preserve">3.62435507774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75192713737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76174068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72412300109863</t>
   </si>
   <si>
     <t xml:space="preserve">3.77809548377991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77646017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79118084907532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73720741271973</t>
+    <t xml:space="preserve">3.77646064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79118013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73720765113831</t>
   </si>
   <si>
     <t xml:space="preserve">3.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79445123672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99071598052979</t>
+    <t xml:space="preserve">3.79445147514343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99071574211121</t>
   </si>
   <si>
     <t xml:space="preserve">3.91548156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86314368247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89258408546448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92529511451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88440632820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86641502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94655656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96454691886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85169506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.043053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96618294715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88767719268799</t>
+    <t xml:space="preserve">3.86314392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89258360862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92529463768005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94655609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86150884628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96454739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85169458389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04305362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88767671585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.86968564987183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8189845085144</t>
+    <t xml:space="preserve">3.81898403167725</t>
   </si>
   <si>
     <t xml:space="preserve">3.91384530067444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94164991378784</t>
+    <t xml:space="preserve">3.941650390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.02669763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99398708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97272539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0021653175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05613708496094</t>
+    <t xml:space="preserve">3.99398684501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97272515296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00216436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0561375617981</t>
   </si>
   <si>
     <t xml:space="preserve">3.97926759719849</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">4.00707149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01524877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04141712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08884906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0839409828186</t>
+    <t xml:space="preserve">4.01524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04141759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">4.16244792938232</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44048929214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41595649719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33009004592896</t>
+    <t xml:space="preserve">4.44048881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41595697402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33009052276611</t>
   </si>
   <si>
     <t xml:space="preserve">4.37506723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59586524963379</t>
+    <t xml:space="preserve">4.59586477279663</t>
   </si>
   <si>
     <t xml:space="preserve">4.76350831985474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78804159164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99248456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8043966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83710765838623</t>
+    <t xml:space="preserve">4.78804111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99248361587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80439710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83710718154907</t>
   </si>
   <si>
     <t xml:space="preserve">4.83301877975464</t>
@@ -575,40 +575,40 @@
     <t xml:space="preserve">4.90661811828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96386241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02928400039673</t>
+    <t xml:space="preserve">4.96386194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02928352355957</t>
   </si>
   <si>
     <t xml:space="preserve">5.03337287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13150453567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830396652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28688097000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36456871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3686580657959</t>
+    <t xml:space="preserve">5.19283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13150501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28688144683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36456918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36865758895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.46270132064819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56492233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56901168823242</t>
+    <t xml:space="preserve">5.56492280960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56901121139526</t>
   </si>
   <si>
     <t xml:space="preserve">5.55265617370605</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">5.26643705368042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54856634140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59354448318481</t>
+    <t xml:space="preserve">5.5485668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59354543685913</t>
   </si>
   <si>
     <t xml:space="preserve">5.601722240448</t>
@@ -635,46 +635,46 @@
     <t xml:space="preserve">5.75709819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82252025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85114240646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43816804885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47905683517456</t>
+    <t xml:space="preserve">5.80207586288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82251977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85114145278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78571939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4790563583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.48723459243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46678972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60581111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56083297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64308214187622</t>
+    <t xml:space="preserve">5.46679067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60581064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56083393096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64308166503906</t>
   </si>
   <si>
     <t xml:space="preserve">5.69674682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46144580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57290363311768</t>
+    <t xml:space="preserve">5.4614462852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57290458679199</t>
   </si>
   <si>
     <t xml:space="preserve">5.65546560287476</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">5.84948539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90315055847168</t>
+    <t xml:space="preserve">5.90315103530884</t>
   </si>
   <si>
     <t xml:space="preserve">6.1012978553772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84122896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82471609115601</t>
+    <t xml:space="preserve">5.84122848510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82471656799316</t>
   </si>
   <si>
     <t xml:space="preserve">5.80820465087891</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">5.75866746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65133714675903</t>
+    <t xml:space="preserve">5.65133810043335</t>
   </si>
   <si>
     <t xml:space="preserve">5.81233263015747</t>
@@ -728,88 +728,88 @@
     <t xml:space="preserve">5.77105188369751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8453574180603</t>
+    <t xml:space="preserve">5.84535694122314</t>
   </si>
   <si>
     <t xml:space="preserve">5.68849039077759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56877517700195</t>
+    <t xml:space="preserve">5.56877613067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.63069677352905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57703256607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5233678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54813528060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48621416091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53162288665771</t>
+    <t xml:space="preserve">5.5770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52336740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54813575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48621463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53162336349487</t>
   </si>
   <si>
     <t xml:space="preserve">5.55639171600342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32934761047363</t>
+    <t xml:space="preserve">5.32934808731079</t>
   </si>
   <si>
     <t xml:space="preserve">5.27568244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009569168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14771270751953</t>
+    <t xml:space="preserve">5.16009664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14771223068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.30045127868652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12294387817383</t>
+    <t xml:space="preserve">5.12294340133667</t>
   </si>
   <si>
     <t xml:space="preserve">5.1931209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10230255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15184020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17248106002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34998798370361</t>
+    <t xml:space="preserve">5.10230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15183973312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17248058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">5.3995246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74628305435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041246414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60592937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71325874328613</t>
+    <t xml:space="preserve">5.74628400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60592889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71325922012329</t>
   </si>
   <si>
     <t xml:space="preserve">5.72977161407471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77518033981323</t>
+    <t xml:space="preserve">5.77518081665039</t>
   </si>
   <si>
     <t xml:space="preserve">5.76692390441895</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">5.87012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86599731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94443130493164</t>
+    <t xml:space="preserve">5.86599779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94443035125732</t>
   </si>
   <si>
     <t xml:space="preserve">5.89489412307739</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">6.04763269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93204689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86187028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97332811355591</t>
+    <t xml:space="preserve">5.93204736709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86186933517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97332715988159</t>
   </si>
   <si>
     <t xml:space="preserve">6.06827306747437</t>
@@ -848,67 +848,67 @@
     <t xml:space="preserve">6.10955429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17560338973999</t>
+    <t xml:space="preserve">6.17560386657715</t>
   </si>
   <si>
     <t xml:space="preserve">6.17973184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19211578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21275615692139</t>
+    <t xml:space="preserve">6.19211626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21275568008423</t>
   </si>
   <si>
     <t xml:space="preserve">6.18385934829712</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12193822860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16734743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13845157623291</t>
+    <t xml:space="preserve">6.12193870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16734790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13845109939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.15083456039429</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98158311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05176115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09717082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18798732757568</t>
+    <t xml:space="preserve">5.98158407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05176162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09716987609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18798780441284</t>
   </si>
   <si>
     <t xml:space="preserve">6.15909147262573</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06001758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98571157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0889139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91140651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87425374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93617582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9609432220459</t>
+    <t xml:space="preserve">6.06001806259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98571252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08891439437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87425327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93617534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96094369888306</t>
   </si>
   <si>
     <t xml:space="preserve">6.00222396850586</t>
@@ -923,49 +923,49 @@
     <t xml:space="preserve">6.64207601547241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88976097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85260915756226</t>
+    <t xml:space="preserve">6.88976144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8526086807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.81958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89801692962646</t>
+    <t xml:space="preserve">6.89801645278931</t>
   </si>
   <si>
     <t xml:space="preserve">6.82371187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77004718780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60492324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69574117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58015489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392871856689</t>
+    <t xml:space="preserve">6.75353479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7700457572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60492420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58015537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392919540405</t>
   </si>
   <si>
     <t xml:space="preserve">6.43980073928833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52649068832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45631217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5718994140625</t>
+    <t xml:space="preserve">6.52649021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45631265640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57189989089966</t>
   </si>
   <si>
     <t xml:space="preserve">6.65446090698242</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">6.53061819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66684484481812</t>
+    <t xml:space="preserve">6.66684436798096</t>
   </si>
   <si>
     <t xml:space="preserve">6.44805669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65858793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55538702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62556409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56777143478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55125856399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6090521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72876596450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84848022460938</t>
+    <t xml:space="preserve">6.65858840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55538654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.625563621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56777095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50585079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7287654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84848070144653</t>
   </si>
   <si>
     <t xml:space="preserve">6.75766277313232</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">6.90214490890503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70812559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68748617172241</t>
+    <t xml:space="preserve">6.70812511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.71225357055664</t>
@@ -1031,31 +1031,31 @@
     <t xml:space="preserve">6.77417421340942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4346661567688</t>
+    <t xml:space="preserve">7.43466663360596</t>
   </si>
   <si>
     <t xml:space="preserve">7.44705152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47594738006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47181987762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46356296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64932775497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95480585098267</t>
+    <t xml:space="preserve">7.47594928741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47182035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46356391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64932680130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95480537414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.76078510284424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84334802627563</t>
+    <t xml:space="preserve">7.84334564208984</t>
   </si>
   <si>
     <t xml:space="preserve">7.80619382858276</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">7.75665712356567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95893239974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92590951919556</t>
+    <t xml:space="preserve">7.95893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92590856552124</t>
   </si>
   <si>
     <t xml:space="preserve">7.57915019989014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28192758560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331842422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22413492202759</t>
+    <t xml:space="preserve">7.28192853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40990018844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28605604171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1333179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">7.41402673721313</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">7.29431200027466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1787257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24890375137329</t>
+    <t xml:space="preserve">7.17872667312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.3810019493103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33972072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19936656951904</t>
+    <t xml:space="preserve">7.3397216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19936752319336</t>
   </si>
   <si>
     <t xml:space="preserve">7.03011560440063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01773166656494</t>
+    <t xml:space="preserve">7.01773071289062</t>
   </si>
   <si>
     <t xml:space="preserve">7.05488395690918</t>
@@ -1130,49 +1130,49 @@
     <t xml:space="preserve">6.96406650543213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79481554031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7494068145752</t>
+    <t xml:space="preserve">6.79481506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74940633773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.68335723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.790687084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25303077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19111108779907</t>
+    <t xml:space="preserve">6.79068756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25303173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19111013412476</t>
   </si>
   <si>
     <t xml:space="preserve">7.07965230941772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84022331237793</t>
+    <t xml:space="preserve">6.84022378921509</t>
   </si>
   <si>
     <t xml:space="preserve">7.05075550079346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23651933670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43053960800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30669641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26128816604614</t>
+    <t xml:space="preserve">7.2365198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43053865432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30669689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26128768920898</t>
   </si>
   <si>
     <t xml:space="preserve">7.25715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36036157608032</t>
+    <t xml:space="preserve">7.36036109924316</t>
   </si>
   <si>
     <t xml:space="preserve">7.2778000831604</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">8.2313871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12405681610107</t>
+    <t xml:space="preserve">8.12405586242676</t>
   </si>
   <si>
     <t xml:space="preserve">8.40476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62768173217773</t>
+    <t xml:space="preserve">8.62768077850342</t>
   </si>
   <si>
     <t xml:space="preserve">8.41302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14056873321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24789810180664</t>
+    <t xml:space="preserve">8.14056777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24789905548096</t>
   </si>
   <si>
     <t xml:space="preserve">8.17359352111816</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">8.09103202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19836235046387</t>
+    <t xml:space="preserve">8.19836139678955</t>
   </si>
   <si>
     <t xml:space="preserve">8.18184947967529</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">8.20661640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14469718933105</t>
+    <t xml:space="preserve">8.14469623565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.15295219421387</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">8.20248985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430183410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35522842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36348438262939</t>
+    <t xml:space="preserve">8.45430088043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36348628997803</t>
   </si>
   <si>
     <t xml:space="preserve">8.33045959472656</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">8.47907066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52035236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79280376434326</t>
+    <t xml:space="preserve">8.52035045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79280471801758</t>
   </si>
   <si>
     <t xml:space="preserve">9.00746440887451</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">8.71024322509766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82582855224609</t>
+    <t xml:space="preserve">8.82582759857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.66070652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83408546447754</t>
+    <t xml:space="preserve">8.83408355712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.86711025238037</t>
@@ -1265,46 +1265,46 @@
     <t xml:space="preserve">8.66896152496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67721748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42953300476074</t>
+    <t xml:space="preserve">8.65244960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67721843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42953395843506</t>
   </si>
   <si>
     <t xml:space="preserve">8.67109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74605751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70440864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77104663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75438594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24628353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30875492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34623718261719</t>
+    <t xml:space="preserve">8.74605655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7044095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77104568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75438690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24628257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30875587463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3462381362915</t>
   </si>
   <si>
     <t xml:space="preserve">8.41287517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55447769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8460111618042</t>
+    <t xml:space="preserve">8.55447673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601211547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.8793306350708</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">8.57946586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82935428619385</t>
+    <t xml:space="preserve">8.82935333251953</t>
   </si>
   <si>
     <t xml:space="preserve">8.81269359588623</t>
@@ -1322,46 +1322,46 @@
     <t xml:space="preserve">8.82102394104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72939682006836</t>
+    <t xml:space="preserve">8.86267280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72939872741699</t>
   </si>
   <si>
     <t xml:space="preserve">8.5044994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62111473083496</t>
+    <t xml:space="preserve">8.62111377716064</t>
   </si>
   <si>
     <t xml:space="preserve">8.47118186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25461292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58779525756836</t>
+    <t xml:space="preserve">8.45452308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25461196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58779621124268</t>
   </si>
   <si>
     <t xml:space="preserve">8.49617004394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36289691925049</t>
+    <t xml:space="preserve">8.3628978729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.42120361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21712875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08802032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59612560272217</t>
+    <t xml:space="preserve">8.21712970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08802127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59612464904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.63777256011963</t>
@@ -1370,31 +1370,31 @@
     <t xml:space="preserve">8.16298770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99639654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92142915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78815650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02554988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76733112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85062742233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61323499679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312198638916</t>
+    <t xml:space="preserve">8.12133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99639558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92142963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78815603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02554893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61323547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86312103271484</t>
   </si>
   <si>
     <t xml:space="preserve">7.74234342575073</t>
@@ -1403,64 +1403,64 @@
     <t xml:space="preserve">7.67154312133789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62572860717773</t>
+    <t xml:space="preserve">7.62573003768921</t>
   </si>
   <si>
     <t xml:space="preserve">7.87145233154297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72151851654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59241056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5715856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82980394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54659843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6340594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84229946136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79231929779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71319055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74650764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68819999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44664287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28838109970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14677858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19259119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47163200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66321182250977</t>
+    <t xml:space="preserve">7.72151899337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59241104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57158660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82980346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5465989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63405895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84229755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.792320728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61740016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74650812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6882004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44664335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28838062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14677810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19259166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47163248062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66321325302124</t>
   </si>
   <si>
     <t xml:space="preserve">8.04637241363525</t>
@@ -1469,94 +1469,94 @@
     <t xml:space="preserve">8.17131805419922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20463562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23378849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37955665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5294885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05425071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99594593048096</t>
+    <t xml:space="preserve">8.47951221466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3295783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20463466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23378944396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37955760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52948665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0542516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99594497680664</t>
   </si>
   <si>
     <t xml:space="preserve">9.01260375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00427436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07923984527588</t>
+    <t xml:space="preserve">9.00427532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07924175262451</t>
   </si>
   <si>
     <t xml:space="preserve">8.80436420440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11255931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09589862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02093410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02926445007324</t>
+    <t xml:space="preserve">9.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09589958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02093315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02926254272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.66276168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57113742828369</t>
+    <t xml:space="preserve">8.57113647460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.02138423919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0838565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15049362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00055980682373</t>
+    <t xml:space="preserve">8.08385562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15049266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00056076049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.35456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98390197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82563924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27127170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07969188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28376483917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53781890869141</t>
+    <t xml:space="preserve">7.9839015007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82563877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9922308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27127075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07969093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28376579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53781700134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.46285152435303</t>
@@ -1574,34 +1574,34 @@
     <t xml:space="preserve">8.00472450256348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54243326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01721954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26294231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04220867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20046997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19214057922363</t>
+    <t xml:space="preserve">7.54243516921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01721858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26294136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04220771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20047092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19214153289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.09635066986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14216327667236</t>
+    <t xml:space="preserve">8.14216232299805</t>
   </si>
   <si>
     <t xml:space="preserve">8.12550449371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17964553833008</t>
+    <t xml:space="preserve">8.17964744567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.94641733169556</t>
@@ -1610,73 +1610,73 @@
     <t xml:space="preserve">8.25877666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97557163238525</t>
+    <t xml:space="preserve">7.97557210922241</t>
   </si>
   <si>
     <t xml:space="preserve">7.8922758102417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81731033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62989377975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79648590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75483751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22129344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32541275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21296501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18381118774414</t>
+    <t xml:space="preserve">7.81730890274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6298942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79648447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75483798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22129535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32541370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21296405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18381023406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.19630527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22962284088135</t>
+    <t xml:space="preserve">8.22962474822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.73772811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43786239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38788509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62944412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3712272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51283073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83768272399902</t>
+    <t xml:space="preserve">8.43786525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38788604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62944316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37122821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69608020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83768177032471</t>
   </si>
   <si>
     <t xml:space="preserve">8.77937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51237869262695</t>
+    <t xml:space="preserve">8.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51237773895264</t>
   </si>
   <si>
     <t xml:space="preserve">9.37910556793213</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">9.59567546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54569721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39576530456543</t>
+    <t xml:space="preserve">9.54569625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39576435089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.28748035430908</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">9.65398216247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49571895599365</t>
+    <t xml:space="preserve">9.49571800231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.35411643981934</t>
@@ -1715,64 +1715,64 @@
     <t xml:space="preserve">9.17086601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03759384155273</t>
+    <t xml:space="preserve">9.03759288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.22917366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2708215713501</t>
+    <t xml:space="preserve">9.27082252502441</t>
   </si>
   <si>
     <t xml:space="preserve">8.96262645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13754749298096</t>
+    <t xml:space="preserve">9.13754940032959</t>
   </si>
   <si>
     <t xml:space="preserve">9.16253662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0709114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56280708312988</t>
+    <t xml:space="preserve">9.07091236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56280612945557</t>
   </si>
   <si>
     <t xml:space="preserve">8.64610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04592227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06258106231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10422992706299</t>
+    <t xml:space="preserve">9.04592132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06258201599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10422897338867</t>
   </si>
   <si>
     <t xml:space="preserve">8.94596767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91264915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83797073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65155124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58376216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47360706329346</t>
+    <t xml:space="preserve">8.91264820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83797168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65155220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58376312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47360515594482</t>
   </si>
   <si>
     <t xml:space="preserve">8.72781372070312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59223747253418</t>
+    <t xml:space="preserve">8.59223651885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98202323913574</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">8.38039684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42700004577637</t>
+    <t xml:space="preserve">8.42700099945068</t>
   </si>
   <si>
     <t xml:space="preserve">8.30413436889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26176643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34226512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39310646057129</t>
+    <t xml:space="preserve">8.2617654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34226417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39310741424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.33379173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31260871887207</t>
+    <t xml:space="preserve">8.31260776519775</t>
   </si>
   <si>
     <t xml:space="preserve">8.27871322631836</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">8.05839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10500335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19397735595703</t>
+    <t xml:space="preserve">8.10500431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19397640228271</t>
   </si>
   <si>
     <t xml:space="preserve">8.75323390960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44394779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32531833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45242214202881</t>
+    <t xml:space="preserve">8.44394874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">8.43971157073975</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">8.52444839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66849708557129</t>
+    <t xml:space="preserve">8.66849803924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.56681537628174</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">8.44818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6091833114624</t>
+    <t xml:space="preserve">8.60918235778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.62613105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57528877258301</t>
+    <t xml:space="preserve">8.57528972625732</t>
   </si>
   <si>
     <t xml:space="preserve">8.20244979858398</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">8.35921192169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17279243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11771488189697</t>
+    <t xml:space="preserve">8.1727933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11771392822266</t>
   </si>
   <si>
     <t xml:space="preserve">8.03297805786133</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">7.89740037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13466262817383</t>
+    <t xml:space="preserve">8.13466167449951</t>
   </si>
   <si>
     <t xml:space="preserve">7.9651894569397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90163660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79995441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82961130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73640203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72792863845825</t>
+    <t xml:space="preserve">7.9016375541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79995536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82961177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73640298843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72792911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.2363452911377</t>
@@ -1925,28 +1925,28 @@
     <t xml:space="preserve">8.22787094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72369146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95671653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82113695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71945571899414</t>
+    <t xml:space="preserve">7.72369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95671606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82113742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71945476531982</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66013956069946</t>
+    <t xml:space="preserve">7.66014003753662</t>
   </si>
   <si>
     <t xml:space="preserve">7.71098184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66002655029297</t>
+    <t xml:space="preserve">8.66002559661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.41429042816162</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">8.31684398651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43123817443848</t>
+    <t xml:space="preserve">8.43123722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.42276382446289</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">8.19821357727051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21939849853516</t>
+    <t xml:space="preserve">8.24058246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21939754486084</t>
   </si>
   <si>
     <t xml:space="preserve">8.46513175964355</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">8.8972864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01591682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90575885772705</t>
+    <t xml:space="preserve">9.01591777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88881206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90575981140137</t>
   </si>
   <si>
     <t xml:space="preserve">8.92270755767822</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">8.97354888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13042449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22363471984863</t>
+    <t xml:space="preserve">8.13042545318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22363376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.18974018096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37192153930664</t>
+    <t xml:space="preserve">8.37192249298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.49902629852295</t>
@@ -2024,70 +2024,70 @@
     <t xml:space="preserve">8.60070991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54139518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69391822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67697238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85491752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02438926696777</t>
+    <t xml:space="preserve">8.54139423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69391918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85491847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02439022064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28707218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57517528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47349262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42264842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30401802062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60906887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56669998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75311946868896</t>
+    <t xml:space="preserve">9.57517433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47349071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42265033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30401992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60906791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6514368057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53280544281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63449001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56670093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75312042236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.76159477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78701591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83785438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.871750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86327743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79548835754395</t>
+    <t xml:space="preserve">9.78701496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83785724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87174987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86327838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79548931121826</t>
   </si>
   <si>
     <t xml:space="preserve">9.82090950012207</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.0242757797241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1344327926636</t>
+    <t xml:space="preserve">10.1344337463379</t>
   </si>
   <si>
     <t xml:space="preserve">10.0835905075073</t>
@@ -2120,37 +2120,37 @@
     <t xml:space="preserve">10.1768007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2276430130005</t>
+    <t xml:space="preserve">10.2276420593262</t>
   </si>
   <si>
     <t xml:space="preserve">10.1598539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2615356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2530641555786</t>
+    <t xml:space="preserve">10.2615365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2530632019043</t>
   </si>
   <si>
     <t xml:space="preserve">10.1683263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1937475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0496950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82938289642334</t>
+    <t xml:space="preserve">10.1937484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0496959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82938385009766</t>
   </si>
   <si>
     <t xml:space="preserve">9.94801330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.998854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92259216308594</t>
+    <t xml:space="preserve">9.99885559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92259311676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.51585865020752</t>
@@ -2159,25 +2159,25 @@
     <t xml:space="preserve">10.0581703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73617362976074</t>
+    <t xml:space="preserve">9.73617267608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.84632968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64296436309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54975414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29554557800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16431999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32108020782471</t>
+    <t xml:space="preserve">9.64296245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54975318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29554653167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16431903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32108116149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.01603126525879</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">8.00332069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70674514770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6008243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39322233200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29153728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99072504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71109533309937</t>
+    <t xml:space="preserve">7.70674467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60082483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39322137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29153680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99072456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71109628677368</t>
   </si>
   <si>
     <t xml:space="preserve">6.61364936828613</t>
@@ -2210,22 +2210,22 @@
     <t xml:space="preserve">5.61376333236694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5247917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9824800491333</t>
+    <t xml:space="preserve">5.52479124069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98248052597046</t>
   </si>
   <si>
     <t xml:space="preserve">5.08416318893433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02484750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09687376022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62647485733032</t>
+    <t xml:space="preserve">5.02484798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09687423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62647438049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.59257984161377</t>
@@ -2234,22 +2234,22 @@
     <t xml:space="preserve">5.80865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50784349441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26210975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84690237045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16042613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89774417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76216650009155</t>
+    <t xml:space="preserve">5.50784397125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26210880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84690284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16042566299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89774465560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76216554641724</t>
   </si>
   <si>
     <t xml:space="preserve">5.27481937408447</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">5.41463422775269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19008350372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20279407501221</t>
+    <t xml:space="preserve">5.19008302688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20279359817505</t>
   </si>
   <si>
     <t xml:space="preserve">5.0163745880127</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">5.10111093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93163871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96129608154297</t>
+    <t xml:space="preserve">4.93163919448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96129655838013</t>
   </si>
   <si>
     <t xml:space="preserve">5.33837175369263</t>
@@ -2297,34 +2297,34 @@
     <t xml:space="preserve">5.53326511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49513339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87220859527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93576049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10099601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13065433502197</t>
+    <t xml:space="preserve">5.49513387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87220907211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93576097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1009955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">5.88068294525146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6773157119751</t>
+    <t xml:space="preserve">5.67731523513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.87644577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81289386749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75357866287231</t>
+    <t xml:space="preserve">5.81289339065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75357818603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.66460561752319</t>
@@ -2333,52 +2333,52 @@
     <t xml:space="preserve">5.65189504623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05015420913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03320741653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3552041053772</t>
+    <t xml:space="preserve">6.05015468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91881418228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03320693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35520458221436</t>
   </si>
   <si>
     <t xml:space="preserve">6.2916522026062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39333581924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79159545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94835710525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91022491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04156637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24917078018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10088157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0034351348877</t>
+    <t xml:space="preserve">6.39333534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79159498214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94835662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04156684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24916982650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10088205337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00343561172485</t>
   </si>
   <si>
     <t xml:space="preserve">6.70685911178589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5755181312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71533298492432</t>
+    <t xml:space="preserve">6.57551860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71533250808716</t>
   </si>
   <si>
     <t xml:space="preserve">6.72804307937622</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">6.64330720901489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55009746551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6094126701355</t>
+    <t xml:space="preserve">6.55009794235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60941314697266</t>
   </si>
   <si>
     <t xml:space="preserve">6.33402013778687</t>
@@ -2408,55 +2408,55 @@
     <t xml:space="preserve">6.14760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12641668319702</t>
+    <t xml:space="preserve">6.28741598129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12641763687134</t>
   </si>
   <si>
     <t xml:space="preserve">6.1518383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01626062393188</t>
+    <t xml:space="preserve">6.01626014709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.31707334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13912677764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07981204986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04591846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36367893218994</t>
+    <t xml:space="preserve">6.13912725448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07981252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04591798782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36367797851562</t>
   </si>
   <si>
     <t xml:space="preserve">6.24504709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47383451461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47807168960571</t>
+    <t xml:space="preserve">6.47383499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47807216644287</t>
   </si>
   <si>
     <t xml:space="preserve">6.27046823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06286573410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10523319244385</t>
+    <t xml:space="preserve">6.06286478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10523271560669</t>
   </si>
   <si>
     <t xml:space="preserve">6.22386360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14336442947388</t>
+    <t xml:space="preserve">6.14336395263672</t>
   </si>
   <si>
     <t xml:space="preserve">6.08404874801636</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">5.95270824432373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07133865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18149518966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0204963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99931287765503</t>
+    <t xml:space="preserve">6.07133817672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18149566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02049732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99931240081787</t>
   </si>
   <si>
     <t xml:space="preserve">6.38486194610596</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">6.32131004333496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23657464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19420623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25775861740112</t>
+    <t xml:space="preserve">6.23657369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25775814056396</t>
   </si>
   <si>
     <t xml:space="preserve">6.2747049331665</t>
@@ -2501,19 +2501,19 @@
     <t xml:space="preserve">6.23233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30859994888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37215137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63483381271362</t>
+    <t xml:space="preserve">6.3085994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37215185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63483333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.98648834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16019678115845</t>
+    <t xml:space="preserve">7.16019630432129</t>
   </si>
   <si>
     <t xml:space="preserve">7.29577398300171</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">6.85938405990601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44417715072632</t>
+    <t xml:space="preserve">6.79583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44417762756348</t>
   </si>
   <si>
     <t xml:space="preserve">6.10946989059448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0543909072876</t>
+    <t xml:space="preserve">6.05439138412476</t>
   </si>
   <si>
     <t xml:space="preserve">6.04168081283569</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">6.09675931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2153902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94847059249878</t>
+    <t xml:space="preserve">6.21538972854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94847202301025</t>
   </si>
   <si>
     <t xml:space="preserve">6.09252309799194</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">6.00778675079346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90610265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57563257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49089622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60105323791504</t>
+    <t xml:space="preserve">5.90610313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57563209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4908971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6010537147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.46547555923462</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">5.25787210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28752994537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06297922134399</t>
+    <t xml:space="preserve">5.28752946853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06297969818115</t>
   </si>
   <si>
     <t xml:space="preserve">5.05874252319336</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">5.01213788986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29176712036133</t>
+    <t xml:space="preserve">5.29176616668701</t>
   </si>
   <si>
     <t xml:space="preserve">5.40616083145142</t>
@@ -2609,46 +2609,46 @@
     <t xml:space="preserve">5.43158149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81713056564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83831453323364</t>
+    <t xml:space="preserve">5.76205205917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83831405639648</t>
   </si>
   <si>
     <t xml:space="preserve">6.93988275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74075412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82125282287598</t>
+    <t xml:space="preserve">6.74075365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82125234603882</t>
   </si>
   <si>
     <t xml:space="preserve">7.04580307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09652996063232</t>
+    <t xml:space="preserve">8.09653091430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.88045310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53303527832031</t>
+    <t xml:space="preserve">7.53303623199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.49914121627808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45253705978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62624549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55845546722412</t>
+    <t xml:space="preserve">7.45253658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62624502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55845642089844</t>
   </si>
   <si>
     <t xml:space="preserve">7.62200880050659</t>
@@ -2657,40 +2657,40 @@
     <t xml:space="preserve">7.77453327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77029609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85079669952393</t>
+    <t xml:space="preserve">7.77029657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84232139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67285013198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79571676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63472032546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91011190414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8253755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85503196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68555974960327</t>
+    <t xml:space="preserve">7.84232187271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67285108566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7957181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6347188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91011047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82537460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8550329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68556070327759</t>
   </si>
   <si>
     <t xml:space="preserve">7.5245623588562</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">7.4779577255249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58811378479004</t>
+    <t xml:space="preserve">7.5881142616272</t>
   </si>
   <si>
     <t xml:space="preserve">7.56693029403687</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">7.41016864776611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28730154037476</t>
+    <t xml:space="preserve">7.2873010635376</t>
   </si>
   <si>
     <t xml:space="preserve">7.22374820709229</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">7.31695890426636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18985462188721</t>
+    <t xml:space="preserve">7.18985414505005</t>
   </si>
   <si>
     <t xml:space="preserve">7.06275033950806</t>
@@ -2729,61 +2729,61 @@
     <t xml:space="preserve">7.18138122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15596008300781</t>
+    <t xml:space="preserve">7.15595960617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.63895606994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64319229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74911212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53727245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85926961898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21515941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23210906982422</t>
+    <t xml:space="preserve">7.64319276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74911308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53727340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85926914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21516036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2321081161499</t>
   </si>
   <si>
     <t xml:space="preserve">8.18550300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30837059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14313507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79148054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65166568756104</t>
+    <t xml:space="preserve">8.20668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30837154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14313411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79148101806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65166616439819</t>
   </si>
   <si>
     <t xml:space="preserve">8.03721523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92282199859619</t>
+    <t xml:space="preserve">7.92282152175903</t>
   </si>
   <si>
     <t xml:space="preserve">8.15160846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88033771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63460350036621</t>
+    <t xml:space="preserve">8.88033866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63460445404053</t>
   </si>
   <si>
     <t xml:space="preserve">8.00755786895752</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">8.93965435028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78712844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68544673919678</t>
+    <t xml:space="preserve">8.78712940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">9.10065269470215</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">9.16844081878662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20233631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5582275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60059547424316</t>
+    <t xml:space="preserve">9.20233535766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55822658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60059452056885</t>
   </si>
   <si>
     <t xml:space="preserve">8.96507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133701324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21928310394287</t>
+    <t xml:space="preserve">9.04133796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">9.04981136322021</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">9.71075248718262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3972282409668</t>
+    <t xml:space="preserve">9.39722919464111</t>
   </si>
   <si>
     <t xml:space="preserve">9.44807052612305</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">9.48196411132812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69380474090576</t>
+    <t xml:space="preserve">9.69380569458008</t>
   </si>
   <si>
     <t xml:space="preserve">10.041223526001</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">9.72769927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52433300018311</t>
+    <t xml:space="preserve">9.52433109283447</t>
   </si>
   <si>
     <t xml:space="preserve">9.43112373352051</t>
@@ -2867,55 +2867,55 @@
     <t xml:space="preserve">9.03613376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91495895385742</t>
+    <t xml:space="preserve">8.91496086120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.01016807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96689224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0880651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20924091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24386215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33907032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43427753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63335037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68527984619141</t>
+    <t xml:space="preserve">8.96689128875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08806610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2092399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24386119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33906841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43427658081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63334941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68528079986572</t>
   </si>
   <si>
     <t xml:space="preserve">9.40831184387207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47755336761475</t>
+    <t xml:space="preserve">9.47755527496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.32175922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21789455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11403179168701</t>
+    <t xml:space="preserve">9.2178955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1140308380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.04478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01882457733154</t>
+    <t xml:space="preserve">9.01882362365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.26117134094238</t>
@@ -2927,22 +2927,22 @@
     <t xml:space="preserve">9.46889877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26982688903809</t>
+    <t xml:space="preserve">9.2698278427124</t>
   </si>
   <si>
     <t xml:space="preserve">9.31310367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33041381835938</t>
+    <t xml:space="preserve">9.33041477203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.30444812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34772491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1313419342041</t>
+    <t xml:space="preserve">9.3477258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13134288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.12268733978271</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.00151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75916481018066</t>
+    <t xml:space="preserve">8.75916385650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.82840633392334</t>
@@ -2981,19 +2981,19 @@
     <t xml:space="preserve">9.252516746521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17461967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94958114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83706283569336</t>
+    <t xml:space="preserve">9.1746187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94958019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.71588802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77647590637207</t>
+    <t xml:space="preserve">8.77647495269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.98420238494873</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">8.69857788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66395568847656</t>
+    <t xml:space="preserve">8.66395664215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.95823669433594</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">8.86302757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78513050079346</t>
+    <t xml:space="preserve">8.78512954711914</t>
   </si>
   <si>
     <t xml:space="preserve">8.72454357147217</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">8.44324588775635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36967658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26581192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19657039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23119163513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28744983673096</t>
+    <t xml:space="preserve">8.3696756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26581287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28745079040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.74185466766357</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">8.39131355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42160797119141</t>
+    <t xml:space="preserve">8.42160701751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.3610200881958</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">8.47353935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6336631774